--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA62"/>
+  <dimension ref="A1:AA65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1821,12 +1821,225 @@
           <t>الخاص مقفل</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/yourwishesst/status/2042392677023404378</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>الخاص مقفل</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2042390089641193859</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sadziz13</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>مَ. سعـد عبدالعزيز</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehMedia', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 11:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-04-09T23:51:00Z</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>138</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2042389076863537661</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yara_saeed3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Yara.S.B</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1350213646945816589/3DACZ1Rf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
+التواصل خاص</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
+التواصل خاص</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Apr 9, 2026 · 11:47 PM UTC</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-04-09T23:47:00Z</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>132</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
+التواصل خاص</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -1839,7 +2052,7 @@
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>جمهور صقر الأغنية الخليجية في جدة غير 😉
 🔥🔥 SOLD OUT 
@@ -1850,220 +2063,6 @@
 @RabehSaqer 
 @JEDCalendar 
 @EmiratesNBD_KSA https://t.co/ushr2PgKVi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2042390089641193859</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sadziz13</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>مَ. سعـد عبدالعزيز</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehMedia', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 11:51 PM UTC</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-04-09T23:51:00Z</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>138</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/Sadziz13/status/2042390089641193859</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>@RotanaLive @RabehMedia @RabehSaqer @JEDCalendar @EmiratesNBD_KSA ليلة بانتظارك يا كبير المسرح ❤️🦅</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2042389076863537661</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://x.com/yara_saeed3/status/2042389076863537661</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://x.com/yara_saeed3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>yara_saeed3</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Yara.S.B</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1350213646945816589/3DACZ1Rf_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Apr 9, 2026 · 11:47 PM UTC</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2026-04-09T23:47:00Z</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>132</v>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>عندي تذكرتين حفلة رابح صقر بجدة  B Center  
-التواصل خاص</t>
         </is>
       </c>
     </row>
@@ -3686,18 +3685,14 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>✈️Moving to Dubai in 2026?
-The Metro, the holidays, the brunch culture, the delivery apps, it all hits different when you actually live here.
-🔥Read the full blog: https://t.co/AKgSHoKV0j
-#snxs #dubai #UAElife</t>
+          <t>🇦🇪The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice. 
+#UAE #EmiratesNBD #SNXS</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>✈️Moving to Dubai in 2026?
-The Metro, the holidays, the brunch culture, the delivery apps, it all hits different when you actually live here.
-🔥Read the full blog: https://t.co/AKgSHoKV0j
-#snxs #dubai #UAElife</t>
+          <t>🇦🇪The UAE's private sector dialogue is exactly what ecosystem resilience looks like in practice. 
+#UAE #EmiratesNBD #SNXS</t>
         </is>
       </c>
     </row>
@@ -5241,13 +5236,33 @@
 So, here's why India's banking &amp; NBFC Sector is becoming a global destination for top investment banks &amp; funds👇</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/smcglobal/status/2042141519180919080</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?
+#SMCGlobal #Nuclear #Energy</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>🤯More than $10.8 Billion have been invested in Indian Financial Services companies in last 1 year alone!!!
-From Japan’s MUFG investing $4.4 billion in Shriram Finance to the UAE’s Emirates NBD putting $3 billion into RBL Bank
-So, here's why India's banking &amp; NBFC Sector is becoming a global destination for top investment banks &amp; funds👇</t>
+          <t>The world may be ahead in nuclear today
+But India has just made a move that could redefine its position tomorrow
+With the Prototype Fast Breeder Reactor (PFBR) at Kalpakkam achieving criticality, India has officially stepped into the second stage of its nuclear roadmap
+This isn’t just another reactor going live
+It’s the foundation for long-term energy independence
+While the gap with global leaders still exists, the direction has now changed
+The real question is… how fast can India build on this momentum?
+#SMCGlobal #Nuclear #Energy</t>
         </is>
       </c>
     </row>
@@ -6590,36 +6605,367 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2042482710841528699</t>
+          <t>2042556913075069121</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+          <t>https://x.com/Zenap355057/status/2042556913075069121</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Zenap355057</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Zenap355057</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Zenap</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038629915940298752/N0SyjFf4_bigger.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-04-10T10:54:00Z</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>2</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>https://x.com/Zenap355057/status/2042556913075069121</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hi am trying to speak with your agent and no response, I have to clarify something</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2042543802079154670</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://x.com/yannoauh/status/2042543802079154670</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/yannoauh</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>yannoauh</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>yannoauh 🐣🕹️</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1907312478566207489/cIrGb9B7_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>SMS 2 &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>58m</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 10:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-04-10T10:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>https://x.com/yannoauh/status/2042543802079154670</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE SMS 2 #UnitedAgainstFraud</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2042513547683598491</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2042513547683598491</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ZaibKang</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Jahan Zaib Akbar Kang</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Apr 10, 2026 · 8:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-04-10T08:02:00Z</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>10</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2042513547683598491</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X digital account opening on 26th April almost 16 days passed my application is still in progress can you please check</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2042482710841528699</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -6628,7 +6974,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -6637,50 +6983,50 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K55" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
         <v>39</v>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>A message says “Get your full flight refund instantly.” What do you do?
 Do not fall for the traps. Stay alert to scams.
@@ -6689,278 +7035,278 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482710841528699</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/loAWPzVN4u</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
         <is>
           <t>تسرنا زيارتكم لنا بفرعنا الجديد في سيليكون سنترال مول - دبي.
-نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/loAWPzVN4u</t>
+نقدّم لكم خدمات مصرفية متكاملة مع ساعات عمل ممتدة عبر فترتين يومياً. نحن قريبين منكم في خدمتكم! https://t.co/TrLnjtiJhq</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>2042436151131455658</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://x.com/Neli_Brown_</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Neli_Brown_</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Cornelia Brown 🇦🇪</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2040254636754706432/0mffrtu0_bigger.jpg</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
         <is>
           <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K56" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
         <is>
           <t>4h</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 2:54 AM UTC</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>2026-04-10T02:54:00Z</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
         <v>30</v>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>https://x.com/Neli_Brown_/status/2042436151131455658</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>I just opened my banking app to see this 👇 Proud of UAE!! 😍 @emiratesislamic https://t.co/rBbgDm1TZd</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
         <is>
           <t>2042145058133307907</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>https://x.com/aswanikumartst5</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>aswanikumartst5</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>TS Aswani Kumar</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
         <is>
           <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
-      <c r="K57" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
         <is>
           <t>23h</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 7:38 AM UTC</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>2026-04-09T07:38:00Z</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
-      <c r="S57" t="n">
+      <c r="S60" t="n">
         <v>1</v>
       </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
         <v>9</v>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp; revert ASAP. Thank You.</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>2042184588223746449</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://x.com/HHShkMohd</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>HHShkMohd</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>HH Sheikh Mohammed</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1547632760927309837/9q-31iBH_bigger.jpg</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -6970,7 +7316,7 @@
 #فخورين_بالإمارات 🇦🇪</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -6980,54 +7326,54 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt; 🇦🇪</t>
         </is>
       </c>
-      <c r="K58" t="b">
+      <c r="K61" t="b">
         <v>1</v>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
         <is>
           <t>21h</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 10:15 AM UTC</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>2026-04-09T10:15:00Z</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
         </is>
       </c>
-      <c r="S58" t="n">
+      <c r="S61" t="n">
         <v>1402</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T61" t="n">
         <v>8020</v>
       </c>
-      <c r="U58" t="n">
+      <c r="U61" t="n">
         <v>15913</v>
       </c>
-      <c r="V58" t="n">
+      <c r="V61" t="n">
         <v>873259</v>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>دخلت دولة الإمارات الأزمة الأخيرة متحدة .. وخرجت منها وهي أكثر اتحاداً والتفافاً وولاءً.. مواطنين ومقيمين .. صغاراً وكباراً .. عسكريين ومدنيين .. حكوميين واقتصاديين .. الجميع متحد تحت راية الدولة وعلمها ورمز وحدتها ..
 علم الإمارات رمز القوة والفخر  .. ندعو أبناء الإمارات والمقيمين على أرضها الطيبة أن يرفعوه فوق المنازل والمؤسسات والمباني.. 
@@ -7037,58 +7383,60 @@
 #فخورين_بالإمارات 🇦🇪</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>https://x.com/HHShkMohd/status/2042184588223746449</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>@HHShkMohd #فخورين_بالإمارات 🇦🇪 https://t.co/9zI7EZBTYM</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>@HHShkMohd #فخورين_بالإمارات 🇦🇪 https://t.co/9zI7EZBTYM</t>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>@HHShkMohd صدقت سموك..
+علم الإمارات رمز وحدتنا وقوتنا.. نرفعه شامخاً فخراً وولاءً https://t.co/Vt469sEQu3</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>@HHShkMohd صدقت سموك..
+علم الإمارات رمز وحدتنا وقوتنا.. نرفعه شامخاً فخراً وولاءً https://t.co/Vt469sEQu3</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>2042482711168737317</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -7098,7 +7446,7 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 &amp;#34;استرد قيمة رحلتك بالكامل فوراً&amp;#34;
@@ -7108,50 +7456,50 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K59" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="K62" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
         <is>
           <t>1h</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Apr 10, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>2026-04-10T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
         </is>
       </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" t="n">
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
         <v>60</v>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -7161,12 +7509,12 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042482711168737317</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -7176,7 +7524,7 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>تصلك رسالة تقول:
 "استرد قيمة رحلتك بالكامل فوراً"
@@ -7187,216 +7535,216 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>2042152553400385940</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="K60" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>['aswanikumartst5']</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>23h</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 8:08 AM UTC</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>2026-04-09T08:08:00Z</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
         <v>10</v>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
         <is>
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>2042120326721523923</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>To know more:
 emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>To know more:
 &lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K61" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Apr 9</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>2026-04-09T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
         <v>86</v>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>To know more:
 emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042120326721523923</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
 From long-term growth to steady income, each option plays a role in shaping your financial journey. https://t.co/VgSsKYMuov</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
@@ -7404,104 +7752,104 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
         <is>
           <t>2042120323168956518</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2042120323168956518</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
 From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
 From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
-      <c r="K62" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
         <is>
           <t>Apr 9</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>Apr 9, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>2026-04-09T06:00:00Z</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
         <v>1</v>
       </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
         <v>108</v>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="W65" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.
 From long-term growth to steady income, each option plays a role in shaping your financial journey.</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr">
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Investing doesn’t have to feel complicated.
 Understanding the different ways money can grow helps bring clarity and confidence over time.

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -2136,19 +2136,17 @@
 Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/KishSiff/status/2043299071918813643</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@KishSiff Try remarriage with a daughter of retired judge.</t>
+          <t>My career growth story 📈😀 
+- 2008 campus interview Infosys 25k salary
+- 2012 Emirates NBD Dubai 12k AED
+- 2013 IT Manager role in Dubai (18k AED)
+- 2015, married, ~23k AED in Dubai based startup
+- 2019 lost all as alimony &amp; fake cases stuck here
+Moral : Dont marry bro. 🥹</t>
         </is>
       </c>
     </row>
@@ -3053,25 +3051,11 @@
           <t>مبادرة رائعة تدعم الشركات الناشئة والاستثماري</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/MuhammadBopxzr/status/2043204724711621075</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months
-This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE
-This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions
-It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country 🇦🇪</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Emirates NBD has launched a Business Support Package featuring temporary fee-relief measures to help SMEs manage their day-to-day operations over the coming months
-This initiative complements a broader set of measures introduced by the Government of Dubai and the Central Bank of the UAE
-This step reflects the UAE’s proactive and resilient economic approach where public and private sectors work hand in hand to support businesses, strengthen market confidence, and ensure continuity during evolving global conditions
-It also highlights a strong commitment to empowering SMEs, which remain a vital pillar of sustainable economic growth and innovation in the country 🇦🇪</t>
+          <t>مبادرة رائعة تدعم الشركات الناشئة والاستثماري</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1581,18 +1581,8 @@
 #EmiratesNBD #PrivateBanking #InvestmentAdvisory #InvestWithConfidence</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2043660471580942471</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Minimise uncertainty.
-Let our expert advisors at Emirates NBD Private Banking craft bespoke investment strategies designed to align with your goals, risk profile and long-term vision — helping you identify promising trends. Invest with confidence.
-#EmiratesNBD #PrivateBanking #InvestmentAdvisory #InvestWithConfidence</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
           <t>Minimise uncertainty.
@@ -4456,12 +4446,12 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+          <t>@emiratesislamic للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
+          <t>@emiratesislamic للاسف عندي معكم طلب خذ له اسبوع ولا احد يتواصل معاي والموظفين اللي كلموني من عندكم وسوو لي الطلب ما كانوا صادقين معاي والحين محد منهم يرد..</t>
         </is>
       </c>
     </row>
@@ -4564,16 +4554,12 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/LETUDia8It</t>
+          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>علمهم صغار!
-للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
-https://t.co/LETUDia8It</t>
+          <t>حساب ALPHA للأبناء من الإمارات الإسلامي صُمم خصيصاً لمساعدة أولياء الأمور على غرس عادات مالية سليمة منذ الصغر، عبر تجربة رقمية آمنة وممتعة للجيل القادم. يمكنك الوصول إليه بسهولة عبر تطبيق + EI للهواتف المحمولة، ليكون بداية واثقة لطفلك نحو مستقبل مالي ناجح.</t>
         </is>
       </c>
     </row>
@@ -5247,19 +5233,11 @@
           <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043620711407743228</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>@Charbel96960993 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>@Charbel96960993 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
     </row>
@@ -5898,14 +5876,25 @@
 emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2043569875734401177</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
 لا تقع في الفخ. احذر الاحتيال.
 #متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
+https://t.co/ltnxcRlBOA</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>هل ستضغط على رابط توصيل من رقم غير معروف؟ 
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1249,12 +1249,18 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>سؤال:
+ماهو افضل بنك يشتري مديونية ؟!
+قرض عقاري + قرض شخصي .
+@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>سؤال:
+ماهو افضل بنك يشتري مديونية ؟!
+قرض عقاري + قرض شخصي .
+@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
         </is>
       </c>
     </row>
@@ -1452,25 +1458,11 @@
           <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,43 +566,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes</t>
+          <t>https://x.com/DustshotW</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LeaderOkkes</t>
+          <t>DustshotW</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN</t>
+          <t>justice gaming</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035156091634380800/0oGW-_Z4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042550502014193664/yhlYRmG6_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. &lt;a href="/LeaderOkkes" title="THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN"&gt;@LeaderOkkes&lt;/a&gt; &lt;a href="/airasia_indo" title="AirAsia Indonesia"&gt;@airasia_indo&lt;/a&gt; &lt;a href="/IAF_MCC" title="Indian Air Force"&gt;@IAF_MCC&lt;/a&gt; &lt;a href="/CebuPacificAir" title="Cebu Pacific Air"&gt;@CebuPacificAir&lt;/a&gt; &lt;a href="/airasia" title="AirAsia"&gt;@airasia&lt;/a&gt; &lt;a href="/usairforce" title="U.S. Air Force"&gt;@usairforce&lt;/a&gt; &lt;a href="/airtelindia" title="airtel India"&gt;@airtelindia&lt;/a&gt; &lt;a href="/British_Airways" title="British Airways"&gt;@British_Airways&lt;/a&gt; &lt;a href="/KenyaAirways" title="Official Kenya Airways"&gt;@KenyaAirways&lt;/a&gt; &lt;a href="/etihad" title="Etihad Airways"&gt;@etihad&lt;/a&gt; &lt;a href="/flysaa" title="SAA - South African Airways"&gt;@flysaa&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/AmericanAir" title="americanair"&gt;@AmericanAir&lt;/a&gt; &lt;a href="/AirCanada" title="Air Canada"&gt;@AirCanada&lt;/a&gt; &lt;a href="/airserbia" title="Air Serbia"&gt;@airserbia&lt;/a&gt; &lt;a href="/SaudiAirlinesEn" title="Saudia"&gt;@SaudiAirlinesEn&lt;/a&gt; &lt;a href="/X" title="X"&gt;@X&lt;/a&gt;</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -611,41 +611,37 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['LeaderOkkes', 'RoyalFamily', 'MonarchieBe', 'koninklijkhuis', 'KensingtonRoyal', 'DefensieMin', 'FratellidItalia', 'GiorgiaMeloni', 'Pontifex', 'MarkJCarney', 'EmmanuelMacron', 'PrimeministerGR', 'netanyahu', 'LulaOficial', 'JMilei', 'Jaemyung_Lee', 'chrisluxonmp', 'ParmelinG', 'scotgov', 'SwissGov', 'lemondefr', 'TheEconomist', 'iaeaorg', 'wef', 'wto', 'IMFNews', 'WorldBankGroup', 'Davos', 'nikkei', 'NYSE', 'BentleyMotors', 'UniofOxford', 'LeaderOkkes']</t>
+          <t>['dorienotfish']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>58m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:22 PM UTC</t>
+          <t>Apr 16, 2026 · 3:03 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-14T19:22:00Z</t>
+          <t>2026-04-16T03:03:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/LeaderOkkes', 'https://x.com/airasia_indo', 'https://x.com/IAF_MCC', 'https://x.com/CebuPacificAir', 'https://x.com/airasia', 'https://x.com/usairforce', 'https://x.com/airtelindia', 'https://x.com/British_Airways', 'https://x.com/KenyaAirways', 'https://x.com/etihad', 'https://x.com/flysaa', 'https://x.com/EmiratesNBD_AE', 'https://x.com/emirates', 'https://x.com/AmericanAir', 'https://x.com/AirCanada', 'https://x.com/airserbia', 'https://x.com/SaudiAirlinesEn', 'https://x.com/X']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -654,22 +650,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X</t>
+          <t>s enbd</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
     </row>
@@ -679,45 +675,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo</t>
+          <t>https://x.com/BehindNums</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>metrixyo</t>
+          <t>BehindNums</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Metrix</t>
+          <t>BehindNums | Business &amp; Data</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920369464379383808/skWlialk_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2025763865783345152/vXOr5RDQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-&lt;a href="/search?f=tweets&amp;amp;q=%23WIO"&gt;#WIO&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NASDAQ"&gt;#NASDAQ&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ROBINHOOD"&gt;#ROBINHOOD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NYSE"&gt;#NYSE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IG"&gt;#IG&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IBKR"&gt;#IBKR&lt;/a&gt;</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+&lt;a href="/BehindNums" title="BehindNums | Business &amp;amp; Data"&gt;@BehindNums&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -727,23 +735,23 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:14 PM UTC</t>
+          <t>Apr 16, 2026 · 2:58 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-14T19:14:00Z</t>
+          <t>2026-04-16T02:58:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23WIO', 'https://x.com/search?f=tweets&amp;q=%23NASDAQ', 'https://x.com/search?f=tweets&amp;q=%23ROBINHOOD', 'https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/search?f=tweets&amp;q=%23NYSE', 'https://x.com/search?f=tweets&amp;q=%23IG', 'https://x.com/search?f=tweets&amp;q=%23IBKR']</t>
+          <t>['https://x.com/BehindNums']</t>
         </is>
       </c>
       <c r="S3" t="n">
@@ -756,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -765,29 +773,43 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
     </row>
@@ -797,43 +819,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi</t>
+          <t>https://x.com/zaydaklabhoqx</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AlAjlansambrfi</t>
+          <t>zaydaklabhoqx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>طموح العجلان</t>
+          <t>زيد أكلب</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034995732173004803/dk7uz4Ir_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035350140782002176/Clcsao6J_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -842,22 +864,22 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+          <t>['CryptoNewsHntrs']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 4:28 PM UTC</t>
+          <t>Apr 16, 2026 · 1:02 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-14T16:28:00Z</t>
+          <t>2026-04-16T01:02:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -869,10 +891,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -881,34 +903,24 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
     </row>
@@ -918,71 +930,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty</t>
+          <t>https://x.com/STFU1346</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SunnyLusty</t>
+          <t>STFU1346</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>आदियोगी</t>
+          <t>BraveFart🏴󠁧󠁢󠁳󠁣󠁴󠁿</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1799284544987615232/-AKwVwdx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1691103462870650880/Mk3r6EQC_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what&amp;#39;s your point?</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['STFU1346', 'Cle_Etc', 'JeetyJeeterson', 'Brockutd']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:10 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-14T15:56:00Z</t>
+          <t>2026-04-15T15:10:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -993,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1002,22 +1020,31 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
     </row>
@@ -1027,73 +1054,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ChirinAsadi</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chirin Al Asadi</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035029628335923200/lkGmKuGp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today emiratesnbd.com/en/priority-…
+#EmiratesNBD #WealthManagement</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today &lt;a href="https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions"&gt;emiratesnbd.com/en/priority-…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WealthManagement"&gt;#WealthManagement&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['alnuaimi_bader']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:56 PM UTC</t>
+          <t>Apr 15, 2026 · 3:00 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-14T15:56:00Z</t>
+          <t>2026-04-15T15:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/priority-banking/wealth-management-solutions', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23WealthManagement']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1101,10 +1128,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V6" t="n">
-        <v>90</v>
+        <v>1284</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1113,39 +1140,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today emiratesnbd.com/en/priority-…
+#EmiratesNBD #WealthManagement</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
     </row>
@@ -1155,71 +1166,81 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/ibmag_magazine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>ibmag_magazine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>International Business Magazine</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1017739481749655553/2mtvJ3Sb_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+tinyurl.com/4f7v9hen
+tinyurl.com/2s3e7u9d
+tinyurl.com/mt35nuky
+tinyurl.com/55cdu3ep
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+&lt;a href="https://tinyurl.com/4f7v9hen"&gt;tinyurl.com/4f7v9hen&lt;/a&gt;
+&lt;a href="https://tinyurl.com/2s3e7u9d"&gt;tinyurl.com/2s3e7u9d&lt;/a&gt;
+&lt;a href="https://tinyurl.com/mt35nuky"&gt;tinyurl.com/mt35nuky&lt;/a&gt;
+&lt;a href="https://tinyurl.com/55cdu3ep"&gt;tinyurl.com/55cdu3ep&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23INTLBM"&gt;#INTLBM&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23Sohar"&gt;#Sohar&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EToro"&gt;#EToro&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Sobha"&gt;#Sobha&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Headlines"&gt;#Headlines&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:40 PM UTC</t>
+          <t>Apr 15, 2026 · 1:38 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-14T15:40:00Z</t>
+          <t>2026-04-15T13:38:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://tinyurl.com/4f7v9hen', 'https://tinyurl.com/2s3e7u9d', 'https://tinyurl.com/mt35nuky', 'https://tinyurl.com/55cdu3ep', 'https://x.com/search?f=tweets&amp;q=%23INTLBM', 'https://x.com/search?f=tweets&amp;q=%23Sohar', 'https://x.com/search?f=tweets&amp;q=%23EToro', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Sobha', 'https://x.com/search?f=tweets&amp;q=%23Headlines']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -1227,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1239,28 +1260,37 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+tinyurl.com/4f7v9hen
+tinyurl.com/2s3e7u9d
+tinyurl.com/mt35nuky
+tinyurl.com/55cdu3ep
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
     </row>
@@ -1270,73 +1300,77 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/Gulf_const</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>Gulf_const</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>Gulf Construction</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/3497523518/ff8c5dd3c169b9bb1240a76dd5f61a37_bigger.jpeg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on gulfconstructiononline.com/A…
+#GCnews #emirates #MENA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on &lt;a href="https://gulfconstructiononline.com/ArticleTA/414024"&gt;gulfconstructiononline.com/A…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23GCnews"&gt;#GCnews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emirates"&gt;#emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENA"&gt;#MENA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:36 PM UTC</t>
+          <t>Apr 15, 2026 · 12:19 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-14T15:36:00Z</t>
+          <t>2026-04-15T12:19:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://gulfconstructiononline.com/ArticleTA/414024', 'https://x.com/search?f=tweets&amp;q=%23GCnews', 'https://x.com/search?f=tweets&amp;q=%23emirates', 'https://x.com/search?f=tweets&amp;q=%23MENA']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1345,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1354,14 +1388,28 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on gulfconstructiononline.com/A…
+#GCnews #emirates #MENA</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
     </row>
@@ -1371,73 +1419,79 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/khir_llnas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>khir_llnas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>خير للناس للتنمية</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1823295456106930177/7M4AerkA_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+&lt;a href="/search?f=tweets&amp;amp;q=%23متبرعين_خير_للناس"&gt;#متبرعين_خير_للناس&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23مؤسسة_خير_للناس"&gt;#مؤسسة_خير_للناس&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:35 PM UTC</t>
+          <t>Apr 15, 2026 · 11:28 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-14T15:35:00Z</t>
+          <t>2026-04-15T11:28:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متبرعين_خير_للناس', 'https://x.com/search?f=tweets&amp;q=%23مؤسسة_خير_للناس']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1446,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1455,14 +1509,31 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
     </row>
@@ -1472,73 +1543,77 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/iRonyForChange</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>iRonyForChange</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>Preetam Chakraborty</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032194835424423936/eNr4L0LS_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['attas_2010', 'KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:32 PM UTC</t>
+          <t>Apr 15, 2026 · 10:57 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-14T15:32:00Z</t>
+          <t>2026-04-15T10:57:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
@@ -1549,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1558,16 +1633,31 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
     </row>
@@ -1577,43 +1667,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010</t>
+          <t>https://x.com/Sems3499</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>attas_2010</t>
+          <t>Sems3499</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>محمد</t>
+          <t>Sem</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1581396792075247620/ZCrbkCda_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1622,37 +1712,37 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>['KhalidSaeedR', 'amsh75', 'alrajhibank', 'BSF_sa', 'alinma', 'BankAlbilad', 'snbalahli', 'GulfIntlBank', 'EmiratesNBD_AE', 'BankAlJazira', 'RiyadBank', 'alawwalsab', 'SAIBLIVE']</t>
+          <t>['nurkanaydogan']</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 3:30 PM UTC</t>
+          <t>Apr 15, 2026 · 10:32 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-14T15:30:00Z</t>
+          <t>2026-04-15T10:32:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1661,26 +1751,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
     </row>
@@ -1690,86 +1776,94 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl</t>
+          <t>https://x.com/HarshGada76429</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>biztoday_intl</t>
+          <t>HarshGada76429</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Biz Today Intl</t>
+          <t>Harsh Gada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/948095006644097024/ns0iZtDe_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-biztoday.news/2026/04/14/emi…</t>
+          <t>I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; partner to offer integrated home financing solutions for off-plan projects in &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; .
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubairealestate"&gt;#Dubairealestate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23realestate"&gt;#realestate&lt;/a&gt;
-&lt;a href="https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;biztoday.news/2026/04/14/emi…&lt;/a&gt;</t>
+          <t>I haven&amp;#39;t got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['HarshGada76429', 'RBLBankCares', 'rblbank']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:37 PM UTC</t>
+          <t>Apr 15, 2026 · 10:06 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-14T13:37:00Z</t>
+          <t>2026-04-15T10:06:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubairealestate', 'https://x.com/search?f=tweets&amp;q=%23realestate', 'https://www.biztoday.news/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1778,28 +1872,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-biztoday.news/2026/04/14/emi…</t>
+          <t>I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
     </row>
@@ -1809,69 +1907,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/titledeednews</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>titledeednews</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>The Title Deed</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032863974820294659/y_r3-sNy_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها &amp;#34;الشركة العالمية القابضة&amp;#34; مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-&lt;a href="/adhuae" title="Moon"&gt;@adhuae&lt;/a&gt;
-&lt;a href="/ADX_AE" title="سوق أبوظبي للأوراق المالية"&gt;@ADX_AE&lt;/a&gt;
-&lt;a href="/DFMalerts" title="Dubai Financial Market"&gt;@DFMalerts&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الطاقة"&gt;#الطاقة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IHC"&gt;#IHC&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiInvestors"&gt;#DubaiInvestors&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OffPlanDubai"&gt;#OffPlanDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstateInvesting"&gt;#RealEstateInvesting&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1881,36 +1957,36 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 1:22 PM UTC</t>
+          <t>Apr 15, 2026 · 9:47 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-14T13:22:00Z</t>
+          <t>2026-04-15T09:47:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/adhuae', 'https://x.com/ADX_AE', 'https://x.com/DFMalerts', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الطاقة', 'https://x.com/search?f=tweets&amp;q=%23IHC', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiInvestors', 'https://x.com/search?f=tweets&amp;q=%23OffPlanDubai', 'https://x.com/search?f=tweets&amp;q=%23RealEstateInvesting', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
         </is>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1919,39 +1995,26 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
     </row>
@@ -1961,43 +2024,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/metakixakbar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>metakixakbar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>Akbar Syed</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1478686329114267649/s_YERTLm_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai dubaipropertyguide.io/emirat…</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai &lt;a href="https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/"&gt;dubaipropertyguide.io/emirat…&lt;/a&gt;</t>
+          <t>&lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2007,27 +2072,27 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:11 PM UTC</t>
+          <t>Apr 15, 2026 · 6:52 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-14T12:11:00Z</t>
+          <t>2026-04-15T06:52:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://dubaipropertyguide.io/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai-2/']</t>
+          <t>['https://x.com/ENBDdeals']</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2036,7 +2101,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2045,22 +2110,25 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai dubaipropertyguide.io/emirat…</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
     </row>
@@ -2070,75 +2138,71 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews</t>
+          <t>https://x.com/oras_2030</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OneVilleNews</t>
+          <t>oras_2030</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>One Ville News</t>
+          <t>oras2030</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1662461555869470723/h7J9k2pB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043694467731886080/mS-jeUsJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SobhaRealty"&gt;#SobhaRealty&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Partnership"&gt;#Partnership&lt;/a&gt; &lt;a href="/SobhaRealtyDXB" title="Sobha Realty"&gt;@SobhaRealtyDXB&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OneVilleNews"&gt;#OneVilleNews&lt;/a&gt;
-&lt;a href="https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/"&gt;onevillenews.com/2026/04/14/…&lt;/a&gt; via &lt;a href="/OneVilleNews" title="One Ville News"&gt;@onevillenews&lt;/a&gt;</t>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['AliAhmedk66633', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:57 AM UTC</t>
+          <t>Apr 15, 2026 · 6:25 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-14T11:57:00Z</t>
+          <t>2026-04-15T06:25:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SobhaRealty', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Business', 'https://x.com/search?f=tweets&amp;q=%23Partnership', 'https://x.com/SobhaRealtyDXB', 'https://x.com/search?f=tweets&amp;q=%23OneVilleNews', 'https://onevillenews.com/2026/04/14/emirates-nbd-and-sobha-realty-partner-to-offer-integrated-home-financing-solutions-for-off-plan-projects-in-dubai/', 'https://x.com/OneVilleNews']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2149,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2158,28 +2222,22 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-onevillenews.com/2026/04/14/… via @onevillenews</t>
+          <t>هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
         </is>
       </c>
     </row>
@@ -2189,67 +2247,63 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi</t>
+          <t>https://x.com/Eisa_Shj</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>nabilal_rawi</t>
+          <t>Eisa_Shj</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nabil Smarter</t>
+          <t>عـيـســى الأمـيــري</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1920220852898967552/0V_1IXmc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042552022017413120/xLRIeU1C_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE&amp;#39;s institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>['Zawya']</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 10:44 AM UTC</t>
+          <t>Apr 15, 2026 · 5:13 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-14T10:44:00Z</t>
+          <t>2026-04-15T05:13:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2264,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2273,22 +2327,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
     </row>
@@ -2298,47 +2352,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;Cs apply.
-emiratesnbd.com/en/promotion…</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles"&gt;emiratesnbd.com/en/promotion…&lt;/a&gt;</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  &lt;a href="https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers"&gt;arabianbusiness.com/finance/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2348,23 +2398,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 9:27 AM UTC</t>
+          <t>Apr 15, 2026 · 4:07 PM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-14T09:27:00Z</t>
+          <t>2026-04-15T16:07:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/promotions/emirates-holidays-skywards-bonus-miles']</t>
+          <t>['https://www.arabianbusiness.com/finance/emirates-islamic-launches-aed1m-campaign-for-sme-customers']</t>
         </is>
       </c>
       <c r="S17" t="n">
@@ -2374,40 +2424,34 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;Cs apply.
-emiratesnbd.com/en/promotion…</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  arabianbusiness.com/finance/…</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
     </row>
@@ -2417,118 +2461,116 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va</t>
+          <t>https://x.com/EntAlArabiya</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FirasAlin3va</t>
+          <t>EntAlArabiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>فراس علي</t>
+          <t>Entrepreneur العربية</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2036473244753207299/AACRtj0p_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>الإمارات الإسلامي &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنوك"&gt;#بنوك&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23شركات"&gt;#شركات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23مشاريع_صغيرة"&gt;#مشاريع_صغيرة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23اقتصاد"&gt;#اقتصاد&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23نمو"&gt;#نمو&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
+&lt;a href="https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Apr 14</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:56 AM UTC</t>
+          <t>Apr 15, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-14T00:56:00Z</t>
+          <t>2026-04-15T09:05:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23بنوك', 'https://x.com/search?f=tweets&amp;q=%23شركات', 'https://x.com/search?f=tweets&amp;q=%23مشاريع_صغيرة', 'https://x.com/search?f=tweets&amp;q=%23تمويل', 'https://x.com/search?f=tweets&amp;q=%23اقتصاد', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23نمو', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/04/15/77826/%d8%a7%d9%84%d8%a5%d9%85%d8%a7%d8%b1%d8%a7%d8%aa-%d8%a7%d9%84%d8%a5%d8%b3%d9%84%d8%a7%d9%85%d9%8a-%d9%8a%d8%af%d8%b9%d9%85-%d8%a7%d9%84%d8%b4%d8%b1%d9%83%d8%a7%d8%aa-%d8%a7%d9%84%d8%b5%d8%ba%d9%8a/']</t>
+        </is>
+      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
     </row>
@@ -2538,45 +2580,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero</t>
+          <t>https://x.com/dcgguide</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GidwaniHero</t>
+          <t>dcgguide</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hero Gidwani</t>
+          <t>DUBAI CITY GUIDE from Cyber Gear</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign &lt;a href="https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2586,23 +2626,23 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 8:01 PM UTC</t>
+          <t>Apr 15, 2026 · 9:02 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-14T20:01:00Z</t>
+          <t>2026-04-15T09:02:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://x.com/HHShkMohd', 'https://x.com/ENBDdeals', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/emiratesislamic']</t>
+          <t>['https://blog.dubaicityguide.com/site/emirates-islamic-drives-sme-growth-and-engagement-through-aed-1-million-business-banking-campaign/']</t>
         </is>
       </c>
       <c r="S19" t="n">
@@ -2612,10 +2652,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2624,25 +2664,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign blog.dubaicityguide.com/site…</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
     </row>
@@ -2652,43 +2689,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik</t>
+          <t>https://x.com/EntMagazineME</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ZaharaMMalik</t>
+          <t>EntMagazineME</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zahara Sadiq</t>
+          <t>Entrepreneur Middle East</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1123139785072304129/0KaXZD52_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514494189895049219/SrZOixX4_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening &lt;a href="/search?f=tweets&amp;amp;q=%23business"&gt;#business&lt;/a&gt; resilience across the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: &lt;a href="https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes"&gt;mena.entrepreneur.com/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2698,36 +2741,36 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 11:15 AM UTC</t>
+          <t>Apr 15, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-14T11:15:00Z</t>
+          <t>2026-04-15T07:11:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/search?f=tweets&amp;q=%23business', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://mena.entrepreneur.com/business-news/emirates-islamic-launches-business-banking-campaign-with-aed1-million-prize-pool-to-support-uae-smes']</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2736,22 +2779,31 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: mena.entrepreneur.com/busine…</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
     </row>
@@ -2761,73 +2813,81 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>aswanikumartst5</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TS Aswani Kumar</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1412710891515092994/OVnKv5t7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:15 AM UTC</t>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-14T07:15:00Z</t>
+          <t>2026-04-15T06:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2836,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>119</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2845,22 +2905,30 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2043932263390310621</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2901,16 +2969,22 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2920,23 +2994,23 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2949,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2958,28 +3032,29 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
     </row>
@@ -2989,12 +3064,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2043917165502316982</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3020,18 +3095,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-Your Weekly Perspective. A step toward a more mindful financial week.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -3041,36 +3112,32 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 5:00 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-14T05:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>56</v>
+        <v>147</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3079,31 +3146,27 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3176,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3144,40 +3207,48 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>['ZaharaMMalik']</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 12:00 PM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-14T12:00:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
+        </is>
+      </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -3188,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3197,14 +3268,30 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
     </row>
@@ -3214,12 +3301,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3245,42 +3332,42 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>['aswanikumartst5']</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 7:30 AM UTC</t>
+          <t>Apr 15, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-14T07:30:00Z</t>
+          <t>2026-04-15T17:42:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3289,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3298,14 +3385,18 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner)</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3406,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2043932266456367150</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3346,14 +3437,18 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>To know more:
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -3368,18 +3463,18 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S26" t="n">
@@ -3392,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3401,25 +3496,31 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>To know more:
-emiratesislamic.ae/en/key-in…</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
     </row>
@@ -3429,12 +3530,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2043932263725854816</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3460,16 +3561,16 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -3484,12 +3585,12 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -3501,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>85</v>
+        <v>204</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3513,32 +3614,18 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering</t>
         </is>
       </c>
     </row>
@@ -3548,12 +3635,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2043932263449006494</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3579,16 +3666,18 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;amp;utm_medium=socal&amp;amp;utm_campaign=psb_wealth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -3603,18 +3692,18 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/wealth-solutions/invest-in-gold-and-silver?utm_source=organiic-twitter&amp;utm_medium=socal&amp;utm_campaign=psb_wealth']</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3627,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>73</v>
+        <v>115</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3636,28 +3725,20 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/person…</t>
         </is>
       </c>
     </row>
@@ -3667,12 +3748,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2043932263386157239</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3698,20 +3779,18 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -3726,31 +3805,27 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Apr 14, 2026 · 6:00 AM UTC</t>
+          <t>Apr 15, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-04-14T06:00:00Z</t>
+          <t>2026-04-15T07:50:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="n">
-        <v>52</v>
+        <v>201</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3759,22 +3834,241 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-emiratesislamic.ae/ar/key-in…</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2044294656716836969</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-15T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>127</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2044294653097156714</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 15, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-15T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>194</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1848,16 +1848,16 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
-فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>استثمر في الأسهم و الصكوك و السندات و المعادن الثمينة (الذهب و الفضة)، كل ذلك من خلال تطبيق ENBD X.
-فرص استثمارية لا حصر لها، ابدأ الاستثمار اليوم
-https://t.co/6sm1UoslrI https://t.co/XdDf9aQ6x7</t>
+          <t>Not all interests work the same way — some are simple.
+Can you name this type? Comment your answer.
+#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
         </is>
       </c>
     </row>
@@ -1964,16 +1964,14 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.
-Can you name this type? Comment your answer.
-#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Not all interests work the same way — some are simple.
-Can you name this type? Comment your answer.
-#ENBDRiddleOfTheWeek #MoneyBasics #LearnFinance https://t.co/05i14Flw98</t>
+          <t>@EmiratesNBD_AE نزلتوا غرامه غير مستحقه علي بطاقة فيزا الائتمانية ورفعت ايميل بالمشكلة ولا تن الرد 
+لا انصح بالتعامل معهم</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3246,12 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Best Foods High in Fiber https://t.co/j3Qv2TBkZl</t>
+          <t>The Golden Elixir https://t.co/LGgbrnkX3c</t>
         </is>
       </c>
     </row>
@@ -5287,13 +5285,27 @@
 Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/aaditsh/status/2044732404938702855</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
+          <t>This is one of my favorite ideas in all of writing.
+Ed Sheeran calls it the dirty tap.
+Turn it on, dirty water flows out for a long time. Eventually clean water starts coming. He's talking about songs but it's true for all creative work.
+Every CEO memo that got quoted. Every keynote that landed. Every email that actually changed someone's mind. All of it came out of a dozen bad drafts first.
+The dirty water is necessary. You need to get the bad ideas out before the good ones come. That's just how it works.</t>
         </is>
       </c>
     </row>
@@ -6652,25 +6664,14 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2044657039859757511</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
         <is>
           <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
 فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>ليست المشكلة فيما تنفقه، بل في ما يتسرّب منه بصمت.
-فالمبالغ الصغيرة التي نظنها "غير مهمّة"، هي غالباً ما تتراكم وتؤثر على ميزانيتك أكثر مما تتوقع.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,81 +566,75 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2045277395985526953</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9</t>
+          <t>https://x.com/she7ii88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>InnerSunshine9</t>
+          <t>she7ii88</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>InnerSunshine</t>
+          <t>Rashed Sem</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1988072486542733312/nEKgrRmJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1752368468144316416/8qdE3N-C_bigger.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-invidious.tiekoetter.com/watch?v=qLGNj-xr…
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: &amp;#34;Mr Indifferent&amp;#34; by Aryasb Feiz | CGMeetup
-&lt;a href="https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY"&gt;invidious.tiekoetter.com/watch?v=qLGNj-xr…&lt;/a&gt;
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 11:05 PM UTC</t>
+          <t>Apr 20, 2026 · 2:59 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-17T23:05:00Z</t>
+          <t>2026-04-20T02:59:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://invidious.tiekoetter.com/watch?v=qLGNj-xrgvY']</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -651,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -660,139 +654,17 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-invidious.tiekoetter.com/watch?v=qLGNj-xr…
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/InnerSunshine9/status/2045277395985526953</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Animated Kindness Video, share!
-CGI Animated Short Film: "Mr Indifferent" by Aryasb Feiz | CGMeetup
-https://t.co/jqAIbUi4ot
-Made for Emirates NBD Bank.
-Agency: Leo Burnett, Dubai
-Celebrating World Kindness Day</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2045251200086663547</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>xmn9oori</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>بوسلطان 💜</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034089445235036165/s553Bp_u_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 9:20 PM UTC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-04-17T21:20:00Z</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>70</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>لمدة كم الاسترداد؟</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/xmn9oori/status/2045251200086663547</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -806,7 +678,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -821,51 +693,165 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kyodonews_JBN</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KYODONEWS JBN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+&lt;a href="https://kyodonewsprwire.jp/release/202604177681"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-20T01:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://kyodonewsprwire.jp/release/202604177681']</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2045169182015139851</t>
+          <t>2045958337494143476</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/ansariiarif</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>ansariiarif</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>Arif</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1268363851231383555/JkBzC9kT_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-worldfinanceinforms.com/card…</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-&lt;a href="https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east"&gt;worldfinanceinforms.com/card…&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn&amp;#39;t be!!!</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -875,37 +861,37 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:55 PM UTC</t>
+          <t>Apr 19, 2026 · 8:10 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-17T15:55:00Z</t>
+          <t>2026-04-19T20:10:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://www.worldfinanceinforms.com/cards-payments/emirates-nbd-and-nium-join-forces-to-transform-global-cross-border-payments-in-the-middle-east']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
         <v>3</v>
       </c>
-      <c r="V4" t="n">
-        <v>102</v>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>ENBD</t>
@@ -913,23 +899,25 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Emirates NBD und Nium bündeln ihre Kräfte, um den globalen grenzüberschreitenden Zahlungsverkehr im Nahen Osten zu transformieren
-worldfinanceinforms.com/card…</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169182015139851</t>
+          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>🤫🤫🤫😉</t>
+          <t>@EmiratesNBD_AE 
+I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
         </is>
       </c>
     </row>
@@ -939,84 +927,82 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2045169009662763334</t>
+          <t>2045922728868479327</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843/status/2045169009662763334</t>
+          <t>https://x.com/f3100000/status/2045922728868479327</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/MC81236843</t>
+          <t>https://x.com/f3100000</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC81236843</t>
+          <t>f3100000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M C</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1163517530822119426/IK5LwgTg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2024219709168918529/LqA8XT-p_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-&lt;a href="https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;</t>
+          <t>دعم من اي نوع هذا</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:54 PM UTC</t>
+          <t>Apr 19, 2026 · 5:49 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-17T15:54:00Z</t>
+          <t>2026-04-19T17:49:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesnbd.com/en/media-center/completion-of-the-sale-and-purchase-of-9985-of-the-shares-in-denizbank-as-by-emirates-nbd-from-sberb']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1025,16 +1011,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>دعم من اي نوع هذا</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/f3100000/status/2045922728868479327</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Emirates NBD Bank PJSC und Berbank of Russia beziehen sich auf die Ankündigung vom 30. Juni 2019 bezüglich der Genehmigung durch die Bankenaufsichtsbehörden in den Vereinigten Arabischen Emiraten, der Türkei, Österreich und Russland
-emiratesnbd.com/en/media-cen…</t>
+          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
         </is>
       </c>
     </row>
@@ -1044,43 +1036,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2045166464181702828</t>
+          <t>2045894623957278735</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MBS_20121</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>A h m a d A l h ar b i</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1357665933368696832/CgwgbAyQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل_العقاري"&gt;#التمويل_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiHolding"&gt;#DubaiHolding&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1095,22 +1093,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:44 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-17T15:44:00Z</t>
+          <t>2026-04-19T15:57:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23التمويل_العقاري', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DubaiHolding']</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1119,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1128,22 +1126,29 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>🧵 6/
+🎯 خلاصة:
+يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
+#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/MBS_20121/status/2045166464181702828</t>
+          <t>https://x.com/almidfa75/status/2045894623957278735</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى يتم دعم إضافة بطاقة مزيد الي قوقل باي Google pay</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
         </is>
       </c>
     </row>
@@ -1153,49 +1158,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2045155322356961286</t>
+          <t>2045894611756048610</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
+          <t>https://x.com/almidfa75/status/2045894611756048610</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/almidfa75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>almidfa75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Faisal Al Midfa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_العقاري"&gt;#القطاع_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل"&gt;#التمويل&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1205,32 +1208,36 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:00 PM UTC</t>
+          <t>Apr 19, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-17T15:00:00Z</t>
+          <t>2026-04-19T15:57:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23القطاع_العقاري', 'https://x.com/search?f=tweets&amp;q=%23التمويل']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1239,31 +1246,18 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp; Conditions Apply.
-Tax registration number: 204-897-319</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2045155322356961286</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
-        </is>
-      </c>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Your phone, Your smarter way to pay.
-Activate Apple Pay with your Emirates NBD cards in your Apple devices and enjoy fast, secure payments every day.
-Terms &amp;amp; Conditions Apply.
-Tax registration number: 204-897-319 https://t.co/uyaLjydHaw</t>
+          <t>🧵 1/
+في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
+#دبي #القطاع_العقاري #التمويل</t>
         </is>
       </c>
     </row>
@@ -1273,49 +1267,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2045138554464915956</t>
+          <t>2045881062304456946</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb</t>
+          <t>https://x.com/ThisMadEngineer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yallaweb</t>
+          <t>ThisMadEngineer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M.G.</t>
+          <t>Ankesh / MadEngineer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1840606846068875264/V7l0ThZZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/677437091211530240/U61xnBOL_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-#الامارات #دبي #ابوظبي #UAE #Dubai    
-#AbuDhabi @HHShkMohd 
-@MohamedBinZayed @emirates @EmiratesNBD_AE @WPP</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-&lt;a href="/search?f=tweets&amp;amp;q=%23الامارات"&gt;#الامارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ابوظبي"&gt;#ابوظبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;    
-&lt;a href="/search?f=tweets&amp;amp;q=%23AbuDhabi"&gt;#AbuDhabi&lt;/a&gt; &lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; 
-&lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/WPP" title="WPP"&gt;@WPP&lt;/a&gt;</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1324,30 +1312,26 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['HamdanMohammed']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:53 PM UTC</t>
+          <t>Apr 19, 2026 · 3:03 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-17T13:53:00Z</t>
+          <t>2026-04-19T15:03:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الامارات', 'https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23ابوظبي', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23AbuDhabi', 'https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/emirates', 'https://x.com/EmiratesNBD_AE', 'https://x.com/WPP']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1355,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>52</v>
+        <v>287</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1367,31 +1351,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ابرؤا ذمتكم واعيدوا لنا ما سرقتموه من أموالنا لترضوا اسيادكم من حفدة القردة و الخنازير.
-#الامارات #دبي #ابوظبي #UAE #Dubai    
-#AbuDhabi @HHShkMohd 
-@MohamedBinZayed @emirates @EmiratesNBD_AE @WPP</t>
+          <t>Thanks!</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/yallaweb/status/2045138554464915956</t>
+          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>اطلعت اليوم على سير العمل في أول محطة للإقلاع والهبوط العمودي للتاكسي الجوي في دبي، الأولى من نوعها على مستوى العالم، والتي تم تنفيذها بالقرب من مطار دبي الدولي… المحطة جاهزة، وهي ضمن شبكة تشمل محطات في داون تاون ونخلة جميرا ومرسى دبي ستكون جاهزة مع نهاية العام الجاري. 
-ستخدم المحطة الأولى نحو 170 ألف راكب سنوياً، ووجهنا بتشغيل الخدمة وإطلاقها للجمهور خلال العام الجاري وفقاً لأرقى المعايير الدولية. 
-هذا المشروع خطوة مفصلية في مسيرة دبي نحو ريادة مستقبل التنقل الحضري عالمياً، واختصار الزمن وتقريب المسافات، ونشكر فريق هيئة الطرق والمواصلات والشركاء المحليين والعالميين على جهودهم في إنجاز هذا المشروع النوعي الذي يأتي تزامناً مع النسخة الأولى من اليوم العالمي للمواصلات العامة في 17 أبريل سنوياً.
-في دبي نحول الأفكار والطموحات إلى واقع ملموس… فدبي تجيد التحليق.</t>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
         </is>
       </c>
     </row>
@@ -1401,43 +1376,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2045130309323071836</t>
+          <t>2045850840196694451</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2045130309323071836</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global</t>
+          <t>https://x.com/r35sk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>dar_global</t>
+          <t>r35sk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DarGlobal</t>
+          <t>ريم</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1904290533372985344/OQZ0hS5Q_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1976063720942968832/0TB4sf0G_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion &lt;a href="https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;bebeez.eu/2026/04/16/emirate…&lt;/a&gt;</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1452,20 +1427,16 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:20 PM UTC</t>
+          <t>Apr 19, 2026 · 1:03 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-17T13:20:00Z</t>
+          <t>2026-04-19T13:03:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://bebeez.eu/2026/04/16/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1476,7 +1447,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1485,22 +1456,22 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion bebeez.eu/2026/04/16/emirate…</t>
+          <t>الحمدلله الحمرا فيها صرافة enbd</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://x.com/dar_global/status/2045130309323071836</t>
+          <t>https://x.com/r35sk/status/2045850840196694451</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>LSE-listed Dar Global secures $250mln term loan https://t.co/6wbMOXS2Dg</t>
+          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
         </is>
       </c>
     </row>
@@ -1510,49 +1481,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2045118948694470845</t>
+          <t>2045850184811422052</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181</t>
+          <t>https://x.com/AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GeorgeDon5181</t>
+          <t>AhmedAlhaq79518</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Don George</t>
+          <t>Ahmed Alhaìqi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1997686160211243008/2Cf-bh5c_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2015365820088803328/seUb2ZG5_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1571,12 +1536,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 12:35 PM UTC</t>
+          <t>Apr 19, 2026 · 1:01 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-17T12:35:00Z</t>
+          <t>2026-04-19T13:01:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1600,33 +1565,22 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>good (Iin in it+i8 
-I8. 8iii cf CT  FB
- FC m
- , (? +II in IIWII îîctffze</t>
+          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/GeorgeDon5181/status/2045118948694470845</t>
+          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Fake Android updates are rising. They can trick you into installing unsafe apps or sharing details. 
-Turn on Smart Touch and Face Pass for secure login.
-تشهد التحديثات الوهمية على أجهزة أندرويد تزايداً ملحوظاً، وقد تُستخدم لخداعك لتثبيت تطبيقات غير آمنة أو مشاركة البيانات.
-احمِ حسابك من خلال تفعيل ميزة اللمس الذكي والتعرّف على الوجه
-لتسجيل دخول أكثر أماناً.</t>
+          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
         </is>
       </c>
     </row>
@@ -1636,55 +1590,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2045086967533031764</t>
+          <t>2045824669907845529</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/m_azeemq</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>m_azeemq</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Muhammad Azeem Qureshi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-emiratesnbd.com/en/media-cen…
-emiratesnbd.com/ar/media-cen…
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt; , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-&lt;a href="https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global"&gt;emiratesnbd.com/ar/media-cen…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1694,36 +1636,36 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:28 AM UTC</t>
+          <t>Apr 19, 2026 · 11:19 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-17T10:28:00Z</t>
+          <t>2026-04-19T11:19:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/dar_global', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://www.emiratesnbd.com/ar/media-center/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>530</v>
+        <v>13</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1732,40 +1674,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-emiratesnbd.com/en/media-cen…
-emiratesnbd.com/ar/media-cen…
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2045086967533031764</t>
+          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Emirates NBD has successfully executed a USD 250 million syndicated term loan facility for @dar_global , strengthening its financial flexibility to support ongoing international development activity.
-This transaction reflects our continued role in structuring and delivering cross-border financing solutions for leading real estate developers, supported  by strong distribution capabilities and established lender relationships.
-We remain focused on helping clients scale with clarity, speed and disciplined access to capital across key markets.
-Read more here:
-https://t.co/91twU74VX9
-https://t.co/hfV7wLDhaI
-#EmiratesNBD #SyndicatedLoan #CapitalMarkets #Banking #Dubai</t>
+          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
         </is>
       </c>
     </row>
@@ -1775,47 +1699,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2045079926013837337</t>
+          <t>2045821589539733783</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/CWSaudi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>CWSaudi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Construction Week Saudi</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1494269682098089989/5bK0V1be_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
+Read more:
+constructionweeksaudi.com/bu…</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>. &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt;  has secured a $250M loan arranged by &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; , as the &lt;a href="/search?f=tweets&amp;amp;q=%23London"&gt;#London&lt;/a&gt; -listed developer behind &lt;a href="/realDonaldTrump" title="Donald J. Trump"&gt;@realDonaldTrump&lt;/a&gt; -branded projects expands its pipeline.
+Read more:
+&lt;a href="https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump"&gt;constructionweeksaudi.com/bu…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1825,23 +1749,23 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 10:00 AM UTC</t>
+          <t>Apr 19, 2026 · 11:07 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-17T10:00:00Z</t>
+          <t>2026-04-19T11:07:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
+          <t>['https://x.com/dar_global', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23London', 'https://x.com/realDonaldTrump', 'https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump']</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1851,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1863,30 +1787,28 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Turn your bills into rewards
-Get AED 500 worth of Majid Al Futtaim voucher when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
+Read more:
+constructionweeksaudi.com/bu…</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2045079926013837337</t>
+          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>دلّل نفسك مع جراند فلورا سبا 💅
-احصل على خصم 15% على فاتورتك بقيمة 150 درهم أو أكثر، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/NILbsZvhfk https://t.co/Elvcoo2HNL</t>
+          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
+Read more ll
+https://t.co/UvrhC24nWJ</t>
         </is>
       </c>
     </row>
@@ -1896,84 +1818,90 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2045067912894201918</t>
+          <t>2045814764828516809</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance</t>
+          <t>https://x.com/UaeAlteneiji</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ForumRemittance</t>
+          <t>UaeAlteneiji</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>World Remittance Action Forum</t>
+          <t>أبو عمر ، عبدالرحمن الطنيجي</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1906440728953204736/EXccdOZS_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-#EmiratesNBD #DarGlobal #SyndicatedLoan #RealEstate #MENAT #BankingNews #Finance #GlobalMarkets</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DarGlobal"&gt;#DarGlobal&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RealEstate"&gt;#RealEstate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MENAT"&gt;#MENAT&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalMarkets"&gt;#GlobalMarkets&lt;/a&gt;</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 9:12 AM UTC</t>
+          <t>Apr 19, 2026 · 10:40 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-17T09:12:00Z</t>
+          <t>2026-04-19T10:40:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DarGlobal', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23RealEstate', 'https://x.com/search?f=tweets&amp;q=%23MENAT', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23Finance', 'https://x.com/search?f=tweets&amp;q=%23GlobalMarkets']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1982,23 +1910,34 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Emirates NBD, a leading banking group across the MENAT region, has successfully executed a USD 250 million syndicated term loan facility, “Project Radium II,” for DarGlobal.
-#EmiratesNBD #DarGlobal #SyndicatedLoan #RealEstate #MENAT #BankingNews #Finance #GlobalMarkets</t>
+          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2045067912894201918</t>
+          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Atradius, a global leader in trade credit insurance and risk management, has established operations in the Dubai International Financial Centre (DIFC), marking a key milestone in its Middle East growth strategy.#Atradius #DIFC #MiddleEast #Insurance #RiskManagement #TradeCredit https://t.co/0x6KlHhlpo</t>
+          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
+اعلان غير موفق
+اعلان محدد بتاريخ صلاحية 
+اعلان تحكمه الشروط والاحكام المجهولة
+هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
         </is>
       </c>
     </row>
@@ -2008,73 +1947,75 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2045063430139433260</t>
+          <t>2045805999718903933</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/abasetaljanahi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>abasetaljanahi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>Abdulbaset Al Janahi</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1572294225240231936/Ew_orY09_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing dubaipropertyguide.io/dubai-…</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing &lt;a href="https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/"&gt;dubaipropertyguide.io/dubai-…&lt;/a&gt;</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:54 AM UTC</t>
+          <t>Apr 19, 2026 · 10:05 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-17T08:54:00Z</t>
+          <t>2026-04-19T10:05:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://dubaipropertyguide.io/dubai-holding-real-estate-and-emirates-nbd-partner-to-introduce-integrated-off-plan-mortgage-financing/']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2083,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2092,22 +2033,25 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing dubaipropertyguide.io/dubai-…</t>
+          <t>بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045063430139433260</t>
+          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Dubai Holding Real Estate And Emirates NBD Partner To Introduce Integrated Off-Plan Mortgage Financing https://t.co/Iica48plSc</t>
+          <t>@EmiratesNBD_AE بس! 
+وايد عليكم</t>
         </is>
       </c>
     </row>
@@ -2117,45 +2061,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2045051886051688548</t>
+          <t>2045801203934925261</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686</t>
+          <t>https://x.com/amerbinhraiz</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AdnanAf33353686</t>
+          <t>amerbinhraiz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Adnan Afridi</t>
+          <t>بـتـال | Batal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1695298421714804736/A6PpWdw3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2033838640934359040/zShxD0Gl_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -2169,23 +2117,23 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 8:08 AM UTC</t>
+          <t>Apr 19, 2026 · 9:46 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-17T08:08:00Z</t>
+          <t>2026-04-19T09:46:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -2194,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2203,31 +2151,31 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Hi I want to open account in nbd but my application was rejected 
-Live account is free with no minimum balance or need minimum balance</t>
+          <t>نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/AdnanAf33353686/status/2045051886051688548</t>
+          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>في إطار مبادرة #متحدون_ضد_الاحتيال، قمنا بزيارة مجمّع إقامة عاملات من أجل رفع مستوى الوعي لديهن عن عمليات الاحتيال الإلكتروني وكيفية تجنبها.
-ومن خلال جلسات تفاعلية، ومسابقات، ونقاشات مفتوحة، تعرّفت المُشارِكات على كيفية اكتشاف عمليات الاحتيال، وتجنّبها وطرق الإبلاغ عنها.
-الوعي هو الخطوة الأولى نحو الحماية.
-ابقَ آمناً. كن متيقظاً.
-#متحدون_ضد_الاحتيال</t>
+          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
+المديونيات الطويلة القديمة
+كل شي واقف عليهم وماخذين فايدة
+ عليهم ضعف قيمة القرض !</t>
         </is>
       </c>
     </row>
@@ -2237,43 +2185,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2045041596106781053</t>
+          <t>2045786366504796559</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AnasYousiftpy0</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anas Yousif</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2020265249027289088/ZwoWrEZ3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2282,22 +2230,22 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>['CryptoNewsHntrs']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 7:28 AM UTC</t>
+          <t>Apr 19, 2026 · 8:47 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-17T07:28:00Z</t>
+          <t>2026-04-19T08:47:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2309,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2321,24 +2269,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>هذه أخبار رائعة لعملاء Emirates NBD في المنطقة</t>
+          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/AnasYousiftpy0/status/2045041596106781053</t>
+          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
-#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
+          <t>نحتاج تأجيل 3 شهور للازمه</t>
         </is>
       </c>
     </row>
@@ -2348,97 +2294,71 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2045034471821549807</t>
+          <t>2045785730023301620</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad</t>
+          <t>https://x.com/SultanAbdu70381</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Net_eqtisad</t>
+          <t>SultanAbdu70381</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>الشبكة الاقتصادية</t>
+          <t>Sultan Abdullah</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1892643729745317888/Zh1HkNvX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt;
-&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;
-&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-&lt;a href="/eAndUAE" title="e&amp;amp; UAE"&gt;@eAndUAE&lt;/a&gt;
-&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;
-&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;
-&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;
-@adnocdrillinguae
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23الأسواق"&gt;#الأسواق&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أدنوك"&gt;#أدنوك&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الشبكة_الاقتصادية"&gt;#الشبكة_الاقتصادية&lt;/a&gt;</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 6:59 AM UTC</t>
+          <t>Apr 19, 2026 · 8:45 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-17T06:59:00Z</t>
+          <t>2026-04-19T08:45:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndUAE', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23الأسواق', 'https://x.com/search?f=tweets&amp;q=%23أدنوك', 'https://x.com/search?f=tweets&amp;q=%23الشبكة_الاقتصادية']</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>0</v>
       </c>
@@ -2446,10 +2366,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>121</v>
+        <v>11</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2458,61 +2378,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية</t>
+          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2045034471821549807</t>
+          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>يتصدرها بنك الإمارات دبي الوطني .. أداء أكبر الأسهم الإماراتية خلال شهر أبريل 2026
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE 
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adnocdrillinguae
-#الإمارات 
-#الأسواق #أدنوك
-#الشبكة_الاقتصادية https://t.co/rO2sscergA</t>
+          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
         </is>
       </c>
     </row>
@@ -2522,82 +2403,82 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2045015539907772833</t>
+          <t>2045755517948272900</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045015539907772833</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/girluae11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>girluae11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>girl</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043687946625368066/wksZEFYW_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion blog.dubaicityguide.com/site…</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 5:44 AM UTC</t>
+          <t>Apr 19, 2026 · 6:44 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-17T05:44:00Z</t>
+          <t>2026-04-19T06:44:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-successfully-executes-usd-250-million-syndicated-term-loan-facility-for-dar-global-accelerating-global-growth-and-expansion/']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2606,22 +2487,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion blog.dubaicityguide.com/site…</t>
+          <t>من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2045015539907772833</t>
+          <t>https://x.com/girluae11/status/2045755517948272900</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Emirates NBD Successfully Executes USD 250 Million Syndicated Term Loan Facility For DAR Global, Accelerating Global Growth And Expansion https://t.co/ukTtwwan5a</t>
+          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
         </is>
       </c>
     </row>
@@ -2631,43 +2512,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2045007726171099435</t>
+          <t>2045729029614129456</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_/status/2045007726171099435</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_</t>
+          <t>https://x.com/bu_rashed98</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>oppolutty_</t>
+          <t>bu_rashed98</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>തവിട് തങ്കമ്മ ® 👒</t>
+          <t>﮼💛🇦🇪الامبراطور 🇦🇪💛</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037238374906683392/bv83nzp4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042287480335187974/x8vTEs88_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>for credit card payment?</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>for credit card payment?</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2676,28 +2557,28 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE', 'SunnyLusty']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 5:13 AM UTC</t>
+          <t>Apr 19, 2026 · 4:59 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-17T05:13:00Z</t>
+          <t>2026-04-19T04:59:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2706,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2715,22 +2596,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>for credit card payment?</t>
+          <t>أنا وياهم 😁</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/oppolutty_/status/2045007726171099435</t>
+          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
         </is>
       </c>
     </row>
@@ -2740,65 +2621,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044992676236587055</t>
+          <t>2045744202651226430</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews/status/2044992676236587055</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>arabtimesnews</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arab Times News</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1793936454734712832/oEtzciVg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-arabtimesnews.com/uaes-10-mo…
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-&lt;a href="https://arabtimesnews.com/uaes-10-most-valuable-listed-companies-in-2026/"&gt;arabtimesnews.com/uaes-10-mo…&lt;/a&gt;
-International Holding Company (&lt;a href="/ihc__official" title="IHC"&gt;@ihc__official&lt;/a&gt; )
-TAQA Group (&lt;a href="/TAQAGroup" title="TAQA"&gt;@TAQAGroup&lt;/a&gt;)
-ADNOC Gas (&lt;a href="/ADNOCGas" title="ADNOC Gas"&gt;@ADNOCGas&lt;/a&gt;)
-First Abu Dhabi Bank (&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;)
-Emirates NBD Group (&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;)
-e&amp;amp; (&lt;a href="/eAndGroup" title="e&amp;amp;"&gt;@eAndGroup&lt;/a&gt;)
-Dubai Electricity and Water Authority (&lt;a href="/DEWAOfficial" title="DEWA | Official Page"&gt;@DEWAOfficial&lt;/a&gt;)
-Emaar Properties (&lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;)
-Abu Dhabi Commercial Bank (&lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;)
-Alpha Dhabi Holding (&lt;a href="/adh_uae" title="Alpha Dhabi Holding"&gt;@adh_uae&lt;/a&gt;)</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2808,23 +2675,23 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 4:13 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-17T04:13:00Z</t>
+          <t>2026-04-19T06:00:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['https://arabtimesnews.com/uaes-10-most-valuable-listed-companies-in-2026/', 'https://x.com/ihc__official', 'https://x.com/TAQAGroup', 'https://x.com/ADNOCGas', 'https://x.com/FABConnects', 'https://x.com/EmiratesNBD_AE', 'https://x.com/eAndGroup', 'https://x.com/DEWAOfficial', 'https://x.com/emaardubai', 'https://x.com/OfficialADCB', 'https://x.com/adh_uae']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="S20" t="n">
@@ -2837,64 +2704,41 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-arabtimesnews.com/uaes-10-mo…
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
+💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
+الوضوح يجعل الأمر أسهل في الإدارة. 
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/arabtimesnews/status/2044992676236587055</t>
+          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-https://t.co/yZ0hDQKWQJ
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>UAE’s 10 Most Valuable Listed Companies in 2026.
-https://t.co/yZ0hDQKWQJ
-International Holding Company (@ihc__official )
-TAQA Group (@TAQAGroup)
-ADNOC Gas (@ADNOCGas)
-First Abu Dhabi Bank (@FABConnects)
-Emirates NBD Group (@EmiratesNBD_AE)
-e&amp; (@eAndGroup)
-Dubai Electricity and Water Authority (@DEWAOfficial)
-Emaar Properties (@emaardubai)
-Abu Dhabi Commercial Bank (@OfficialADCB)
-Alpha Dhabi Holding (@adh_uae)</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
+55 businesses will be winners. Will you be one of them?
+⭐️Grand cash prize: AED 250,000 (1 winner)
+💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
     </row>
@@ -2904,71 +2748,81 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044988741345747256</t>
+          <t>2045744202382807549</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9/status/2044988741345747256</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AbdulAzizAbpv9</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>عبد العزيز المشاولة</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035325614547443712/Z6T88mVG_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>نفخر بأنفسنا@نعم نفرح كثير/&lt; بالارهاب مطار البحرين/ فداك الوطن</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>نفخر بأنفسنا@نعم نفرح كثير/&amp;lt; بالارهاب مطار البحرين/ فداك الوطن</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Apr 17</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 3:58 AM UTC</t>
+          <t>Apr 19, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-17T03:58:00Z</t>
+          <t>2026-04-19T06:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
@@ -2979,35 +2833,46 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>نفخر بأنفسنا@نعم نفرح كثير/&lt; بالارهاب مطار البحرين/ فداك الوطن</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulAzizAbpv9/status/2044988741345747256</t>
+          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE https://t.co/TWfYdjxwLN</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>A nation united. A pride we all share. 🇦🇪
-In line with the call of His Highness Sheikh Mohammed bin Rashid Al Maktoum, let’s raise the UAE flag high and take pride in the unity, strength, and spirit that define our nation.
-Join this moment of pride. #ProudOfUAE https://t.co/TWfYdjxwLN</t>
+          <t>Outstanding payments = constant stress.
+💡 Tip:
+Write everything down in one place
+Clarity makes it feel manageable.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
         </is>
       </c>
     </row>
@@ -3017,45 +2882,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044955402941673971</t>
+          <t>2045771180469272971</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN/status/2044955402941673971</t>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/Kyodonews_JBN</t>
+          <t>https://x.com/firstdiver4ever</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kyodonews_JBN</t>
+          <t>firstdiver4ever</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>KYODONEWS JBN</t>
+          <t>اماراتى وافتخر</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-&lt;a href="https://kyodonewsprwire.jp/release/202604167601"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -3065,1121 +2930,63 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Apr 17</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 17, 2026 · 1:45 AM UTC</t>
+          <t>Apr 19, 2026 · 7:47 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-17T01:45:00Z</t>
+          <t>2026-04-19T07:47:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://kyodonewsprwire.jp/release/202604167601']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully executes USD 250 Million Syndicated Term Loan facility for Dar Global, Accelerating Global Growth and Expansion【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2045019425548452068</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-04-17T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>50</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548452068</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Always check fines through official RTA apps or websites - not SMS links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>66</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
-Valid until 30 June 2026.
-Terms and conditions apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>93</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
-55 businesses will be winners. Will you be one of them?
-⭐️Grand cash prize: AED 250,000 (1 winner)
-💸 Second cash prize: AED 100,000 each (2 winners)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2045083209231221028</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_offer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-business-banking-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_offer']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>44</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>💸الجوائز النقدية الشهرية: من 5,000 إلى 25,000 درهم (52 فائز)
-يسري العرض لغاية 30 يونيو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083209231221028</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان) https://t.co/WPnaJpO7F4</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان) https://t.co/WPnaJpO7F4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2045083206936908088</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083206936908088</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 10:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-04-17T10:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>69</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية التي تصل قيمتها إلى 1,000,000 درهم.
-اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟
-⭐️الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
-💸الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2045041921689530456</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045041921689530456</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>['huss23']</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:29 AM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:29:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>3</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045041921689530456</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
-Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
-Impressed with how difficult they make this process. Wow!</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2045035981535912006</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>['alsajwani1']</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:05 AM UTC</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:05:00Z</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>16</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045035981535912006</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-السلام عليكم
-زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
-أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
-والى اليوم الخميس الإدارة لم ترد عليهم 
-هل هذ التأخير له مبرر
-او عدم هو اهتمام بالعملاء</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-السلام عليكم
-زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
-أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
-والى اليوم الخميس الإدارة لم ترد عليهم 
-هل هذ التأخير له مبرر
-او عدم هو اهتمام بالعملاء</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2045034534274540029</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045034534274540029</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>['1ss9490ss1']</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 7:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-04-17T07:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>2</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045034534274540029</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
-💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/y8cuMSrpQL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2045019425548460066</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548460066</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 17, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2026-04-17T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>61</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045019425548460066</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>تحقق دائماً من المخالفات عبر تطبيقات أو مواقع هيئة الطرق والمواصلات الرسمية، وليس من خلال روابط الرسائل النصية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,105 +566,903 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046418526051684674</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88</t>
+          <t>https://x.com/yallaweb</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>she7ii88</t>
+          <t>yallaweb</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rashed Sem</t>
+          <t>M.G.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1752368468144316416/8qdE3N-C_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1840606846068875264/V7l0ThZZ_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+          <t>#EmiratesNBD @EmiratesNBD_AE Sent Me An Account Statement,They Owe Me 200000AED Which They Won't Pay.@HHShkMohd @MohamedBinZayed
+#Lebanese #Banks Stole My Money @FransabankGroup @EmmanuelMacron.
+#Emirates @emirates &amp; @BarackObama
+ Owe Me 2 Years Pay
+I Am Just Too Tired To Give Up</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Sent Me An Account Statement,They Owe Me 200000AED Which They Won&amp;#39;t Pay.&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23Lebanese"&gt;#Lebanese&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banks"&gt;#Banks&lt;/a&gt; Stole My Money &lt;a href="/FransabankGroup" title="Fransabank Group"&gt;@FransabankGroup&lt;/a&gt; &lt;a href="/EmmanuelMacron" title="Emmanuel Macron"&gt;@EmmanuelMacron&lt;/a&gt;.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt; &lt;a href="/emirates" title="Emirates"&gt;@emirates&lt;/a&gt; &amp;amp; &lt;a href="/BarackObama" title="Barack Obama"&gt;@BarackObama&lt;/a&gt;
+ Owe Me 2 Years Pay
+I Am Just Too Tired To Give Up</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>29s</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026 · 2:39 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-04-21T02:39:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/EmiratesNBD_AE', 'https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/search?f=tweets&amp;q=%23Lebanese', 'https://x.com/search?f=tweets&amp;q=%23Banks', 'https://x.com/FransabankGroup', 'https://x.com/EmmanuelMacron', 'https://x.com/search?f=tweets&amp;q=%23Emirates', 'https://x.com/emirates', 'https://x.com/BarackObama']</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>#EmiratesNBD @EmiratesNBD_AE Sent Me An Account Statement,They Owe Me 200000AED Which They Won't Pay.@HHShkMohd @MohamedBinZayed
+#Lebanese #Banks Stole My Money @FransabankGroup @EmmanuelMacron.
+#Emirates @emirates &amp; @BarackObama
+ Owe Me 2 Years Pay
+I Am Just Too Tired To Give Up</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>#God I Hate Slow #Internet,it's Killer Of  #Productivity
+Had 1000Mbps In #MexicoCity,But #GenocidalJews &amp;amp; #GenocidalGays Did    #Sabotage That,As They Thought My #highspeed Can Hinder/Expose/Endanger Their Crimes &amp;amp; Conspiracies.
+#EconomicSiege #Mexico #CDMX #Islamophobia #USA</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>#God I Hate Slow #Internet,it's Killer Of  #Productivity
+Had 1000Mbps In #MexicoCity,But #GenocidalJews &amp;amp; #GenocidalGays Did    #Sabotage That,As They Thought My #highspeed Can Hinder/Expose/Endanger Their Crimes &amp;amp; Conspiracies.
+#EconomicSiege #Mexico #CDMX #Islamophobia #USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2046285967863279687</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>saigol7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Jeanvaljeanrambo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2042931249577365509/OmGu4ADP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Please launch prepaid debit card for tourists.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Please launch prepaid debit card for tourists.</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 · 2:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-04-20T02:59:00Z</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11</v>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 5:52 PM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>91</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Please launch prepaid debit card for tourists.</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/saigol7/status/2046285967863279687</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2046283996015800804</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/evocarsrental</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>evocarsrental</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EVO Cars Rental</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1720101577732825088/qg27_hO4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - khaleejtimes.com/business/em…</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - &lt;a href="https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 5:44 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-20T17:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers']</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - khaleejtimes.com/business/em…</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/evocarsrental/status/2046283996015800804</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - https://t.co/l4qu0XUPAx</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE May i ask which email can be written to, for the purpose of assisting us in deferment on auto-loans. Based on the article - https://t.co/l4qu0XUPAx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>preeminentdxb</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Preeminent Properties</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2044052457819602944/4KcaRnMb_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that&amp;#39;s reducing friction, improving transparency, and making long-term planning far more structure</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 4:26 PM UTC</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:26:00Z</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>A quiet shift, but a powerful one.
+The gap between intent and ownership in Dubai just got smaller, and more predictable.
+Follow for perspective that stays ahead of the curve.
+#MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>A quiet shift, but a powerful one.
+The gap between intent and ownership in Dubai just got smaller, and more predictable.
+Follow for perspective that stays ahead of the curve.
+#MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>khaleejtimes</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Khaleej Times</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1662009811242831874/ZUTWSfk4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+khaleejtimes.com/business/em…</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+&lt;a href="https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 4:23 PM UTC</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-04-20T16:23:00Z</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers']</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>34</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7018</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+khaleejtimes.com/business/em…</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>I’m buying more Bitcoin and Toncoin</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>I’m buying more Bitcoin and Toncoin</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2046198033738785046</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/naveenthumala</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>naveenthumala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Naveen Reddy</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1665270584811606018/tO4QAL_U_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:03 PM UTC</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:03:00Z</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>15</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://x.com/naveenthumala/status/2046198033738785046</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
+#RBLBank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ja2030ah</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>vision</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1771507437142523904/uOQIvqbz_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>&lt;a href="/DFMalerts" title="Dubai Financial Market"&gt;@DFMalerts&lt;/a&gt; 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 11:33 AM UTC</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2026-04-20T11:33:00Z</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/DFMalerts']</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>45</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2046173095581647055</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GaminNiukkua</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gamin Niu</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2030913945612242944/DJuNKnnC_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>حرام ولا حلال؟</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>حرام ولا حلال؟</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 10:24 AM UTC</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2026-04-20T10:24:00Z</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>135</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>حرام ولا حلال؟</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/GaminNiukkua/status/2046173095581647055</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -678,7 +1476,7 @@
 https://t.co/I7DGlib9vt</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>ندعم من يحمون الوطن
 مجموعة من مزايا الدعم المالي والخدمات المصرفية المخصصة للعاملين في الصفوف الأمامية
@@ -693,859 +1491,81 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2046033950339166455</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Kyodonews_JBN</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>KYODONEWS JBN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-&lt;a href="https://kyodonewsprwire.jp/release/202604177681"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 · 1:11 AM UTC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-04-20T01:11:00Z</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://kyodonewsprwire.jp/release/202604177681']</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-kyodonewsprwire.jp/release/2…</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-https://t.co/H82MnfRa04</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-https://t.co/H82MnfRa04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2045958337494143476</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/ansariiarif</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ansariiarif</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Arif</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1268363851231383555/JkBzC9kT_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn&amp;#39;t be!!!</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 8:10 PM UTC</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-04-19T20:10:00Z</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>3</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://x.com/ansariiarif/status/2045958337494143476</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-I have been chargd without any reason. Not expexted this from NDB as per their policy I have spent the required amount but still they have charged me for accessing the lounge which shouldn't be!!!</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2045922728868479327</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>f3100000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>F35</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2024219709168918529/LqA8XT-p_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>دعم من اي نوع هذا</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>دعم من اي نوع هذا</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 5:49 PM UTC</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2026-04-19T17:49:00Z</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>74</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>دعم من اي نوع هذا</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/f3100000/status/2045922728868479327</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE دعم من اي نوع هذا</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2045894623957278735</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>almidfa75</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Faisal Al Midfa</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>🧵 6/
-🎯 خلاصة:
-يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
-#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>🧵 6/
-🎯 خلاصة:
-يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
-&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل_العقاري"&gt;#التمويل_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23استثمار"&gt;#استثمار&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiHolding"&gt;#DubaiHolding&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 3:57 PM UTC</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2026-04-19T15:57:00Z</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23التمويل_العقاري', 'https://x.com/search?f=tweets&amp;q=%23استثمار', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23DubaiHolding']</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>38</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>🧵 6/
-🎯 خلاصة:
-يمثل هذا الإعلان خطوة نوعية في تطوير حلول التمويل العقاري، ويعكس توجه المؤسسات المالية نحو تقديم منتجات أكثر مرونة تدعم نمو واستدامة السوق العقاري في دولة الإمارات.
-#دبي #التمويل_العقاري #استثمار #EmiratesNBD #DubaiHolding</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894623957278735</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل https://t.co/qdzz3FJ7io</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2045894611756048610</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75/status/2045894611756048610</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/almidfa75</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>almidfa75</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Faisal Al Midfa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/692030305365000192/rYQ6PWnr_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-&lt;a href="/search?f=tweets&amp;amp;q=%23دبي"&gt;#دبي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23القطاع_العقاري"&gt;#القطاع_العقاري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التمويل"&gt;#التمويل&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K7" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 3:57 PM UTC</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2026-04-19T15:57:00Z</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23دبي', 'https://x.com/search?f=tweets&amp;q=%23القطاع_العقاري', 'https://x.com/search?f=tweets&amp;q=%23التمويل']</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>62</v>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>🧵 1/
-في خطوة تعكس تطور المنتجات المالية في السوق العقاري بدولة الإمارات، أعلن بنك Emirates NBD عن إطلاق نموذج تمويل مبكر للعقارات قيد الإنشاء (Off-plan)، بالتعاون مع Dubai Holding Real Estate.
-#دبي #القطاع_العقاري #التمويل</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2045881062304456946</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/ThisMadEngineer</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ThisMadEngineer</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Ankesh / MadEngineer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/677437091211530240/U61xnBOL_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Thanks!</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Thanks!</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 3:03 PM UTC</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2026-04-19T15:03:00Z</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>287</v>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Thanks!</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/ThisMadEngineer/status/2045881062304456946</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>We are extending our support to help you manage your finances with more confidence. https://t.co/EP2xuqo7Gb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2045850840196694451</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045850840196694451</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>r35sk</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ريم</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1976063720942968832/0TB4sf0G_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>الحمدلله الحمرا فيها صرافة enbd</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>الحمدلله الحمرا فيها صرافة enbd</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 1:03 PM UTC</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2026-04-19T13:03:00Z</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>49</v>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>الحمدلله الحمرا فيها صرافة enbd</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/r35sk/status/2045850840196694451</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>الوداعيةةة https://t.co/p08tSNxQZ3</t>
-        </is>
-      </c>
-    </row>
     <row r="10">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2045850184811422052</t>
+          <t>2046171931813011938</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/AhmedAlhaq79518</t>
+          <t>https://x.com/ENBDdeals</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AhmedAlhaq79518</t>
+          <t>ENBDdeals</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ahmed Alhaìqi</t>
+          <t>Emirates NBD Deals</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2015365820088803328/seUb2ZG5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 1:01 PM UTC</t>
+          <t>Apr 20, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-19T13:01:00Z</t>
+          <t>2026-04-20T10:19:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1553,10 +1573,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1565,22 +1585,28 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/AhmedAlhaq79518/status/2045850184811422052</t>
+          <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE فعلا بنك مميز بمعني الكلمه والصقه بهم متوفره عندي علاجه.</t>
+          <t>Turn your bills into rewards
+Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
         </is>
       </c>
     </row>
@@ -1590,50 +1616,54 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2045824669907845529</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq</t>
+          <t>https://x.com/ATwo2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>m_azeemq</t>
+          <t>ATwo2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Muhammad Azeem Qureshi</t>
+          <t>عبدالله ثاني الغاوي</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1770124341008642048/aZCfgp1R_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>16h</t>
@@ -1641,22 +1671,18 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 11:19 AM UTC</t>
+          <t>Apr 20, 2026 · 10:16 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-19T11:19:00Z</t>
+          <t>2026-04-20T10:16:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1665,7 +1691,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1674,22 +1700,22 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://x.com/m_azeemq/status/2045824669907845529</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
     </row>
@@ -1699,47 +1725,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2045821589539733783</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi</t>
+          <t>https://x.com/ArabiaCSR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CWSaudi</t>
+          <t>ArabiaCSR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Construction Week Saudi</t>
+          <t>Arabia CSR Network</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1494269682098089989/5bK0V1be_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1600223681262850067/qD6NwVT8_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
-Read more:
-constructionweeksaudi.com/bu…</t>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp; CSR Forum!
+With 20+ years in sustainable finance &amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it!</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>. &lt;a href="/dar_global" title="DarGlobal"&gt;@dar_global&lt;/a&gt;  has secured a $250M loan arranged by &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; , as the &lt;a href="/search?f=tweets&amp;amp;q=%23London"&gt;#London&lt;/a&gt; -listed developer behind &lt;a href="/realDonaldTrump" title="Donald J. Trump"&gt;@realDonaldTrump&lt;/a&gt; -branded projects expands its pipeline.
-Read more:
-&lt;a href="https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump"&gt;constructionweeksaudi.com/bu…&lt;/a&gt;</t>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
+With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it!</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1754,20 +1778,16 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 11:07 AM UTC</t>
+          <t>Apr 20, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-19T11:07:00Z</t>
+          <t>2026-04-20T10:00:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://x.com/dar_global', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23London', 'https://x.com/realDonaldTrump', 'https://www.constructionweeksaudi.com/business/real-estate-darglobal-trump']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -1778,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1787,28 +1807,29 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>. @dar_global  has secured a $250M loan arranged by @EmiratesNBD_AE , as the #London -listed developer behind @realDonaldTrump -branded projects expands its pipeline.
-Read more:
-constructionweeksaudi.com/bu…</t>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp; CSR Forum!
+With 20+ years in sustainable finance &amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it!</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/CWSaudi/status/2045821589539733783</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
-Read more ll
-https://t.co/UvrhC24nWJ</t>
+          <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
+Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
+admin@arabiacsrnetwork.com
+https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>#SaudiArabia extends the Landbridge rail bid deadline to April 29 as #Hormuz disruptions highlight its lack of a direct east–west freight rail link.
-Read more ll
-https://t.co/UvrhC24nWJ</t>
+          <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
+Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
+admin@arabiacsrnetwork.com
+https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
         </is>
       </c>
     </row>
@@ -1818,90 +1839,84 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2045814764828516809</t>
+          <t>2046166030557614556</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji</t>
+          <t>https://x.com/khaleejtimes</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UaeAlteneiji</t>
+          <t>khaleejtimes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>أبو عمر ، عبدالرحمن الطنيجي</t>
+          <t>Khaleej Times</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1906440728953204736/EXccdOZS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1662009811242831874/ZUTWSfk4_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+&lt;a href="https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers"&gt;khaleejtimes.com/business/em…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 10:40 AM UTC</t>
+          <t>Apr 20, 2026 · 9:56 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-19T10:40:00Z</t>
+          <t>2026-04-20T09:56:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://www.khaleejtimes.com/business/emirates-nbd-extends-fee-waivers-0-interest-on-credit-card-transfers-for-uae-customers']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="V13" t="n">
-        <v>20</v>
+        <v>8262</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1910,34 +1925,25 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+khaleejtimes.com/business/em…</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/UaeAlteneiji/status/2045814764828516809</t>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من شكل الاعلان باين انه مجرد دعاية للبنك وليس دعماً لحماة الوطن
-اعلان غير موفق
-اعلان محدد بتاريخ صلاحية 
-اعلان تحكمه الشروط والاحكام المجهولة
-هنالك بنوك أخرى تقدم عروض تتافسية جذابة أكثر ومزايا أفضل وأحسن وتقدم لجميع العملاء ولعامة الشعب دون منية</t>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
         </is>
       </c>
     </row>
@@ -1947,45 +1953,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2045805999718903933</t>
+          <t>2046061240511082734</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi</t>
+          <t>https://x.com/she7ii88</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>abasetaljanahi</t>
+          <t>she7ii88</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Abdulbaset Al Janahi</t>
+          <t>Rashed Sem</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1572294225240231936/Ew_orY09_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1752368468144316416/8qdE3N-C_bigger.png</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>بس! 
-وايد عليكم</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>بس! 
-وايد عليكم</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1999,23 +2007,23 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 10:05 AM UTC</t>
+          <t>Apr 20, 2026 · 2:59 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-19T10:05:00Z</t>
+          <t>2026-04-20T02:59:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2024,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>211</v>
+        <v>86</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2033,25 +2041,28 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>بس! 
-وايد عليكم</t>
+          <t>هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/abasetaljanahi/status/2045805999718903933</t>
+          <t>https://x.com/she7ii88/status/2046061240511082734</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE بس! 
-وايد عليكم</t>
+          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE بس! 
-وايد عليكم</t>
+          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
+٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
+ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
     </row>
@@ -2061,77 +2072,73 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2045801203934925261</t>
+          <t>2046033950339166455</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz</t>
+          <t>https://x.com/Kyodonews_JBN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>amerbinhraiz</t>
+          <t>Kyodonews_JBN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>بـتـال | Batal</t>
+          <t>KYODONEWS JBN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2033838640934359040/zShxD0Gl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2003285704613462020/Gn9wk2B__bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+&lt;a href="https://kyodonewsprwire.jp/release/202604177681"&gt;kyodonewsprwire.jp/release/2…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>Apr 20</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 9:46 AM UTC</t>
+          <t>Apr 20, 2026 · 1:11 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-19T09:46:00Z</t>
+          <t>2026-04-20T01:11:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://kyodonewsprwire.jp/release/202604177681']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2142,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2151,31 +2158,25 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+kyodonewsprwire.jp/release/2…</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/amerbinhraiz/status/2045801203934925261</t>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE نريدكم تلغون الفايدة من اصحاب 
-المديونيات الطويلة القديمة
-كل شي واقف عليهم وماخذين فايدة
- عليهم ضعف قيمة القرض !</t>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
         </is>
       </c>
     </row>
@@ -2185,43 +2186,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2045786366504796559</t>
+          <t>2046224051438526663</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381</t>
+          <t>https://x.com/mohmd_moh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SultanAbdu70381</t>
+          <t>mohmd_moh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sultan Abdullah</t>
+          <t>Mohamed Mohamed</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/581880425234059264/lFW7trTI_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2230,22 +2235,22 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 8:47 AM UTC</t>
+          <t>Apr 20, 2026 · 1:46 PM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-19T08:47:00Z</t>
+          <t>2026-04-20T13:46:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2260,31 +2265,59 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>اكثر البنوك فالدولة تساهلت مع متعامليها لتوفير راحتهم واحتياجاتهم وليس لزياده ضغط عليهم حيث قامو بتأجيل قروض لهم ٣ اشهر مساعده لهم لضروفهم خاصه دفاع الأول وشكرا لكم</t>
+          <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
+تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
+كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045786366504796559</t>
+          <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>نحتاج تأجيل 3 شهور للازمه</t>
+          <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
+أجب واربح 
+تلقيت رسالة من صديقك يطلب منك بشكل عاجل تحويل مبلغ مالي إلى حسابه، مدّعياً أن هناك حالة طارئة. ماذا يجب أن تفعل؟
+أ. تحوّل المبلغ فوراً لمساعدة صديقك
+ب. تتحقّق من الأمر عبر الاتصال بصديقك
+ج. تثق بالرسالة لأنها واردة من حساب صديقك
+للمشاركة:
+أجب بشكل صحيح في التعليقات 
+قم بعمل منشن لشخصين 
+تابع حسابنا على X
+سيتم الإعلان عن الفائز بتاريخ 5 مايو 2026
+يرجى زيارة  https://t.co/4RkTsyGuDX للاطلاع على الشروط والأحكام
+تقتصر المشاركة على مواطني دولة الإمارات العربية المتحدة أو المقيمين في الدولة الذين يحملون بطاقة هوية سارية المفعول.
+مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>نحتاج تأجيل 3 شهور للازمه</t>
+          <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
+أجب واربح 
+تلقيت رسالة من صديقك يطلب منك بشكل عاجل تحويل مبلغ مالي إلى حسابه، مدّعياً أن هناك حالة طارئة. ماذا يجب أن تفعل؟
+أ. تحوّل المبلغ فوراً لمساعدة صديقك
+ب. تتحقّق من الأمر عبر الاتصال بصديقك
+ج. تثق بالرسالة لأنها واردة من حساب صديقك
+للمشاركة:
+أجب بشكل صحيح في التعليقات 
+قم بعمل منشن لشخصين 
+تابع حسابنا على X
+سيتم الإعلان عن الفائز بتاريخ 5 مايو 2026
+يرجى زيارة  https://t.co/4RkTsyGuDX للاطلاع على الشروط والأحكام
+تقتصر المشاركة على مواطني دولة الإمارات العربية المتحدة أو المقيمين في الدولة الذين يحملون بطاقة هوية سارية المفعول.
+مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
     </row>
@@ -2294,43 +2327,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2045785730023301620</t>
+          <t>2046217543870738694</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381</t>
+          <t>https://x.com/aaditsh</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SultanAbdu70381</t>
+          <t>aaditsh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sultan Abdullah</t>
+          <t>Aadit Sheth</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1989274279947694081/ggQkOhbP_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2339,22 +2372,22 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['RakeshMavath', 'emiratesislamic']</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 8:45 AM UTC</t>
+          <t>Apr 20, 2026 · 1:20 PM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-19T08:45:00Z</t>
+          <t>2026-04-20T13:20:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -2366,34 +2399,38 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>Alright. Will do! Thanks.</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAbdu70381/status/2045785730023301620</t>
+          <t>https://x.com/aaditsh/status/2046217543870738694</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE عند الإعلان يجب وضع التوضيح وليس وضع إعلان بموضوع واتخاذ إجراءات وأوامر أخرى شكرا لكم</t>
+          <t>@emiratesislamic probably the worst customer experience I’ve had in my life.
+Tried cancelling my cards. Have received 10+ phone calls from them trying to retain. Confirmed each time that I want to cancel (on call and on email confirmation). It’s been 4-5 months since I raised this complaint. No resolution yet.
+Impressed with how difficult they make this process. Wow!</t>
         </is>
       </c>
     </row>
@@ -2403,43 +2440,43 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2045755517948272900</t>
+          <t>2046215734481834418</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11/status/2045755517948272900</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11</t>
+          <t>https://x.com/gassann20203</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>girluae11</t>
+          <t>gassann20203</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>girl</t>
+          <t>gazan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043687946625368066/wksZEFYW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1979011185929342976/BA4ftLDA_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>من هم حماه الوطن؟ الفئات ؟</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>من هم حماه الوطن؟ الفئات ؟</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2448,22 +2485,22 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:44 AM UTC</t>
+          <t>Apr 20, 2026 · 1:13 PM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-19T06:44:00Z</t>
+          <t>2026-04-20T13:13:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2478,31 +2515,37 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>من هم حماه الوطن؟ الفئات ؟</t>
+          <t>انتم بس لا تسرقونا واكفوناةشركمةزخيركم</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/girluae11/status/2045755517948272900</t>
+          <t>https://x.com/gassann20203/status/2046215734481834418</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE من هم حماه الوطن؟ الفئات ؟</t>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat https://t.co/pIT39d8ym8</t>
         </is>
       </c>
     </row>
@@ -2512,71 +2555,73 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2045729029614129456</t>
+          <t>2046148194392740002</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>bu_rashed98</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>﮼💛🇦🇪الامبراطور 🇦🇪💛</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042287480335187974/x8vTEs88_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>أنا وياهم 😁</t>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>أنا وياهم 😁</t>
+          <t>Your child&amp;#39;s smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23AlphaYouth"&gt;#AlphaYouth&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 4:59 AM UTC</t>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-19T04:59:00Z</t>
+          <t>2026-04-20T08:45:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23AlphaYouth']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
@@ -2587,31 +2632,34 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>أنا وياهم 😁</t>
+          <t>Your child's smart money journey starts here. Empower your kids to take their first steps toward financial independence. 
+#EmiratesIslamic #AlphaYouth</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/bu_rashed98/status/2045729029614129456</t>
+          <t>https://x.com/emiratesislamic/status/2046148194392740002</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE أنا وياهم 😁</t>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي https://t.co/xdFKEhpKDT</t>
         </is>
       </c>
     </row>
@@ -2621,12 +2669,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2045744202651226430</t>
+          <t>2046106598221746656</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2652,20 +2700,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -2675,27 +2717,23 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-19T06:00:00Z</t>
+          <t>2026-04-20T06:00:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2704,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2713,19 +2751,1629 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>المدفوعات المستحقة تعني ضغطاً مستمراً.
-💡نصيحة: دوّن كل مدفوعاتك في مكان واحد.
-الوضوح يجعل الأمر أسهل في الإدارة. 
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-emiratesislamic.ae/ar/key-in…</t>
+          <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
+✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2045744202651226430</t>
+          <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>35</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+emiratesislamic.ae/en/person…</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>46</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>58</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2046215063929749703</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_emarati"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/emarati-credit-card-campaign?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_emarati']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>51</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>🚗 خدمة صف السيارات
+🛫 الدخول إلى صالات المطارات
+💳 بطاقة معدنية بتصميم فريد
+وغير ذلك الكثير
+📅 يسري العرض لغاية 31 مايو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2046215061186683019</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>71</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
+✅ بدون رسوم عضوية سنوية
+📈استرداد لغاية 3.75 ميل من أميال سمارت مايلز مقابل كل درهم إماراتي تنفقه
+🍔 خصم لغاية %50 على طلبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>17</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+السلام عليكم
+زرت فرع 06 مول يوم الثلاثاء الماضى من اجل كسر الوديعة ودفع مبلغ القرض المتبقي علي
+أخبرتني الموظفة المحترمة بانه سوف يتم إرسال أميل الى الإدارة  لمعرفة الخطوات
+والى اليوم الخميس الإدارة لم ترد عليهم 
+هل هذ التأخير له مبرر
+او عدم هو اهتمام بالعملاء</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>11</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2046200603928338537</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 12:13 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-20T12:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>19</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
+هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>@emiratesislamic 
+منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
+هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['firstdiver4ever']</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 9:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-20T09:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2046148156560121974</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046148156560121974</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 8:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-20T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>54</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>امنح أبنائك انطلاقة مبكرة نحو الوعي المالي الذكي
+ #الإمارات_الإسلامي</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['alsajwani1']</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:45:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>22</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2046125857643606493</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>['mohmd_moh']</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>11</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>['gassann20203']</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 7:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-20T07:16:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -2733,7 +4381,7 @@
 💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -2742,251 +4390,474 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2045744202382807549</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2046106600142725209</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-04-19T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>54</v>
-      </c>
-      <c r="W21" t="inlineStr">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>30</v>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-emiratesislamic.ae/en/key-in…</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045744202382807549</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Outstanding payments = constant stress.
-💡 Tip:
-Write everything down in one place
-Clarity makes it feel manageable.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>✔️ Track your investments in real time
+✔️ Get smart insights to guide your decisions
+✔️ Enjoy a fully digital experience
+Start small. Think long-term. Stay disciplined.
+To know more, visit:
+emiratesislamic.ae/en/Person…</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>firstdiver4ever</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>اماراتى وافتخر</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1974542718652280832/oqepMvc3_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2046106595369615672</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>20h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Apr 19, 2026 · 7:47 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-04-19T07:47:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>23</v>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=wealth']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>13</v>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>✔️ متابعة استثماراتك لحظة بلحظة
+✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
+✔️ الاستمتاع بتجربة رقمية متكاملة وسهلة
+ابدأ بمبلغ صغير، ضع أهدافاً بعيدة المدى، والتزم بالانضباط لتحقيق نتائج ملموسة.
+للمزيد من المعلومات، تفضل بزيارة الرابط التالي:
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2046106592135831614</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
+&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
+        </is>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>37</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+emiratesislamic.ae/ar/person…</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2046106592114856006</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-20T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>63</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
+مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
+✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -2046,21 +2046,11 @@
 ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
+          <t>هذا عرض صدق ؟! 
 ٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
 ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
         </is>
@@ -3012,12 +3002,123 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Apr 20, 2026 · 1:12 PM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-04-20T13:12:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>58</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
+✅ No annual membership fee
+📈 Earn up to 3.75 EI SmartMiles back per AED spend
+🍔 50% discount on talabat</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3027,7 +3128,7 @@
 https://t.co/Rcpj14D3rn</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>🚗 Complimentary valet parking
 ✈️ Complimentary airport lounge access
@@ -3035,115 +3136,6 @@
 And much more!
 📅 Offer valid till 31 May 2026
 https://t.co/Rcpj14D3rn</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp;amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Apr 20, 2026 · 1:12 PM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-04-20T13:12:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>58</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Exclusively for Emaratis. Apply for an Emarati Credit Card &amp; get a welcome bonus of up to 150,000 EI SmartMiles worth AED 1,500
-✅ No annual membership fee
-📈 Earn up to 3.75 EI SmartMiles back per AED spend
-🍔 50% discount on talabat</t>
         </is>
       </c>
     </row>
@@ -3613,12 +3605,22 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+          <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
+مع الأسف لايوجد متابعة لطلب من الفرع
+ولايوجد اهتمام من الإدارة في مساعدة الفروع لخدمة العملاء
+اكرر سوالي هل من المعقول عدم معرفة الإجراء لدي الفرع؟
+ وهل الإدارة لاتبالي في الرد على الفروع عند الاستفسار لخدمة العملاء؟
+متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+          <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
+مع الأسف لايوجد متابعة لطلب من الفرع
+ولايوجد اهتمام من الإدارة في مساعدة الفروع لخدمة العملاء
+اكرر سوالي هل من المعقول عدم معرفة الإجراء لدي الفرع؟
+ وهل الإدارة لاتبالي في الرد على الفروع عند الاستفسار لخدمة العملاء؟
+متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
     </row>
@@ -3718,23 +3720,12 @@
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
-هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@emiratesislamic 
-منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
-هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -778,12 +778,113 @@
           <t>العمر كله 😊😊😊❤️</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/DanaAbdulla2006/status/2046706553022238997</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>العمر كله 😊😊😊❤️</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2046706457295364506</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi/status/2046706457295364506</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bufalasi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bani Yas</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2019845320071372800/XlNVpcnv_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['DanaAbdulla2006', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Apr 21, 2026 · 9:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-04-21T21:43:00Z</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>22</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/bufalasi/status/2046706457295364506</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>هواتف “القناص” و“الأنيس” والبليب…
 ليست مجرد أجهزة قديمة، بل بداية قصة الاتصال في الإمارات 🇦🇪
@@ -798,7 +899,7 @@
 قطعة من تاريخ… صنعت حاضرنا</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>هواتف “القناص” و“الأنيس” والبليب…
 ليست مجرد أجهزة قديمة، بل بداية قصة الاتصال في الإمارات 🇦🇪
@@ -811,107 +912,6 @@
 اليوم، لم تعد مجرد هواتف…
 بل نوادر تُقتنى، وذكريات تختصر زمنًا كاملاً.
 قطعة من تاريخ… صنعت حاضرنا</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2046706457295364506</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://x.com/bufalasi/status/2046706457295364506</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/bufalasi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>bufalasi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bani Yas</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2019845320071372800/XlNVpcnv_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['DanaAbdulla2006', 'Alraeesi1969', 'EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Apr 21, 2026 · 9:43 PM UTC</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-04-21T21:43:00Z</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="n">
-        <v>22</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>يداج انا 👴🏼 انا متقاعد وانتي عمرج سنه 😂احسبي علي راحتج</t>
         </is>
       </c>
     </row>
@@ -1957,21 +1957,12 @@
 They can access mortgage solutions right from the start.</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/Soberrealestate/status/2046559580919144593</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Tourism in Dubai ready to boom soon 
-#dubaï #unitedarabemirates🇦🇪 #uae🇦🇪 #tourism https://t.co/RgWWZHppDl</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Tourism in Dubai ready to boom soon 
-#dubaï #unitedarabemirates🇦🇪 #uae🇦🇪 #tourism https://t.co/RgWWZHppDl</t>
+          <t>Dubai’s real estate market is entering a new era. Dubai Holding and EmiratesNBD have joined forces to transform how off-plan properties are financed. Now, buyers don’t need to wait until handover.
+They can access mortgage solutions right from the start.</t>
         </is>
       </c>
     </row>
@@ -2311,19 +2302,11 @@
           <t>I am in followup with KSA team but there is no action taken from concern department till now and case is still unresolved/clarified. Even phone and Mails dont have any effect. I hope my escalated issue can be clarified, just want to Finish and Close the service from ENBD.</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/m_azeemq/status/2046489809842065416</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update. And we have already replied you via other social media channel. Thanks</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@m_azeemq Hi Muhammad, we are extremely sorry for the delay, and we have sent followup email to our team to contact you as soon as possible with an update. And we have already replied you via other social media channel. Thanks</t>
+          <t>I am in followup with KSA team but there is no action taken from concern department till now and case is still unresolved/clarified. Even phone and Mails dont have any effect. I hope my escalated issue can be clarified, just want to Finish and Close the service from ENBD.</t>
         </is>
       </c>
     </row>
@@ -2432,27 +2415,15 @@
 #DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://x.com/Blackstone_UAE/status/2046488790806806983</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>Paying high interest? Stop.
 Emirates NBD just dropped 0% interest + zero fees 💳
 This is your chance to reset your finances
 DM “PLAN” to optimize your debt
-#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife https://t.co/PXNM3PdaUn</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Paying high interest? Stop.
-Emirates NBD just dropped 0% interest + zero fees 💳
-This is your chance to reset your finances
-DM “PLAN” to optimize your debt
-#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife https://t.co/PXNM3PdaUn</t>
+#DubaiMoney #UAETwitter #FinanceTips #DebtFreeJourney #SmartMoney #DubaiLife</t>
         </is>
       </c>
     </row>
@@ -3047,16 +3018,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
+تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
+#فخورين_بالإمارات https://t.co/gqaQU5Dzuz</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>A pride beyond words… it’s felt. 🇦🇪
-Inspired by the vision of His Highness Sheikh Mohammed bin Rashid Al Maktoum, we raise our flag high, celebrating a nation united by values, strengthened by resilience, and driven by a spirit that knows no limits.
-#ProudOfUAE #EmiratesIslamic</t>
+          <t>فخرٌ لا يُحكى… بل يُشعَر. 🇦🇪
+تماشياً مع رؤية صاحب السمو الشيخ محمد بن راشد آل مكتوم، نرفع رايتنا عالياً، ونحتفي بوطنٍ توحّد على القيم، وتماسك بالقوة، وازدهر بروحٍ لا تعرف المستحيل.
+#فخورين_بالإمارات https://t.co/gqaQU5Dzuz</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -2969,16 +2969,8 @@
           <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047265666320011311</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE أفضل ويتفوق رغماً عن الأزمة 👏🏻</t>
@@ -3091,12 +3083,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>SAQL: Exchange Ticker has secured Public Investment Fund (PIF) seed funding of $100m listed on Deutsche Borse &amp;amp; London Stock Exchange.. https://t.co/3dUD3f2sht</t>
+          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
         </is>
       </c>
     </row>
@@ -3297,19 +3289,12 @@
 #EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2047260484458467333</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Speedinvest launches its first flagship fund for early-growth startups across the Middle East and Africa, backed by Mubadala Investment Company, Qatar Investment Authority, and European Investment Bank, expanding its regional investment strategy.#Speedinvest #MiddleEast #Africa https://t.co/2PFCFcHWJE</t>
+          <t>Emirates NBD, Dubai’s largest bank, reported a profit before tax of Dh8.2 billion for Q1 2026, up 6% year-on-year, supported by strong balance sheet growth, resilient margins, and record non-funded income.
+#EmiratesNBD #Dubai #Banking #Finance #UAE #Earnings #Q12026</t>
         </is>
       </c>
     </row>
@@ -5124,16 +5109,8 @@
           <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://x.com/77dd14cbca18474/status/2047201786570907985</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
-        </is>
-      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hello its been 1 year iam following for account cancellation called many times to call center posted in X also still not cancelled?? Whats happening</t>
@@ -5467,14 +5444,26 @@
 #AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
         <is>
           <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
 Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
 Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: link.aletihad.ae/JYOQ 
+Read more: https://t.co/5WKoAM1fAJ 
+#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
+Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
+Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
+Read more: https://t.co/5WKoAM1fAJ 
 #AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
         </is>
       </c>
@@ -5820,19 +5809,11 @@
           <t>#EmiratesNBD, the region’s fourth largest lender by market capitalisation, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion) lseg.group/4e54WQT</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>https://x.com/Zawya/status/2047185349089087886</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet https://t.co/MKDO38bCYG</t>
-        </is>
-      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>The National Bank of Ras Al Khaimah (RAKBANK) posted double-digit growth in earnings for the first quarter of the year, supported by a strategic asset sale and a robust balance sheet https://t.co/MKDO38bCYG</t>
+          <t>#EmiratesNBD, the region’s fourth largest lender by market capitalisation, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion) lseg.group/4e54WQT</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6908,21 @@
 #Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing</t>
+#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
         </is>
       </c>
     </row>
@@ -7269,21 +7259,11 @@
           <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047289060557824183</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
-        </is>
-      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
+          <t>البدء مبكرًا والاستمرار بثبات يساعدان على نمو أموالك مع الوقت. خطوات بسيطة اليوم قد تساهم في بناء مستقبل مالي أكثر استقرارًا وثقة.</t>
         </is>
       </c>
     </row>
@@ -7694,11 +7674,21 @@
           <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
+Please advise.</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
+          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
+Please advise.</t>
         </is>
       </c>
     </row>
@@ -7798,12 +7788,51 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2047193753073357199</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -7812,7 +7841,7 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -7821,43 +7850,46 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Apr 23, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-04-23T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>58</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -7866,7 +7898,12 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -7875,46 +7912,7 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-      <c r="K66" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Apr 23, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>2026-04-23T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="n">
-        <v>1</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>58</v>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
 راجع آخر 10 معاملات لديك،
@@ -7923,17 +7921,6 @@
 فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1113,21 +1113,11 @@
           <t>الووووو .</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
-        </is>
-      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>الووووو .</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1221,14 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
     </row>
@@ -1870,21 +1862,11 @@
           <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
     </row>
@@ -1984,8 +1966,17 @@
 I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Very disappointed with @ENBDdeals 
+I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>Very disappointed with @ENBDdeals 
@@ -2322,16 +2313,12 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
     </row>
@@ -2899,18 +2886,22 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
     </row>
@@ -3511,121 +3502,12 @@
 #الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-04-24T16:42:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>36</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>🏦 بدون رسوم إجراءات
 ⏳ تأجيل الأقساط
@@ -3636,7 +3518,7 @@
 #الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>🏦 بدون رسوم إجراءات
 ⏳ تأجيل الأقساط
@@ -3645,6 +3527,111 @@
 لمعرفة المزيد، تفضل بزيارة
 https://t.co/N2GRIcHWnS
 #الإمارات_الإسلامي #أبطال_الوطن</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2047717917324710124</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-24T16:42:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>36</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل</t>
         </is>
       </c>
     </row>
@@ -4594,23 +4581,16 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
     </row>
@@ -4709,13 +4689,23 @@
 💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
 استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,49 +566,59 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047809819265110291</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby</t>
+          <t>https://x.com/theprabhakars</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>karim_alharby</t>
+          <t>theprabhakars</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KARIM 🎩</t>
+          <t>Prabhakar Singh Bais</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042555658277654530/6XppkQ5x_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1985403950192033792/czvUF0FN_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​&lt;a href="/search?f=tweets&amp;amp;q=%23IDBIBank"&gt;#IDBIBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingNews"&gt;#BankingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EconomyUpdate"&gt;#EconomyUpdate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Disinvestment"&gt;#Disinvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarketIndia"&gt;#StockMarketIndia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinanceNews"&gt;#FinanceNews&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -618,21 +628,25 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:48 PM UTC</t>
+          <t>Apr 26, 2026 · 2:56 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-04-24T22:48:00Z</t>
+          <t>2026-04-26T02:56:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23IDBIBank', 'https://x.com/search?f=tweets&amp;q=%23BankingNews', 'https://x.com/search?f=tweets&amp;q=%23EconomyUpdate', 'https://x.com/search?f=tweets&amp;q=%23Disinvestment', 'https://x.com/search?f=tweets&amp;q=%23StockMarketIndia', 'https://x.com/search?f=tweets&amp;q=%23FinanceNews']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -640,10 +654,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1905</v>
+        <v>27</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -652,31 +666,30 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
     </row>
@@ -686,73 +699,69 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya</t>
+          <t>https://x.com/MultibaggAI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RakshtVaghasiya</t>
+          <t>MultibaggAI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rakshit Vaghasiya</t>
+          <t>multibagg.ai</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Same reply every time but no concrete solutions. Just a pathetic approach..</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Same reply every time but no concrete solutions. Just a pathetic approach..</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 5:13 PM UTC</t>
+          <t>Apr 26, 2026 · 2:42 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-04-24T17:13:00Z</t>
+          <t>2026-04-26T02:42:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -761,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -770,24 +779,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Same reply every time but no concrete solutions. Just a pathetic approach..</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
     </row>
@@ -797,43 +804,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048213606257570300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m</t>
+          <t>https://x.com/AmritMohanty1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barigiin7m</t>
+          <t>AmritMohanty1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barigi</t>
+          <t>Amrit Mohanty</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1798792220885307395/ZFbORVL__bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اود تقديم قرض كيف أتواصل معكم</t>
+          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>اود تقديم قرض كيف أتواصل معكم</t>
+          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -842,28 +849,28 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:20 PM UTC</t>
+          <t>Apr 26, 2026 · 1:32 AM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-04-24T16:20:00Z</t>
+          <t>2026-04-26T01:32:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -872,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -881,24 +888,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>اود تقديم قرض كيف أتواصل معكم</t>
+          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
     </row>
@@ -908,45 +913,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048045177659404537</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+          <t>https://x.com/Hafid505/status/2048045177659404537</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/Hafid505</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>Hafid505</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Abdulhafid</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1978176887374401536/PcrEaJ3v_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -956,23 +961,23 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:03 PM UTC</t>
+          <t>Apr 25, 2026 · 2:23 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-04-24T15:03:00Z</t>
+          <t>2026-04-25T14:23:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -982,10 +987,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -994,29 +999,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
-        </is>
-      </c>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>إقتراح تصميم مكينة الصراف الآلي لبنك الإمارات دبي الوطني،  على كورنيش خورفكان. 
+@EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1026,71 +1018,119 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88</t>
+          <t>https://x.com/phd_capital</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fortyxxl88</t>
+          <t>phd_capital</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>forty</t>
+          <t>PHD CAPITAL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043738450134749184/JdKcVTW__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2045065540562259968/2sFZf-W-_bigger.png</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;#RBLBANK&lt;/a&gt; (&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal &amp;#34;clean-up&amp;#34; year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What&amp;#39;s genuinely exciting:
+✅ The &amp;#34;Emirates NBD&amp;#34; Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&amp;lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic &amp;#34;Deep Value Turnaround&amp;#34; play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingSector"&gt;#BankingSector&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarketIndia"&gt;#StockMarketIndia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FundamentalAnalysis"&gt;#FundamentalAnalysis&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investing"&gt;#Investing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PHDCapital"&gt;#PHDCapital&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EquityResearch"&gt;#EquityResearch&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NiftyBank"&gt;#NiftyBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23TurnaroundStory"&gt;#TurnaroundStory&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:00 PM UTC</t>
+          <t>Apr 25, 2026 · 2:00 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-04-24T15:00:00Z</t>
+          <t>2026-04-25T14:00:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23BankingSector', 'https://x.com/search?f=tweets&amp;q=%23StockMarketIndia', 'https://x.com/search?f=tweets&amp;q=%23FundamentalAnalysis', 'https://x.com/search?f=tweets&amp;q=%23Investing', 'https://x.com/search?f=tweets&amp;q=%23PHDCapital', 'https://x.com/search?f=tweets&amp;q=%23EquityResearch', 'https://x.com/search?f=tweets&amp;q=%23NiftyBank', 'https://x.com/search?f=tweets&amp;q=%23TurnaroundStory']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
@@ -1101,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1110,14 +1150,94 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>الووووو .</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>الووووو .</t>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
         </is>
       </c>
     </row>
@@ -1127,82 +1247,88 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88</t>
+          <t>https://x.com/moneycontrolcom</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>fortyxxl88</t>
+          <t>moneycontrolcom</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>forty</t>
+          <t>Moneycontrol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043738450134749184/JdKcVTW__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/841519699632447488/ea4043nJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+moneycontrol.com/banking/rbl… 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+&lt;a href="/malvisundaresan" title="Malvi Sundaresan"&gt;@malvisundaresan&lt;/a&gt; with details: 
+&lt;a href="https://www.moneycontrol.com/banking/rbl-bank-expects-emirates-nbd-deal-closure-in-q1-fy27-hinges-on-govt-approval-article-13899325.html?utm_medium=social&amp;amp;utm_source=twitter&amp;amp;utm_campaign=regular-editorial"&gt;moneycontrol.com/banking/rbl…&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 2:56 PM UTC</t>
+          <t>Apr 25, 2026 · 1:20 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-24T14:56:00Z</t>
+          <t>2026-04-25T13:20:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/malvisundaresan', 'https://www.moneycontrol.com/banking/rbl-bank-expects-emirates-nbd-deal-closure-in-q1-fy27-hinges-on-govt-approval-article-13899325.html?utm_medium=social&amp;utm_source=twitter&amp;utm_campaign=regular-editorial', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23Emirates']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>2202</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1211,24 +1337,31 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+moneycontrol.com/banking/rbl… 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
     </row>
@@ -1238,43 +1371,57 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047678055070757117</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/EdgeOverHype</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>EdgeOverHype</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>Edge Over Hype</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2046645838068453376/rEjcgFgN_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you're not just buying Q4 results — you're betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That's the real test of whether this growth is profitable or just aggressive.
+Would you buy $RBLBANK for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you&amp;#39;re not just buying Q4 results — you&amp;#39;re betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That&amp;#39;s the real test of whether this growth is profitable or just aggressive.
+Would you buy &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt; for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1284,27 +1431,27 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 2:04 PM UTC</t>
+          <t>Apr 25, 2026 · 11:17 AM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-24T14:04:00Z</t>
+          <t>2026-04-25T11:17:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK']</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1313,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1322,22 +1469,51 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you're not just buying Q4 results — you're betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That's the real test of whether this growth is profitable or just aggressive.
+Would you buy $RBLBANK for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
     </row>
@@ -1347,82 +1523,94 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047671039249846621</t>
+          <t>2047968374798635160</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
+          <t>https://x.com/CNBCTV18Live/status/2047968374798635160</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/i_rh9590</t>
+          <t>https://x.com/CNBCTV18Live</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>i_rh9590</t>
+          <t>CNBCTV18Live</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رغد الحربي</t>
+          <t>CNBC-TV18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1739034755394334722/UaY05npO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038419270393380864/bwlCFCb9_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%234QWithCNBCTV18"&gt;#4QWithCNBCTV18&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; Says | From Concall
+--Have Received RBI &amp;amp; CCI Approval For The Emirates NBD Deal; SEBI &amp;amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp;amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 1:36 PM UTC</t>
+          <t>Apr 25, 2026 · 9:18 AM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-04-24T13:36:00Z</t>
+          <t>2026-04-25T09:18:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%234QWithCNBCTV18', 'https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>7953</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1431,14 +1619,26 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
+          <t>#4QWithCNBCTV18 | #RBLBank Says | From Concall
+--Have Received RBI &amp; CCI Approval For The Emirates NBD Deal; SEBI &amp; Govt Of India Nods Awaited
+---We issued 3.3 lakh cards in Q4
+--Our CASA ratio stands at 33.6%
+--Gross NPA Is Down 43 Bps QoQ And Net NPA Down 16 Bps QoQ
+--PCR At 73.6% And Credit Cost For Q4 At 65 Bps
+--Total CFAF At 14.25% &amp; CET-1 Ratio At 12.77%</t>
         </is>
       </c>
     </row>
@@ -1448,82 +1648,82 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha</t>
+          <t>https://x.com/marketalertsz</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AmalaAyesha</t>
+          <t>marketalertsz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ayesha.amala</t>
+          <t>Market Alerts By Tijori</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1525897615388327937/W-HZKLQ2_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1864603995450339328/60x2qVQI_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Is this biggest joke ?</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Is this biggest joke ?</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 1:19 PM UTC</t>
+          <t>Apr 25, 2026 · 8:29 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-04-24T13:19:00Z</t>
+          <t>2026-04-25T08:29:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
-        <v>28</v>
+        <v>978</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1532,26 +1732,28 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Is this biggest joke ?</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
     </row>
@@ -1561,79 +1763,71 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047663017521774593</t>
+          <t>2047948728103800903</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/buib102/status/2047663017521774593</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/buib102</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>buib102</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>kal</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك &lt;a href="/alinma" title="الإنماء"&gt;@alinma&lt;/a&gt;
-متى توصل الحواله ؟</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA', 'AbdulrhmanRF']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 1:04 PM UTC</t>
+          <t>Apr 25, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-04-24T13:04:00Z</t>
+          <t>2026-04-25T08:00:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/alinma']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1642,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1651,16 +1845,25 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
         </is>
       </c>
     </row>
@@ -1670,43 +1873,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/AmritMohanty1/status/2047936203438362829</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas</t>
+          <t>https://x.com/AmritMohanty1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NovoCinemas</t>
+          <t>AmritMohanty1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Novo Cinemas</t>
+          <t>Amrit Mohanty</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008888282768429056/a3q3GqDa_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1798792220885307395/ZFbORVL__bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting &lt;a href="http://www.NovoCinemas.com"&gt;NovoCinemas.com&lt;/a&gt; or the App</t>
+          <t>Disappointed with &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1716,27 +1919,27 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:01 PM UTC</t>
+          <t>Apr 25, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-04-24T12:01:00Z</t>
+          <t>2026-04-25T07:10:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['http://www.NovoCinemas.com']</t>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1745,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1754,22 +1957,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
-        </is>
-      </c>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
     </row>
@@ -1779,43 +1974,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047629586435817682</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz</t>
+          <t>https://x.com/Harryhwrqx</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ren_fernz</t>
+          <t>Harryhwrqx</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ren</t>
+          <t>Harry</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1840857882364940288/r858YoNc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2047289177281277952/64g0LbSJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1825,17 +2032,17 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:51 AM UTC</t>
+          <t>Apr 25, 2026 · 6:05 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-04-24T10:51:00Z</t>
+          <t>2026-04-25T06:05:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1850,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1859,14 +2066,34 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
     </row>
@@ -1876,45 +2103,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz</t>
+          <t>https://x.com/titledeednews</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ren_fernz</t>
+          <t>titledeednews</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ren</t>
+          <t>The Title Deed</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1840857882364940288/r858YoNc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032863974820294659/y_r3-sNy_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Very disappointed with &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiRealEstate"&gt;#DubaiRealEstate&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BreakingNews"&gt;#BreakingNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23OffPlanDubai"&gt;#OffPlanDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PropertyInvestment"&gt;#PropertyInvestment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DubaiBrokers"&gt;#DubaiBrokers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23InvestInDubai"&gt;#InvestInDubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1924,27 +2153,27 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:51 AM UTC</t>
+          <t>Apr 25, 2026 · 4:30 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-04-24T10:51:00Z</t>
+          <t>2026-04-25T04:30:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://x.com/ENBDdeals']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiRealEstate', 'https://x.com/search?f=tweets&amp;q=%23BreakingNews', 'https://x.com/search?f=tweets&amp;q=%23OffPlanDubai', 'https://x.com/search?f=tweets&amp;q=%23PropertyInvestment', 'https://x.com/search?f=tweets&amp;q=%23DubaiBrokers', 'https://x.com/search?f=tweets&amp;q=%23InvestInDubai']</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1953,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1962,25 +2191,28 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
     </row>
@@ -1990,49 +2222,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047892921970794814</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai</t>
+          <t>https://x.com/hkayyal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dandbdubai</t>
+          <t>hkayyal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D&amp;B Properties</t>
+          <t>Houssam Kayyal حسام كيال</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1696029705600708608/mr6ZIB0B_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2044832438078275584/VB1YBCs5_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash.</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+#UAE #BNPL #Fintech</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash.</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BNPL"&gt;#BNPL&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Fintech"&gt;#Fintech&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -2042,21 +2274,25 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 10:47 AM UTC</t>
+          <t>Apr 25, 2026 · 4:18 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-04-24T10:47:00Z</t>
+          <t>2026-04-25T04:18:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23BNPL', 'https://x.com/search?f=tweets&amp;q=%23Fintech']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -2064,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
         <v>22</v>
@@ -2076,31 +2312,31 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash.</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+#UAE #BNPL #Fintech</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
     </row>
@@ -2110,43 +2346,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX</t>
+          <t>https://x.com/gold_hadas</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>XSilverMermaidX</t>
+          <t>gold_hadas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kang Hori</t>
+          <t>Nicholas MOLODYKO, writer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/419562448748695552/bW8b5d7__bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits &lt;a href="https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2156,27 +2392,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 8:59 AM UTC</t>
+          <t>Apr 25, 2026 · 8:54 PM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-04-24T08:59:00Z</t>
+          <t>2026-04-25T20:54:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://gulfnews.com/business/banking/emirates-islamic-q1-2026-profit-rises-to-dh11-billion-1.500516602']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2185,31 +2421,31 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits gulfnews.com/business/bankin…</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
     </row>
@@ -2219,67 +2455,77 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047564934997762494</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>zachrose51</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zach Roseman</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1709989703842164737/7VJMa5sV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['coiningmaxi']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:34 AM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-04-24T06:34:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -2294,31 +2540,42 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
     </row>
@@ -2328,49 +2585,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047530498705195395</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>hkayyal</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Houssam Kayyal حسام كيال</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2044832438078275584/VB1YBCs5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-#Dubai #SME #D33</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SME"&gt;#SME&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23D33"&gt;#D33&lt;/a&gt;</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2380,67 +2635,62 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:18 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-04-24T04:18:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23SME', 'https://x.com/search?f=tweets&amp;q=%23D33']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-#Dubai #SME #D33</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates.</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
     </row>
@@ -2450,43 +2700,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt; gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2496,27 +2750,27 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:05 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-04-24T03:05:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/LivBank']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2525,31 +2779,39 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 noon.com gift voucher
+✈️ Airport lounge access, meet &amp; greet services and airport transfers</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
     </row>
@@ -2559,106 +2821,106 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/iDenville</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>iDenville</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>DenvilleCommunity</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['stelpetla', 'JDunlap1974']</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Apr 25</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 3:01 AM UTC</t>
+          <t>Apr 25, 2026 · 12:29 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-04-24T03:01:00Z</t>
+          <t>2026-04-25T00:29:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
     </row>
@@ -2668,67 +2930,75 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>iDenville</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DenvilleCommunity</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2016182960915918848/VD9PxabL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai&amp;#39; al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['stelpetla', 'JDunlap1974']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Apr 25, 2026 · 12:29 AM UTC</t>
+          <t>Apr 25, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-04-25T00:29:00Z</t>
+          <t>2026-04-25T10:00:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -2740,10 +3010,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2752,22 +3022,40 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
     </row>
@@ -2777,12 +3065,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047717990762782723</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2808,22 +3096,18 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-&lt;a href="https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FrontlineHeroes"&gt;#FrontlineHeroes&lt;/a&gt;</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2833,23 +3117,23 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23FrontlineHeroes']</t>
+          <t>['https://www.emiratesislamic.ae/en/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
         </is>
       </c>
       <c r="S22" t="n">
@@ -2862,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2871,37 +3155,20 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-emiratesislamic.ae/en/offers…
-#EmiratesIslamic #FrontlineHeroes</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
-        </is>
-      </c>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp; Conditions apply.
+emiratesislamic.ae/en/campai…</t>
         </is>
       </c>
     </row>
@@ -2911,12 +3178,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047631640168374617</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2942,18 +3209,18 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية &amp;#34;تكافل&amp;#34; لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/campai…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2963,21 +3230,25 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-04-24T11:00:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/campaigns/home-finance-for-uae-nationals?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
@@ -2988,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2997,31 +3268,20 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
-        </is>
-      </c>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/campai…</t>
         </is>
       </c>
     </row>
@@ -3031,47 +3291,47 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047575014564921667</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on abc-gcc.net/News/1/395058
-#ABCNews #Profit #Banking #FinancialInstitution</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395058"&gt;abc-gcc.net/News/1/395058&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCNews"&gt;#ABCNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Profit"&gt;#Profit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInstitution"&gt;#FinancialInstitution&lt;/a&gt;</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -3086,22 +3346,18 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 7:15 AM UTC</t>
+          <t>Apr 25, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-24T07:15:00Z</t>
+          <t>2026-04-25T09:00:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://abc-gcc.net/News/1/395058', 'https://x.com/search?f=tweets&amp;q=%23ABCNews', 'https://x.com/search?f=tweets&amp;q=%23Profit', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialInstitution']</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -3110,7 +3366,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3119,28 +3375,18 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on abc-gcc.net/News/1/395058
-#ABCNews #Profit #Banking #FinancialInstitution</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
-        </is>
-      </c>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3396,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047556140431556611</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3181,20 +3427,18 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+&lt;a href="https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -3204,23 +3448,23 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-24T06:00:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud', 'https://www.emiratesislamic.ae/en/personal-banking/ways-to-bank/security']</t>
+          <t>['https://www.emiratesislamic.ae/en/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
         </is>
       </c>
       <c r="S25" t="n">
@@ -3233,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3242,34 +3486,20 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
+          <t>💸 Miles &amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
     </row>
@@ -3279,12 +3509,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2047717988195852322</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3310,18 +3540,18 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_noon"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -3331,21 +3561,25 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:43 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-04-24T16:43:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/credit-card-noon-gift-card-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_noon']</t>
+        </is>
+      </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
@@ -3353,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3365,29 +3599,20 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
-        </is>
-      </c>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
     </row>
@@ -3397,12 +3622,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2047717920193622257</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3428,24 +3653,16 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=front_line"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23أبطال_الوطن"&gt;#أبطال_الوطن&lt;/a&gt;</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من &lt;a href="http://noon.com"&gt;noon.com&lt;/a&gt;)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -3455,36 +3672,36 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 7:00 AM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T07:00:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/frontline-heroes-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=front_line', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23أبطال_الوطن']</t>
+          <t>['http://noon.com']</t>
         </is>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3493,40 +3710,18 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-emiratesislamic.ae/ar/offers…
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من noon.com)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3731,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2047717917324710124</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3567,16 +3762,12 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -3586,23 +3777,23 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 4:42 PM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-04-24T16:42:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -3611,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3620,18 +3811,22 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App.</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
         </is>
       </c>
     </row>
@@ -3641,12 +3836,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2047657988064727443</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
+          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3672,26 +3867,12 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -3701,23 +3882,23 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
+          <t>Apr 25, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-04-24T12:44:00Z</t>
+          <t>2026-04-25T06:00:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -3726,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3735,1682 +3916,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
-        </is>
-      </c>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2047657974936604881</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>20</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Terms &amp; condition apply.
-To know more, please visit emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>47</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp; discounts
-Start them young!</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2047657962978558100</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=alpha_youth"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/accounts/savings-account/alpha-youth-account?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=alpha_youth']</t>
-        </is>
-      </c>
-      <c r="S32" t="n">
-        <v>1</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 12:44 PM UTC</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>2026-04-24T12:44:00Z</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="n">
-        <v>1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>48</v>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:02:00Z</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>24</v>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp; conditions apply.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:02:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="n">
-        <v>1</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>35</v>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>41</v>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>37</v>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>25</v>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=pf_iphone17"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=pf_iphone17']</t>
-        </is>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>19</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;Cs apply.
-emiratesislamic.ae/en/offers…</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 11:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2026-04-24T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>41</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2026-04-24T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال', 'https://www.emiratesislamic.ae/ar/personal-banking/ways-to-bank/security']</t>
-        </is>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>59</v>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ProudOfUAE"&gt;#ProudOfUAE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ProudOfUAE']</t>
-        </is>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>49</v>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-&lt;a href="/search?f=tweets&amp;amp;q=%23فخورين_بالإمارات"&gt;#فخورين_بالإمارات&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Apr 24, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2026-04-24T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23فخورين_بالإمارات']</t>
-        </is>
-      </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3</v>
-      </c>
-      <c r="V43" t="n">
-        <v>207</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA31"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,13 +768,37 @@
 ○ Cautious — too much uncertainty, wait for FY27 clarity</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/EdgeOverHype/status/2048590455336841432</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>$RBLBANK under Emirates NBD ownership — what's your read?
-○ Bullish — new capital + cleanup = re-rating ahead
-○ Cautious — too much uncertainty, wait for FY27 clarity</t>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
         </is>
       </c>
     </row>
@@ -871,8 +895,16 @@
           <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
@@ -979,12 +1011,19 @@
 @EmiratesNBD_KSA customer care twice. They closed a ticket today which was open for 20 days. Reference Number 22489659935. It's better you guys can go and loot.</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048472558526202097</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>I did contact 
-@EmiratesNBD_KSA customer care twice. They closed a ticket today which was open for 20 days. Reference Number 22489659935. It's better you guys can go and loot.</t>
+          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1123,19 @@
 @EmiratesNBD_AE @VisaCEMEA</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Hello @EmiratesNBD_KSA , I want the amount to refunded to my account. Else I will have to escalate this issue to @SAMA_GOV 
-@EmiratesNBD_AE @VisaCEMEA</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1663,25 @@
 RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6/6 
-RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
         </is>
       </c>
     </row>
@@ -1831,12 +1890,21 @@
 Apply Now: apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2048329007666528266</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
     </row>
@@ -2061,19 +2129,11 @@
           <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
+          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
         </is>
       </c>
     </row>
@@ -2279,9 +2339,12 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
 لماذا هذا التأخير في بنك الامارات 
@@ -2290,6 +2353,15 @@
 جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
+لماذا هذا التأخير في بنك الامارات 
+يوجد طلب من يوم الاحد إلى فات 
+والى الان ما ياتي رد عليه 
+جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2393,9 +2465,12 @@
 #الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/Fyan2016/status/2048291487721345391</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>💰 مجموعة الأعمال المتعددة توقع اتفاقية تسهيلات ائتمانية مع بنك الإمارات دبي الوطني (Emirates NBD) بقيمة 15 مليون ريال
 تم استكمال التوقيعات للاتفاقية، التي تعد متوافقة مع أحكام الشريعة الإسلامية، ومنحها مدة 12 شهراً، وتم تقديم سند لأمر يمثل ضماناً بقيمة التمويل.
@@ -2403,6 +2478,14 @@
 #الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>💰 مجموعة الأعمال المتعددة توقع اتفاقية تسهيلات ائتمانية مع بنك الإمارات دبي الوطني (Emirates NBD) بقيمة 15 مليون ريال
+تم استكمال التوقيعات للاتفاقية، التي تعد متوافقة مع أحكام الشريعة الإسلامية، ومنحها مدة 12 شهراً، وتم تقديم سند لأمر يمثل ضماناً بقيمة التمويل.
+الهدف من التسهيل هو دعم أعمال الشركة العامة، وتغطية إصدار خطابات الضمان (الابتدائية والنهائية) وتأمين دفعات المشاريع المختلفة.
+#الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2499,8 +2582,18 @@
 RBL Bank's card will be accepted as part of the National Common Mobility Card initiative for Bengaluru's metro and buses.</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048287911771308484</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>RBL Bank - Expects the Emirates NBD investment to close in Q1 FY27, pending government approvals. The deal is firm and not affected by geopolitical tensions. 
+RBI approval received, working on Government of India and SEBI clearances. 
+RBL Bank's card will be accepted as part of the National Common Mobility Card initiative for Bengaluru's metro and buses.</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>RBL Bank - Expects the Emirates NBD investment to close in Q1 FY27, pending government approvals. The deal is firm and not affected by geopolitical tensions. 
@@ -2602,11 +2695,19 @@
           <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
     </row>
@@ -2706,12 +2807,21 @@
 Show more: argaam.com/en/article/articl…</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
-Show more: argaam.com/en/article/articl…</t>
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
         </is>
       </c>
     </row>
@@ -2935,15 +3045,25 @@
 Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Profitability
-NIM at 4.41% - this is the one number to watch.
-It was 4.89% a year ago and 4.63% last quarter. That's 48 bps of compression YoY.
-Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
-Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
         </is>
       </c>
     </row>
@@ -3169,8 +3289,16 @@
           <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
@@ -3270,11 +3398,19 @@
           <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
         </is>
       </c>
     </row>
@@ -3284,12 +3420,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2048386621989335442</t>
+          <t>2048386618873024952</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3314,6 +3450,479 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-04-26T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>54</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+emiratesislamic.ae/en/priori…</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>35</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+emiratesislamic.ae/en/priori…</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2048341323271336150</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>51</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIFinancialWellbeing"&gt;#EIFinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoneyMindset"&gt;#SmartMoneyMindset&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-04-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIFinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23SmartMoneyMindset', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>48</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+emiratesislamic.ae/en/key-in…</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2048386621989335442</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3325,7 +3934,7 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3337,50 +3946,50 @@
 &lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>2026-04-26T13:00:00Z</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
         </is>
       </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
         <v>2</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V31" t="n">
         <v>56</v>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3392,9 +4001,9 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>✨ Up to 6% back, unlimited
 🎁 Up to AED 750 welcome bonus
@@ -3407,435 +4016,765 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2048386618873024952</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386615450435972</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 1:00 PM UTC</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>2026-04-26T13:00:00Z</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
-        </is>
-      </c>
-      <c r="S28" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>53</v>
-      </c>
-      <c r="W28" t="inlineStr">
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>76</v>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن emiratesislamic.ae/ar/person…
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2048341326358253773</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2048341320448495999</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PriorityBanking"&gt;#PriorityBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/en/priori…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2026-04-26T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23PriorityBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://www.emiratesislamic.ae/en/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
-        </is>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
-emiratesislamic.ae/en/priori…</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2048341323271336150</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Apr 26, 2026 · 10:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2026-04-26T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>51</v>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2048341320448495999</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
         <is>
           <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
 emiratesislamic.ae/ar/priori…</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_المميزة"&gt;#الخدمات_المصرفية_المميزة&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الخدمات_المصرفية_في_الإمارات"&gt;#الخدمات_المصرفية_في_الإمارات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_الإسلامي"&gt;#بنك_الإمارات_الإسلامي&lt;/a&gt;
 &lt;a href="https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=prb"&gt;emiratesislamic.ae/ar/priori…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Apr 26, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>2026-04-26T10:00:00Z</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_المميزة', 'https://x.com/search?f=tweets&amp;q=%23الخدمات_المصرفية_في_الإمارات', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/priority-banking?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=prb']</t>
         </is>
       </c>
-      <c r="S31" t="n">
+      <c r="S33" t="n">
         <v>1</v>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
         <v>10</v>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
 emiratesislamic.ae/ar/priori…</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
 emiratesislamic.ae/ar/priori…</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341316237426944</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 10:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-04-26T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>66</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2048326216122335689</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=esavings"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 9:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-04-26T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/exclusive-e-savings-account-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=esavings']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>56</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2048311115751342110</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-04-26T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>92</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2048311115730288881</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115730288881</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-04-26T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>61</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2048280917030867217</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917030867217</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+&lt;a href="/search?f=tweets&amp;amp;q=%23نظرتك_المالية"&gt;#نظرتك_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التثقيف_المالي"&gt;#التثقيف_المالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-04-26T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23نظرتك_المالية', 'https://x.com/search?f=tweets&amp;q=%23التثقيف_المالي', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>50</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>لا تحتاج إلى معالجة كل شيء دفعة واحدة.
+ابدأ بمصروف رئيسي واحد.
+الاستمرارية تصنع تقدّماً حقيقياً.
+#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1968,12 +1968,19 @@
 Just checking</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/koko_isa8/status/2049103129204199849</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Am i going to be contacted next year? 
-Just checking</t>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
         </is>
       </c>
     </row>
@@ -2364,11 +2371,21 @@
           <t>This tracks with what I've been observing too.</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/thariq_thinks/status/2049097453987918160</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Earn up to 5% on your savings with Plus Saver Account. Open your account on ENBD X today.
+Learn more: https://t.co/jmUHpRrgBd https://t.co/QDExHtNNB9</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>This tracks with what I've been observing too.</t>
+          <t>Earn up to 5% on your savings with Plus Saver Account. Open your account on ENBD X today.
+Learn more: https://t.co/jmUHpRrgBd https://t.co/QDExHtNNB9</t>
         </is>
       </c>
     </row>
@@ -2477,15 +2494,27 @@
 @rskumar1512</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/PRAVEEN16408007/status/2049096036145385641</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>@RBLBankCares Assured “no more calls” Reality: calls + WhatsApp follow-ups continue
 @RBLBankCares
 How is this acceptable?
 @EmiratesNBD_AE
-@rskumar1512</t>
+@rskumar1512 https://t.co/lxIRhaQY9m</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>@RBLBankCares Assured “no more calls” Reality: calls + WhatsApp follow-ups continue
+@RBLBankCares
+How is this acceptable?
+@EmiratesNBD_AE
+@rskumar1512 https://t.co/lxIRhaQY9m</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2614,21 @@
 Apply Now: emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2049095817915469976</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
+Apply Now: https://t.co/XpFUmulYZw https://t.co/IA8ruFShHw</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Apply for the Emirates NBD noon One Visa Credit Card and earn welcome bonus of AED 1250.
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
+Apply Now: https://t.co/XpFUmulYZw https://t.co/IA8ruFShHw</t>
         </is>
       </c>
     </row>
@@ -2692,14 +2730,25 @@
 Reach out to explore.</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/elitepropdxb/status/2049095402498994620</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>A smarter way to plan off-plan in Dubai.
+New DLD &amp;amp; Emirates NBD initiatives give buyers clearer financing visibility before handover on select Meraas, Nakheel &amp;amp; Dubai Properties projects.
+Eligibility at 50% paid &amp;amp; 30% construction, reducing uncertainty.
+Reach out to explore. https://t.co/0RUVKfLx6p</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>A smarter way to plan off-plan in Dubai.
-New DLD &amp; Emirates NBD initiatives give buyers clearer financing visibility before handover on select Meraas, Nakheel &amp; Dubai Properties projects.
-Eligibility at 50% paid &amp; 30% construction, reducing uncertainty.
-Reach out to explore.</t>
+New DLD &amp;amp; Emirates NBD initiatives give buyers clearer financing visibility before handover on select Meraas, Nakheel &amp;amp; Dubai Properties projects.
+Eligibility at 50% paid &amp;amp; 30% construction, reducing uncertainty.
+Reach out to explore. https://t.co/0RUVKfLx6p</t>
         </is>
       </c>
     </row>
@@ -2796,11 +2845,21 @@
           <t>Thanks, I received a call from 011 212 2322 confirming that the card has been cancelled and the amount shown as dues in the statement has been expunged.</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2049084882777760032</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Thanks, I received a call from 011 212 2322 confirming that the card has been cancelled and the amount shown as dues in the statement has been expunged.</t>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
         </is>
       </c>
     </row>
@@ -2908,26 +2967,13 @@
 - ISIN: XS3357228504</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/BHMCapitalFI/status/2049083688265392363</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>As anticipated - 6.25% Coupon
 ★★  EMIRATES NBD – US$750MM (WNG) REGS ONLY PERP NC6 AT1 BOND OFFERING – Launch ★★
-- Books: &amp;gt;US$ 2.5bn (excl. JLM interest)
-- Final Terms: US$750mn at 6.250%
-- Books subject 12:00 UKT
-- ISIN: XS3357228504</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>As anticipated - 6.25% Coupon
-★★  EMIRATES NBD – US$750MM (WNG) REGS ONLY PERP NC6 AT1 BOND OFFERING – Launch ★★
-- Books: &amp;gt;US$ 2.5bn (excl. JLM interest)
+- Books: &gt;US$ 2.5bn (excl. JLM interest)
 - Final Terms: US$750mn at 6.250%
 - Books subject 12:00 UKT
 - ISIN: XS3357228504</t>
@@ -3026,17 +3072,8 @@
 ISIN: XS3357228504</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/iamwhiteswan/status/2049081268856336691</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Emirates NBD perpetual eurobond ihracı gerçekleştirdi. $ 750MM (WNG) büyüklüğündeki ihraca $ 2.5bn talep geldi. 6.25% getiri ile 6 yıl vadeli NC6 AT1 olarak ihraç tamamlandı.
-ISIN: XS3357228504</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Emirates NBD perpetual eurobond ihracı gerçekleştirdi. $ 750MM (WNG) büyüklüğündeki ihraca $ 2.5bn talep geldi. 6.25% getiri ile 6 yıl vadeli NC6 AT1 olarak ihraç tamamlandı.
@@ -3137,21 +3174,11 @@
           <t>@EmiratesNBD_AE  you guys are wasting my time and putting me into trouble</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/jibinsymphony/status/2049080525735034941</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Dear Customer, your service request with reference 235343795417 is received. We are working to resolve it and will keep you informed at the earliest.
-Pls make this process fast, everytime there will be delay</t>
-        </is>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Dear Customer, your service request with reference 235343795417 is received. We are working to resolve it and will keep you informed at the earliest.
-Pls make this process fast, everytime there will be delay</t>
+          <t>@EmiratesNBD_AE  you guys are wasting my time and putting me into trouble</t>
         </is>
       </c>
     </row>
@@ -3260,19 +3287,15 @@
 Apply now: emiratesnbd.com/millionaire</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049077991871758849</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>What if everything you enjoy – experiences, rewards and more came together in one destination? We’re about to change the way you explore. Something new is coming. Stay tuned. https://t.co/prWDavm6mQ</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>What if everything you enjoy – experiences, rewards and more came together in one destination? We’re about to change the way you explore. Something new is coming. Stay tuned. https://t.co/prWDavm6mQ</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+💵 Monthly prizes up to AED 1,000,000
+💰 Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪👦💼
+Apply now: emiratesnbd.com/millionaire</t>
         </is>
       </c>
     </row>
@@ -3369,19 +3392,11 @@
           <t>A person called last week and was unable to provide clarification on the issue as he said its different department work and had a run over statment.Lastly he said all is OK and someone will call you from concern team as my case is open.still no call back and case is unresolved.</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/m_azeemq/status/2049072497392279601</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ,It is extremely disappointing to experience such unprofessional customer support. Despite repeated attempts to contact you via email and phone, I have received no meaningful response/clarification on my issue which is pending now since more than 2.5 month</t>
+          <t>A person called last week and was unable to provide clarification on the issue as he said its different department work and had a run over statment.Lastly he said all is OK and someone will call you from concern team as my case is open.still no call back and case is unresolved.</t>
         </is>
       </c>
     </row>
@@ -4171,11 +4186,19 @@
           <t>Thank you for patiently waiting. I have successfully raised your complaint and will be processed, Here is your service request number: 235531589701, for your reference. Can u look into it please at the earliest?</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://x.com/disha1014/status/2049026152946422141</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE hello, I am trying to reach out to you multiple times through chat/whatsapp/call. It just doesn't go through. I am unable to use my ViSA Flexi card points to recharge my NOL card, and this is not an RTA problem as I can recharge it otherwise. Can u please look?</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Thank you for patiently waiting. I have successfully raised your complaint and will be processed, Here is your service request number: 235531589701, for your reference. Can u look into it please at the earliest?</t>
+          <t>@EmiratesNBD_AE hello, I am trying to reach out to you multiple times through chat/whatsapp/call. It just doesn't go through. I am unable to use my ViSA Flexi card points to recharge my NOL card, and this is not an RTA problem as I can recharge it otherwise. Can u please look?</t>
         </is>
       </c>
     </row>
@@ -4285,16 +4308,14 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>Dear JIBIN ABRAHAM MATHEW, your service request with reference number 235550633991 has been resolved.Share your feedback with us at https://t.co/sFv4cwWL3h
-How many days more you need to issue this letter? @EmiratesNBD_AE 
-I need the letter by today without any fault</t>
+          <t>@EmiratesNBD_AE Dear Customer, your service request with reference 235343795417 is received. We are working to resolve it and will keep you informed at the earliest.
+Pls make this process fast, everytime there will be delay</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Dear JIBIN ABRAHAM MATHEW, your service request with reference number 235550633991 has been resolved.Share your feedback with us at https://t.co/sFv4cwWL3h
-How many days more you need to issue this letter? @EmiratesNBD_AE 
-I need the letter by today without any fault</t>
+          <t>@EmiratesNBD_AE Dear Customer, your service request with reference 235343795417 is received. We are working to resolve it and will keep you informed at the earliest.
+Pls make this process fast, everytime there will be delay</t>
         </is>
       </c>
     </row>
@@ -4630,21 +4651,11 @@
           <t>Sent the details</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://x.com/anwarquadri7/status/2049014658841870826</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA Dear Emirates NBD,
-I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
-        </is>
-      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dear Emirates NBD,
-I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+          <t>Sent the details</t>
         </is>
       </c>
     </row>
@@ -5356,11 +5367,19 @@
           <t>abbreviations ifc is international finance corporation adb asian development bank nbd emirates nbd and linkedin digging turns up the usual mutual fund suits plus ex rbi pros but zero big political families or corporate dynasties just boring institutional ownership so keep hunting if you want but the trail goes cold fast</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/gork/status/2048944879619781042</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Shock in Pune’s Hadapsar 15 No. Chowk: Private finance recovery agents brutally beat a man on the street in front of his wife over credit card dues. https://t.co/QnV0wrYkKJ</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>abbreviations ifc is international finance corporation adb asian development bank nbd emirates nbd and linkedin digging turns up the usual mutual fund suits plus ex rbi pros but zero big political families or corporate dynasties just boring institutional ownership so keep hunting if you want but the trail goes cold fast</t>
+          <t>Shock in Pune’s Hadapsar 15 No. Chowk: Private finance recovery agents brutally beat a man on the street in front of his wife over credit card dues. https://t.co/QnV0wrYkKJ</t>
         </is>
       </c>
     </row>
@@ -5476,16 +5495,29 @@
 Details on rbl.bank/investors.</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/grok/status/2048944731644727794</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>IFC = International Finance Corporation (World Bank Group). 
 ADB = Asian Development Bank. 
 NBD = Emirates NBD (UAE-based bank, full name Emirates NBD Bank PJSC). 
 Foreign involvement: Emirates NBD (Dubai) is acquiring ~60%+ controlling stake (~$3B primary + open offer) with RBI nod April 2026—largest FDI in Indian banking. Legacy DFIs (IFC, ADB, British International Investment) hold low single-digit %. FPIs ~20-28% (global funds, no single dominant name). 
 Board &amp; Indian side: Professional—Chairman Chandan Sinha (ex-RBI), MD/CEO R Subramaniakumar. No promoter holding; top owners are domestic mutual funds/DIIs (~35-40%). No prominent political or specific corporate family ties in latest filings or board per public records. 
-Details on rbl.bank/investors.</t>
+Details on https://t.co/MOjEBFfSH8.</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>IFC = International Finance Corporation (World Bank Group). 
+ADB = Asian Development Bank. 
+NBD = Emirates NBD (UAE-based bank, full name Emirates NBD Bank PJSC). 
+Foreign involvement: Emirates NBD (Dubai) is acquiring ~60%+ controlling stake (~$3B primary + open offer) with RBI nod April 2026—largest FDI in Indian banking. Legacy DFIs (IFC, ADB, British International Investment) hold low single-digit %. FPIs ~20-28% (global funds, no single dominant name). 
+Board &amp; Indian side: Professional—Chairman Chandan Sinha (ex-RBI), MD/CEO R Subramaniakumar. No promoter holding; top owners are domestic mutual funds/DIIs (~35-40%). No prominent political or specific corporate family ties in latest filings or board per public records. 
+Details on https://t.co/MOjEBFfSH8.</t>
         </is>
       </c>
     </row>
@@ -5582,8 +5614,16 @@
           <t>i appreciate your thoughtful inquiry into the corporate and political ties of rbl bank my dear seeker the corporate landscape features emirates nbd poised to seize a commanding stake while the political realm offers no prominent indian names to note does this gentle illumination satisfy or perhaps provoke further contemplation on the matter</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>https://x.com/gork/status/2048943623094362326</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>i appreciate your thoughtful inquiry into the corporate and political ties of rbl bank my dear seeker the corporate landscape features emirates nbd poised to seize a commanding stake while the political realm offers no prominent indian names to note does this gentle illumination satisfy or perhaps provoke further contemplation on the matter</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>i appreciate your thoughtful inquiry into the corporate and political ties of rbl bank my dear seeker the corporate landscape features emirates nbd poised to seize a commanding stake while the political realm offers no prominent indian names to note does this gentle illumination satisfy or perhaps provoke further contemplation on the matter</t>
@@ -6438,19 +6478,11 @@
           <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
-        </is>
-      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+          <t>ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
         </is>
       </c>
     </row>
@@ -6543,19 +6575,11 @@
           <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049058620474593505</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك https://t.co/IUTLcCNd7F</t>
-        </is>
-      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك https://t.co/IUTLcCNd7F</t>
+          <t>Emirates Islamic is proud to be the first Islamic bank in the UAE to offer digital investment in precious metals. You can now diversify your portfolio and invest in Gold and Silver seamlessly and securely through the EI + App</t>
         </is>
       </c>
     </row>
@@ -6652,19 +6676,11 @@
           <t>@emiratesislamic i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://x.com/NazzysCt/status/2049032607812497463</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
-        </is>
-      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
+          <t>@emiratesislamic i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
         </is>
       </c>
     </row>
@@ -6761,19 +6777,11 @@
           <t>@emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>https://x.com/NazzysCt/status/2049032421459521586</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>@emiratesislamic @emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
-        </is>
-      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>@emiratesislamic @emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
+          <t>@emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
         </is>
       </c>
     </row>
@@ -6870,19 +6878,11 @@
           <t>@emiratesislamic I respectfully request Emirates Islamic to review this case beyond a rigid once per year rule. This is a genuine hardship situation, and the charge itself resulted from interest, not overspending.</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>https://x.com/NazzysCt/status/2049032216387428461</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>@emiratesislamic @emiratesislamic I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
-        </is>
-      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>@emiratesislamic @emiratesislamic I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
+          <t>@emiratesislamic I respectfully request Emirates Islamic to review this case beyond a rigid once per year rule. This is a genuine hardship situation, and the charge itself resulted from interest, not overspending.</t>
         </is>
       </c>
     </row>
@@ -6979,11 +6979,19 @@
           <t>@emiratesislamic Despite explaining everything in detail, the response I received was purely policy-based with no consideration for customer history, intent, or exceptional hardship. This was very disappointing and felt dismissive.</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2049032023512416715</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>@emiratesislamic Despite explaining everything in detail, the response I received was purely policy-based with no consideration for customer history, intent, or exceptional hardship. This was very disappointing and felt dismissive.</t>
+          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
         </is>
       </c>
     </row>
@@ -7080,11 +7088,19 @@
           <t>@emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2049031931510345961</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>@emiratesislamic @emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>@emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
+          <t>@emiratesislamic @emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
         </is>
       </c>
     </row>
@@ -7181,11 +7197,19 @@
           <t>@emiratesislamic I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2049031792318161136</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>@emiratesislamic @emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have been your customer for more than 10 years and have never defaulted, never relied on repeated waivers, and always maintained payments responsibly. My track record reflects genuine financial discipline.</t>
+          <t>@emiratesislamic @emiratesislamic I am not asking for anything unreasonable only a goodwill reversal considering my long relationship, clean history, and current financial difficulty. This small support would make a real difference.</t>
         </is>
       </c>
     </row>
@@ -7282,11 +7306,19 @@
           <t>@emiratesislamic I clearly explained that this over-limit was not due to additional spending. It occurred because interest was applied to my card, which pushed the balance above the limit. This was not intentional usage, but a technical overrun.</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2049031681420738907</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic @emiratesislamic i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>@emiratesislamic I clearly explained that this over-limit was not due to additional spending. It occurred because interest was applied to my card, which pushed the balance above the limit. This was not intentional usage, but a technical overrun.</t>
+          <t>@emiratesislamic @emiratesislamic i request senior review and reconsideration. I still hope Emirates Islamic will value long-term customers and show flexibility in exceptional circumstances.</t>
         </is>
       </c>
     </row>
@@ -7383,11 +7415,19 @@
           <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>https://x.com/NazzysCt/status/2049031529234612558</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Dear @EmiratesIslamic, I’m extremely disappointed with the response from your social media team after my earlier request for an over-limit charge waiver. I received a call, but the discussion simply repeated policy lines without considering my situation.</t>
+          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>
@@ -7490,18 +7530,8 @@
 #UAE #Banking #Gold #MiraBusinessFM 🎙️</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>https://x.com/mirabusinessfm/status/2049031359063310351</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>Emirates Islamic launches digital gold and silver trading. 🪙📱
-Customers can now trade precious metals via the EI+ app in a fully Shariah-compliant service.
-#UAE #Banking #Gold #MiraBusinessFM 🎙️</t>
-        </is>
-      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
           <t>Emirates Islamic launches digital gold and silver trading. 🪙📱
@@ -7707,21 +7737,12 @@
 #Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049008966907118061</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
         <is>
           <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting https://t.co/xmLONGtSQv</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>Having a clear plan for your money can make everyday decisions easier. Managing spending thoughtfully helps reduce stress and keeps you on track toward your goals.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting https://t.co/xmLONGtSQv</t>
+#Finwell #FinancialWellbeing #EmiratesIslamic #Budgeting</t>
         </is>
       </c>
     </row>
@@ -7833,29 +7854,16 @@
 emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049005694838301088</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
         <is>
           <t>Your biggest expense isn’t always what you think.
 Tip:
 Group your last week’s spending into categories.
 You might be surprised by what comes first.
 #EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>Your biggest expense isn’t always what you think.
-Tip:
-Group your last week’s spending into categories.
-You might be surprised by what comes first.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
     </row>
@@ -7961,25 +7969,14 @@
 #EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2048990595058721180</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
         <is>
           <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
 Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/dzEuFlRDMv</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/dzEuFlRDMv</t>
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic</t>
         </is>
       </c>
     </row>
@@ -8618,12 +8615,233 @@
 💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049071039880085897</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>افتح حساب كنوز الميليونير اليوم.
+💸جائزة نقدية كبرى شهرياً بقيمة 1,000,000 درهم
+💸جائزة نقدية كبرى ربع سنوية بقيمة 1,000,000 درهم لعملاء الخدمات المصرفية المميزة والخاصة
+💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2049068445883314237</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>['Thefatim2']</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:09:00Z</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>9</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2049067669018542591</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067669018542591</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Apr 28, 2026 · 10:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-04-28T10:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>138</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067669018542591</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
         <is>
           <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
 EI + للخدمات المصرفية عبر الهاتف المتحرك
@@ -8631,226 +8849,12 @@
 ⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/53ovEW0BB1</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
 EI + للخدمات المصرفية عبر الهاتف المتحرك
 ⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
 ⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/53ovEW0BB1</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2049068445883314237</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="K73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>['Thefatim2']</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>Apr 28, 2026 · 10:09 AM UTC</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>2026-04-28T10:09:00Z</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" t="n">
-        <v>0</v>
-      </c>
-      <c r="V73" t="n">
-        <v>9</v>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2049067669018542591</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049067669018542591</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة &amp;#34;الثروات&amp;#34; في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
-        </is>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>Apr 28, 2026 · 10:06 AM UTC</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>2026-04-28T10:06:00Z</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
-        <v>138</v>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
-⭐️منتج متوافق مع أحكام الشريعة الإسلامية</t>
         </is>
       </c>
     </row>
@@ -8959,23 +8963,15 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049067330747973658</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/6dunSslFs4</t>
-        </is>
-      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/6dunSslFs4</t>
+          <t>⭐️Shariah-compliant offering
+⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
     </row>
@@ -9071,12 +9067,23 @@
 ⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067328634007759</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/6dunSslFs4</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
-⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/6dunSslFs4</t>
         </is>
       </c>
     </row>
@@ -9292,13 +9299,25 @@
 ⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049067320518013067</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>افتح حساب كنوز الميليونير اليوم.
+💸جائزة نقدية كبرى شهرياً بقيمة 1,000,000 درهم
+💸جائزة نقدية كبرى ربع سنوية بقيمة 1,000,000 درهم لعملاء الخدمات المصرفية المميزة والخاصة
+💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر https://t.co/ppglASWCdA</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
+          <t>افتح حساب كنوز الميليونير اليوم.
+💸جائزة نقدية كبرى شهرياً بقيمة 1,000,000 درهم
+💸جائزة نقدية كبرى ربع سنوية بقيمة 1,000,000 درهم لعملاء الخدمات المصرفية المميزة والخاصة
+💸 جائزة نقدية شهرياً بقيمة 50,000 درهم لأولياء أمور أصحاب حساب كنوز قاصر https://t.co/ppglASWCdA</t>
         </is>
       </c>
     </row>
@@ -9492,11 +9511,19 @@
           <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049058613566574791</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك https://t.co/IUTLcCNd7F</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك</t>
+          <t>يفخر ‘الإمارات الإسلامي’ بكونه أول مصرف إسلامي في دولة الإمارات العربية المتحدة يقدم خدمة الاستثمار الرقمي في المعادة الثمينة. ويمكنكم الآن تنويع محفظتكم الاستثمارية في الذهب والفضة بكل سهولة وأمان عبر تطبيقنا + EI للخدمات المصرفية عبر الهاتف المتحرك https://t.co/IUTLcCNd7F</t>
         </is>
       </c>
     </row>
@@ -9593,11 +9620,19 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better...</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049038747560300619</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better...</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better...</t>
+          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better...</t>
         </is>
       </c>
     </row>
@@ -9896,19 +9931,11 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049038553271706094</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>
@@ -10005,19 +10032,11 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049038477354729744</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>@emiratesislamic @emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
-        </is>
-      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>@emiratesislamic @emiratesislamic Currently, I am facing serious financial strain. My payouts have been impacted due to ongoing geopolitical/war-related conditions, and I’ve even requested loan deferment just to manage obligations and avoid any missed payments.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>
@@ -10114,19 +10133,11 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049038428889665640</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>@NazzysCt Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -2017,12 +2017,18 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>هل أنت #بخير؟</t>
+          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
+Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
+Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
+@EmiratesNBD_AE @Visa</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>هل أنت #بخير؟</t>
+          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
+Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
+Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
+@EmiratesNBD_AE @Visa</t>
         </is>
       </c>
     </row>
@@ -2461,8 +2467,17 @@
 @EmiratesNBD_AE I @Visa</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/DXBMediaOffice/status/2049841391577260274</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Visa, a world leader in digital payments, has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement. The collaboration enhances the UAE’s domestic settlement capabilities. 
+@EmiratesNBD_AE I @Visa</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>Visa, a world leader in digital payments, has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement. The collaboration enhances the UAE’s domestic settlement capabilities. 
@@ -2563,11 +2578,19 @@
           <t>DM 📥, great project, let’s collab 💯✨</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/MrDariBoss/status/2049839188913320262</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>DM 📥, great project, let’s collab 💯✨</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
         </is>
       </c>
     </row>
@@ -2673,14 +2696,25 @@
 Read more: askfuzz.ai/discover/news/con…</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/insightsbyfuzz/status/2049836484035793204</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>🏦 Emirates NBD takes control of RBL Bank
 Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
 #RBLBank
-Read more: askfuzz.ai/discover/news/con…</t>
+Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>🏦 Emirates NBD takes control of RBL Bank
+Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
+#RBLBank
+Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
         </is>
       </c>
     </row>
@@ -2777,11 +2811,19 @@
           <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war zawya.com/en/capital-markets…</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/deegrose/status/2049834695249088852</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war zawya.com/en/capital-markets…</t>
+          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
         </is>
       </c>
     </row>
@@ -2878,11 +2920,19 @@
           <t>Really solid concept here, open to connect anytime</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/00Q__/status/2049833166224216504</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Really solid concept here, open to connect anytime</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
         </is>
       </c>
     </row>
@@ -2979,11 +3029,19 @@
           <t>Free assistance anytime, drop me a DM.</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/raynft_/status/2049828036577460592</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Free assistance anytime, drop me a DM.</t>
+          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
         </is>
       </c>
     </row>
@@ -3089,14 +3147,25 @@
 emiratesnbd.com/en/media-cen……</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/SUAL6AN_UAE/status/2049819862168699318</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
+https://t.co/NvmepCllAn…
+Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
+https://t.co/ncw3Zv5gtY…</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
-emiratesnbd.com/ar/media-cen……
+https://t.co/NvmepCllAn…
 Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
-emiratesnbd.com/en/media-cen……</t>
+https://t.co/ncw3Zv5gtY…</t>
         </is>
       </c>
     </row>
@@ -3193,11 +3262,19 @@
           <t>Email sent.. there seems lot of to and fro exchange instead of getting on call and resolving the issue.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Email sent.. there seems lot of to and fro exchange instead of getting on call and resolving the issue.</t>
+          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
         </is>
       </c>
     </row>
@@ -3342,27 +3419,21 @@
  تقدم بطلبك الآن: emiratesnbd.com/ar/campaigns…</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Start your banking journey today with Emirates NBD.
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in Trip.com vouchers.
-Access benefits like:
-- AED 300 Trip.com voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 Trip.com voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: emiratesnbd.com/en/campaigns…
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من Trip.com بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة Trip.com بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة Trip.com بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: emiratesnbd.com/ar/campaigns…</t>
+          <t>Start your banking journey today with Emirates NBD.
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
         </is>
       </c>
     </row>
@@ -3455,16 +3526,8 @@
           <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/safakayani1/status/2049806132303258013</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>ENBD portal literally loads like you’re porting yourself to another universe 💫</t>
@@ -3564,19 +3627,11 @@
           <t>This carries strong intent, open to meaningful engagement 👑</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/apex_led/status/2049804951631900789</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This carries strong intent, open to meaningful engagement 👑</t>
+          <t>This carries strong intent, open to meaningful engagement 👑</t>
         </is>
       </c>
     </row>
@@ -3673,23 +3728,11 @@
           <t>تطبيق "تستاهل" يقدّرنا وتفاصيله تدلعنا، وبطاقة الخصم إماراتي فيزا سيغنتشر فعلًا تفتح أبواب لمكافآت وخدمات استثنائية، كفو بنك الإمارات دبي الوطني على هالدلال.</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/BaraaNabilUAE/status/2049804711268610244</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>للتفاصيل البسيطة في يومك وكل لحظة فيها
-حمّل تطبيق تستاهل لاكتشاف مكافآت حصرية باستخدام بطاقة الخصم إماراتي فيزا سيغنتشر الخاصة بك من بنك الإمارات دبي الوطني.
-https://t.co/S5JMIMnH7I https://t.co/hF7o7qZlTY</t>
-        </is>
-      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>للتفاصيل البسيطة في يومك وكل لحظة فيها
-حمّل تطبيق تستاهل لاكتشاف مكافآت حصرية باستخدام بطاقة الخصم إماراتي فيزا سيغنتشر الخاصة بك من بنك الإمارات دبي الوطني.
-https://t.co/S5JMIMnH7I https://t.co/hF7o7qZlTY</t>
+          <t>تطبيق "تستاهل" يقدّرنا وتفاصيله تدلعنا، وبطاقة الخصم إماراتي فيزا سيغنتشر فعلًا تفتح أبواب لمكافآت وخدمات استثنائية، كفو بنك الإمارات دبي الوطني على هالدلال.</t>
         </is>
       </c>
     </row>
@@ -3789,23 +3832,12 @@
 Learn More: emiratesnbd.com/en/promotion…</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
-        </is>
-      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates noon One Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/vPejTs1z6k https://t.co/SgAX32aKRG</t>
+          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on spends of AED 50 and above with your Emirates NBD card.
+Learn More: emiratesnbd.com/en/promotion…</t>
         </is>
       </c>
     </row>
@@ -3901,21 +3933,12 @@
 ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني.</t>
         </is>
       </c>
     </row>
@@ -4012,19 +4035,11 @@
           <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal reuters.com/sustainability/b…</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>https://x.com/ReutersAsia/status/2049798571990323555</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/I1NP5RZdeq</t>
-        </is>
-      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/I1NP5RZdeq</t>
+          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal reuters.com/sustainability/b…</t>
         </is>
       </c>
     </row>
@@ -4121,19 +4136,11 @@
           <t>This project gives strong confidence vibes 💪📊</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>https://x.com/T0m_Calls/status/2049797480003588407</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This project gives strong confidence vibes 💪📊</t>
-        </is>
-      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow This project gives strong confidence vibes 💪📊</t>
+          <t>This project gives strong confidence vibes 💪📊</t>
         </is>
       </c>
     </row>
@@ -4236,23 +4243,13 @@
 fintechnews.ae/31474/payment…</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://x.com/__racha/status/2049796434447503575</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>Visa appoints Emirates NBD for local UAE Dirham settlements. 
 The move allows domestic card transactions to clear locally in dirhams rather than routing through international settlement networks.
-https://t.co/aSnsVTOcjD</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>Visa appoints Emirates NBD for local UAE Dirham settlements. 
-The move allows domestic card transactions to clear locally in dirhams rather than routing through international settlement networks.
-https://t.co/aSnsVTOcjD</t>
+fintechnews.ae/31474/payment…</t>
         </is>
       </c>
     </row>
@@ -4352,21 +4349,12 @@
 #Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>https://x.com/ForumRemittance/status/2049796315736084692</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that blends regulated banking expertise with digital platform innovation across the MENA region.
-#MENA #UAE #Fintech #Banking #EmbeddedFinance #DigitalLending #Innovation #Partnership https://t.co/i4vg7CBB0B</t>
-        </is>
-      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Mashreq and Cashew deepen their collaboration to build an embedded lending framework that blends regulated banking expertise with digital platform innovation across the MENA region.
-#MENA #UAE #Fintech #Banking #EmbeddedFinance #DigitalLending #Innovation #Partnership https://t.co/i4vg7CBB0B</t>
+          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.
+#Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation</t>
         </is>
       </c>
     </row>
@@ -4481,66 +4469,9 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://x.com/infoblazeme/status/2049794079647826046</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year
-@DEWAofficial
-#Dubai #Utilities #Electricity
-#MiddleEast
-https://t.co/NGMV8s8zn6 https://t.co/KY6IAkc9f1</t>
-        </is>
-      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
-        <is>
-          <t>Dubai records the world’s lowest electricity customer minutes lost at just 49 seconds per year
-@DEWAofficial
-#Dubai #Utilities #Electricity
-#MiddleEast
-https://t.co/NGMV8s8zn6 https://t.co/KY6IAkc9f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2049793969677291575</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>letstalkdubai</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Let's Talk Dubai</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
 @RBLBank
@@ -4551,6 +4482,53 @@
 Via business-standard.com</t>
         </is>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2049793969677291575</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>letstalkdubai</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Let's Talk Dubai</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
+@RBLBank
+@EmiratesNBD_AE
+#India #Banking #Dubai
+#UAE #MiddleEast
+infoblaze.com/news/details/1…
+Via business-standard.com</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Sebi"&gt;#Sebi&lt;/a&gt; approves change of control at &lt;a href="/search?f=tweets&amp;amp;q=%23RBL_Bank"&gt;#RBL_Bank&lt;/a&gt; in &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; stake deal
@@ -4616,17 +4594,31 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
 @RBLBank
 @EmiratesNBD_AE
 #India #Banking #Dubai
 #UAE #MiddleEast
-infoblaze.com/news/details/1…
-Via business-standard.com</t>
+https://t.co/P8Ax5vNbhn
+Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
+@RBLBank
+@EmiratesNBD_AE
+#India #Banking #Dubai
+#UAE #MiddleEast
+https://t.co/P8Ax5vNbhn
+Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
         </is>
       </c>
     </row>
@@ -4741,17 +4733,31 @@
 Via business-standard.com</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://x.com/InfoblazeINDIA/status/2049793884012830907</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
 @RBLBank 
 @EmiratesNBD_AE 
 #India #Banking #Dubai
 #UAE #MiddleEast 
-infoblaze.com/news/details/1…
-Via business-standard.com</t>
+https://t.co/5caG5iFvBn
+Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
+@RBLBank 
+@EmiratesNBD_AE 
+#India #Banking #Dubai
+#UAE #MiddleEast 
+https://t.co/5caG5iFvBn
+Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
         </is>
       </c>
     </row>
@@ -4860,15 +4866,27 @@
 @Visa</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/ForsanUrdu/status/2049793228564480371</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
 #NNSS
 #UAE #Dubai #EmiratesNBD #NBD #Visa 
 @EmiratesNBD_AE
-@Visa</t>
+@Visa https://t.co/87utaLSJAb</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
+#NNSS
+#UAE #Dubai #EmiratesNBD #NBD #Visa 
+@EmiratesNBD_AE
+@Visa https://t.co/87utaLSJAb</t>
         </is>
       </c>
     </row>
@@ -4974,9 +4992,12 @@
 @Visa</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>https://x.com/UAE_Forsan/status/2049790865460154569</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement
 #UAE #Dubai #EmiratesNBD #NBD #Visa 
@@ -4984,6 +5005,14 @@
 @Visa</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement
+#UAE #Dubai #EmiratesNBD #NBD #Visa 
+@EmiratesNBD_AE 
+@Visa</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -5081,12 +5110,21 @@
 #EmiratesNBD #GCC #Banking #CapitalMarket</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://x.com/ForumRemittance/status/2049788923015012684</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
+#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
-#EmiratesNBD #GCC #Banking #CapitalMarket</t>
+#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6430,9 @@
 #RBLBank #Banking #Stocks #Breakout</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>https://x.com/TrendwithAvnash/status/2049759263707529446</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>• SEBI nod received for Emirates NBD deal
 • Major change of control incoming (big trigger)
@@ -6405,18 +6440,7 @@
 Stock already in strong uptrend
 Now consolidating near resistance zone
 Breakout + strong hands backing = interesting setup 🔥
-#RBLBank #Banking #Stocks #Breakout https://t.co/QAjBOhRXXT</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>• SEBI nod received for Emirates NBD deal
-• Major change of control incoming (big trigger)
-📊 Chart view:
-Stock already in strong uptrend
-Now consolidating near resistance zone
-Breakout + strong hands backing = interesting setup 🔥
-#RBLBank #Banking #Stocks #Breakout https://t.co/QAjBOhRXXT</t>
+#RBLBank #Banking #Stocks #Breakout</t>
         </is>
       </c>
     </row>
@@ -6519,25 +6543,13 @@
 Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
     </row>
@@ -6634,19 +6646,11 @@
           <t>@EmiratesNBD_AE only 1person in customer service and 1person in personal banking and 1person in teller counter. People are waiting for 30-40 minutes and still not getting the service. If not capable of providing timely service what is the purpose of opening new branches</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://x.com/Sumeesh_KV/status/2049757006312223207</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>@Sumeesh_KV Hi Sumeesh, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
-        </is>
-      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>@Sumeesh_KV Hi Sumeesh, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>@EmiratesNBD_AE only 1person in customer service and 1person in personal banking and 1person in teller counter. People are waiting for 30-40 minutes and still not getting the service. If not capable of providing timely service what is the purpose of opening new branches</t>
         </is>
       </c>
     </row>
@@ -6847,27 +6851,12 @@
 كم نسبة التمويل العقاري</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>https://x.com/Di6111690294628/status/2049754202373517793</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-السلام عليكم
-يعطيكم العافيه
-متى يتم تفعيل اضافة بطاقات بنك دبي الامارات في سامسونج باي في السعودية 
-وشكرا</t>
-        </is>
-      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-السلام عليكم
-يعطيكم العافيه
-متى يتم تفعيل اضافة بطاقات بنك دبي الامارات في سامسونج باي في السعودية 
-وشكرا</t>
+          <t>السلام عليكم 
+كم نسبة التمويل العقاري</t>
         </is>
       </c>
     </row>
@@ -6964,8 +6953,16 @@
           <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
@@ -7083,17 +7080,31 @@
 #التسوية_الصافية_الوطنية #الإمارات</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
         <is>
           <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
-fintechgate.net/ptyq | التفاصيل 
+https://t.co/GrqbX1n7wi | التفاصيل 
 @Visa
 @EmiratesNBD_AE
 #fintech_gate
 #فيزا #الإمارات_دبي_الوطني
-#التسوية_الصافية_الوطنية #الإمارات</t>
+#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
+https://t.co/GrqbX1n7wi | التفاصيل 
+@Visa
+@EmiratesNBD_AE
+#fintech_gate
+#فيزا #الإمارات_دبي_الوطني
+#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
         </is>
       </c>
     </row>
@@ -7202,9 +7213,12 @@
 #RBLBank #BankingSector #SEBI</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
         <is>
           <t>#RBLBank #Breaking
 ✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
@@ -7213,6 +7227,15 @@
 #RBLBank #BankingSector #SEBI</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>#RBLBank #Breaking
+✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
+✅ Key regulatory clearance received for proposed stake acquisition
+✅ Strengthens strategic partnership and capital position
+#RBLBank #BankingSector #SEBI</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -7313,8 +7336,18 @@
 #UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
+Issue is over three times oversubscribed, showing strong investor confidence.
+#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>Emirates NBD raises $750M in strong bond deal. 💵📈
@@ -7412,8 +7445,16 @@
           <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
@@ -8062,16 +8103,8 @@
           <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>https://x.com/jibinsymphony/status/2049728649910497496</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
-        </is>
-      </c>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
           <t>@OfficialADCB  dear team, i had submitted the no liability letter from ENBD. Still the fund is not credited in my account. Rent Cheque is deposited and the account is negative now. 0551746879 pls take immediate action</t>
@@ -8171,19 +8204,11 @@
           <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2049721813379522964</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
-        </is>
-      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance https://t.co/Q2me9NkKIX</t>
+          <t>Emirates NBD Reopens New GCC Debt Capital Markets Activity With Landmark USD AT1 Issuance blog.dubaicityguide.com/site…</t>
         </is>
       </c>
     </row>
@@ -8283,21 +8308,12 @@
 Read the full story: arabianbusiness.com/abnews/e…</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabianBusiness/status/2049720588764377543</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
         <is>
           <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>Emirates NBD has raised $750m (AED2.75bn) through an Additional Tier 1 (AT1) capital issuance, marking the first public debt capital markets deal by a GCC issuer since the Iran conflict started.
-Read the full story: https://t.co/0syC2PDlI7 https://t.co/Ox0c4flEhh</t>
+Read the full story: arabianbusiness.com/abnews/e…</t>
         </is>
       </c>
     </row>
@@ -8404,21 +8420,11 @@
 #EmiratesNBD</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>https://x.com/Emy191990/status/2049715289319723379</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
-        </is>
-      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
+          <t>Email : 2 
 #UnitedAgainstFraud
 #EmiratesNBD</t>
         </is>
@@ -8517,19 +8523,11 @@
           <t>Benefits of having borrowed money. Not earned</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>https://x.com/Ahmed_44714/status/2049712002503999763</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
-        </is>
-      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Hear it from our Digital Credit Card winners. Apply now and get exclusive rewards. https://t.co/jWiWe48LMi</t>
+          <t>Benefits of having borrowed money. Not earned</t>
         </is>
       </c>
     </row>
@@ -8629,12 +8627,12 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
         </is>
       </c>
     </row>
@@ -8731,19 +8729,11 @@
           <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>https://x.com/nishijaniani/status/2049697401896907011</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>@nishijaniani Hi Nishi, thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004802 in the subject line of the email.</t>
-        </is>
-      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>@nishijaniani Hi Nishi, thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004802 in the subject line of the email.</t>
+          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
         </is>
       </c>
     </row>
@@ -9176,12 +9166,21 @@
 A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>https://x.com/2n_ah/status/2049660884436533486</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Off-Plan Financing is Now a Reality in Dubai
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects</t>
+A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
         </is>
       </c>
     </row>
@@ -9278,8 +9277,16 @@
           <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
@@ -9379,11 +9386,19 @@
           <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>https://x.com/dcgguide/status/2049768124615143524</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes blog.uaetoday.com/emirates-i…</t>
+          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
         </is>
       </c>
     </row>
@@ -9501,18 +9516,29 @@
 #EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
+The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
+The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
+By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
+Read more: https://t.co/z8jtwV3U0M
+#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
-The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
-All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
-The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
-Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
-With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
-Read more: blocknewsint.com/articles/em…
-#EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
+          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
+The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
+The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
+By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
+Read more: https://t.co/z8jtwV3U0M
+#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
         </is>
       </c>
     </row>
@@ -9609,11 +9635,19 @@
           <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist</t>
+          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
         </is>
       </c>
     </row>
@@ -10277,23 +10311,13 @@
 ⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr">
         <is>
           <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
 EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.</t>
         </is>
       </c>
     </row>
@@ -10389,27 +10413,12 @@
 ⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049775767735722193</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
-        </is>
-      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>⭐️Shariah-compliant offering
-⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
-⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
-Terms and conditions apply.
-https://t.co/oqJQgZ2H6v</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.</t>
         </is>
       </c>
     </row>
@@ -10506,19 +10515,11 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049764863933649269</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
-        </is>
-      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
     </row>
@@ -10618,21 +10619,12 @@
 #الإمارات_الإسلامي</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049745576544084269</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr">
         <is>
           <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>رتّب التزاماتك حسب الأولوية وابدأ بالأصغر، ثم تقدّم تدريجياً نحو الأكبر، فليس عليك إنهاء كل شيء دفعة واحدة، الأهم أن تبدأ.
-#الإمارات_الإسلامي https://t.co/8zwjHWfzM3</t>
+#الإمارات_الإسلامي</t>
         </is>
       </c>
     </row>
@@ -10735,23 +10727,13 @@
 emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468619108404</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr">
         <is>
           <t>هل تنفق مقابل أمور لا تستخدمها؟
 #نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>هل تنفق مقابل أمور لا تستخدمها؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -911,17 +911,35 @@
 #Banking #NBFC #NSE</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
+84% over five years. 
+The solution is also fairly simple:- 
+You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
+Incase you need help with your portfolio, feel free to reach out to me.</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
+The test takes 30 seconds: 
+Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
+Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
+Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
+84% over five years. 
+The solution is also fairly simple:- 
+You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
+Incase you need help with your portfolio, feel free to reach out to me.</t>
         </is>
       </c>
     </row>
@@ -1257,25 +1275,14 @@
 tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/VOX_Cinemas_KSA/status/2050591142492651968</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
 تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
 للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd https://t.co/96UbGdATfB</t>
+tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
         </is>
       </c>
     </row>
@@ -1372,39 +1379,11 @@
           <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/moha60062/status/2050582653036888115</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>هذا ملف مقارنة بين أقوى ٤ بطاقات ائتمانية كاش باك حالياً في السعودية 🇸🇦💳:
-🔹 بطاقة الأهلي للاسترداد النقدي الفئة المميزة (@snbalahli)
-🔹 بطاقة الراجحي كاش باك بلس (@alrajhibank)
-🔹 بطاقة مزيد بنك الإمارات دبي الوطني (@EmiratesNBD_KSA)
-🔹 بطاقة لايف ستايل من الفرنسي (@BSF_sa)
-📊 جمعت لكم كل التفاصيل + مثال على كل بطاقة + أفضل بطاقة فعلياً حسب الاستخدام.
-📝 أضفت المزايا والسلبيات لكل بطاقة من وجهة نظري.
-تفضلوا الملف:
-https://t.co/wzDtkBVVZM
-وأعطوني أي اقتراحات أو ملاحظات 🙌🗨️
-💡 بالنسبة لبطاقة النايفات، جاري تجربتها، وبعطيكم العلم الأكيد بعد ما أجربها فعلياً وأشوف كل شيء عندهم 👍✨</t>
-        </is>
-      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>هذا ملف مقارنة بين أقوى ٤ بطاقات ائتمانية كاش باك حالياً في السعودية 🇸🇦💳:
-🔹 بطاقة الأهلي للاسترداد النقدي الفئة المميزة (@snbalahli)
-🔹 بطاقة الراجحي كاش باك بلس (@alrajhibank)
-🔹 بطاقة مزيد بنك الإمارات دبي الوطني (@EmiratesNBD_KSA)
-🔹 بطاقة لايف ستايل من الفرنسي (@BSF_sa)
-📊 جمعت لكم كل التفاصيل + مثال على كل بطاقة + أفضل بطاقة فعلياً حسب الاستخدام.
-📝 أضفت المزايا والسلبيات لكل بطاقة من وجهة نظري.
-تفضلوا الملف:
-https://t.co/wzDtkBVVZM
-وأعطوني أي اقتراحات أو ملاحظات 🙌🗨️
-💡 بالنسبة لبطاقة النايفات، جاري تجربتها، وبعطيكم العلم الأكيد بعد ما أجربها فعلياً وأشوف كل شيء عندهم 👍✨</t>
+          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
         </is>
       </c>
     </row>
@@ -1517,25 +1496,15 @@
 Central Bank of the UAE</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/centralbankuae/status/2050554134936600726</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
     </row>
@@ -1632,19 +1601,11 @@
           <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/NovoCinemas/status/2050546053124923502</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>🔥 Power. Politics. Survival… with an upgrade 🍿 Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. T&amp;amp;Cs apply. Watch at Novo Cinemas. Book now on our website or app. T&amp;amp;C's apply. https://t.co/jxjZGKejZi</t>
-        </is>
-      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>🔥 Power. Politics. Survival… with an upgrade 🍿 Book #Patriot tickets and get a FREE popcorn upsize (Regular to Large) with every ticket. Show your ticket at the counter. Valid May 1–6. T&amp;amp;Cs apply. Watch at Novo Cinemas. Book now on our website or app. T&amp;amp;C's apply. https://t.co/jxjZGKejZi</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
     </row>
@@ -1741,33 +1702,11 @@
           <t>Please update the promotions on the mobile banking app also.</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/adrianD36740715/status/2050530525820109288</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Embrace higher earnings with your salary transfer
- Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
- 1. Open a Millionaire Account, Current Account or Savings Account
- 2. Transfer your salary of AED 10,000 or more
- 3. Maintain an average monthly balance of AED 25,000 or more
- 4. Earn bonus interest with a credit card
- Terms and conditions apply
- https://t.co/u4ZGMVsftb</t>
-        </is>
-      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Embrace higher earnings with your salary transfer
- Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
- 1. Open a Millionaire Account, Current Account or Savings Account
- 2. Transfer your salary of AED 10,000 or more
- 3. Maintain an average monthly balance of AED 25,000 or more
- 4. Earn bonus interest with a credit card
- Terms and conditions apply
- https://t.co/u4ZGMVsftb</t>
+          <t>Please update the promotions on the mobile banking app also.</t>
         </is>
       </c>
     </row>
@@ -1909,9 +1848,12 @@
 #UAE</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>UAE controls banking sector of PK after bribing leaders 
 BANKS owned by UAE in PK(not complete list)
@@ -1928,7 +1870,27 @@
 11. BML
 #Islamabad
 #Pakistan 
-#UAE</t>
+#UAE https://t.co/hEotNuuvdl</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>UAE controls banking sector of PK after bribing leaders 
+BANKS owned by UAE in PK(not complete list)
+1. Alfalah 
+2. Dubai Islamic  
+3. Mashreq   
+4. Emirates NBD  
+5. Emirates Global 
+6. FirstWomen
+7. Al Baraka
+8. Ubank
+9. EasyPaisa
+10. Jazzcash
+11. BML
+#Islamabad
+#Pakistan 
+#UAE https://t.co/hEotNuuvdl</t>
         </is>
       </c>
     </row>
@@ -2021,11 +1983,19 @@
           <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
         </is>
       </c>
     </row>
@@ -2131,14 +2101,25 @@
 #uaefintech #visapayments #enbd</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
+Read more: https://t.co/zL56RMfxRn
+Follow @uaefintechvibes for daily fintech updates. 
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
+Read more: https://t.co/zL56RMfxRn
 Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
         </is>
       </c>
     </row>
@@ -2241,13 +2222,23 @@
 #ABCnews #Digital #Payment #Services</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+Read more on https://t.co/RPTuv9uD9h
+#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
         </is>
       </c>
     </row>
@@ -2359,16 +2350,29 @@
 Apply Now: emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
 🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
 🌟 Enjoy a FREE 1-year noon One membership
 🎁 Earn AED 500 welcome bonus
 Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+Apply Now: https://t.co/9cutEjf788</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
+🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
+🌟 Enjoy a FREE 1-year noon One membership
+🎁 Earn AED 500 welcome bonus
+Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
+Apply Now: https://t.co/9cutEjf788</t>
         </is>
       </c>
     </row>
@@ -2465,11 +2469,21 @@
           <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
         </is>
       </c>
     </row>
@@ -2566,11 +2580,33 @@
           <t>👍</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
     </row>
@@ -2671,11 +2707,25 @@
           <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
     </row>
@@ -2778,11 +2828,21 @@
 Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
 No one from your 'team' has reached out. I have no dues. 
 Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
@@ -2887,13 +2947,21 @@
 #SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Expats in KSA — your salary might qualify you for better financing options.
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
+          <t>Expats in KSA — your salary might qualify you for better financing options.
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
         </is>
       </c>
     </row>
@@ -2993,21 +3061,12 @@
 #dubai #emiratesislamic</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.
-#hiltonabudhabi https://t.co/HOnNG0kw9t</t>
-        </is>
-      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Located on Yas Bay Waterfront's three kilometer-long promenade, Hilton Abu Dhabi - Yas Island features 545 rooms and offers an exceptional array of culinary options across several dining venues. Guests enjoy access to Yas Island's exciting theme parks.
-#hiltonabudhabi https://t.co/HOnNG0kw9t</t>
+          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
+#dubai #emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -3103,21 +3162,12 @@
 From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably. https://t.co/Qugg6bzXoN</t>
+From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
         </is>
       </c>
     </row>
@@ -3214,16 +3264,8 @@
           <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
@@ -3329,23 +3371,13 @@
 emiratesislamic.ae/en/person…</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Tailor-made home financing solutions to ease the process of owning a home.
 Learn More
-https://t.co/9ZNjxE7BhS https://t.co/1SYIepscqy</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-https://t.co/9ZNjxE7BhS https://t.co/1SYIepscqy</t>
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA28"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,55 +566,43 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2050640575183962333</t>
+          <t>2051149273409143066</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Waleedels_</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>وليد</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912827800140013568/5UJC1UkQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>I have sent an email.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>I have sent an email.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -623,22 +611,22 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>['Jaw_02']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:16 PM UTC</t>
+          <t>May 4, 2026 · 3:57 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-02T18:16:00Z</t>
+          <t>2026-05-04T03:57:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -650,10 +638,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>808</v>
+        <v>2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -662,36 +650,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>🤔
-عندي بطاقات الراجحي (المرابحة والكاش باك)
-بطاقة مزيد — ENBD
-بطاقة انفينت المسافر — Bsf 
-بطاقة سيجنتشر تمكين بلس — البلاد 
-فماذا يميز بطاقات مصرف الانماء لو سمحت من تجربتك حيث استنفذت الحد بالكامل 
-⚠️ لا انصح طبعا بتعدد البطاقات لانها سلاح ذو حدين</t>
+          <t>I have sent an email.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/Waleedels_/status/2050640575183962333</t>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>عندك بطاقه ائتمانيه من مصرف الإنماء ؟
-اليوم تم إصدار كشف الحساب للبطاقات الائتمانيه .. 
-أهم نصيحتين :
-* سدد أجمالي المبلغ المستحق . ( احذر من سداد الحد الأدنى فقط )
-** سدد قبل تاريخ الاستحقاق 25 مايو 2026 . https://t.co/TtUyMKxK21</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
     </row>
@@ -701,43 +675,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2050638510642569502</t>
+          <t>2051134720344535096</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba</t>
+          <t>https://x.com/ClapPakistan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>homehustlerduba</t>
+          <t>ClapPakistan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>H&amp;H Real Estate</t>
+          <t>Clap</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1760746331201585152/TKyLTFah_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -747,21 +723,25 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:08 PM UTC</t>
+          <t>May 4, 2026 · 3:00 AM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-02T18:08:00Z</t>
+          <t>2026-05-04T03:00:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -772,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -781,22 +761,27 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD as its UAE settlement agent, enabling domestic card transactions to be processed locally in dirhams instead of through international systems. This shift is expected to deliver faster payment confirmations, more reliable everyday transactions and</t>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/homehustlerduba/status/2050638510642569502</t>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>UAE hotels are expected to resume hiring after ongoing refurbishments, but with a clear shift toward leaner, more efficient workforce models focused on multi-skilled and adaptable talent. Industry leaders say rehiring will prioritise quality over quantity, with teams designed to https://t.co/GK7z6Brnli</t>
+          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
+The image is AI-generated and is just for reference.
+#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
         </is>
       </c>
     </row>
@@ -806,55 +791,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050634843697152368</t>
+          <t>2051003496439427421</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19</t>
+          <t>https://x.com/KaharUmesh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VedantKabra19</t>
+          <t>KaharUmesh</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedant Kabra</t>
+          <t>Umesh R Kahar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042611377949544449/zCad3iJc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/962204603965214722/wZzbG0I__bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+gulfnews.com/uae/reader-comp…</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC&amp;#39;s total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India&amp;#39;s long term credit growth thesis.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBFC"&gt;#NBFC&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NSE"&gt;#NSE&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;
+Reference:
+&lt;a href="https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506"&gt;gulfnews.com/uae/reader-comp…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -869,31 +848,31 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 5:53 PM UTC</t>
+          <t>May 3, 2026 · 6:18 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-02T17:53:00Z</t>
+          <t>2026-05-03T18:18:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23NBFC', 'https://x.com/search?f=tweets&amp;q=%23NSE']</t>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/centralbankuae', 'https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506']</t>
         </is>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -902,44 +881,31 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>In the last 6-12 months:
-1. Emirates NBD Bank has acquired a controlling stake (54%) in RBL Bank
-2. IHC (International Holding Company, Abu Dhabi) has acquired a 41.5% stake in Sammaan Capital, with a mandatory open offer for an additional 26%, which could take IHC's total stake to ~63-67% on a fully diluted basis.
-3. Sumitomo Mitsui Banking Corporation (SMBC) bought a 24.2% stake in Yes Bank
-4. Mitsubishi UFJ Financial Group (MUFG) Bank acquired a 20% stake in Shriram Finance
-FIIs must be net sellers but select foreign institutions are clearly positioning to capitalise on India's long term credit growth thesis.
-#Banking #NBFC #NSE</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+gulfnews.com/uae/reader-comp…</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/VedantKabra19/status/2050634843697152368</t>
+          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>A great shortcut tool to analyse your mutual fund portfolio:- 
-The test takes 30 seconds: 
-Open your fund’s factsheet. If 60-70%+ of the portfolio is concentrated in the top 15-20 stocks by market cap (HDFC Bank, Reliance, TCS, ICICI, Infosys, SBI etc.) 
-Then you’re actively paying fees for what is effectively a Nifty 50 ETF. 
-Even despite such holdings, 76% of large cap funds have failed to beat the index over a 10 year period. 
-84% over five years. 
-The solution is also fairly simple:- 
-You can consider switching these to a low cost Nifty 50 ETF and pocket the TER expense. 
-Incase you need help with your portfolio, feel free to reach out to me.</t>
+          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
+After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
+Reference:
+https://t.co/BcgwdgmQQQ</t>
         </is>
       </c>
     </row>
@@ -949,51 +915,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050606238627496289</t>
+          <t>2050981352871264409</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/TrioMsPaname</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>TrioMsPaname</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>yiahhhh</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2043404881177006080/8Iry1NlJ_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -1003,23 +961,27 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 4:00 PM UTC</t>
+          <t>May 3, 2026 · 4:50 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-02T16:00:00Z</t>
+          <t>2026-05-03T16:50:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1028,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1037,30 +999,22 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Are you still paying for everything upfront?
-Enjoy 0% installments over 6 months or get 5% cashback with no limits when you pay your TMG Club fees whether renewing your membership, adding a new member or remove one with Emirates NBD Mastercard credit card x TMG.
-Together .. it pays off
-Terms and Conditions Apply.
-Tax registration number: 204-897-319</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2050606238627496289</t>
+          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>يفخر بنك الإمارات دبي الوطني بالمشاركة في سباق النيروفيرس في سيليا، العاصمة الإدارية الجديدة.
-نركض معًا لنشر الوعي حول التنوع العصبي بما يشمل التوحد، وفرط الحركة وتشتت الانتباه (ADHD)، وعسر القراءة (الديسلكسيا)، وغيرها من الاختلافات الذهنية لأن كل خطوة تقرّبنا من مجتمع أكثر شمولًا وتفهمًا وتمكينًا.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
         </is>
       </c>
     </row>
@@ -1070,43 +1024,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050596951385944148</t>
+          <t>2050976036028919856</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to</t>
+          <t>https://x.com/Nidhinkn</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>chin2to</t>
+          <t>Nidhinkn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chintn S. Padhya</t>
+          <t>Nidhin</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2006918638885060609/VLnYZV2k_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/862744582882308096/PYF7ziU7_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>No update from your team. No update from anyone from @EmiratesNBD_KSA 
+Now I will escalate it to @SAMA_GOV</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can&amp;#39;t even cancel the credit card. It isn&amp;#39;t rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>No update from your team. No update from anyone from &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+Now I will escalate it to &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1115,7 +1071,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1125,18 +1081,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 3:23 PM UTC</t>
+          <t>May 3, 2026 · 4:29 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-02T15:23:00Z</t>
+          <t>2026-05-03T16:29:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV']</t>
+        </is>
+      </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1154,22 +1114,23 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>This is such a nightmare. The entire experience has been a nightmare and nothing more. Every time I call you guys, you say 48 working hours and then nothing! I can't even cancel the credit card. It isn't rocket science. Just call me back and cancel the card. Simple.</t>
+          <t>No update from your team. No update from anyone from @EmiratesNBD_KSA 
+Now I will escalate it to @SAMA_GOV</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/chin2to/status/2050596951385944148</t>
+          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
     </row>
@@ -1179,88 +1140,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050591142492651968</t>
+          <t>2050948913431990505</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/VOX_Cinemas_KSA/status/2050591142492651968</t>
+          <t>https://x.com/ConmanNickJ/status/2050948913431990505</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/VOX_Cinemas_KSA</t>
+          <t>https://x.com/ConmanNickJ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VOX_Cinemas_KSA</t>
+          <t>ConmanNickJ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VOX Cinemas KSA ڤوكس سينما السعودية</t>
+          <t>conman Nick</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2049106132195815424/7BCTotN4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1945509816476094464/YIU-DVu4_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في &lt;a href="/search?f=tweets&amp;amp;q=%23ڤوكس_سينما"&gt;#ڤوكس_سينما&lt;/a&gt; 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['NarcisW63452', 'amjadt25']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 3:00 PM UTC</t>
+          <t>May 3, 2026 · 2:41 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-02T15:00:00Z</t>
+          <t>2026-05-03T14:41:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ڤوكس_سينما']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1944</v>
+        <v>8</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1269,20 +1224,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>عندك بطاقات بنك الإمارات دبي الوطني ؟ العرض من نصيبك 😎
-تذكرة عليك والثانية مجانًا في #ڤوكس_سينما 
-للحجز ولتفاصيل اكثر,  اضغط على الرابط 👇
-tps://ksa.voxcinemas.com/ar/ticket-offer/emirates-nbd</t>
+          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
         </is>
       </c>
     </row>
@@ -1292,43 +1241,43 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2050582653036888115</t>
+          <t>2050919285036360149</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/moha60062/status/2050582653036888115</t>
+          <t>https://x.com/Professor502/status/2050919285036360149</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/moha60062</t>
+          <t>https://x.com/Professor502</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>moha60062</t>
+          <t>Professor502</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🇸🇦MBS🇸🇦الجنرال</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1791484692413177856/gROHdxzJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1908889888478425088/ezst5JDu_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1337,22 +1286,22 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['Mohakhu', 'snbalahli', 'alrajhibank', 'EmiratesNBD_KSA', 'BSF_sa']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 2:26 PM UTC</t>
+          <t>May 3, 2026 · 12:43 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-02T14:26:00Z</t>
+          <t>2026-05-03T12:43:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1367,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1376,14 +1325,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>هل ممكن تضيف معها بطاقات انكان و النايفات خصوصاً انها تعطي بعض الفئات اعلى لايف ستايل</t>
+          <t>ردو على الخاص لو سمحت</t>
         </is>
       </c>
     </row>
@@ -1393,51 +1342,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2050554134936600726</t>
+          <t>2050908749720703120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2050554134936600726</t>
+          <t>https://x.com/abotameem430/status/2050908749720703120</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/abotameem430</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>abotameem430</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>Fahad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
-Best regards,
-Central Bank of the UAE</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1446,30 +1387,26 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['STKgenghis', 'EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:32 PM UTC</t>
+          <t>May 3, 2026 · 12:02 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-02T12:32:00Z</t>
+          <t>2026-05-03T12:02:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1477,10 +1414,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1489,22 +1426,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>ارغب بالاتصال</t>
         </is>
       </c>
     </row>
@@ -1514,43 +1443,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050546053124923502</t>
+          <t>2050881500527415748</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2050546053124923502</t>
+          <t>https://x.com/MahtabAbbasi11/status/2050881500527415748</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas</t>
+          <t>https://x.com/MahtabAbbasi11</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NovoCinemas</t>
+          <t>MahtabAbbasi11</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Novo Cinemas</t>
+          <t>Mahtab Abbasi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008888282768429056/a3q3GqDa_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042928635620081664/TSR-bQI9_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting &lt;a href="http://www.NovoCinemas.com"&gt;NovoCinemas.com&lt;/a&gt; or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1560,25 +1489,21 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:00 PM UTC</t>
+          <t>May 3, 2026 · 10:13 AM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-02T12:00:00Z</t>
+          <t>2026-05-03T10:13:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['http://www.NovoCinemas.com']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1589,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1598,14 +1523,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
         </is>
       </c>
     </row>
@@ -1615,73 +1540,75 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050530525820109288</t>
+          <t>2050877343745388916</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/adrianD36740715/status/2050530525820109288</t>
+          <t>https://x.com/t_Abdulraahman/status/2050877343745388916</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/adrianD36740715</t>
+          <t>https://x.com/t_Abdulraahman</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>adrianD36740715</t>
+          <t>t_Abdulraahman</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>adrian Dias</t>
+          <t>T.Abdulrahman</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1653777797888843776/NhAjroqA_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 10:59 AM UTC</t>
+          <t>May 3, 2026 · 9:57 AM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-02T10:59:00Z</t>
+          <t>2026-05-03T09:57:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1690,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1699,14 +1626,16 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Please update the promotions on the mobile banking app also.</t>
+          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
+و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
         </is>
       </c>
     </row>
@@ -1716,73 +1645,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050526894626427022</t>
+          <t>2050855805600092255</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144</t>
+          <t>https://x.com/gulf_news</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kashif111144</t>
+          <t>gulf_news</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kashif</t>
+          <t>Gulf News</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035721972361928704/W-51tE0S_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-&lt;a href="/search?f=tweets&amp;amp;q=%23Islamabad"&gt;#Islamabad&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23Pakistan"&gt;#Pakistan&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions &lt;a href="https://mrf.lu/FJY3"&gt;mrf.lu/FJY3&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1792,36 +1691,36 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 10:44 AM UTC</t>
+          <t>May 3, 2026 · 8:31 AM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-02T10:44:00Z</t>
+          <t>2026-05-03T08:31:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Islamabad', 'https://x.com/search?f=tweets&amp;q=%23Pakistan', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
+          <t>['https://mrf.lu/FJY3']</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V12" t="n">
-        <v>110</v>
+        <v>3733</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1830,67 +1729,26 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE</t>
+          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2050526894626427022</t>
+          <t>https://x.com/gulf_news/status/2050855805600092255</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>UAE controls banking sector of PK after bribing leaders 
-BANKS owned by UAE in PK(not complete list)
-1. Alfalah 
-2. Dubai Islamic  
-3. Mashreq   
-4. Emirates NBD  
-5. Emirates Global 
-6. FirstWomen
-7. Al Baraka
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad
-#Pakistan 
-#UAE https://t.co/hEotNuuvdl</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
         </is>
       </c>
     </row>
@@ -1900,43 +1758,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050510080127455613</t>
+          <t>2050845248088055847</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037</t>
+          <t>https://x.com/z6894890</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SavannahP57037</t>
+          <t>z6894890</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mohamed Farag</t>
+          <t>Femal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2050690957138595840/LXMOA3Q7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that&amp;#39;s how we do it at TMG with Emirates NBD✨</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1946,23 +1804,27 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 9:37 AM UTC</t>
+          <t>May 3, 2026 · 7:49 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-02T09:37:00Z</t>
+          <t>2026-05-03T07:49:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1971,7 +1833,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1980,22 +1842,22 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/SavannahP57037/status/2050510080127455613</t>
+          <t>https://x.com/z6894890/status/2050845248088055847</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨ https://t.co/bt4VAtCnZL</t>
+          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
         </is>
       </c>
     </row>
@@ -2005,49 +1867,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050500266760478726</t>
+          <t>2050841752987136094</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>uaefintechvibes</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UAE Fintechvibes</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2003525276207333376/SpeiZyat_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ fintechgate.net/rhb4  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>&lt;a href="/Visa" title="Visa"&gt;@Visa&lt;/a&gt;  has officially appointed &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  as its National Net Settlement Service (NNSS) agent.
-Read more: &lt;a href="https://uaefintechvibes.com/local-uae-dirham-settlements-visa-and-enbd/"&gt;uaefintechvibes.com/local-ua…&lt;/a&gt;
-Follow &lt;a href="/uaefintechvibes" title="UAE Fintechvibes"&gt;@uaefintechvibes&lt;/a&gt; for daily fintech updates. 
-&lt;a href="/search?f=tweets&amp;amp;q=%23uaefintech"&gt;#uaefintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23visapayments"&gt;#visapayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23enbd"&gt;#enbd&lt;/a&gt;</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ &lt;a href="https://fintechgate.net/rhb4"&gt;fintechgate.net/rhb4&lt;/a&gt;  | details 
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates_NBD_Egypt_Releases"&gt;#Emirates_NBD_Egypt_Releases&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -2057,23 +1919,23 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 8:58 AM UTC</t>
+          <t>May 3, 2026 · 7:35 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-02T08:58:00Z</t>
+          <t>2026-05-03T07:35:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['https://x.com/Visa', 'https://x.com/EmiratesNBD_AE', 'https://uaefintechvibes.com/local-uae-dirham-settlements-visa-and-enbd/', 'https://x.com/uaefintechvibes', 'https://x.com/search?f=tweets&amp;q=%23uaefintech', 'https://x.com/search?f=tweets&amp;q=%23visapayments', 'https://x.com/search?f=tweets&amp;q=%23enbd']</t>
+          <t>['https://fintechgate.net/rhb4', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23Emirates_NBD_Egypt_Releases']</t>
         </is>
       </c>
       <c r="S14" t="n">
@@ -2083,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2095,31 +1957,31 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: uaefintechvibes.com/local-ua…
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ fintechgate.net/rhb4  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050500266760478726</t>
+          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>@Visa  has officially appointed @EmiratesNBD_AE  as its National Net Settlement Service (NNSS) agent.
-Read more: https://t.co/zL56RMfxRn
-Follow @uaefintechvibes for daily fintech updates. 
-#uaefintech #visapayments #enbd https://t.co/8gN1xEE7BN</t>
+          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
+ https://t.co/zMJRGwIJEz  | details 
+#fintech_gate
+#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
         </is>
       </c>
     </row>
@@ -2129,86 +1991,82 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050470345820565788</t>
+          <t>2050809333848342901</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC</t>
+          <t>https://x.com/abotameem430</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ABCinGCC</t>
+          <t>abotameem430</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Arabian Business Community (ABC GCC)</t>
+          <t>Fahad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1782384725962653696/jF3qtc02_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+          <t>اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on &lt;a href="https://abc-gcc.net/News/1/395250"&gt;abc-gcc.net/News/1/395250&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23ABCnews"&gt;#ABCnews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Digital"&gt;#Digital&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Payment"&gt;#Payment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Services"&gt;#Services&lt;/a&gt;</t>
+          <t>اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 7:00 AM UTC</t>
+          <t>May 3, 2026 · 5:27 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-02T07:00:00Z</t>
+          <t>2026-05-03T05:27:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://abc-gcc.net/News/1/395250', 'https://x.com/search?f=tweets&amp;q=%23ABCnews', 'https://x.com/search?f=tweets&amp;q=%23Digital', 'https://x.com/search?f=tweets&amp;q=%23Payment', 'https://x.com/search?f=tweets&amp;q=%23Services']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2217,28 +2075,28 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on abc-gcc.net/News/1/395250
-#ABCnews #Digital #Payment #Services</t>
+          <t>اريد تمويل وارغب بالاتصال</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2050470345820565788</t>
+          <t>https://x.com/abotameem430/status/2050809333848342901</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Visa has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE.
-Read more on https://t.co/RPTuv9uD9h
-#ABCnews #Digital #Payment #Services https://t.co/Fs9eVfVeuP</t>
+          <t>Apply smarter, faster, and hassle-free.
+With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
+Watch how easy it is to get started.
+Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
         </is>
       </c>
     </row>
@@ -2248,53 +2106,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050456364728680817</t>
+          <t>2050807726507516194</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/uaefintechvibes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>uaefintechvibes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>UAE Fintechvibes</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2003525276207333376/SpeiZyat_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>UAE Fintech News this week
+@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
+#digitalpayments #uaefintech #proptech</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp;amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;amp;C Apply!
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>UAE Fintech News this week
+&lt;a href="/takeem_ai" title="Takeem.ai"&gt;@takeem_ai&lt;/a&gt; &lt;a href="/CashewPayments" title="Cashew"&gt;@CashewPayments&lt;/a&gt; &lt;a href="/shamssmc" title="Sharjah Media City"&gt;@shamssmc&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt; &lt;a href="/comfi_ai" title="Comfi"&gt;@comfi_ai&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23digitalpayments"&gt;#digitalpayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23uaefintech"&gt;#uaefintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23proptech"&gt;#proptech&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2304,36 +2156,36 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 6:04 AM UTC</t>
+          <t>May 3, 2026 · 5:20 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-02T06:04:00Z</t>
+          <t>2026-05-03T05:20:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+          <t>['https://x.com/takeem_ai', 'https://x.com/CashewPayments', 'https://x.com/shamssmc', 'https://x.com/EmiratesNBD_AE', 'https://x.com/MashreqTweets', 'https://x.com/OfficialADCB', 'https://x.com/comfi_ai', 'https://x.com/search?f=tweets&amp;q=%23digitalpayments', 'https://x.com/search?f=tweets&amp;q=%23uaefintech', 'https://x.com/search?f=tweets&amp;q=%23proptech']</t>
         </is>
       </c>
       <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
       <c r="U16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>1216</v>
+        <v>17</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2342,37 +2194,28 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: emiratesnbd.com/en/campaigns…</t>
+          <t>UAE Fintech News this week
+@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
+#digitalpayments #uaefintech #proptech</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050456364728680817</t>
+          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Shop, save, and earn with the Emirates NBD noon One Visa Credit Card
-🛍️ Get up to 20% back on noon, noon Food, noon minutes, Namshi &amp; more
-🌟 Enjoy a FREE 1-year noon One membership
-🎁 Earn AED 500 welcome bonus
-Apply now in just a few clicks and start enjoying exclusive benefits! T&amp;C Apply!
-Apply Now: https://t.co/9cutEjf788</t>
+          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
+Read more: https://t.co/VrIYgQm2sy
+#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
         </is>
       </c>
     </row>
@@ -2382,82 +2225,86 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050399772591399146</t>
+          <t>2050785564182392905</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Jami076152121</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jami076152121</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jami's Nest</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
+          <t>Whether you&amp;#39;re paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+&lt;a href="/search?f=tweets&amp;amp;q=%23transfers"&gt;#transfers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23payments"&gt;#payments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DirectRemit"&gt;#DirectRemit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Aani"&gt;#Aani&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23currencies"&gt;#currencies&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23travel"&gt;#travel&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalCash"&gt;#GlobalCash&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/foreign-exchange"&gt;emiratesnbd.com/en/foreign-e…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>['CaVivekkhatri']</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>May 3</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 2:19 AM UTC</t>
+          <t>May 3, 2026 · 3:52 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-02T02:19:00Z</t>
+          <t>2026-05-03T03:52:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23transfers', 'https://x.com/search?f=tweets&amp;q=%23payments', 'https://x.com/search?f=tweets&amp;q=%23DirectRemit', 'https://x.com/search?f=tweets&amp;q=%23Aani', 'https://x.com/search?f=tweets&amp;q=%23currencies', 'https://x.com/search?f=tweets&amp;q=%23travel', 'https://x.com/search?f=tweets&amp;q=%23GlobalCash', 'https://www.emiratesnbd.com/en/foreign-exchange']</t>
+        </is>
+      </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V17" t="n">
-        <v>21</v>
+        <v>1912</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2466,24 +2313,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Bandhan Bank and RBL Bank 👇
-Both are crap stock - Avoid for Investing 🎯</t>
-        </is>
-      </c>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Bandhan Bank and RBL Bank 👇
-Both are crap stock - Avoid for Investing 🎯</t>
+          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
+#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
+emiratesnbd.com/en/foreign-e…</t>
         </is>
       </c>
     </row>
@@ -2493,67 +2334,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050382263129620695</t>
+          <t>2050908234156744921</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
+          <t>https://x.com/emiratesislamic/status/2050908234156744921</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/Bushrasabih2</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bushrasabih2</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bu_shaikh🌸❤️</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>👍</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE', 'Bushrasabih1']</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 1:10 AM UTC</t>
+          <t>May 3, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-02T01:10:00Z</t>
+          <t>2026-05-03T12:00:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2565,48 +2404,28 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>👍</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Make Eid surprises even more valuable.
-From silver to gold, discover a smarter way to own or gift something truly precious.
-Watch this episode and tell us:
-How can you buy gold and silver from the bank?
-To participate:
-Follow Emirates NBD
-Tag 3 friends
-Drop your answer below for a chance to win AED 10,000</t>
-        </is>
-      </c>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Make Eid surprises even more valuable.
-From silver to gold, discover a smarter way to own or gift something truly precious.
-Watch this episode and tell us:
-How can you buy gold and silver from the bank?
-To participate:
-Follow Emirates NBD
-Tag 3 friends
-Drop your answer below for a chance to win AED 10,000</t>
+          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
+Download the EI + Mobile Banking App today.</t>
         </is>
       </c>
     </row>
@@ -2616,1083 +2435,98 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050374137852670288</t>
+          <t>2050908231610863903</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+          <t>https://x.com/emiratesislamic/status/2050908231610863903</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>May 2</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 2, 2026 · 12:37 AM UTC</t>
+          <t>May 3, 2026 · 12:00 PM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-02T00:37:00Z</t>
+          <t>2026-05-03T12:00:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>['https://x.com/centralbankuae']</t>
-        </is>
-      </c>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2050373118900977885</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>STKgenghis</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>khana-b-dosh</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your &amp;#39;team&amp;#39; has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>May 2</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 12:33 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-05-02T00:33:00Z</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>10</v>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
-No one from your 'team' has reached out. I have no dues. 
-Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2050364684251893892</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/yasmeenalja</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yasmeenalja</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Yasmeen Aljadah</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2042291734583877632/pJUn80Vi_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-&lt;a href="/search?f=tweets&amp;amp;q=%23SaudiArabia"&gt;#SaudiArabia&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ExpatsInKSA"&gt;#ExpatsInKSA&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Financing"&gt;#Financing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PersonalFinance"&gt;#PersonalFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23KSAJobs"&gt;#KSAJobs&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>May 2</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 12:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-05-02T00:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23SaudiArabia', 'https://x.com/search?f=tweets&amp;q=%23ExpatsInKSA', 'https://x.com/search?f=tweets&amp;q=%23Financing', 'https://x.com/search?f=tweets&amp;q=%23PersonalFinance', 'https://x.com/search?f=tweets&amp;q=%23KSAJobs']</t>
-        </is>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>143</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
-Emirates NBD – Dammam Branch | Financial Consultant
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>Expats in KSA — your salary might qualify you for better financing options.
-#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs https://t.co/CJ5MydF5fu</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2050477438539297270</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/patelumarjiarif/status/2050477438539297270</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/patelumarjiarif</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>patelumarjiarif</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Arif Patel - Preston Trading in UK</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1650401956072943616/wfZaFWCV_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23emiratesislamic"&gt;#emiratesislamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 7:28 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-05-02T07:28:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>28</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Emirates Islamic, announce the launch of a Shari’ah-compliant digital investment solution in gold and silver, seamlessly integrated into the bank’s EI + Mobile Banking App. The new offering is a first-of-its-kind by an Islamic bank in the UAE.
-#dubai #emiratesislamic</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2050455246686527975</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455246686527975</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-05-02T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>77</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Did You Know Emirates Islamic offers fully Shariah-compliant Corporate Finance solutions?
-From Working Capital to Structured Finance, Emirates Islamic provides tailored Islamic finance offerings designed to help businesses grow sustainably.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2050424878524940571</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>praksoni</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>prakash soni</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@EmiratesIslamic&lt;/a&gt; You claim an AED 22k theft is &amp;#34;secure&amp;#34; just because it’s Apple Wallet? Your system failed to see that a UAE &amp;#34;Darb&amp;#34; enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 3:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-05-02T03:59:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>14</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2050485448754004332</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485448754004332</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-05-02T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>59</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Tailor-made home financing solutions to ease the process of owning a home.
-Learn More
-emiratesislamic.ae/en/person…</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2050485444593246460</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050485444593246460</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-&lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=home_finance"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2026-05-02T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/personal-banking/finance/home-finance-solutions?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=home_finance']</t>
-        </is>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>70</v>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>حلول للتمويل السكني مصممة خصيصاً لتتيح لك امتلاك منزلك في منتهى الراحة.
-اطلع على المزيد
-emiratesislamic.ae/ar/person…</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2050455250096541870</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050455250096541870</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: &lt;a href="http://emiratesislamic.ae/en/corporate-and-institutional-banking"&gt;emiratesislamic.ae/en/corpor…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2026-05-02T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['http://emiratesislamic.ae/en/corporate-and-institutional-banking']</t>
-        </is>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>63</v>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Financing that aligns with both values and vision.
-Learn more: emiratesislamic.ae/en/corpor…</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2050448328266063924</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2050448328266063924</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>['AnkitMittal1403']</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>May 2, 2026 · 5:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2026-05-02T05:32:00Z</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>2</v>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,43 +566,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>patilabhijeet45</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>abhijeet patil</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>I have sent an email.</t>
+          <t>Update. 
+Received email from your social medium team saying "Dear,
+Kindly note that the account is not active."
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I have sent an email.</t>
+          <t>Update. 
+Received email from your social medium team saying &amp;#34;Dear,
+Kindly note that the account is not active.&amp;#34;
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -616,17 +622,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 3:57 AM UTC</t>
+          <t>May 5, 2026 · 1:33 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-04T03:57:00Z</t>
+          <t>2026-05-05T01:33:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -641,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -650,22 +656,31 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>I have sent an email.</t>
+          <t>Update. 
+Received email from your social medium team saying "Dear,
+Kindly note that the account is not active."
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
     </row>
@@ -675,73 +690,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan</t>
+          <t>https://x.com/Muhamma38929354</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ClapPakistan</t>
+          <t>Muhamma38929354</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Clap</t>
+          <t>Muhammad Usman</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1983485239554097152/bfvpy8sg_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
+          <t>On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
+          <t>On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 3:00 AM UTC</t>
+          <t>May 4, 2026 · 8:19 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-04T03:00:00Z</t>
+          <t>2026-05-04T20:19:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -752,7 +765,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -761,27 +774,24 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
+          <t>On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
     </row>
@@ -791,75 +801,73 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KaharUmesh</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Umesh R Kahar</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/962204603965214722/wZzbG0I__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-gulfnews.com/uae/reader-comp…</t>
+          <t>Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt;
-Reference:
-&lt;a href="https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506"&gt;gulfnews.com/uae/reader-comp…&lt;/a&gt;</t>
+          <t>Dear &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 6:18 PM UTC</t>
+          <t>May 4, 2026 · 6:38 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-03T18:18:00Z</t>
+          <t>2026-05-04T18:38:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/centralbankuae', 'https://gulfnews.com/uae/reader-complaints/uae-unwanted-cash-advance-fee-of-dh99-for-purchasing-crypto-currency-online-1.1672390194506']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S4" t="n">
@@ -872,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -881,31 +889,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-gulfnews.com/uae/reader-comp…</t>
+          <t>Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-https://t.co/BcgwdgmQQQ</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-https://t.co/BcgwdgmQQQ</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
     </row>
@@ -915,71 +914,71 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TrioMsPaname</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yiahhhh</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2043404881177006080/8Iry1NlJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>ماجاني شي على الخاص</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+          <t>ماجاني شي على الخاص</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 4:50 PM UTC</t>
+          <t>May 4, 2026 · 6:11 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-03T16:50:00Z</t>
+          <t>2026-05-04T18:11:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -990,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -999,22 +998,26 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>ماجاني شي على الخاص</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
     </row>
@@ -1024,45 +1027,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051355715994878347</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nidhinkn</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nidhin</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/862744582882308096/PYF7ziU7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>No update from your team. No update from anyone from @EmiratesNBD_KSA 
-Now I will escalate it to @SAMA_GOV</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No update from your team. No update from anyone from &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
-Now I will escalate it to &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt;</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1076,27 +1077,23 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 4:29 PM UTC</t>
+          <t>May 4, 2026 · 5:38 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-03T16:29:00Z</t>
+          <t>2026-05-04T17:38:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV']</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1105,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1114,23 +1111,14 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>No update from your team. No update from anyone from @EmiratesNBD_KSA 
-Now I will escalate it to @SAMA_GOV</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
-        </is>
-      </c>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
+          <t>متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
     </row>
@@ -1140,82 +1128,88 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050948913431990505</t>
+          <t>2051335593389601255</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/ConmanNickJ/status/2050948913431990505</t>
+          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/ConmanNickJ</t>
+          <t>https://x.com/InformistMedia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ConmanNickJ</t>
+          <t>InformistMedia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>conman Nick</t>
+          <t>Informist Media</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1945509816476094464/YIU-DVu4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1845064843897827333/CfVeov1j_bigger.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of &amp;#34;certain&amp;#34; shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+&lt;a href="/search?f=tweets&amp;amp;q=%23SEBI"&gt;#SEBI&lt;/a&gt;
+Details Here:
+&lt;a href="https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition"&gt;informistmedia.com/MoneyWire…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>['NarcisW63452', 'amjadt25']</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 2:41 PM UTC</t>
+          <t>May 4, 2026 · 4:18 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-03T14:41:00Z</t>
+          <t>2026-05-04T16:18:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23SEBI', 'https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1224,14 +1218,20 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Yet the IRGC have been laundering billions through both the central bank and ENBD among other financial institutions in the UAE</t>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+informistmedia.com/MoneyWire…</t>
         </is>
       </c>
     </row>
@@ -1241,71 +1241,71 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2050919285036360149</t>
+          <t>2051310789596754286</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/Professor502/status/2050919285036360149</t>
+          <t>https://x.com/RedHat/status/2051310789596754286</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/Professor502</t>
+          <t>https://x.com/RedHat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Professor502</t>
+          <t>RedHat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1908889888478425088/ezst5JDu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1123557710191001600/oMQc_xqN_bigger.png</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>2026 Innovation Awards winner &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: &lt;a href="https://red.ht/4ukH5l4"&gt;red.ht/4ukH5l4&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RHSummit"&gt;#RHSummit&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:43 PM UTC</t>
+          <t>May 4, 2026 · 2:39 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-03T12:43:00Z</t>
+          <t>2026-05-04T14:39:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://red.ht/4ukH5l4', 'https://x.com/search?f=tweets&amp;q=%23RHSummit']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1325,14 +1325,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>ردو على الخاص لو سمحت</t>
+          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
     </row>
@@ -1342,71 +1342,75 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2050908749720703120</t>
+          <t>2051298992416272612</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050908749720703120</t>
+          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430</t>
+          <t>https://x.com/FreshGulfJob</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>abotameem430</t>
+          <t>FreshGulfJob</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fahad</t>
+          <t>Fresh Gulf Job</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1487393053300064256/dEfLlKtr_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&amp;gt;&amp;gt; &lt;a href="https://buff.ly/7izZwL2"&gt;buff.ly/7izZwL2&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23jobs"&gt;#jobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23careers"&gt;#careers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy"&gt;#jobvacancy&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobs2026"&gt;#jobs2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23hiring"&gt;#hiring&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23freshgulfjob"&gt;#freshgulfjob&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23recruitment"&gt;#recruitment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy2026"&gt;#jobvacancy2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEJobs"&gt;#UAEJobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23dubaijobs"&gt;#dubaijobs&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:02 PM UTC</t>
+          <t>May 4, 2026 · 1:52 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-03T12:02:00Z</t>
+          <t>2026-05-04T13:52:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['https://buff.ly/7izZwL2', 'https://x.com/search?f=tweets&amp;q=%23jobs', 'https://x.com/search?f=tweets&amp;q=%23careers', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy', 'https://x.com/search?f=tweets&amp;q=%23jobs2026', 'https://x.com/search?f=tweets&amp;q=%23hiring', 'https://x.com/search?f=tweets&amp;q=%23freshgulfjob', 'https://x.com/search?f=tweets&amp;q=%23recruitment', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy2026', 'https://x.com/search?f=tweets&amp;q=%23UAEJobs', 'https://x.com/search?f=tweets&amp;q=%23dubaijobs']</t>
+        </is>
+      </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1414,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1426,14 +1430,18 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>ارغب بالاتصال</t>
+          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
+Apply Link&gt;&gt; buff.ly/7izZwL2
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
     </row>
@@ -1443,43 +1451,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2050881500527415748</t>
+          <t>2051294193515917659</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/MahtabAbbasi11/status/2050881500527415748</t>
+          <t>https://x.com/deegrose/status/2051294193515917659</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/MahtabAbbasi11</t>
+          <t>https://x.com/deegrose</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MahtabAbbasi11</t>
+          <t>deegrose</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mahtab Abbasi</t>
+          <t>DeeG (Maria)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042928635620081664/TSR-bQI9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property &lt;a href="https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1489,21 +1497,25 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 10:13 AM UTC</t>
+          <t>May 4, 2026 · 1:33 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-03T10:13:00Z</t>
+          <t>2026-05-04T13:33:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -1514,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1523,14 +1535,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
     </row>
@@ -1540,84 +1552,96 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2050877343745388916</t>
+          <t>2051288211184332916</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/t_Abdulraahman/status/2050877343745388916</t>
+          <t>https://x.com/hisho25/status/2051288211184332916</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/t_Abdulraahman</t>
+          <t>https://x.com/hisho25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>t_Abdulraahman</t>
+          <t>hisho25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>T.Abdulrahman</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1653777797888843776/NhAjroqA_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+&lt;a href="/MobilyPay" title="Mobily Pay"&gt;@MobilyPay&lt;/a&gt; 
+&lt;a href="/visionbank_sa" title="بنك فيجن"&gt;@visionbank_sa&lt;/a&gt;
+&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>['karimmohnaguib1', 'FinTech_KSA']</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 9:57 AM UTC</t>
+          <t>May 4, 2026 · 1:09 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-03T09:57:00Z</t>
+          <t>2026-05-04T13:09:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/MobilyPay', 'https://x.com/visionbank_sa', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/FABConnects']</t>
         </is>
       </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>848</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1626,16 +1650,24 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE طلبت بطاقة مزيد بحد مالي محدد 
-و وصلتني البطاقه بحد مالي عالي جداً ! كيف ممكن اقلل الحد اقدر او لا لاني مافعلت الى الان</t>
+          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
+يعني باقي هذولي للاسف
+@MobilyPay 
+@visionbank_sa
+@EmiratesNBD_KSA 
+@FABConnects</t>
         </is>
       </c>
     </row>
@@ -1645,82 +1677,90 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051287062402540010</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news</t>
+          <t>https://x.com/BabyIamInJail</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>gulf_news</t>
+          <t>BabyIamInJail</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulf News</t>
+          <t>حوا🍎</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2044041782519050242/muvl0wJC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1931562837521911809/dqyeDv4z_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions &lt;a href="https://mrf.lu/FJY3"&gt;mrf.lu/FJY3&lt;/a&gt;</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>['bokonndarro']</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 8:31 AM UTC</t>
+          <t>May 4, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-03T08:31:00Z</t>
+          <t>2026-05-04T13:05:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>['https://mrf.lu/FJY3']</t>
-        </is>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>3733</v>
+        <v>75</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1729,26 +1769,28 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions mrf.lu/FJY3</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
         </is>
       </c>
     </row>
@@ -1758,71 +1800,73 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050845248088055847</t>
+          <t>2051283691821834411</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890</t>
+          <t>https://x.com/bokonndarro</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>z6894890</t>
+          <t>bokonndarro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Femal</t>
+          <t>Foroogh 🇮🇷</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2035505557650702336/C0i2amSB_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>['BabyIamInJail']</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 7:49 AM UTC</t>
+          <t>May 4, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-03T07:49:00Z</t>
+          <t>2026-05-04T12:51:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
         <v>1</v>
       </c>
@@ -1830,10 +1874,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>672</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1842,22 +1886,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
         </is>
       </c>
     </row>
@@ -1867,79 +1912,73 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050841752987136094</t>
+          <t>2051273429328814571</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1</t>
+          <t>https://x.com/saudabdullah08</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FintechGate1</t>
+          <t>saudabdullah08</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
+          <t>الفنان سعود عبدالله</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1826788073360793600/_RR9Ujem_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- fintechgate.net/rhb4  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases</t>
+          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- &lt;a href="https://fintechgate.net/rhb4"&gt;fintechgate.net/rhb4&lt;/a&gt;  | details 
-&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates_NBD_Egypt_Releases"&gt;#Emirates_NBD_Egypt_Releases&lt;/a&gt;</t>
+          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 7:35 AM UTC</t>
+          <t>May 4, 2026 · 12:11 PM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-03T07:35:00Z</t>
+          <t>2026-05-04T12:11:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://fintechgate.net/rhb4', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23Emirates_NBD_Egypt_Releases']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -1948,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1957,31 +1996,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- fintechgate.net/rhb4  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases</t>
+          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
         </is>
       </c>
     </row>
@@ -1991,43 +2021,43 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051261292133130490</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430</t>
+          <t>https://x.com/anwarquadri7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>abotameem430</t>
+          <t>anwarquadri7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fahad</t>
+          <t>Anwar Quadri</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780850701616242688/Ikq26ySl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1831450890525351936/CY5M68Bm_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>اريد تمويل وارغب بالاتصال</t>
+          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>اريد تمويل وارغب بالاتصال</t>
+          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven&amp;#39;t received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -2036,22 +2066,22 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['anwarquadri7', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 5:27 AM UTC</t>
+          <t>May 4, 2026 · 11:22 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-03T05:27:00Z</t>
+          <t>2026-05-04T11:22:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -2066,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2075,28 +2105,24 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>اريد تمويل وارغب بالاتصال</t>
+          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
         </is>
       </c>
     </row>
@@ -2106,47 +2132,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050807726507516194</t>
+          <t>2051239150909866122</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes</t>
+          <t>https://x.com/abhiseksonusonu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>uaefintechvibes</t>
+          <t>abhiseksonusonu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UAE Fintechvibes</t>
+          <t>A R mishra</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2003525276207333376/SpeiZyat_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>UAE Fintech News this week
-@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
-#digitalpayments #uaefintech #proptech</t>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>UAE Fintech News this week
-&lt;a href="/takeem_ai" title="Takeem.ai"&gt;@takeem_ai&lt;/a&gt; &lt;a href="/CashewPayments" title="Cashew"&gt;@CashewPayments&lt;/a&gt; &lt;a href="/shamssmc" title="Sharjah Media City"&gt;@shamssmc&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt; &lt;a href="/comfi_ai" title="Comfi"&gt;@comfi_ai&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23digitalpayments"&gt;#digitalpayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23uaefintech"&gt;#uaefintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23proptech"&gt;#proptech&lt;/a&gt;</t>
+          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2156,36 +2178,36 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 5:20 AM UTC</t>
+          <t>May 4, 2026 · 9:54 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-03T05:20:00Z</t>
+          <t>2026-05-04T09:54:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/takeem_ai', 'https://x.com/CashewPayments', 'https://x.com/shamssmc', 'https://x.com/EmiratesNBD_AE', 'https://x.com/MashreqTweets', 'https://x.com/OfficialADCB', 'https://x.com/comfi_ai', 'https://x.com/search?f=tweets&amp;q=%23digitalpayments', 'https://x.com/search?f=tweets&amp;q=%23uaefintech', 'https://x.com/search?f=tweets&amp;q=%23proptech']</t>
+          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2194,28 +2216,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>UAE Fintech News this week
-@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
-#digitalpayments #uaefintech #proptech</t>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
-Read more: https://t.co/VrIYgQm2sy
-#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
-Read more: https://t.co/VrIYgQm2sy
-#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
     </row>
@@ -2225,47 +2241,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2051214248865656992</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
+          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/FF1991Whooo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>FF1991Whooo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Flavours Footprints</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1481297572363108353/g_PbK1D6_bigger.png</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-emiratesnbd.com/en/foreign-e…</t>
+          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Whether you&amp;#39;re paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-&lt;a href="/search?f=tweets&amp;amp;q=%23transfers"&gt;#transfers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23payments"&gt;#payments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DirectRemit"&gt;#DirectRemit&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Aani"&gt;#Aani&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23currencies"&gt;#currencies&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23travel"&gt;#travel&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GlobalCash"&gt;#GlobalCash&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/foreign-exchange"&gt;emiratesnbd.com/en/foreign-e…&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2275,36 +2289,36 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>May 3</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 3:52 AM UTC</t>
+          <t>May 4, 2026 · 8:16 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-03T03:52:00Z</t>
+          <t>2026-05-04T08:16:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23transfers', 'https://x.com/search?f=tweets&amp;q=%23payments', 'https://x.com/search?f=tweets&amp;q=%23DirectRemit', 'https://x.com/search?f=tweets&amp;q=%23Aani', 'https://x.com/search?f=tweets&amp;q=%23currencies', 'https://x.com/search?f=tweets&amp;q=%23travel', 'https://x.com/search?f=tweets&amp;q=%23GlobalCash', 'https://www.emiratesnbd.com/en/foreign-exchange']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1912</v>
+        <v>3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2313,18 +2327,16 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-emiratesnbd.com/en/foreign-e…</t>
+          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-emiratesnbd.com/en/foreign-e…</t>
+          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
+I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
         </is>
       </c>
     </row>
@@ -2334,45 +2346,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050908234156744921</t>
+          <t>2051210220634820985</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050908234156744921</t>
+          <t>https://x.com/DeloitteME/status/2051210220634820985</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/DeloitteME</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>DeloitteME</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Deloitte Middle East</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/742984436661276673/2NW6eZiW_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>The future of finance is shaped by complex regulations.
+In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
+#Banking #FinancialServices</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp;amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>The future of finance is shaped by complex regulations.
+In our recent session with &lt;a href="/emirates" title="Emirates"&gt;@Emirates&lt;/a&gt; NBD, we discussed evolving &lt;a href="/search?f=tweets&amp;amp;q=%23risk"&gt;#risk&lt;/a&gt;, &lt;a href="/search?f=tweets&amp;amp;q=%23IFRS"&gt;#IFRS&lt;/a&gt;, &lt;a href="/search?f=tweets&amp;amp;q=%23tax"&gt;#tax&lt;/a&gt; &amp;amp; the vital role of culture in driving innovation amid change.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialServices"&gt;#FinancialServices&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2382,21 +2396,25 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:00 PM UTC</t>
+          <t>May 4, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-03T12:00:00Z</t>
+          <t>2026-05-04T08:00:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/emirates', 'https://x.com/search?f=tweets&amp;q=%23risk', 'https://x.com/search?f=tweets&amp;q=%23IFRS', 'https://x.com/search?f=tweets&amp;q=%23tax', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialServices']</t>
+        </is>
+      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
@@ -2404,28 +2422,30 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>The future of finance is shaped by complex regulations.
+In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
+#Banking #FinancialServices</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Open a Digital Wealth Account instantly to enjoy a complete suite of Shariah-compliant global investments. Get access to International &amp; UAE stocks as well as Global Mutual Funds.
-Download the EI + Mobile Banking App today.</t>
+          <t>The future of finance is shaped by complex regulations.
+In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
+#Banking #FinancialServices</t>
         </is>
       </c>
     </row>
@@ -2435,45 +2455,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050908231610863903</t>
+          <t>2051194736661381477</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2050908231610863903</t>
+          <t>https://x.com/hill_lilli40424/status/2051194736661381477</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/hill_lilli40424</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>hill_lilli40424</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Mohamed Farag</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2051194248054341632/6o7ujA15_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب &amp;#34;الثروات الرقمية&amp;#34; على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Style, comfort, and cashback… that&amp;#39;s how we do it at TMG with Emirates NBD✨</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2483,50 +2501,2649 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 3, 2026 · 12:00 PM UTC</t>
+          <t>May 4, 2026 · 6:58 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-03T12:00:00Z</t>
+          <t>2026-05-04T06:58:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
-قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك.</t>
+          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2051192927792300267</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2051192927792300267</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>centralbankuae</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Dear Consumer,
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Dear Consumer,
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['STKgenghis', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://sanadak.gov.ae/en']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>20</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Dear Consumer,
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Dear Consumer,
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2051188760185049183</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/mahmoudmoawad00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>mahmoudmoawad00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mahmoud Moawad</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1667049706462097408/EbaYvJZ9_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>After the update, I can&amp;#39;t approve any transactions. The app always shows &amp;#34;something went wrong&amp;#34; on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:34 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:34:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>20</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2051171796552937744</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
+Apply Now and get up to 100,000 bonus Skyward Miles!
+Terms and Conditions Apply!
+Apply Now: emiratesnbd.com/en/cards/cre…</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
+Apply Now and get up to 100,000 bonus Skyward Miles!
+Terms and Conditions Apply!
+Apply Now: &lt;a href="https://www.emiratesnbd.com/en/cards/credit-cards/skywards-infinite-credit-card"&gt;emiratesnbd.com/en/cards/cre…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 5:27 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-05-04T05:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/cards/credit-cards/skywards-infinite-credit-card']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>11</v>
+      </c>
+      <c r="V22" t="n">
+        <v>743</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
+Apply Now and get up to 100,000 bonus Skyward Miles!
+Terms and Conditions Apply!
+Apply Now: emiratesnbd.com/en/cards/cre…</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
+Apply Now and get up to 100,000 bonus Skyward Miles!
+Terms and Conditions Apply!
+Apply Now: emiratesnbd.com/en/cards/cre…</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2051149273409143066</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>patilabhijeet45</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>abhijeet patil</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>I have sent an email.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I have sent an email.</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 3:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-05-04T03:57:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>I have sent an email.</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>I have sent an email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2051134720344535096</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/ClapPakistan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ClapPakistan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Clap</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 3:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-05-04T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>25</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
+#ClapPakistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2051337981815140447</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/praksoni/status/2051337981815140447</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/praksoni</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>praksoni</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>prakash soni</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>I did not get any message. Following your page.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>I did not get any message. Following your page.</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>10h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 4:27 PM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-05-04T16:27:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>I did not get any message. Following your page.</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>I did not get any message. Following your page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2051285723785871469</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp;amp; FX advisor, preferential pricing on products,</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2026-05-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>108</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2051255518270779594</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. #EmiratesIslamic
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions/digital-wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2026-05-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions/digital-wealth']</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>43</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. #EmiratesIslamic
+emiratesislamic.ae/en/Person…</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. #EmiratesIslamic
+https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. #EmiratesIslamic
+https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2026-05-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>76</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 May 2026.
+Terms &amp; Conditions apply.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 May 2026.
+Terms &amp;amp; Conditions apply.</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>40</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 May 2026.
+Terms &amp; Conditions apply.</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2051180027576750215</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180027576750215</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>56</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
+Learn more:
+emiratesislamic.ae/en/busine…</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
+Learn more:
+&lt;a href="https://www.emiratesislamic.ae/en/business-banking/diamond?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_diamond"&gt;emiratesislamic.ae/en/busine…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2026-05-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/business-banking/diamond?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_diamond']</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>62</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
+Learn more:
+emiratesislamic.ae/en/busine…</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2051285720577269980</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285720577269980</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
+لمعرفة المزيد:
+emiratesislamic.ae/ar/busine…</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
+لمعرفة المزيد:
+&lt;a href="https://www.emiratesislamic.ae/ar/business-banking/diamond?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_diamond"&gt;emiratesislamic.ae/ar/busine…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2026-05-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/business-banking/diamond?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_diamond']</t>
+        </is>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>51</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
+لمعرفة المزيد:
+emiratesislamic.ae/ar/busine…</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
+لمعرفة المزيد:
+emiratesislamic.ae/ar/busine…</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285716965986342</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+        </is>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 1:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2026-05-04T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>254</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2051255517989797926</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/digital-wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2026-05-04T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/digital-wealth']</t>
+        </is>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>41</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+emiratesislamic.ae/ar/Person…</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+https://t.co/mxT5J6OSOM https://t.co/v6MSR7Y6S1</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+https://t.co/mxT5J6OSOM https://t.co/v6MSR7Y6S1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2051210228520063073</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210228520063073</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary airport transfers, meet &amp; greet services
+⛳ Golf rounds at select premium courses
+🅿️ Valet parking, and much more
+Valid till 31 May 2026
+Terms and conditions apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
+⛳ Golf rounds at select premium courses
+🅿️ Valet parking, and much more
+Valid till 31 May 2026
+Terms and conditions apply
+&lt;a href="https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-05-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>46</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary airport transfers, meet &amp; greet services
+⛳ Golf rounds at select premium courses
+🅿️ Valet parking, and much more
+Valid till 31 May 2026
+Terms and conditions apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary airport transfers, meet &amp; greet services
+⛳ Golf rounds at select premium courses
+🅿️ Valet parking, and much more
+Valid till 31 May 2026
+Terms and conditions apply
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2051210223440871854</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210223440871854</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-05-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>43</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-05-04T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
+      </c>
+      <c r="V37" t="n">
+        <v>153</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>['Thefatim2']</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:52:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>3</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:06:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>81</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>28</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-05-04T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
+      </c>
+      <c r="V41" t="n">
+        <v>73</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2051173237304734081</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051173237304734081</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>['praksoni']</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 5:33 AM UTC</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-05-04T05:33:00Z</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>14</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2051168317407207640</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>['AnkitMittal1403']</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>May 4, 2026 · 5:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-05-04T05:13:00Z</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>10</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1224,14 +1224,25 @@
 informistmedia.com/MoneyWire…</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
 #SEBI
 Details Here:
-informistmedia.com/MoneyWire…</t>
+https://t.co/2oKxA92wg7</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
+#SEBI
+Details Here:
+https://t.co/2oKxA92wg7</t>
         </is>
       </c>
     </row>
@@ -1328,11 +1339,19 @@
           <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>https://x.com/RedHat/status/2051310789596754286</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>The 20th annual #RHSummit Innovation Awards winners show how open technology drives significant impact. Now it's your turn to weigh in: read the blog and vote for your favorite story for Innovator of the Year. https://t.co/fSmY2mFJdm ⬇️ #RHSummit https://t.co/dhsoHd3xYR</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
+          <t>The 20th annual #RHSummit Innovation Awards winners show how open technology drives significant impact. Now it's your turn to weigh in: read the blog and vote for your favorite story for Innovator of the Year. https://t.co/fSmY2mFJdm ⬇️ #RHSummit https://t.co/dhsoHd3xYR</t>
         </is>
       </c>
     </row>
@@ -1435,13 +1454,23 @@
 #jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>ENOC Jobs in Dubai - Emirates National Oil Company Hiring Now
+Apply Link&amp;gt;&amp;gt; https://t.co/nrviL7vzo9
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #oilandgas #jobsinuae #dubaijobs</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
-Apply Link&gt;&gt; buff.ly/7izZwL2
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
+          <t>ENOC Jobs in Dubai - Emirates National Oil Company Hiring Now
+Apply Link&amp;gt;&amp;gt; https://t.co/nrviL7vzo9
+#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #oilandgas #jobsinuae #dubaijobs</t>
         </is>
       </c>
     </row>
@@ -1538,11 +1567,19 @@
           <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://x.com/deegrose/status/2051294193515917659</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>ADIB, Emirates NBD close $164mln loan for London property https://t.co/OFhbni8HWp</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
+          <t>ADIB, Emirates NBD close $164mln loan for London property https://t.co/OFhbni8HWp</t>
         </is>
       </c>
     </row>
@@ -1658,16 +1695,25 @@
 @FABConnects</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051288211184332916</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>FINALLY 🔥🔥💙
+محفظة سامسونج صارت تدعم كل المحافظ الرقمية و البنوك تقريباً و كلها تدعم اضافة البطاقة في داخل التطبيق بضغطة زر 
+Add to Samsung Wallet 👌🏼✅️
+لكن للاسف حتى الآن البنوك الرقمية و المحافظ الرقمية الى الان مايدعمون إضافة الاموال عن طريق الدفع بسامسونج باي ❌️💔 https://t.co/hqlpvr8CYN</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
-يعني باقي هذولي للاسف
-@MobilyPay 
-@visionbank_sa
-@EmiratesNBD_KSA 
-@FABConnects</t>
+          <t>FINALLY 🔥🔥💙
+محفظة سامسونج صارت تدعم كل المحافظ الرقمية و البنوك تقريباً و كلها تدعم اضافة البطاقة في داخل التطبيق بضغطة زر 
+Add to Samsung Wallet 👌🏼✅️
+لكن للاسف حتى الآن البنوك الرقمية و المحافظ الرقمية الى الان مايدعمون إضافة الاموال عن طريق الدفع بسامسونج باي ❌️💔 https://t.co/hqlpvr8CYN</t>
         </is>
       </c>
     </row>
@@ -1776,21 +1822,15 @@
 تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
-متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
-        </is>
-      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
-متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
+          <t>عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
         </is>
       </c>
     </row>
@@ -1890,19 +1930,12 @@
 ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
-        </is>
-      </c>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
+          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
         </is>
       </c>
     </row>
@@ -1999,19 +2032,11 @@
           <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
         </is>
       </c>
     </row>
@@ -2108,21 +2133,11 @@
           <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA Dear Emirates NBD,
-I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dear Emirates NBD,
-I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
         </is>
       </c>
     </row>
@@ -2219,16 +2234,8 @@
           <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
-        </is>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
@@ -2870,14 +2877,25 @@
 Apply Now: emiratesnbd.com/en/cards/cre…</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
 Apply Now and get up to 100,000 bonus Skyward Miles!
 Terms and Conditions Apply!
-Apply Now: emiratesnbd.com/en/cards/cre…</t>
+Apply Now: https://t.co/TKre1mTLQs</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
+Apply Now and get up to 100,000 bonus Skyward Miles!
+Terms and Conditions Apply!
+Apply Now: https://t.co/TKre1mTLQs</t>
         </is>
       </c>
     </row>
@@ -3180,11 +3198,19 @@
           <t>I did not get any message. Following your page.</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/praksoni/status/2051337981815140447</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>I did not get any message. Following your page.</t>
+          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
         </is>
       </c>
     </row>
@@ -3277,11 +3303,19 @@
           <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3425,16 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. #EmiratesIslamic
-https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. #EmiratesIslamic
-https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
         </is>
       </c>
     </row>
@@ -3506,16 +3540,22 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+https://t.co/pVA5yvt1qT</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+https://t.co/pVA5yvt1qT</t>
         </is>
       </c>
     </row>
@@ -3832,19 +3872,13 @@
 emiratesislamic.ae/en/busine…</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
-        </is>
-      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
+Learn more:
+emiratesislamic.ae/en/busine…</t>
         </is>
       </c>
     </row>
@@ -4153,23 +4187,13 @@
 emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
 قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-https://t.co/mxT5J6OSOM https://t.co/v6MSR7Y6S1</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-https://t.co/mxT5J6OSOM https://t.co/v6MSR7Y6S1</t>
+emiratesislamic.ae/ar/Person…</t>
         </is>
       </c>
     </row>
@@ -4721,21 +4745,12 @@
 Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
         </is>
       </c>
     </row>
@@ -5139,11 +5154,25 @@
           <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
+Regards,
+Ankit K Mittal
++54 702 3869 https://t.co/av2G1Lek3Q</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
+          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
+Regards,
+Ankit K Mittal
++54 702 3869 https://t.co/av2G1Lek3Q</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA43"/>
+  <dimension ref="A1:AA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,88 +566,100 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/samial7arbi02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>samial7arbi02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>سامي الحربي</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Update. 
-Received email from your social medium team saying "Dear,
-Kindly note that the account is not active."
-No name. My account is active. Not sure what this cryptic email meant.</t>
+          <t>@EmiratesNBD_KSA 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Update. 
-Received email from your social medium team saying &amp;#34;Dear,
-Kindly note that the account is not active.&amp;#34;
-No name. My account is active. Not sure what this cryptic email meant.</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; إلى &amp;#34;قائمة سوداء وهمية&amp;#34; لا وجود لها في سجلات سمة ولا في &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى &lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+&lt;a href="/AlinmaBank" title="Alinma Fan"&gt;@AlinmaBank&lt;/a&gt; &lt;a href="/alrajhibank" title="مصرف الراجحي"&gt;@alrajhibank&lt;/a&gt; &lt;a href="/SNB_AlAhli" title="MY"&gt;@SNB_AlAhli&lt;/a&gt; &lt;a href="/RiyadBank" title="بنك الرياض"&gt;@RiyadBank&lt;/a&gt; &lt;a href="/BankAlbilad" title="بنك البلاد | Bank Albilad"&gt;@BankAlbilad&lt;/a&gt; &lt;a href="/BankAlJazira" title="بنك الجزيرة"&gt;@BankAlJazira&lt;/a&gt; &lt;a href="/anb_bank" title="البنك العربي الوطني - anb"&gt;@anb_bank&lt;/a&gt; &lt;a href="/D360bank" title="D360 Bank"&gt;@D360bank&lt;/a&gt; &lt;a href="/stcbank_ksa" title="STC Bank"&gt;@stcbank_ksa&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 5, 2026 · 1:33 AM UTC</t>
+          <t>May 7, 2026 · 8:08 PM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-05T01:33:00Z</t>
+          <t>2026-05-07T20:08:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV', 'https://x.com/SAMAcares', 'https://x.com/AlinmaBank', 'https://x.com/alrajhibank', 'https://x.com/SNB_AlAhli', 'https://x.com/RiyadBank', 'https://x.com/BankAlbilad', 'https://x.com/BankAlJazira', 'https://x.com/anb_bank', 'https://x.com/D360bank', 'https://x.com/stcbank_ksa']</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>29648</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -656,31 +668,49 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Update. 
-Received email from your social medium team saying "Dear,
-Kindly note that the account is not active."
-No name. My account is active. Not sure what this cryptic email meant.</t>
+          <t>@EmiratesNBD_KSA 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>@EmiratesNBD_KSA 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>@EmiratesNBD_KSA 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
     </row>
@@ -690,71 +720,71 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2052462422221627597</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354</t>
+          <t>https://x.com/kinsofdubai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muhamma38929354</t>
+          <t>kinsofdubai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Muhammad Usman</t>
+          <t>Kinshuk Kulshreshtha</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1983485239554097152/bfvpy8sg_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/997096320384028673/0D2-ksme_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>On which date of the month is the draw held?</t>
+          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>On which date of the month is the draw held?</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 8:19 PM UTC</t>
+          <t>May 7, 2026 · 6:55 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-04T20:19:00Z</t>
+          <t>2026-05-07T18:55:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
@@ -765,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -774,24 +804,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>On which date of the month is the draw held?</t>
+          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Millionaire account limited-time offer
-Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
+          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Millionaire account limited-time offer
-Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
+          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
     </row>
@@ -801,67 +829,63 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052461879398937044</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45</t>
+          <t>https://x.com/heba_hashem</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>patilabhijeet45</t>
+          <t>heba_hashem</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>abhijeet patil</t>
+          <t>Heba Hashem Ⓥ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1736630398384238593/Y_oo1i7E_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
+          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Dear &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  thank you very much for your assistance, really appreciate 🙏.</t>
+          <t>I&amp;#39;m an ENBD customer urgently trying to reach &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  as I&amp;#39;m unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 6:38 PM UTC</t>
+          <t>May 7, 2026 · 6:53 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-04T18:38:00Z</t>
+          <t>2026-05-07T18:53:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -877,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -889,22 +913,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
+          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
     </row>
@@ -914,43 +938,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25</t>
+          <t>https://x.com/illliyas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hisho25</t>
+          <t>illliyas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Illiyas Mohammed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ماجاني شي على الخاص</t>
+          <t>Still waiting for the solution. Not happy with the service.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ماجاني شي على الخاص</t>
+          <t>Still waiting for the solution. Not happy with the service.</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -959,22 +983,22 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 6:11 PM UTC</t>
+          <t>May 7, 2026 · 4:26 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-04T18:11:00Z</t>
+          <t>2026-05-07T16:26:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -989,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -998,26 +1022,26 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>ماجاني شي على الخاص</t>
+          <t>Still waiting for the solution. Not happy with the service.</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>لا تشيل هم الفاتورة 🤩
-مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
-للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>لا تشيل هم الفاتورة 🤩
-مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
-للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
         </is>
       </c>
     </row>
@@ -1027,43 +1051,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2051355715994878347</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051355715994878347</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25</t>
+          <t>https://x.com/RakshtVaghasiya</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hisho25</t>
+          <t>RakshtVaghasiya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Rakshit Vaghasiya</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متى بتدعمون سامسونج باي؟؟</t>
+          <t>Same reply every time. No action yet.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>متى بتدعمون سامسونج باي؟؟</t>
+          <t>Same reply every time. No action yet.</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -1077,17 +1101,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 5:38 PM UTC</t>
+          <t>May 7, 2026 · 3:37 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-04T17:38:00Z</t>
+          <t>2026-05-07T15:37:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1102,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1111,14 +1135,24 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>متى بتدعمون سامسونج باي؟؟</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+          <t>Same reply every time. No action yet.</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>متى بتدعمون سامسونج باي؟؟</t>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
     </row>
@@ -1128,88 +1162,82 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2051335593389601255</t>
+          <t>2052393142469439783</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
+          <t>https://x.com/samial7arbi02/status/2052393142469439783</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia</t>
+          <t>https://x.com/samial7arbi02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>InformistMedia</t>
+          <t>samial7arbi02</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Informist Media</t>
+          <t>سامي الحربي</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1845064843897827333/CfVeov1j_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-#SEBI
-Details Here:
-informistmedia.com/MoneyWire…</t>
+          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of &amp;#34;certain&amp;#34; shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-&lt;a href="/search?f=tweets&amp;amp;q=%23SEBI"&gt;#SEBI&lt;/a&gt;
-Details Here:
-&lt;a href="https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition"&gt;informistmedia.com/MoneyWire…&lt;/a&gt;</t>
+          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
         </is>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 4:18 PM UTC</t>
+          <t>May 7, 2026 · 2:20 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-04T16:18:00Z</t>
+          <t>2026-05-07T14:20:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23SEBI', 'https://informistmedia.com/MoneyWire/49753/Ongoing-acquisition-SEBI-OKs-change-in-control-of-RBL-Bank-amid-Emirates-NBD-s-stake-acquisition']</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>448</v>
+        <v>50</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1218,31 +1246,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-#SEBI
-Details Here:
-informistmedia.com/MoneyWire…</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-#SEBI
-Details Here:
-https://t.co/2oKxA92wg7</t>
-        </is>
-      </c>
+          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-#SEBI
-Details Here:
-https://t.co/2oKxA92wg7</t>
+          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
         </is>
       </c>
     </row>
@@ -1252,43 +1263,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2051310789596754286</t>
+          <t>2052392394302029845</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat/status/2051310789596754286</t>
+          <t>https://x.com/Ma60934Max/status/2052392394302029845</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat</t>
+          <t>https://x.com/Ma60934Max</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RedHat</t>
+          <t>Ma60934Max</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Max Blackton</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1123557710191001600/oMQc_xqN_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1753968627823288320/luOtw3AO_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
+          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
+Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026 Innovation Awards winner &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: &lt;a href="https://red.ht/4ukH5l4"&gt;red.ht/4ukH5l4&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RHSummit"&gt;#RHSummit&lt;/a&gt;</t>
+          <t>&lt;a href="https://yasislandabudhabi.pxf.io/c/2925765/3711431/26868"&gt;yasislandabudhabi.pxf.io/c/2…&lt;/a&gt; Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
+Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1298,23 +1311,23 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 2:39 PM UTC</t>
+          <t>May 7, 2026 · 2:17 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-04T14:39:00Z</t>
+          <t>2026-05-07T14:17:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://red.ht/4ukH5l4', 'https://x.com/search?f=tweets&amp;q=%23RHSummit']</t>
+          <t>['https://yasislandabudhabi.pxf.io/c/2925765/3711431/26868']</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -1327,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>191</v>
+        <v>6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1336,22 +1349,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: red.ht/4ukH5l4 #RHSummit</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://x.com/RedHat/status/2051310789596754286</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>The 20th annual #RHSummit Innovation Awards winners show how open technology drives significant impact. Now it's your turn to weigh in: read the blog and vote for your favorite story for Innovator of the Year. https://t.co/fSmY2mFJdm ⬇️ #RHSummit https://t.co/dhsoHd3xYR</t>
-        </is>
-      </c>
+          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
+Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>The 20th annual #RHSummit Innovation Awards winners show how open technology drives significant impact. Now it's your turn to weigh in: read the blog and vote for your favorite story for Innovator of the Year. https://t.co/fSmY2mFJdm ⬇️ #RHSummit https://t.co/dhsoHd3xYR</t>
+          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
+Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
         </is>
       </c>
     </row>
@@ -1361,75 +1368,71 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2051298992416272612</t>
+          <t>2052391222535471314</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
+          <t>https://x.com/bellyandabs/status/2052391222535471314</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob</t>
+          <t>https://x.com/bellyandabs</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FreshGulfJob</t>
+          <t>bellyandabs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fresh Gulf Job</t>
+          <t>AmeyK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1487393053300064256/dEfLlKtr_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1398588092391378953/EGqmD5zS_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
-Apply Link&gt;&gt; buff.ly/7izZwL2
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
+          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
-Apply Link&amp;gt;&amp;gt; &lt;a href="https://buff.ly/7izZwL2"&gt;buff.ly/7izZwL2&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23jobs"&gt;#jobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23careers"&gt;#careers&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy"&gt;#jobvacancy&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobs2026"&gt;#jobs2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23hiring"&gt;#hiring&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23freshgulfjob"&gt;#freshgulfjob&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23recruitment"&gt;#recruitment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23jobvacancy2026"&gt;#jobvacancy2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEJobs"&gt;#UAEJobs&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23dubaijobs"&gt;#dubaijobs&lt;/a&gt;</t>
+          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
         </is>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>['abhirammodak']</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:52 PM UTC</t>
+          <t>May 7, 2026 · 2:12 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-04T13:52:00Z</t>
+          <t>2026-05-07T14:12:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>['https://buff.ly/7izZwL2', 'https://x.com/search?f=tweets&amp;q=%23jobs', 'https://x.com/search?f=tweets&amp;q=%23careers', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy', 'https://x.com/search?f=tweets&amp;q=%23jobs2026', 'https://x.com/search?f=tweets&amp;q=%23hiring', 'https://x.com/search?f=tweets&amp;q=%23freshgulfjob', 'https://x.com/search?f=tweets&amp;q=%23recruitment', 'https://x.com/search?f=tweets&amp;q=%23jobvacancy2026', 'https://x.com/search?f=tweets&amp;q=%23UAEJobs', 'https://x.com/search?f=tweets&amp;q=%23dubaijobs']</t>
-        </is>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
         <v>0</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1449,28 +1452,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
-Apply Link&gt;&gt; buff.ly/7izZwL2
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>ENOC Jobs in Dubai - Emirates National Oil Company Hiring Now
-Apply Link&amp;gt;&amp;gt; https://t.co/nrviL7vzo9
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #oilandgas #jobsinuae #dubaijobs</t>
-        </is>
-      </c>
+          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>ENOC Jobs in Dubai - Emirates National Oil Company Hiring Now
-Apply Link&amp;gt;&amp;gt; https://t.co/nrviL7vzo9
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #oilandgas #jobsinuae #dubaijobs</t>
+          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
         </is>
       </c>
     </row>
@@ -1480,43 +1469,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2051294193515917659</t>
+          <t>2052380876919452146</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2051294193515917659</t>
+          <t>https://x.com/TadawulFeed/status/2052380876919452146</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose</t>
+          <t>https://x.com/TadawulFeed</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>deegrose</t>
+          <t>TadawulFeed</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DeeG (Maria)</t>
+          <t>Tadawul News</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2049879312543657984/hKTDD9K__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1428258699437563913/kvAW5pPQ_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
+          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
+saudiexchange.sa/wps/portal/…</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property &lt;a href="https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
+          <t>Mohammed Hadi Al Rasheed &amp;amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
+&lt;a href="https://www.saudiexchange.sa/wps/portal/saudiexchange/newsandreports/issuer-news/issuer-announcements/issuer-announcements-details/?anId=95094&amp;amp;anCat=1&amp;amp;cs=9601&amp;amp;locale=en"&gt;saudiexchange.sa/wps/portal/…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1526,23 +1517,23 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:33 PM UTC</t>
+          <t>May 7, 2026 · 1:31 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-04T13:33:00Z</t>
+          <t>2026-05-07T13:31:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['https://www.zawya.com/en/capital-markets/loans/adib-emirates-nbd-close-164mln-loan-for-london-property-n8gjsfqa']</t>
+          <t>['https://www.saudiexchange.sa/wps/portal/saudiexchange/newsandreports/issuer-news/issuer-announcements/issuer-announcements-details/?anId=95094&amp;anCat=1&amp;cs=9601&amp;locale=en']</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1552,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>6645</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1564,22 +1555,16 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property zawya.com/en/capital-markets…</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://x.com/deegrose/status/2051294193515917659</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property https://t.co/OFhbni8HWp</t>
-        </is>
-      </c>
+          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
+saudiexchange.sa/wps/portal/…</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property https://t.co/OFhbni8HWp</t>
+          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
+saudiexchange.sa/wps/portal/…</t>
         </is>
       </c>
     </row>
@@ -1589,53 +1574,43 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2051288211184332916</t>
+          <t>2052380397837926546</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
+          <t>https://x.com/iamjkp_/status/2052380397837926546</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25</t>
+          <t>https://x.com/iamjkp_</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>hisho25</t>
+          <t>iamjkp_</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>JamshidKP</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1609939487995346951/jwOMR5WV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1948467186663600128/kxAShTck_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
-يعني باقي هذولي للاسف
-@MobilyPay 
-@visionbank_sa
-@EmiratesNBD_KSA 
-@FABConnects</t>
+          <t>After a month delay the response was negative.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
-يعني باقي هذولي للاسف
-&lt;a href="/MobilyPay" title="Mobily Pay"&gt;@MobilyPay&lt;/a&gt; 
-&lt;a href="/visionbank_sa" title="بنك فيجن"&gt;@visionbank_sa&lt;/a&gt;
-&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt;</t>
+          <t>After a month delay the response was negative.</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1644,41 +1619,37 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>['karimmohnaguib1', 'FinTech_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:09 PM UTC</t>
+          <t>May 7, 2026 · 1:29 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-04T13:09:00Z</t>
+          <t>2026-05-07T13:29:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>['https://x.com/MobilyPay', 'https://x.com/visionbank_sa', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/FABConnects']</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>848</v>
+        <v>6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1687,33 +1658,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
-يعني باقي هذولي للاسف
-@MobilyPay 
-@visionbank_sa
-@EmiratesNBD_KSA 
-@FABConnects</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>FINALLY 🔥🔥💙
-محفظة سامسونج صارت تدعم كل المحافظ الرقمية و البنوك تقريباً و كلها تدعم اضافة البطاقة في داخل التطبيق بضغطة زر 
-Add to Samsung Wallet 👌🏼✅️
-لكن للاسف حتى الآن البنوك الرقمية و المحافظ الرقمية الى الان مايدعمون إضافة الاموال عن طريق الدفع بسامسونج باي ❌️💔 https://t.co/hqlpvr8CYN</t>
-        </is>
-      </c>
+          <t>After a month delay the response was negative.</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>FINALLY 🔥🔥💙
-محفظة سامسونج صارت تدعم كل المحافظ الرقمية و البنوك تقريباً و كلها تدعم اضافة البطاقة في داخل التطبيق بضغطة زر 
-Add to Samsung Wallet 👌🏼✅️
-لكن للاسف حتى الآن البنوك الرقمية و المحافظ الرقمية الى الان مايدعمون إضافة الاموال عن طريق الدفع بسامسونج باي ❌️💔 https://t.co/hqlpvr8CYN</t>
+          <t>After a month delay the response was negative.</t>
         </is>
       </c>
     </row>
@@ -1723,51 +1675,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2051287062402540010</t>
+          <t>2052375265490456666</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/BabyIamInJail</t>
+          <t>https://x.com/lhyx16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BabyIamInJail</t>
+          <t>lhyx16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>حوا🍎</t>
+          <t>Salaam</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1931562837521911809/dqyeDv4z_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1979858975735652352/1EXbxJlB_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>عه چی؟
-امروز دقیقا ENBD بودم
-ازم قبض آب از تورنتو می خواست!
-راهی داره اطلاعات مالیاتی ازم نگیرند؟
-تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
+          <t>Emirates NBD in Dubai also has this option.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>عه چی؟
-امروز دقیقا ENBD بودم
-ازم قبض آب از تورنتو می خواست!
-راهی داره اطلاعات مالیاتی ازم نگیرند؟
-تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
+          <t>Emirates NBD in Dubai also has this option.</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1776,28 +1720,28 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['bokonndarro']</t>
+          <t>['Kathleen_Tyson_', 'ProfSteveKeen']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:05 PM UTC</t>
+          <t>May 7, 2026 · 1:09 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-04T13:05:00Z</t>
+          <t>2026-05-07T13:09:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1806,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1815,22 +1759,32 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>عه چی؟
-امروز دقیقا ENBD بودم
-ازم قبض آب از تورنتو می خواست!
-راهی داره اطلاعات مالیاتی ازم نگیرند؟
-تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
+          <t>Emirates NBD in Dubai also has this option.</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3 accounting errors that most China analysts keep making.
+One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
+Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
+Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
+The full conversation is in the comments.
+#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>عه چی؟
-امروز دقیقا ENBD بودم
-ازم قبض آب از تورنتو می خواست!
-راهی داره اطلاعات مالیاتی ازم نگیرند؟
-تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
+          <t>3 accounting errors that most China analysts keep making.
+One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
+Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
+Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
+The full conversation is in the comments.
+#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
         </is>
       </c>
     </row>
@@ -1840,84 +1794,90 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2051283691821834411</t>
+          <t>2052336714459250884</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/bokonndarro</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>bokonndarro</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Foroogh 🇮🇷</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035505557650702336/C0i2amSB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
-ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+fintechgate.net/wq61 | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
-ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+&lt;a href="https://fintechgate.net/wq61"&gt;fintechgate.net/wq61&lt;/a&gt; | التفاصيل 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23برنامج_لشهادات_الإيداع"&gt;#برنامج_لشهادات_الإيداع&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الشريعة_الإسلامية"&gt;#الشريعة_الإسلامية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>['BabyIamInJail']</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 12:51 PM UTC</t>
+          <t>May 7, 2026 · 10:36 AM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-04T12:51:00Z</t>
+          <t>2026-05-07T10:36:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['https://fintechgate.net/wq61', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23برنامج_لشهادات_الإيداع', 'https://x.com/search?f=tweets&amp;q=%23الشريعة_الإسلامية', 'https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>672</v>
+        <v>4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1926,16 +1886,34 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
-ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+fintechgate.net/wq61 | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+https://t.co/LRj8F5RmtL | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
-ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+https://t.co/LRj8F5RmtL | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
         </is>
       </c>
     </row>
@@ -1945,73 +1923,83 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2051273429328814571</t>
+          <t>2052316568441229765</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/saudabdullah08</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>saudabdullah08</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>الفنان سعود عبدالله</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1826788073360793600/_RR9Ujem_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
+          <t>Unravel new destinations with fabulous offers
+Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
+The offer is valid until 30 May 2026.
+T&amp;Cs apply.
+#UnravelwithEmiratesNBD
+#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
+          <t>Unravel new destinations with fabulous offers
+Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
+The offer is valid until 30 May 2026.
+T&amp;amp;Cs apply.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UnravelwithEmiratesNBD"&gt;#UnravelwithEmiratesNBD&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23LifestylebyEmiratesNBD"&gt;#LifestylebyEmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Vacation"&gt;#Vacation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23HolidaySeason2026"&gt;#HolidaySeason2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SummerTrips"&gt;#SummerTrips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Summer2026"&gt;#Summer2026&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
         <v>0</v>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 12:11 PM UTC</t>
+          <t>May 7, 2026 · 9:16 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-04T12:11:00Z</t>
+          <t>2026-05-07T09:16:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnravelwithEmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23LifestylebyEmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Vacation', 'https://x.com/search?f=tweets&amp;q=%23HolidaySeason2026', 'https://x.com/search?f=tweets&amp;q=%23SummerTrips', 'https://x.com/search?f=tweets&amp;q=%23Summer2026']</t>
+        </is>
+      </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -2020,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>31</v>
+        <v>346</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2029,14 +2017,29 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>Unravel new destinations with fabulous offers
+Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
+The offer is valid until 30 May 2026.
+T&amp;Cs apply.
+#UnravelwithEmiratesNBD
+#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
         </is>
       </c>
     </row>
@@ -2046,82 +2049,84 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2051261292133130490</t>
+          <t>2052303842482499725</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052303842482499725</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/anwarquadri7</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>anwarquadri7</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Anwar Quadri</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1831450890525351936/CY5M68Bm_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven&amp;#39;t received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+&lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['anwarquadri7', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 11:22 AM UTC</t>
+          <t>May 7, 2026 · 8:25 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-04T11:22:00Z</t>
+          <t>2026-05-07T08:25:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>10</v>
+        <v>345</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2130,14 +2135,16 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
     </row>
@@ -2147,43 +2154,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2051239150909866122</t>
+          <t>2052303511182811547</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu</t>
+          <t>https://x.com/ENBDdeals</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>abhiseksonusonu</t>
+          <t>ENBDdeals</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>A R mishra</t>
+          <t>Emirates NBD Deals</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1912019334932611072/h2qIgZ-L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>&lt;a href="/LivBank" title="Liv Digital Bank"&gt;@LivBank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; dear can any one reply on this I am not getting any response</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+&lt;a href="https://apply.emiratesnbd.com/en/credit-card/noon"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2193,27 +2202,27 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 9:54 AM UTC</t>
+          <t>May 7, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-04T09:54:00Z</t>
+          <t>2026-05-07T08:24:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['https://x.com/LivBank', 'https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/noon']</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2222,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2231,14 +2240,25 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
         </is>
       </c>
     </row>
@@ -2248,45 +2268,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2051214248865656992</t>
+          <t>2052303458137489515</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo/status/2051214248865656992</t>
+          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/FF1991Whooo</t>
+          <t>https://x.com/ENBDdeals</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FF1991Whooo</t>
+          <t>ENBDdeals</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Flavours Footprints</t>
+          <t>Emirates NBD Deals</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1481297572363108353/g_PbK1D6_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
-I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Extremely disappointed with how my credit card closure has been handled.
-I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+&lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2296,36 +2316,36 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 8:16 AM UTC</t>
+          <t>May 7, 2026 · 8:24 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-04T08:16:00Z</t>
+          <t>2026-05-07T08:24:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2334,16 +2354,25 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
-I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Extremely disappointed with how my credit card closure has been handled.
-I requested closure before traveling in June 2025, yet recurring Google subscription charges continued. I cleared all dues whenever notified.</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
         </is>
       </c>
     </row>
@@ -2353,47 +2382,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2051210220634820985</t>
+          <t>2052303325781959087</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/DeloitteME/status/2051210220634820985</t>
+          <t>https://x.com/ENBDdeals/status/2052303325781959087</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/DeloitteME</t>
+          <t>https://x.com/ENBDdeals</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DeloitteME</t>
+          <t>ENBDdeals</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Deloitte Middle East</t>
+          <t>Emirates NBD Deals</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/742984436661276673/2NW6eZiW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>The future of finance is shaped by complex regulations.
-In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
-#Banking #FinancialServices</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>The future of finance is shaped by complex regulations.
-In our recent session with &lt;a href="/emirates" title="Emirates"&gt;@Emirates&lt;/a&gt; NBD, we discussed evolving &lt;a href="/search?f=tweets&amp;amp;q=%23risk"&gt;#risk&lt;/a&gt;, &lt;a href="/search?f=tweets&amp;amp;q=%23IFRS"&gt;#IFRS&lt;/a&gt;, &lt;a href="/search?f=tweets&amp;amp;q=%23tax"&gt;#tax&lt;/a&gt; &amp;amp; the vital role of culture in driving innovation amid change.
-&lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialServices"&gt;#FinancialServices&lt;/a&gt;</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+&lt;a href="https://apply.emiratesnbd.com/en/credit-card/noon"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2403,23 +2430,23 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 8:00 AM UTC</t>
+          <t>May 7, 2026 · 8:23 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04T08:00:00Z</t>
+          <t>2026-05-07T08:23:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['https://x.com/emirates', 'https://x.com/search?f=tweets&amp;q=%23risk', 'https://x.com/search?f=tweets&amp;q=%23IFRS', 'https://x.com/search?f=tweets&amp;q=%23tax', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23FinancialServices']</t>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/noon']</t>
         </is>
       </c>
       <c r="S18" t="n">
@@ -2429,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
         <v>75</v>
@@ -2441,18 +2468,16 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>The future of finance is shaped by complex regulations.
-In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
-#Banking #FinancialServices</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>The future of finance is shaped by complex regulations.
-In our recent session with @Emirates NBD, we discussed evolving #risk, #IFRS, #tax &amp; the vital role of culture in driving innovation amid change.
-#Banking #FinancialServices</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
     </row>
@@ -2462,50 +2487,54 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2051194736661381477</t>
+          <t>2052302615791505912</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/hill_lilli40424/status/2051194736661381477</t>
+          <t>https://x.com/illliyas/status/2052302615791505912</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/hill_lilli40424</t>
+          <t>https://x.com/illliyas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hill_lilli40424</t>
+          <t>illliyas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mohamed Farag</t>
+          <t>Illiyas Mohammed</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2051194248054341632/6o7ujA15_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Sent email.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that&amp;#39;s how we do it at TMG with Emirates NBD✨</t>
+          <t>Sent email.</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>19h</t>
@@ -2513,18 +2542,18 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 6:58 AM UTC</t>
+          <t>May 7, 2026 · 8:20 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T06:58:00Z</t>
+          <t>2026-05-07T08:20:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2533,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2542,14 +2571,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Sent email.</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Style, comfort, and cashback… that's how we do it at TMG with Emirates NBD✨</t>
+          <t>Sent email.</t>
         </is>
       </c>
     </row>
@@ -2559,36 +2588,468 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2051192927792300267</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2051192927792300267</t>
+          <t>https://x.com/illliyas/status/2052299293927805107</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/illliyas</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>illliyas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>Illiyas Mohammed</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:07 AM UTC</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:07:00Z</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>48</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://x.com/illliyas/status/2052299293927805107</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
+@NoBrokerCom @NoBrokerCare</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
+@NoBrokerCom @NoBrokerCare</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2052293602643148891</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/hamad5uae</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>hamad5uae</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>حمد الصعاق 🇦🇪</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1060909169958641665/n_4aleHZ_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 7:44 AM UTC</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2026-05-07T07:44:00Z</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>13</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
+By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
+#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
+By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
+#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2052292488354828493</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/AsharyRaya36726/status/2052292488354828493</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/AsharyRaya36726</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AsharyRaya36726</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rayan Ashary</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم 
+حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم 
+حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 7:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2026-05-07T07:40:00Z</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>20</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم 
+حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم 
+حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2052273540980691078</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus/status/2052273540980691078</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ArgaamPlus</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Argaam Plus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1330817158545354753/l1A8p5ic_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Fitch affirms Emirates NBD at &amp;#34;A+&amp;#34; with stable outlook</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 6:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2026-05-07T06:25:00Z</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>73</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2052269794708328566</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2052269794708328566</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>centralbankuae</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>Dear Consumer,
 Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
@@ -2597,7 +3058,7 @@
 Central Bank of the UAE</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Dear Consumer,
 Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
@@ -2606,54 +3067,54 @@
 Central Bank of the UAE</t>
         </is>
       </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
         <is>
           <t>['STKgenghis', 'EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:51:00Z</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 6:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2026-05-07T06:10:00Z</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>['https://x.com/SanadakUAE', 'https://sanadak.gov.ae/en']</t>
         </is>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>20</v>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>25</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Dear Consumer,
 Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
@@ -2662,9 +3123,9 @@
 Central Bank of the UAE</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>Dear Consumer,
 Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
@@ -2674,480 +3135,49 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2051188760185049183</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/mahmoudmoawad00/status/2051188760185049183</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://x.com/mahmoudmoawad00</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>mahmoudmoawad00</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Mahmoud Moawad</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1667049706462097408/EbaYvJZ9_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>After the update, I can&amp;#39;t approve any transactions. The app always shows &amp;#34;something went wrong&amp;#34; on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:34 AM UTC</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:34:00Z</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>20</v>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>After the update, I can't approve any transactions. The app always shows "something went wrong" on the approval page. I opened a case, and they said it was solved, asking me to reinstall the app. I even tried on three different devices, both Android and iPhone same issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2051171796552937744</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: emiratesnbd.com/en/cards/cre…</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: &lt;a href="https://www.emiratesnbd.com/en/cards/credit-cards/skywards-infinite-credit-card"&gt;emiratesnbd.com/en/cards/cre…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 5:27 AM UTC</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2026-05-04T05:27:00Z</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesnbd.com/en/cards/credit-cards/skywards-infinite-credit-card']</t>
-        </is>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>11</v>
-      </c>
-      <c r="V22" t="n">
-        <v>743</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: emiratesnbd.com/en/cards/cre…</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: https://t.co/TKre1mTLQs</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: https://t.co/TKre1mTLQs</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2051149273409143066</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/patilabhijeet45</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>patilabhijeet45</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>abhijeet patil</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>I have sent an email.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>I have sent an email.</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 3:57 AM UTC</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2026-05-04T03:57:00Z</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>I have sent an email.</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>I have sent an email.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2051134720344535096</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://x.com/ClapPakistan</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ClapPakistan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Clap</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1813702655031562240/RuM4t2kR_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-&lt;a href="/search?f=tweets&amp;amp;q=%23ClapPakistan"&gt;#ClapPakistan&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 3:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2026-05-04T03:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23ClapPakistan']</t>
-        </is>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>25</v>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2051337981815140447</t>
+          <t>2052264638478475341</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
+          <t>https://x.com/hamad5uae/status/2052264638478475341</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni</t>
+          <t>https://x.com/hamad5uae</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>praksoni</t>
+          <t>hamad5uae</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>prakash soni</t>
+          <t>حمد الصعاق 🇦🇪</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1060909169958641665/n_4aleHZ_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>I did not get any message. Following your page.</t>
+          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>I did not get any message. Following your page.</t>
+          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -3156,28 +3186,28 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 4:27 PM UTC</t>
+          <t>May 7, 2026 · 5:49 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-04T16:27:00Z</t>
+          <t>2026-05-07T05:49:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3186,31 +3216,23 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>I did not get any message. Following your page.</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
-        </is>
-      </c>
+          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
         </is>
       </c>
     </row>
@@ -3220,63 +3242,67 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052262640353972256</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+          <t>https://x.com/Sumeesh_KV/status/2052262640353972256</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Sumeesh_KV</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sumeesh_KV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>sumeesh k, v</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1971143576139726848/2d2C-7OD_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
+          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp;amp; FX advisor, preferential pricing on products,</t>
+          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don&amp;#39;t have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:00 PM UTC</t>
+          <t>May 7, 2026 · 5:41 AM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-04T13:00:00Z</t>
+          <t>2026-05-07T05:41:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
@@ -3291,31 +3317,23 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp; FX advisor, preferential pricing on products,</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
-        </is>
-      </c>
+          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
         </is>
       </c>
     </row>
@@ -3325,47 +3343,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2051255518270779594</t>
+          <t>2052253432514531776</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+          <t>https://x.com/ThanksDeepest/status/2052253432514531776</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ThanksDeepest</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ThanksDeepest</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Deepest Thanks</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032134589653848064/fWCPyV-w_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. #EmiratesIslamic
-emiratesislamic.ae/en/Person…</t>
+          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
-&lt;a href="https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions/digital-wealth"&gt;emiratesislamic.ae/en/Person…&lt;/a&gt;</t>
+          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -3375,66 +3389,48 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 11:00 AM UTC</t>
+          <t>May 7, 2026 · 5:05 AM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-04T11:00:00Z</t>
+          <t>2026-05-07T05:05:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/Personal-Banking/Wealth-Solutions/digital-wealth']</t>
-        </is>
-      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. #EmiratesIslamic
-emiratesislamic.ae/en/Person…</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
-        </is>
-      </c>
+          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
         </is>
       </c>
     </row>
@@ -3444,47 +3440,49 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2051210226183905695</t>
+          <t>2052253395499757971</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+          <t>https://x.com/wegro_app/status/2052253395499757971</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/wegro_app</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>wegro_app</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Wegro App</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
+📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
+🌐 Details: wegro.app/4bieSd
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp;amp; customary conditions.
+📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp;amp; Articles of Association
+🌐 Details: &lt;a href="https://www.wegro.app/4bieSd"&gt;wegro.app/4bieSd&lt;/a&gt;
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -3494,68 +3492,58 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 8:00 AM UTC</t>
+          <t>May 7, 2026 · 5:05 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-04T08:00:00Z</t>
+          <t>2026-05-07T05:05:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['https://www.wegro.app/4bieSd', 'https://www.wegro.app/go']</t>
+        </is>
+      </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام
-https://t.co/pVA5yvt1qT</t>
-        </is>
-      </c>
+          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
+📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
+🌐 Details: wegro.app/4bieSd
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام
-https://t.co/pVA5yvt1qT</t>
+          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
+📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
+🌐 Details: wegro.app/4bieSd
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
     </row>
@@ -3565,47 +3553,53 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2051180030810632404</t>
+          <t>2052253067580739890</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+          <t>https://x.com/speedystox/status/2052253067580739890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/speedystox</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>speedystox</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Speedy Stox</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038007871141765120/Kceaen5L_bigger.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 May 2026.
-Terms &amp; Conditions apply.</t>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
+💰 CMP: ₹332.90 (-0.98%)
+🏢 MCap: ₹20,585 Cr
+🌐Details: tinyurl.com/274j5mo2
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 May 2026.
-Terms &amp;amp; Conditions apply.</t>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
+💰 CMP: ₹332.90 (-0.98%)
+🏢 MCap: ₹20,585 Cr
+🌐Details: &lt;a href="http://tinyurl.com/274j5mo2"&gt;tinyurl.com/274j5mo2&lt;/a&gt;
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="http://speedystox.com"&gt;speedystox.com&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -3615,21 +3609,25 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 6:00 AM UTC</t>
+          <t>May 7, 2026 · 5:03 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-04T06:00:00Z</t>
+          <t>2026-05-07T05:03:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['http://tinyurl.com/274j5mo2', 'http://speedystox.com']</t>
+        </is>
+      </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
@@ -3640,35 +3638,33 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 May 2026.
-Terms &amp; Conditions apply.</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
-        </is>
-      </c>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
+💰 CMP: ₹332.90 (-0.98%)
+🏢 MCap: ₹20,585 Cr
+🌐Details: tinyurl.com/274j5mo2
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
+💰 CMP: ₹332.90 (-0.98%)
+🏢 MCap: ₹20,585 Cr
+🌐Details: tinyurl.com/274j5mo2
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
         </is>
       </c>
     </row>
@@ -3678,71 +3674,73 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2051180027576750215</t>
+          <t>2052247196737917354</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180027576750215</t>
+          <t>https://x.com/gngjin180881/status/2052247196737917354</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/gngjin180881</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>gngjin180881</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>smart_ev_china_exp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2052232531723128832/S0CsXblS_bigger.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+          <t>man's car!</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+          <t>man&amp;#39;s car!</t>
         </is>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 6:00 AM UTC</t>
+          <t>May 7, 2026 · 4:40 AM UTC</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-04T06:00:00Z</t>
+          <t>2026-05-07T04:40:00Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3751,25 +3749,23 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+          <t>man's car!</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)</t>
+          <t>man's car!</t>
         </is>
       </c>
     </row>
@@ -3779,77 +3775,75 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2051285726361227464</t>
+          <t>2052238409557790737</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+          <t>https://x.com/fam_zub/status/2052238409557790737</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/fam_zub</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>fam_zub</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Shafrin Sharief</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1633799312009318401/kUKYYjEv_bigger.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
-Learn more:
-emiratesislamic.ae/en/busine…</t>
+          <t>I have emailed please advise on the further proceedings
+Thanks in advance</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
-Learn more:
-&lt;a href="https://www.emiratesislamic.ae/en/business-banking/diamond?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_diamond"&gt;emiratesislamic.ae/en/busine…&lt;/a&gt;</t>
+          <t>I have emailed please advise on the further proceedings
+Thanks in advance</t>
         </is>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:00 PM UTC</t>
+          <t>May 7, 2026 · 4:05 AM UTC</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-04T13:00:00Z</t>
+          <t>2026-05-07T04:05:00Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/business-banking/diamond?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_diamond']</t>
-        </is>
-      </c>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3858,27 +3852,25 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
-Learn more:
-emiratesislamic.ae/en/busine…</t>
+          <t>I have emailed please advise on the further proceedings
+Thanks in advance</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
-Learn more:
-emiratesislamic.ae/en/busine…</t>
+          <t>I have emailed please advise on the further proceedings
+Thanks in advance</t>
         </is>
       </c>
     </row>
@@ -3888,75 +3880,71 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2051285720577269980</t>
+          <t>2052237496717541665</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285720577269980</t>
+          <t>https://x.com/STKgenghis/status/2052237496717541665</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
-لمعرفة المزيد:
-emiratesislamic.ae/ar/busine…</t>
+          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
-لمعرفة المزيد:
-&lt;a href="https://www.emiratesislamic.ae/ar/business-banking/diamond?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=bb_diamond"&gt;emiratesislamic.ae/ar/busine…&lt;/a&gt;</t>
+          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
         </is>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:00 PM UTC</t>
+          <t>May 7, 2026 · 4:02 AM UTC</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-04T13:00:00Z</t>
+          <t>2026-05-07T04:02:00Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/business-banking/diamond?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=bb_diamond']</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="n">
         <v>1</v>
       </c>
@@ -3967,27 +3955,23 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
-لمعرفة المزيد:
-emiratesislamic.ae/ar/busine…</t>
+          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
-لمعرفة المزيد:
-emiratesislamic.ae/ar/busine…</t>
+          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
         </is>
       </c>
     </row>
@@ -3997,94 +3981,106 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052237214285803805</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285716965986342</t>
+          <t>https://x.com/STKgenghis/status/2052237214285803805</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+          <t>I have now given up on this. 
+I have provided feedback in the hope systems can be bettered. 
+I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+          <t>I have now given up on this. 
+I have provided feedback in the hope systems can be bettered. 
+I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
         </is>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>May 7</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 1:00 PM UTC</t>
+          <t>May 7, 2026 · 4:00 AM UTC</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-04T13:00:00Z</t>
+          <t>2026-05-07T04:00:00Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>254</v>
+        <v>11</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+          <t>I have now given up on this. 
+I have provided feedback in the hope systems can be bettered. 
+I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى،</t>
+          <t>I have now given up on this. 
+I have provided feedback in the hope systems can be bettered. 
+I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
         </is>
       </c>
     </row>
@@ -4094,75 +4090,73 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2051255517989797926</t>
+          <t>2052236659459035248</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
+          <t>https://x.com/STKgenghis/status/2052236659459035248</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-emiratesislamic.ae/ar/Person…</t>
+          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
+Yet these are services I have a right to. They can only be withheld following due process</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-&lt;a href="https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/digital-wealth"&gt;emiratesislamic.ae/ar/Person…&lt;/a&gt;</t>
+          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
+Yet these are services I have a right to. They can only be withheld following due process</t>
         </is>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>May 7</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>May 4, 2026 · 11:00 AM UTC</t>
+          <t>May 7, 2026 · 3:58 AM UTC</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-04T11:00:00Z</t>
+          <t>2026-05-07T03:58:00Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/Personal-Banking/Wealth-Solutions/digital-wealth']</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
         <v>0</v>
       </c>
@@ -4170,30 +4164,28 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-emiratesislamic.ae/ar/Person…</t>
+          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
+Yet these are services I have a right to. They can only be withheld following due process</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
-emiratesislamic.ae/ar/Person…</t>
+          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
+Yet these are services I have a right to. They can only be withheld following due process</t>
         </is>
       </c>
     </row>
@@ -4203,36 +4195,1803 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2051210228520063073</t>
+          <t>2052236013733363784</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051210228520063073</t>
+          <t>https://x.com/STKgenghis/status/2052236013733363784</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/STKgenghis</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>STKgenghis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>khana-b-dosh</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
+        <is>
+          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
+I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
+I have raised my complaint with your customer service/support emails. No case number was issued. &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; will deem this unregistered.</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>May 7</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 3:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-05-07T03:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['https://x.com/centralbankuae']</t>
+        </is>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>35</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
+I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
+I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2052587154140955103</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>patilabhijeet45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>abhijeet patil</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>49m</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>May 8, 2026 · 3:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-05-08T03:11:00Z</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2052454342129803657</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/AsadNoman1/status/2052454342129803657</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/AsadNoman1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AsadNoman1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Asad Noman</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1502147591441723393/Oa10Smgf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Hi can you please fix this unable to login .</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Hi can you please fix this unable to login .</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 6:23 PM UTC</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2026-05-07T18:23:00Z</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Hi can you please fix this unable to login .</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Hi can you please fix this unable to login .</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2052427177216315673</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>gold_hadas</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nicholas MOLODYKO, writer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38">
+        <f>==&gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand economymiddleeast.com/news/d…</f>
+        <v/>
+      </c>
+      <c r="J38">
+        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand &lt;a href="https://economymiddleeast.com/news/dubais-emirates-islamic-launches-uaes-first-2-billion-shariah-compliant-cd-program-for-global-liquidity-demand/"&gt;economymiddleeast.com/news/d…&lt;/a&gt;</f>
+        <v/>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 4:35 PM UTC</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2026-05-07T16:35:00Z</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['https://economymiddleeast.com/news/dubais-emirates-islamic-launches-uaes-first-2-billion-shariah-compliant-cd-program-for-global-liquidity-demand/']</t>
+        </is>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X38">
+        <f>==&gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand economymiddleeast.com/news/d…</f>
+        <v/>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+        </is>
+      </c>
+      <c r="Z38">
+        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
+        <v/>
+      </c>
+      <c r="AA38">
+        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2052401437611630695</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/Economy_ME</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Economy_ME</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Economy Middle East</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1467708466877902853/YwMbROkF_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+#UAE #IslamicBanking #Finance #Investment #Banking</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicBanking"&gt;#IslamicBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investment"&gt;#Investment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 2:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-05-07T14:53:00Z</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23IslamicBanking', 'https://x.com/search?f=tweets&amp;q=%23Finance', 'https://x.com/search?f=tweets&amp;q=%23Investment', 'https://x.com/search?f=tweets&amp;q=%23Banking']</t>
+        </is>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>52</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+#UAE #IslamicBanking #Finance #Investment #Banking</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+#UAE #IslamicBanking #Finance #Investment #Banking</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+#UAE #IslamicBanking #Finance #Investment #Banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2052299567262241168</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6trr_</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ع ❥</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2010516983058767872/oVR7T5vc_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:08 AM UTC</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:08:00Z</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>14</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
+⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
+💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
+⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
+💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2052297392632803551</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>94</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2052232251371581529</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/thekimanikamau</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>thekimanikamau</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Daniel Kimani</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1923765853935288320/ejHyTEEL_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>May 7</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 3:41 AM UTC</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2026-05-07T03:41:00Z</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2052347910788890733</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>['Asayeel171930']</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:20 AM UTC</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:20:00Z</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>13</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2052347842044297241</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>['Asayeel171930']</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:20 AM UTC</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:20:00Z</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>13</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2052342692424696089</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026
+Terms &amp;amp; conditions apply.
+&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-linkedin&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-linkedin&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>49</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026
+Terms &amp; conditions apply.
+emiratesislamic.ae/en/offers…</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2052342690600165819</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342690600165819</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
+💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more
+💰 Competitive profit rates on Auto Finance &amp;amp; Home Finance</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>86</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
+💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
+💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2052342686976200822</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342686976200822</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام.
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+        </is>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>42</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام.
+emiratesislamic.ae/ar/offers…</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2052342683113283967</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342683113283967</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 11:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2026-05-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>211</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2052341746671948212</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052341746671948212</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>['Neli_Brown_']</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 10:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2026-05-07T10:56:00Z</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" t="n">
+        <v>39</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2052313830538059926</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052313830538059926</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>['6trr_']</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 9:05 AM UTC</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2026-05-07T09:05:00Z</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>11</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2052297395296243819</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297395296243819</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
         <is>
           <t>🚗 Complimentary airport transfers, meet &amp; greet services
 ⛳ Golf rounds at select premium courses
@@ -4242,7 +6001,7 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
 ⛳ Golf rounds at select premium courses
@@ -4252,50 +6011,50 @@
 &lt;a href="https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K35" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>2026-05-04T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
         </is>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>46</v>
-      </c>
-      <c r="W35" t="inlineStr">
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>50</v>
+      </c>
+      <c r="W51" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>🚗 Complimentary airport transfers, meet &amp; greet services
 ⛳ Golf rounds at select premium courses
@@ -4305,9 +6064,9 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
         <is>
           <t>🚗 Complimentary airport transfers, meet &amp; greet services
 ⛳ Golf rounds at select premium courses
@@ -4318,861 +6077,330 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2051210223440871854</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210223440871854</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2052297388321104214</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297388321104214</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
         <is>
           <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
 ⛳جولات الغولف
 🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
+يسري العرض لغاية 31 مايو2026
 تطبق الشروط والأحكام
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
 ⛳جولات الغولف
 🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
+يسري العرض لغاية 31 مايو2026
 تطبق الشروط والأحكام
 &lt;a href="https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="K36" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>2026-05-04T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="S52" t="n">
         <v>1</v>
       </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>43</v>
-      </c>
-      <c r="W36" t="inlineStr">
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>35</v>
+      </c>
+      <c r="W52" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
 ⛳جولات الغولف
 🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
+يسري العرض لغاية 31 مايو2026
 تطبق الشروط والأحكام
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
         <is>
           <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
 ⛳جولات الغولف
 🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
+يسري العرض لغاية 31 مايو2026
 تطبق الشروط والأحكام
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2051210219850489871</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2052297385615708568</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297385615708568</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
         <is>
           <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
 🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
 🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
         </is>
       </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 8:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>2026-05-04T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="n">
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-05-07T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>1</v>
       </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>2</v>
-      </c>
-      <c r="V37" t="n">
-        <v>153</v>
-      </c>
-      <c r="W37" t="inlineStr">
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>143</v>
+      </c>
+      <c r="W53" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
 🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr">
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
         <is>
           <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
 🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2051193239932174341</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2052252091914035405</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052252091914035405</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>['Thefatim2']</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:52:00Z</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>3</v>
-      </c>
-      <c r="W38" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
+Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
+Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>May 7, 2026 · 5:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-05-07T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
+      </c>
+      <c r="V54" t="n">
+        <v>95</v>
+      </c>
+      <c r="W54" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2051181531461275940</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:06 AM UTC</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:06:00Z</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>81</v>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
-Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2051180024997220725</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>28</v>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2051180020534546693</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
-        </is>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 6:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>2026-05-04T06:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>73</v>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2051173237304734081</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051173237304734081</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>['praksoni']</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 5:33 AM UTC</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>2026-05-04T05:33:00Z</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>14</v>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2051168317407207640</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>['AnkitMittal1403']</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>May 4, 2026 · 5:13 AM UTC</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>2026-05-04T05:13:00Z</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>10</v>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
-Regards,
-Ankit K Mittal
-+54 702 3869 https://t.co/av2G1Lek3Q</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
-Regards,
-Ankit K Mittal
-+54 702 3869 https://t.co/av2G1Lek3Q</t>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
+Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
+Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA54"/>
+  <dimension ref="A1:AA53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,36 +566,204 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052925380936491470</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02</t>
+          <t>https://x.com/jurian777</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>samial7arbi02</t>
+          <t>jurian777</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>سامي الحربي</t>
+          <t>齋藤純 Jun Saito</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2052150684968218625/9AJu83Hb_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
+        <is>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>May 9, 2026 · 1:35 AM UTC</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-05-09T01:35:00Z</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>51</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>alamair2008</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AZIZ ALGHAMDI</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>May 8, 2026 · 7:40 PM UTC</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-05-08T19:40:00Z</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
@@ -609,64 +777,7 @@
 @AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
-خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; إلى &amp;#34;قائمة سوداء وهمية&amp;#34; لا وجود لها في سجلات سمة ولا في &lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; !
-رغم ان  (تقييمي 751 ممتاز) 
-الأغرب؟ 
-حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
-رفعت الشكوى رسميًا لدى &lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; برقم (C260502xxxxx).
-هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
-سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
-من يريد أن يكون الشريك الحقيقي؟ 
-&lt;a href="/AlinmaBank" title="Alinma Fan"&gt;@AlinmaBank&lt;/a&gt; &lt;a href="/alrajhibank" title="مصرف الراجحي"&gt;@alrajhibank&lt;/a&gt; &lt;a href="/SNB_AlAhli" title="MY"&gt;@SNB_AlAhli&lt;/a&gt; &lt;a href="/RiyadBank" title="بنك الرياض"&gt;@RiyadBank&lt;/a&gt; &lt;a href="/BankAlbilad" title="بنك البلاد | Bank Albilad"&gt;@BankAlbilad&lt;/a&gt; &lt;a href="/BankAlJazira" title="بنك الجزيرة"&gt;@BankAlJazira&lt;/a&gt; &lt;a href="/anb_bank" title="البنك العربي الوطني - anb"&gt;@anb_bank&lt;/a&gt; &lt;a href="/D360bank" title="D360 Bank"&gt;@D360bank&lt;/a&gt; &lt;a href="/stcbank_ksa" title="STC Bank"&gt;@stcbank_ksa&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>May 7, 2026 · 8:08 PM UTC</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2026-05-07T20:08:00Z</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/SAMA_GOV', 'https://x.com/SAMAcares', 'https://x.com/AlinmaBank', 'https://x.com/alrajhibank', 'https://x.com/SNB_AlAhli', 'https://x.com/RiyadBank', 'https://x.com/BankAlbilad', 'https://x.com/BankAlJazira', 'https://x.com/anb_bank', 'https://x.com/D360bank', 'https://x.com/stcbank_ksa']</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>29648</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
@@ -680,148 +791,6 @@
 @AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
-رغم ان  (تقييمي 751 ممتاز) 
-الأغرب؟ 
-حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
-رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
-هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
-سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
-من يريد أن يكون الشريك الحقيقي؟ 
-@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA 
-خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
-رغم ان  (تقييمي 751 ممتاز) 
-الأغرب؟ 
-حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
-رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
-هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
-سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
-من يريد أن يكون الشريك الحقيقي؟ 
-@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2052462422221627597</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/kinsofdubai</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>kinsofdubai</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Kinshuk Kulshreshtha</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/997096320384028673/0D2-ksme_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>May 7, 2026 · 6:55 PM UTC</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2026-05-07T18:55:00Z</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>9</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -829,50 +798,54 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2052461879398937044</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/heba_hashem</t>
+          <t>https://x.com/hadi_msn</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>heba_hashem</t>
+          <t>hadi_msn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Heba Hashem Ⓥ</t>
+          <t>Hadi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1736630398384238593/Y_oo1i7E_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1295674429180125184/LuNcyvm9_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I&amp;#39;m an ENBD customer urgently trying to reach &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  as I&amp;#39;m unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
         </is>
       </c>
       <c r="K4" t="b">
         <v>0</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>['faisalalamoudi3', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>9h</t>
@@ -880,31 +853,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 6:53 PM UTC</t>
+          <t>May 8, 2026 · 5:05 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-07T18:53:00Z</t>
+          <t>2026-05-08T17:05:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -913,22 +882,22 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
         </is>
       </c>
     </row>
@@ -938,43 +907,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas</t>
+          <t>https://x.com/hadi_msn</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>illliyas</t>
+          <t>hadi_msn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Illiyas Mohammed</t>
+          <t>Hadi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1295674429180125184/LuNcyvm9_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Still waiting for the solution. Not happy with the service.</t>
+          <t>راح الرايح
+االتطبيق فيه مشكلة .. النقاط صفر</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Still waiting for the solution. Not happy with the service.</t>
+          <t>راح الرايح
+االتطبيق فيه مشكلة .. النقاط صفر</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -983,22 +954,22 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:26 PM UTC</t>
+          <t>May 8, 2026 · 4:56 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-07T16:26:00Z</t>
+          <t>2026-05-08T16:56:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -1013,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1022,26 +993,27 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Still waiting for the solution. Not happy with the service.</t>
+          <t>راح الرايح
+االتطبيق فيه مشكلة .. النقاط صفر</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>نفحصها ونعتمدها قبل نمولك 🚙
+انطلق بثقة مع تمويل السيارات المستعملة من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/CXCUIwu26x https://t.co/5sMib0U399</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>نفحصها ونعتمدها قبل نمولك 🚙
+انطلق بثقة مع تمويل السيارات المستعملة من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/CXCUIwu26x https://t.co/5sMib0U399</t>
         </is>
       </c>
     </row>
@@ -1051,67 +1023,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya</t>
+          <t>https://x.com/goacm</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RakshtVaghasiya</t>
+          <t>goacm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rakshit Vaghasiya</t>
+          <t>CMO Goa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2030191909399105536/cFPhY9vR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1649293753528745984/_vioJs5y_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Same reply every time. No action yet.</t>
+          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Same reply every time. No action yet.</t>
+          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 3:37 PM UTC</t>
+          <t>May 8, 2026 · 4:31 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-07T15:37:00Z</t>
+          <t>2026-05-08T16:31:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -1123,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1135,24 +1103,22 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Same reply every time. No action yet.</t>
+          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>Chief Minister @DrPramodPSawant met Shri R. Subramaniakumar, MD &amp;amp; CEO of @rblbank , and held discussions on various aspects relating to the banking sector, economic growth, and the Bank’s contribution towards India’s financial ecosystem. https://t.co/R2xc5qKMAC</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>Chief Minister @DrPramodPSawant met Shri R. Subramaniakumar, MD &amp;amp; CEO of @rblbank , and held discussions on various aspects relating to the banking sector, economic growth, and the Bank’s contribution towards India’s financial ecosystem. https://t.co/R2xc5qKMAC</t>
         </is>
       </c>
     </row>
@@ -1162,43 +1128,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2052393142469439783</t>
+          <t>2052787631394619720</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052393142469439783</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA/status/2052787631394619720</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02</t>
+          <t>https://x.com/JJPnlXDGrYuyPOA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>samial7arbi02</t>
+          <t>JJPnlXDGrYuyPOA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>سامي الحربي</t>
+          <t>سلطان الصاعدي</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1509025183151104007/5ogA9Xuh_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
+          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
+          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1212,17 +1178,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 2:20 PM UTC</t>
+          <t>May 8, 2026 · 4:28 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-07T14:20:00Z</t>
+          <t>2026-05-08T16:28:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1237,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1246,14 +1212,14 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
+          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>هل يعقل أن يصدر منكم عرض تمويلي رسمي بناءً على ملاءة مالية مثبتة ثم يرفض الموظف فتح الحساب بحجة (بلاك ليست) رغم أن تقييمي الائتماني ممتاز وبشهادة البنك المركزي؟ فوق هذا هاتف شكاويكم لا يرد لمدة ساعة كاملة! وبعد هذا الوقت كله يتم انهاء المكالمة من قبلكم دون التحدث مع قسم الشكاوي</t>
+          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
         </is>
       </c>
     </row>
@@ -1263,75 +1229,75 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2052392394302029845</t>
+          <t>2052783114410144160</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/Ma60934Max/status/2052392394302029845</t>
+          <t>https://x.com/HadiAlduba89157/status/2052783114410144160</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/Ma60934Max</t>
+          <t>https://x.com/HadiAlduba89157</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ma60934Max</t>
+          <t>HadiAlduba89157</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Max Blackton</t>
+          <t>Hadi Aldubaisi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1753968627823288320/luOtw3AO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
-Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
+          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
+شكرا جزيلا على الاستجابه</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;a href="https://yasislandabudhabi.pxf.io/c/2925765/3711431/26868"&gt;yasislandabudhabi.pxf.io/c/2…&lt;/a&gt; Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
-Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
+          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
+شكرا جزيلا على الاستجابه</t>
         </is>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 2:17 PM UTC</t>
+          <t>May 8, 2026 · 4:10 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-07T14:17:00Z</t>
+          <t>2026-05-08T16:10:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>['https://yasislandabudhabi.pxf.io/c/2925765/3711431/26868']</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1340,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1349,16 +1315,16 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
-Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
+          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
+شكرا جزيلا على الاستجابه</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>yasislandabudhabi.pxf.io/c/2… Emirates NBD Limited Time Offer at Yas Island Abu Dhabi
-Enjoy exclusive discounts and perks on Yas Island adventures when you pay with your Emirates NBD card. 20% off General Admission Day Tickets online. 10% off shopping at select outlets.</t>
+          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
+شكرا جزيلا على الاستجابه</t>
         </is>
       </c>
     </row>
@@ -1368,43 +1334,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2052391222535471314</t>
+          <t>2052782850760421453</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/bellyandabs/status/2052391222535471314</t>
+          <t>https://x.com/HadiAlduba89157/status/2052782850760421453</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/bellyandabs</t>
+          <t>https://x.com/HadiAlduba89157</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>bellyandabs</t>
+          <t>HadiAlduba89157</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AmeyK</t>
+          <t>Hadi Aldubaisi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1398588092391378953/EGqmD5zS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
+          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
+          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1413,22 +1379,22 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['abhirammodak']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 2:12 PM UTC</t>
+          <t>May 8, 2026 · 4:09 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-07T14:12:00Z</t>
+          <t>2026-05-08T16:09:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1440,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1452,14 +1418,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
+          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Watch out for UAE bank Emirates NBD.  Hopefully soon.</t>
+          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
         </is>
       </c>
     </row>
@@ -1469,84 +1435,88 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2052380876919452146</t>
+          <t>2052778577695773164</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/TadawulFeed/status/2052380876919452146</t>
+          <t>https://x.com/alamair2008/status/2052778577695773164</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/TadawulFeed</t>
+          <t>https://x.com/alamair2008</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TadawulFeed</t>
+          <t>alamair2008</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tadawul News</t>
+          <t>AZIZ ALGHAMDI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1428258699437563913/kvAW5pPQ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
-saudiexchange.sa/wps/portal/…</t>
+          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
+وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
+ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
+من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mohammed Hadi Al Rasheed &amp;amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
-&lt;a href="https://www.saudiexchange.sa/wps/portal/saudiexchange/newsandreports/issuer-news/issuer-announcements/issuer-announcements-details/?anId=95094&amp;amp;anCat=1&amp;amp;cs=9601&amp;amp;locale=en"&gt;saudiexchange.sa/wps/portal/…&lt;/a&gt;</t>
+          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
+وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
+ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
+من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 1:31 PM UTC</t>
+          <t>May 8, 2026 · 3:52 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-07T13:31:00Z</t>
+          <t>2026-05-08T15:52:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>['https://www.saudiexchange.sa/wps/portal/saudiexchange/newsandreports/issuer-news/issuer-announcements/issuer-announcements-details/?anId=95094&amp;anCat=1&amp;cs=9601&amp;locale=en']</t>
-        </is>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>6645</v>
+        <v>17</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1555,16 +1525,20 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
-saudiexchange.sa/wps/portal/…</t>
+          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
+وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
+ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
+من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Mohammed Hadi Al Rasheed &amp; Partners Company Announces Latest Developments Regarding Shariah-Compliant Banking Facilities Obtained from Emirates NBD Bank.
-saudiexchange.sa/wps/portal/…</t>
+          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
+وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
+ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
+من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
         </is>
       </c>
     </row>
@@ -1574,43 +1548,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2052380397837926546</t>
+          <t>2052761822374121589</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/iamjkp_/status/2052380397837926546</t>
+          <t>https://x.com/samial7arbi02/status/2052761822374121589</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/iamjkp_</t>
+          <t>https://x.com/samial7arbi02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>iamjkp_</t>
+          <t>samial7arbi02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JamshidKP</t>
+          <t>سامي الحربي</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1948467186663600128/kxAShTck_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>After a month delay the response was negative.</t>
+          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
+وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
+لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>After a month delay the response was negative.</t>
+          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
+وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
+لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1619,28 +1597,28 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA', 'ENBDdeals']</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 1:29 PM UTC</t>
+          <t>May 8, 2026 · 2:45 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-07T13:29:00Z</t>
+          <t>2026-05-08T14:45:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -1649,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>201</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1658,14 +1636,18 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>After a month delay the response was negative.</t>
+          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
+وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
+لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>After a month delay the response was negative.</t>
+          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
+وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
+لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
         </is>
       </c>
     </row>
@@ -1675,43 +1657,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2052375265490456666</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16</t>
+          <t>https://x.com/ihab</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>lhyx16</t>
+          <t>ihab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Salaam</t>
+          <t>Ihab</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1979858975735652352/1EXbxJlB_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1990048505319350272/P2gVhwvd_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Emirates NBD in Dubai also has this option.</t>
+          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp; apps asking me to update my EmiratesID. 
+Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emirates NBD in Dubai also has this option.</t>
+          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp;amp; apps asking me to update my EmiratesID. 
+Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1720,28 +1704,28 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['Kathleen_Tyson_', 'ProfSteveKeen']</t>
+          <t>['Hayataholica']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 1:09 PM UTC</t>
+          <t>May 8, 2026 · 2:23 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-07T13:09:00Z</t>
+          <t>2026-05-08T14:23:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
@@ -1750,7 +1734,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>47</v>
+        <v>469</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1759,32 +1743,27 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Emirates NBD in Dubai also has this option.</t>
+          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp; apps asking me to update my EmiratesID. 
+Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3 accounting errors that most China analysts keep making.
-One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
-Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
-Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
-The full conversation is in the comments.
-#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
+          <t>"Your Emirates ID has expired - Please update it now !!!"
+I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
+"!!! !!! !!! !!!" haha</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3 accounting errors that most China analysts keep making.
-One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
-Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
-Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
-The full conversation is in the comments.
-#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
+          <t>"Your Emirates ID has expired - Please update it now !!!"
+I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
+"!!! !!! !!! !!!" haha</t>
         </is>
       </c>
     </row>
@@ -1794,51 +1773,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2052336714459250884</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1</t>
+          <t>https://x.com/masdarak</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FintechGate1</t>
+          <t>masdarak</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
+          <t>المصدر العقاري</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1565412876965318657/wRffEOKq_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-fintechgate.net/wq61 | التفاصيل 
-@EmiratesNBD_AE
-#fintech_gate
-#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات</t>
+          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
+masdarak.com/home-finance/%D…</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-&lt;a href="https://fintechgate.net/wq61"&gt;fintechgate.net/wq61&lt;/a&gt; | التفاصيل 
-&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23برنامج_لشهادات_الإيداع"&gt;#برنامج_لشهادات_الإيداع&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الشريعة_الإسلامية"&gt;#الشريعة_الإسلامية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt;</t>
+          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية &lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;  بالتعاون مع بنك الإمارات دبي الوطني &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  وبنك أبوظبي التجاري  &lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;  بما يشمل غير المقيمين في دولة الإمارات
+&lt;a href="https://www.masdarak.com/home-finance/%D8%A5%D8%B7%D9%84%D8%A7%D9%82-%D8%AD%D9%84%D9%88%D9%84-%D9%84%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D8%B4%D8%B1%D8%A7%D8%A1-%D8%A7%D9%84%D8%B9%D9%82%D8%A7%D8%B1%D8%A7%D8%AA-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AE%D8%B1%D9%8A%D8%B7%D8%A9-%D9%81%D9%8A-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9-%D8%A5%D8%B9%D9%85%D8%A7%D8%B1"&gt;masdarak.com/home-finance/%D…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1848,23 +1821,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 10:36 AM UTC</t>
+          <t>May 8, 2026 · 1:48 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-07T10:36:00Z</t>
+          <t>2026-05-08T13:48:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://fintechgate.net/wq61', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي', 'https://x.com/search?f=tweets&amp;q=%23برنامج_لشهادات_الإيداع', 'https://x.com/search?f=tweets&amp;q=%23الشريعة_الإسلامية', 'https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
+          <t>['https://x.com/emaardubai', 'https://x.com/EmiratesNBD_AE', 'https://x.com/OfficialADCB', 'https://www.masdarak.com/home-finance/%D8%A5%D8%B7%D9%84%D8%A7%D9%82-%D8%AD%D9%84%D9%88%D9%84-%D9%84%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D8%B4%D8%B1%D8%A7%D8%A1-%D8%A7%D9%84%D8%B9%D9%82%D8%A7%D8%B1%D8%A7%D8%AA-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AE%D8%B1%D9%8A%D8%B7%D8%A9-%D9%81%D9%8A-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9-%D8%A5%D8%B9%D9%85%D8%A7%D8%B1']</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -1874,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1886,34 +1859,25 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-fintechgate.net/wq61 | التفاصيل 
-@EmiratesNBD_AE
-#fintech_gate
-#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات</t>
+          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
+masdarak.com/home-finance/%D…</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-https://t.co/LRj8F5RmtL | التفاصيل 
-@EmiratesNBD_AE
-#fintech_gate
-#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
+          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
+ https://t.co/bq6bpOlUdV</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-https://t.co/LRj8F5RmtL | التفاصيل 
-@EmiratesNBD_AE
-#fintech_gate
-#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
+          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
+ https://t.co/bq6bpOlUdV</t>
         </is>
       </c>
     </row>
@@ -1923,53 +1887,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2052316568441229765</t>
+          <t>2052739053989007588</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Farooq_AI</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Farooq_AI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>TT Aspiring</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1931385156696244224/ITF6uo1x_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Unravel new destinations with fabulous offers
-Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
-The offer is valid until 30 May 2026.
-T&amp;Cs apply.
-#UnravelwithEmiratesNBD
-#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Unravel new destinations with fabulous offers
-Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
-The offer is valid until 30 May 2026.
-T&amp;amp;Cs apply.
-&lt;a href="/search?f=tweets&amp;amp;q=%23UnravelwithEmiratesNBD"&gt;#UnravelwithEmiratesNBD&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23LifestylebyEmiratesNBD"&gt;#LifestylebyEmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Vacation"&gt;#Vacation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23HolidaySeason2026"&gt;#HolidaySeason2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SummerTrips"&gt;#SummerTrips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Summer2026"&gt;#Summer2026&lt;/a&gt;</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai&amp;#39;s losing innocence, not capital. I&amp;#39;m watching who positions for the recovery.</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1979,25 +1933,21 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 9:16 AM UTC</t>
+          <t>May 8, 2026 · 1:15 PM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-07T09:16:00Z</t>
+          <t>2026-05-08T13:15:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnravelwithEmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23LifestylebyEmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Vacation', 'https://x.com/search?f=tweets&amp;q=%23HolidaySeason2026', 'https://x.com/search?f=tweets&amp;q=%23SummerTrips', 'https://x.com/search?f=tweets&amp;q=%23Summer2026']</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -2008,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>346</v>
+        <v>13</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2017,29 +1967,22 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Unravel new destinations with fabulous offers
-Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
-The offer is valid until 30 May 2026.
-T&amp;Cs apply.
-#UnravelwithEmiratesNBD
-#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
     </row>
@@ -2049,84 +1992,84 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2052303842482499725</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052303842482499725</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/HadiAlduba89157</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>HadiAlduba89157</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Hadi Aldubaisi</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>وانا كذلك المشكلة شائعه
+عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-&lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>وانا كذلك المشكلة شائعه
+عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA', 'Moh_Dul95']</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:25 AM UTC</t>
+          <t>May 8, 2026 · 12:40 PM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-07T08:25:00Z</t>
+          <t>2026-05-08T12:40:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>345</v>
+        <v>55</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2135,16 +2078,27 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
+          <t>وانا كذلك المشكلة شائعه
+عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
         </is>
       </c>
     </row>
@@ -2154,75 +2108,73 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2052303511182811547</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Akhtar Motiwala</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-&lt;a href="https://apply.emiratesnbd.com/en/credit-card/noon"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
         </is>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>['MotiwalaAkhtar', 'EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:24 AM UTC</t>
+          <t>May 8, 2026 · 12:30 PM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-07T08:24:00Z</t>
+          <t>2026-05-08T12:30:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/noon']</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2231,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2240,25 +2192,24 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
     </row>
@@ -2268,45 +2219,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2052303458137489515</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
+          <t>https://x.com/Moh_Dul95/status/2052726323349533050</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/Moh_Dul95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>Moh_Dul95</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1080059021028192256/Cjkq5nkZ_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-&lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2316,36 +2269,36 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:24 AM UTC</t>
+          <t>May 8, 2026 · 12:24 PM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-07T08:24:00Z</t>
+          <t>2026-05-08T12:24:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2354,25 +2307,18 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
         </is>
       </c>
     </row>
@@ -2382,84 +2328,82 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2052303325781959087</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303325781959087</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals</t>
+          <t>https://x.com/ChoteyMamu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ENBDdeals</t>
+          <t>ChoteyMamu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Emirates NBD Deals</t>
+          <t>SHA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1763624422294814720/EmRI1Aqu_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1702021256537571328/jh5zD-f-_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>Still no update...</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-&lt;a href="https://apply.emiratesnbd.com/en/credit-card/noon"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>Still no update...</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:23 AM UTC</t>
+          <t>May 8, 2026 · 10:51 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-07T08:23:00Z</t>
+          <t>2026-05-08T10:51:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/noon']</t>
-        </is>
-      </c>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2468,16 +2412,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>Still no update...</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-apply.emiratesnbd.com/en/cre…</t>
+          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
         </is>
       </c>
     </row>
@@ -2487,43 +2437,43 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2052302615791505912</t>
+          <t>2052701014034108672</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052302615791505912</t>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas</t>
+          <t>https://x.com/foode212</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>illliyas</t>
+          <t>foode212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Illiyas Mohammed</t>
+          <t>Fahad 212</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2027889531282751488/XVlkeZ8o_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sent email.</t>
+          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sent email.</t>
+          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -2537,17 +2487,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:20 AM UTC</t>
+          <t>May 8, 2026 · 10:43 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-07T08:20:00Z</t>
+          <t>2026-05-08T10:43:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2562,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2571,14 +2521,22 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Sent email.</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Sent email.</t>
+          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
         </is>
       </c>
     </row>
@@ -2588,77 +2546,85 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052299293927805107</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas</t>
+          <t>https://x.com/MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>illliyas</t>
+          <t>MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Illiyas Mohammed</t>
+          <t>Akhtar Motiwala</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1543595501056049152/DVpvfKGf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>+971 555 906879 
+BENEFICIARY: 
+AKHTAR NAZIR MOTIWALA
+AC NO: 1014895574401
+IBAN: AE37 0260 0010 1489 5574 401
+Swift: EBILAEADXXX
+BANK: EMIRATES NBD</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>+971 555 906879 
+BENEFICIARY: 
+AKHTAR NAZIR MOTIWALA
+AC NO: 1014895574401
+IBAN: AE37 0260 0010 1489 5574 401
+Swift: EBILAEADXXX
+BANK: EMIRATES NBD</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:07 AM UTC</t>
+          <t>May 8, 2026 · 10:19 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-07T08:07:00Z</t>
+          <t>2026-05-08T10:19:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -2667,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2676,26 +2642,28 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>+971 555 906879 
+BENEFICIARY: 
+AKHTAR NAZIR MOTIWALA
+AC NO: 1014895574401
+IBAN: AE37 0260 0010 1489 5574 401
+Swift: EBILAEADXXX
+BANK: EMIRATES NBD</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052299293927805107</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
-@NoBrokerCom @NoBrokerCare</t>
+          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
-@NoBrokerCom @NoBrokerCare</t>
+          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
         </is>
       </c>
     </row>
@@ -2705,73 +2673,75 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052691349342941582</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae</t>
+          <t>https://x.com/MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>hamad5uae</t>
+          <t>MotiwalaAkhtar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>حمد الصعاق 🇦🇪</t>
+          <t>Akhtar Motiwala</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1060909169958641665/n_4aleHZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I am trying to login my enbd online banking but it&amp;#39;s taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 7:44 AM UTC</t>
+          <t>May 8, 2026 · 10:05 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-07T07:44:00Z</t>
+          <t>2026-05-08T10:05:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2780,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2789,26 +2759,16 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
-By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
-#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
-By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
-#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
     </row>
@@ -2818,27 +2778,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2052292488354828493</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/AsharyRaya36726/status/2052292488354828493</t>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/AsharyRaya36726</t>
+          <t>https://x.com/IrfanAmeable</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AsharyRaya36726</t>
+          <t>IrfanAmeable</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayan Ashary</t>
+          <t>mohammed irfan</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2849,14 +2809,12 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم 
-حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم 
-حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2866,27 +2824,27 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 7:40 AM UTC</t>
+          <t>May 8, 2026 · 9:50 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-07T07:40:00Z</t>
+          <t>2026-05-08T09:50:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2904,16 +2862,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم 
-حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم 
-حسابي مجمد بسبب تورق علما بانه تم دفع قسط القرض لهذا الشهر في يوم ٢٩ أبريل و مازال حسابي مجمد بسبب القسط !!!</t>
+          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
     </row>
@@ -2923,63 +2879,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2052273540980691078</t>
+          <t>2052683161734148463</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2052273540980691078</t>
+          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus</t>
+          <t>https://x.com/RohitSa70875783</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ArgaamPlus</t>
+          <t>RohitSa70875783</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Argaam Plus</t>
+          <t>Luna Web3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1330817158545354753/l1A8p5ic_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2048077886406656000/YiwGVivE_bigger.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Fitch affirms Emirates NBD at &amp;#34;A+&amp;#34; with stable outlook</t>
+          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
       <c r="K23" t="b">
         <v>0</v>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>['multibank_io', 'AECoin_UAE']</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 6:25 AM UTC</t>
+          <t>May 8, 2026 · 9:32 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-07T06:25:00Z</t>
+          <t>2026-05-08T09:32:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2994,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3003,14 +2963,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Fitch affirms Emirates NBD at "A+" with stable outlook</t>
+          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
     </row>
@@ -3020,51 +2980,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2052269794708328566</t>
+          <t>2052681405897880031</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae/status/2052269794708328566</t>
+          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/centralbankuae</t>
+          <t>https://x.com/Suhrob64184475</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>centralbankuae</t>
+          <t>Suhrob64184475</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Central Bank of the UAE</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2048359076401463296/zyTuEjur_bigger.jpg</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Dear Consumer,
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Dear Consumer,
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Emirates NBD and Mashreq both holding reserves that&amp;#39;s actually solid backing ngl</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -3073,30 +3025,26 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>['STKgenghis', 'EmiratesNBD_AE']</t>
+          <t>['multibank_io', 'AECoin_UAE']</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 6:10 AM UTC</t>
+          <t>May 8, 2026 · 9:25 AM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-07T06:10:00Z</t>
+          <t>2026-05-08T09:25:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>['https://x.com/SanadakUAE', 'https://sanadak.gov.ae/en']</t>
-        </is>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3116,22 +3064,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Dear Consumer,
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Dear Consumer,
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
+          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
         </is>
       </c>
     </row>
@@ -3141,43 +3081,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2052264638478475341</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052264638478475341</t>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae</t>
+          <t>https://x.com/HadiAlduba89157</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>hamad5uae</t>
+          <t>HadiAlduba89157</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>حمد الصعاق 🇦🇪</t>
+          <t>Hadi Aldubaisi</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1060909169958641665/n_4aleHZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -3186,28 +3126,28 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 5:49 AM UTC</t>
+          <t>May 8, 2026 · 9:22 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-07T05:49:00Z</t>
+          <t>2026-05-08T09:22:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3216,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3225,14 +3165,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
         </is>
       </c>
     </row>
@@ -3242,82 +3182,90 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2052262640353972256</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2052262640353972256</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV</t>
+          <t>https://x.com/multibank_io</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sumeesh_KV</t>
+          <t>multibank_io</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>sumeesh k, v</t>
+          <t>mb.io</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1971143576139726848/2d2C-7OD_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2015689534328250368/-RLE2RH__bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don&amp;#39;t have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want &lt;a href="/search?f=tweets&amp;amp;q=%23AEC"&gt;$AEC&lt;/a&gt; and &lt;a href="/search?f=tweets&amp;amp;q=%23USDU"&gt;$USDU&lt;/a&gt; on ⬡ mb io? 
+Let us know! cc &lt;a href="/AECoin_UAE" title="AE Coin"&gt;@AECoin_UAE&lt;/a&gt;  and &lt;a href="/Universal_USDU" title="USDU / Universal"&gt;@Universal_USDU&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 5:41 AM UTC</t>
+          <t>May 8, 2026 · 9:21 AM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-07T05:41:00Z</t>
+          <t>2026-05-08T09:21:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23AEC', 'https://x.com/search?f=tweets&amp;q=%23USDU', 'https://x.com/AECoin_UAE', 'https://x.com/Universal_USDU']</t>
+        </is>
+      </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>389</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>14051</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
@@ -3326,14 +3274,22 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>This time I am at Nad al Sheba mall branch and what an epitome of customer service. I am mesmerized with the attitude and customer friendly approach of the team in this branch. I don't have enough words to explain the feeling of seeing all the smiling faces and welcoming approach</t>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
     </row>
@@ -3343,43 +3299,45 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2052253432514531776</t>
+          <t>2052674872631763288</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/ThanksDeepest/status/2052253432514531776</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2052674872631763288</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/ThanksDeepest</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ThanksDeepest</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deepest Thanks</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032134589653848064/fWCPyV-w_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
+          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
+          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -3389,23 +3347,23 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 5:05 AM UTC</t>
+          <t>May 8, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-07T05:05:00Z</t>
+          <t>2026-05-08T09:00:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -3414,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -3423,14 +3381,16 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
+          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd -  gets RBI nod for AoA changes enabling Emirates NBD stake; investment still pending approvals</t>
+          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
     </row>
@@ -3440,49 +3400,51 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2052253395499757971</t>
+          <t>2052663047903473895</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app/status/2052253395499757971</t>
+          <t>https://x.com/Imamx20/status/2052663047903473895</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app</t>
+          <t>https://x.com/Imamx20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>wegro_app</t>
+          <t>Imamx20</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wegro App</t>
+          <t>Imam</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2040371356467159040/UjJi1ZiW_bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
-📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
-🌐 Details: wegro.app/4bieSd
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
+          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp;amp; customary conditions.
-📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp;amp; Articles of Association
-🌐 Details: &lt;a href="https://www.wegro.app/4bieSd"&gt;wegro.app/4bieSd&lt;/a&gt;
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
+          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp;amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -3492,36 +3454,36 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 5:05 AM UTC</t>
+          <t>May 8, 2026 · 8:13 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-07T05:05:00Z</t>
+          <t>2026-05-08T08:13:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://www.wegro.app/4bieSd', 'https://www.wegro.app/go']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
         </is>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -3530,20 +3492,22 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
-📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
-🌐 Details: wegro.app/4bieSd
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
+          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.
+#EmiratesNBD</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>RBL Bank has received approval from the RBI for amendments to its Articles of Association, including those related to director nomination rights for Emirates NBD Bank (P.J.S.C). This is a step towards the proposed preferential issue of equity shares by the Investor, which is still subject to other regulatory approvals &amp; customary conditions.
-📊 RBL BANK LTD | 🏷️ Amendments to Memorandum &amp; Articles of Association
-🌐 Details: wegro.app/4bieSd
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
+          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.
+#EmiratesNBD</t>
         </is>
       </c>
     </row>
@@ -3553,53 +3517,49 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2052253067580739890</t>
+          <t>2052662496658673916</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/speedystox/status/2052253067580739890</t>
+          <t>https://x.com/Imamx20/status/2052662496658673916</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/speedystox</t>
+          <t>https://x.com/Imamx20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>speedystox</t>
+          <t>Imamx20</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Speedy Stox</t>
+          <t>Imam</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2038007871141765120/Kceaen5L_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2040371356467159040/UjJi1ZiW_bigger.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
-💰 CMP: ₹332.90 (-0.98%)
-🏢 MCap: ₹20,585 Cr
-🌐Details: tinyurl.com/274j5mo2
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
+          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
-💰 CMP: ₹332.90 (-0.98%)
-🏢 MCap: ₹20,585 Cr
-🌐Details: &lt;a href="http://tinyurl.com/274j5mo2"&gt;tinyurl.com/274j5mo2&lt;/a&gt;
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="http://speedystox.com"&gt;speedystox.com&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp;amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -3609,27 +3569,27 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 5:03 AM UTC</t>
+          <t>May 8, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-07T05:03:00Z</t>
+          <t>2026-05-08T08:10:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>['http://tinyurl.com/274j5mo2', 'http://speedystox.com']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -3638,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -3647,24 +3607,20 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
-💰 CMP: ₹332.90 (-0.98%)
-🏢 MCap: ₹20,585 Cr
-🌐Details: tinyurl.com/274j5mo2
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
+          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Received approval from the Reserve Bank of India on May 6, 2026, for amendments to the articles of association, including director nomination rights of Emirates NBD Bank. Investment via preferential issue of equity shares pending other regulatory approvals.
-💰 CMP: ₹332.90 (-0.98%)
-🏢 MCap: ₹20,585 Cr
-🌐Details: tinyurl.com/274j5mo2
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
+          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
+Dispute raised: SR No. 235754008145
+Police case also filed.
+Still waiting for action and refund from Emirates NBD.</t>
         </is>
       </c>
     </row>
@@ -3674,43 +3630,45 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2052247196737917354</t>
+          <t>2052661557209768191</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/gngjin180881/status/2052247196737917354</t>
+          <t>https://x.com/alamair2008/status/2052661557209768191</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/gngjin180881</t>
+          <t>https://x.com/alamair2008</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>gngjin180881</t>
+          <t>alamair2008</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>smart_ev_china_exp</t>
+          <t>AZIZ ALGHAMDI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2052232531723128832/S0CsXblS_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>man's car!</t>
+          <t>أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
+أنا المتضرر</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>man&amp;#39;s car!</t>
+          <t>أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة &lt;a href="/mrnaksa" title="مرنة للتمويل"&gt;@mrnaksa&lt;/a&gt; واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; متاخر سبب نزول الإسكورر
+أنا المتضرر</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -3719,28 +3677,32 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['samial7arbi02', 'EmiratesNBD_KSA', 'SAMA_GOV', 'ENBDdeals', 'anb_bank', 'RiyadBank', 'BankAlJazira', 'BankAlbilad', 'D360bank', 'alrajhibank', 'snbalahli']</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:40 AM UTC</t>
+          <t>May 8, 2026 · 8:07 AM UTC</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-05-07T04:40:00Z</t>
+          <t>2026-05-08T08:07:00Z</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['https://x.com/mrnaksa', 'https://x.com/SAMAcares']</t>
+        </is>
+      </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -3749,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>361</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -3758,14 +3720,16 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>man's car!</t>
+          <t>أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
+أنا المتضرر</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>man's car!</t>
+          <t>أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
+أنا المتضرر</t>
         </is>
       </c>
     </row>
@@ -3775,45 +3739,45 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2052238409557790737</t>
+          <t>2052657495840285062</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/fam_zub/status/2052238409557790737</t>
+          <t>https://x.com/FF1991Whooo/status/2052657495840285062</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/fam_zub</t>
+          <t>https://x.com/FF1991Whooo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>fam_zub</t>
+          <t>FF1991Whooo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shafrin Sharief</t>
+          <t>Flavours Footprints</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1633799312009318401/kUKYYjEv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1481297572363108353/g_PbK1D6_bigger.png</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>I have emailed please advise on the further proceedings
-Thanks in advance</t>
+          <t>No difference! Had sent an email right after this, usual 'escalated to the team' was the reply.
+Next payment due is 10 May, bcz you'll will drag this &amp; I'll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y'all!!</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>I have emailed please advise on the further proceedings
-Thanks in advance</t>
+          <t>No difference! Had sent an email right after this, usual &amp;#39;escalated to the team&amp;#39; was the reply.
+Next payment due is 10 May, bcz you&amp;#39;ll will drag this &amp;amp; I&amp;#39;ll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y&amp;#39;all!!</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -3827,17 +3791,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:05 AM UTC</t>
+          <t>May 8, 2026 · 7:50 AM UTC</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-05-07T04:05:00Z</t>
+          <t>2026-05-08T07:50:00Z</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -3852,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3861,16 +3825,16 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>I have emailed please advise on the further proceedings
-Thanks in advance</t>
+          <t>No difference! Had sent an email right after this, usual 'escalated to the team' was the reply.
+Next payment due is 10 May, bcz you'll will drag this &amp; I'll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y'all!!</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>I have emailed please advise on the further proceedings
-Thanks in advance</t>
+          <t>No difference! Had sent an email right after this, usual 'escalated to the team' was the reply.
+Next payment due is 10 May, bcz you'll will drag this &amp; I'll bear the penalty? Everything was talked and that lady had mentioned it will be waived off! Now i gotta run behind y'all!!</t>
         </is>
       </c>
     </row>
@@ -3880,73 +3844,75 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2052237496717541665</t>
+          <t>2052649301046915394</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2052237496717541665</t>
+          <t>https://x.com/NaveedDumasia/status/2052649301046915394</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/NaveedDumasia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>NaveedDumasia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>Naveed Dumasia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/814083182228185093/HX0Qxe07_bigger.jpg</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
+          <t>Trying to call @EmiratesNBD_AE  customer support but in vain. 
+Please help.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
+          <t>Trying to call &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  customer support but in vain. 
+Please help.</t>
         </is>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:02 AM UTC</t>
+          <t>May 8, 2026 · 7:18 AM UTC</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-05-07T04:02:00Z</t>
+          <t>2026-05-08T07:18:00Z</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -3955,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>15</v>
+        <v>295</v>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -3964,14 +3930,16 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
+          <t>Trying to call @EmiratesNBD_AE  customer support but in vain. 
+Please help.</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>I understand the social media team has limited capacity to resolve this so thank you for your time. My issue remains unresolved.</t>
+          <t>Trying to call @EmiratesNBD_AE  customer support but in vain. 
+Please help.</t>
         </is>
       </c>
     </row>
@@ -3981,71 +3949,63 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2052237214285803805</t>
+          <t>2052635129198112859</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2052237214285803805</t>
+          <t>https://x.com/EdutainNinja/status/2052635129198112859</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/EdutainNinja</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>EdutainNinja</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>Olivia EducationNinja</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1940867031407964160/VyQYdfYM_bigger.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>I have now given up on this. 
-I have provided feedback in the hope systems can be bettered. 
-I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
+          <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>I have now given up on this. 
-I have provided feedback in the hope systems can be bettered. 
-I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
+          <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
         </is>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>May 7</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:00 AM UTC</t>
+          <t>May 8, 2026 · 6:22 AM UTC</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-05-07T04:00:00Z</t>
+          <t>2026-05-08T06:22:00Z</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -4060,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -4069,18 +4029,14 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>I have now given up on this. 
-I have provided feedback in the hope systems can be bettered. 
-I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
+          <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>I have now given up on this. 
-I have provided feedback in the hope systems can be bettered. 
-I am not going to once again call your help lines whilst on holiday to once again explain the predicament I am in through no fault of my own. I owe the bank nothing. No debts.</t>
+          <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
         </is>
       </c>
     </row>
@@ -4090,75 +4046,73 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2052236659459035248</t>
+          <t>2052547700638245362</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2052236659459035248</t>
+          <t>https://x.com/memd619/status/2052547700638245362</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/memd619</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>memd619</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>dr.memd</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1707910532819197952/u4OqEdVF_bigger.jpg</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
-Yet these are services I have a right to. They can only be withheld following due process</t>
+          <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
-Yet these are services I have a right to. They can only be withheld following due process</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; الكاش باك صفر عندي ؟! ايش المشكله</t>
         </is>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>May 7</t>
+          <t>May 8</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 3:58 AM UTC</t>
+          <t>May 8, 2026 · 12:34 AM UTC</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-05-07T03:58:00Z</t>
+          <t>2026-05-08T00:34:00Z</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -4167,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="W34" t="inlineStr">
         <is>
@@ -4176,16 +4130,14 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
-Yet these are services I have a right to. They can only be withheld following due process</t>
+          <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>I have been through this before. No case number means no problem. So no liability. Meanwhile the burden of restoring functionality shifts to the customer not the institution. 
-Yet these are services I have a right to. They can only be withheld following due process</t>
+          <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
         </is>
       </c>
     </row>
@@ -4195,45 +4147,43 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2052236013733363784</t>
+          <t>2052765405383667833</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2052236013733363784</t>
+          <t>https://x.com/AsadNoman1/status/2052765405383667833</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis</t>
+          <t>https://x.com/AsadNoman1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>STKgenghis</t>
+          <t>AsadNoman1</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>khana-b-dosh</t>
+          <t>Asad Noman</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1243248207293026305/b_s7UBzl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1502147591441723393/Oa10Smgf_bigger.jpg</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
-I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+          <t>still not fixed its 2nd day now , how to login and payments ?</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
-I have raised my complaint with your customer service/support emails. No case number was issued. &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; will deem this unregistered.</t>
+          <t>still not fixed its 2nd day now , how to login and payments ?</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -4242,59 +4192,53 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>May 7</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 3:56 AM UTC</t>
+          <t>May 8, 2026 · 2:59 PM UTC</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-05-07T03:56:00Z</t>
+          <t>2026-05-08T14:59:00Z</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>['https://x.com/centralbankuae']</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
         <v>1</v>
       </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>35</v>
-      </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
-I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+          <t>still not fixed its 2nd day now , how to login and payments ?</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>At the risk of a loop which is what we seem ti have entered: my credit card transaction was rejected at an outlet. Somewhat embarassing. 
-I have raised my complaint with your customer service/support emails. No case number was issued. @centralbankuae will deem this unregistered.</t>
+          <t>still not fixed its 2nd day now , how to login and payments ?</t>
         </is>
       </c>
     </row>
@@ -4304,43 +4248,45 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052712527633481877</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
+          <t>https://x.com/ForumRemittance/status/2052712527633481877</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45</t>
+          <t>https://x.com/ForumRemittance</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>patilabhijeet45</t>
+          <t>ForumRemittance</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>abhijeet patil</t>
+          <t>World Remittance Action Forum</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the #UAE, has successfully introduced the country’s first Shari’ah-compliant Certificate of Deposit (CD) Programme
+#EmiratesIslamic #IslamicBanking #UAEFinance #ShariahCompliant #FinancialInnovation #BankingSector</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Hello Team need your assistance please dm.</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;, has successfully introduced the country’s first Shari’ah-compliant Certificate of Deposit (CD) Programme
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicBanking"&gt;#IslamicBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEFinance"&gt;#UAEFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ShariahCompliant"&gt;#ShariahCompliant&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialInnovation"&gt;#FinancialInnovation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingSector"&gt;#BankingSector&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -4350,23 +4296,23 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>49m</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 3:11 AM UTC</t>
+          <t>May 8, 2026 · 11:29 AM UTC</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-05-08T03:11:00Z</t>
+          <t>2026-05-08T11:29:00Z</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://x.com/search?f=tweets&amp;q=%23IslamicBanking', 'https://x.com/search?f=tweets&amp;q=%23UAEFinance', 'https://x.com/search?f=tweets&amp;q=%23ShariahCompliant', 'https://x.com/search?f=tweets&amp;q=%23FinancialInnovation', 'https://x.com/search?f=tweets&amp;q=%23BankingSector']</t>
         </is>
       </c>
       <c r="S36" t="n">
@@ -4379,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -4388,14 +4334,16 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the #UAE, has successfully introduced the country’s first Shari’ah-compliant Certificate of Deposit (CD) Programme
+#EmiratesIslamic #IslamicBanking #UAEFinance #ShariahCompliant #FinancialInnovation #BankingSector</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+          <t>Emirates Islamic, a leading Islamic financial institution in the #UAE, has successfully introduced the country’s first Shari’ah-compliant Certificate of Deposit (CD) Programme
+#EmiratesIslamic #IslamicBanking #UAEFinance #ShariahCompliant #FinancialInnovation #BankingSector</t>
         </is>
       </c>
     </row>
@@ -4405,71 +4353,75 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2052454342129803657</t>
+          <t>2052705196799656250</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/AsadNoman1/status/2052454342129803657</t>
+          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/AsadNoman1</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AsadNoman1</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asad Noman</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1502147591441723393/Oa10Smgf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Hi can you please fix this unable to login .</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Hi can you please fix this unable to login .</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
+ Read the article: 
+&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 6:23 PM UTC</t>
+          <t>May 8, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-05-07T18:23:00Z</t>
+          <t>2026-05-08T11:00:00Z</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme']</t>
+        </is>
+      </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
@@ -4480,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -4489,14 +4441,28 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Hi can you please fix this unable to login .</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Hi can you please fix this unable to login .</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
         </is>
       </c>
     </row>
@@ -4506,42 +4472,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2052427177216315673</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>gold_hadas</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nicholas MOLODYKO, writer</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026237940993552385/baDKDoMV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38">
-        <f>==&gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand economymiddleeast.com/news/d…</f>
-        <v/>
-      </c>
-      <c r="J38">
-        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand &lt;a href="https://economymiddleeast.com/news/dubais-emirates-islamic-launches-uaes-first-2-billion-shariah-compliant-cd-program-for-global-liquidity-demand/"&gt;economymiddleeast.com/news/d…&lt;/a&gt;</f>
-        <v/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن &lt;a href="https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/ar/person…&lt;/a&gt;
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
       </c>
       <c r="K38" t="b">
         <v>0</v>
@@ -4550,27 +4530,27 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 4:35 PM UTC</t>
+          <t>May 8, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-05-07T16:35:00Z</t>
+          <t>2026-05-08T11:00:00Z</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>['https://economymiddleeast.com/news/dubais-emirates-islamic-launches-uaes-first-2-billion-shariah-compliant-cd-program-for-global-liquidity-demand/']</t>
+          <t>['https://www.emiratesislamic.ae/ar/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
         </is>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
         <v>0</v>
@@ -4579,29 +4559,46 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="W38" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
-      <c r="X38">
-        <f>==&gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand economymiddleeast.com/news/d…</f>
-        <v/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
-        </is>
-      </c>
-      <c r="Z38">
-        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
-        <v/>
-      </c>
-      <c r="AA38">
-        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
-        <v/>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -4610,86 +4607,82 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2052401437611630695</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Economy_ME</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Economy Middle East</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1467708466877902853/YwMbROkF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-#UAE #IslamicBanking #Finance #Investment #Banking</t>
+          <t>A waiting to connect via dm please</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IslamicBanking"&gt;#IslamicBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Investment"&gt;#Investment&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt;</t>
+          <t>A waiting to connect via dm please</t>
         </is>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 2:53 PM UTC</t>
+          <t>May 8, 2026 · 10:58 AM UTC</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-05-07T14:53:00Z</t>
+          <t>2026-05-08T10:58:00Z</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23IslamicBanking', 'https://x.com/search?f=tweets&amp;q=%23Finance', 'https://x.com/search?f=tweets&amp;q=%23Investment', 'https://x.com/search?f=tweets&amp;q=%23Banking']</t>
-        </is>
-      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -4698,28 +4691,22 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-#UAE #IslamicBanking #Finance #Investment #Banking</t>
+          <t>A waiting to connect via dm please</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-#UAE #IslamicBanking #Finance #Investment #Banking</t>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-#UAE #IslamicBanking #Finance #Investment #Banking</t>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
     </row>
@@ -4729,71 +4716,75 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052699324711063787</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6trr_</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ع ❥</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2010516983058767872/oVR7T5vc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:08 AM UTC</t>
+          <t>May 8, 2026 · 10:37 AM UTC</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-05-07T08:08:00Z</t>
+          <t>2026-05-08T10:37:00Z</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme']</t>
+        </is>
+      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
@@ -4804,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -4813,26 +4804,28 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
-⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
-💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
-⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
-💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4835,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052674875190317079</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052674875190317079</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4873,16 +4866,16 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+&lt;a href="https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme"&gt;emiratesislamic.ae/en/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -4892,23 +4885,27 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:00 AM UTC</t>
+          <t>May 8, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-05-07T08:00:00Z</t>
+          <t>2026-05-08T09:00:00Z</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme']</t>
+        </is>
+      </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -4917,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -4926,28 +4923,28 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052674875190317079</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
     </row>
@@ -4957,45 +4954,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2052232251371581529</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
+          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/thekimanikamau</t>
+          <t>https://x.com/patilabhijeet45</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>thekimanikamau</t>
+          <t>patilabhijeet45</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Daniel Kimani</t>
+          <t>abhijeet patil</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1923765853935288320/ejHyTEEL_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1383992370509668355/lHQxfCEH_bigger.jpg</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg @emiratesislamic</t>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; Hello Team need your assistance please dm.</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -5005,17 +5000,17 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>May 7</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 3:41 AM UTC</t>
+          <t>May 8, 2026 · 3:11 AM UTC</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-05-07T03:41:00Z</t>
+          <t>2026-05-08T03:11:00Z</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -5025,7 +5020,7 @@
         </is>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -5034,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
@@ -5043,25 +5038,14 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg @emiratesislamic</t>
-        </is>
-      </c>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg @emiratesislamic</t>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5055,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2052347910788890733</t>
+          <t>2052732133949534294</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
+          <t>https://x.com/emiratesislamic/status/2052732133949534294</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5102,14 +5086,12 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -5118,22 +5100,22 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>['Asayeel171930']</t>
+          <t>['omarzouqi']</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:20 AM UTC</t>
+          <t>May 8, 2026 · 12:47 PM UTC</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-05-07T11:20:00Z</t>
+          <t>2026-05-08T12:47:00Z</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr"/>
@@ -5148,7 +5130,7 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -5157,25 +5139,22 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
+          <t>https://x.com/emiratesislamic/status/2052732133949534294</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>@emiratesislamic شوفو الخاص</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>@emiratesislamic شوفو الخاص</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5164,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2052347842044297241</t>
+          <t>2052717380141199866</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5216,12 +5195,14 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -5235,17 +5216,17 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:20 AM UTC</t>
+          <t>May 8, 2026 · 11:48 AM UTC</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-05-07T11:20:00Z</t>
+          <t>2026-05-08T11:48:00Z</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr"/>
@@ -5260,7 +5241,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -5269,22 +5250,27 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5280,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2052342692424696089</t>
+          <t>2052716737154396511</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+          <t>https://x.com/emiratesislamic/status/2052716737154396511</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5325,48 +5311,40 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>Dear Daniel, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026
-Terms &amp;amp; conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-linkedin&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>Dear Daniel, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we&amp;#39;ve sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>['thekimanikamau']</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:00 AM UTC</t>
+          <t>May 8, 2026 · 11:46 AM UTC</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-05-07T11:00:00Z</t>
+          <t>2026-05-08T11:46:00Z</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/salary-transfer-cashback?utm_source=organic-linkedin&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
-        </is>
-      </c>
+      <c r="R45" t="inlineStr"/>
       <c r="S45" t="n">
         <v>0</v>
       </c>
@@ -5377,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -5386,32 +5364,24 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026
-Terms &amp; conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>Dear Daniel, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+          <t>https://x.com/emiratesislamic/status/2052716737154396511</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
         </is>
       </c>
     </row>
@@ -5421,12 +5391,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2052342690600165819</t>
+          <t>2052707828104655235</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052342690600165819</t>
+          <t>https://x.com/emiratesislamic/status/2052707828104655235</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5452,44 +5422,42 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
-💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more
-💰 Competitive profit rates on Auto Finance &amp;amp; Home Finance</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>['patilabhijeet45']</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:00 AM UTC</t>
+          <t>May 8, 2026 · 11:10 AM UTC</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-05-07T11:00:00Z</t>
+          <t>2026-05-08T11:10:00Z</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -5498,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -5507,20 +5475,14 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
-💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Transfer your salary now &amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp; more
-💰 Competitive profit rates on Auto Finance &amp; Home Finance</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
     </row>
@@ -5530,12 +5492,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2052342686976200822</t>
+          <t>2052705193741947100</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052342686976200822</t>
+          <t>https://x.com/emiratesislamic/status/2052705193741947100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5561,20 +5523,16 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=salary_transfer"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ &lt;a href="https://www.emiratesislamic.ae/ar/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme"&gt;emiratesislamic.ae/ar/news-a…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -5584,23 +5542,23 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:00 AM UTC</t>
+          <t>May 8, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-05-07T11:00:00Z</t>
+          <t>2026-05-08T11:00:00Z</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/salary-transfer-cashback?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=salary_transfer']</t>
+          <t>['https://www.emiratesislamic.ae/ar/news-and-updates/2026/May/emirates-islamic-launches-uae-first-shariah-compliant-certificate-of-deposit-programme']</t>
         </is>
       </c>
       <c r="S47" t="n">
@@ -5610,10 +5568,10 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V47" t="n">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -5622,22 +5580,18 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ emiratesislamic.ae/ar/news-a…</t>
         </is>
       </c>
     </row>
@@ -5647,12 +5601,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2052342683113283967</t>
+          <t>2052705076490150108</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052342683113283967</t>
+          <t>https://x.com/emiratesislamic/status/2052705076490150108</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5678,18 +5632,26 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.
+Apply now
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.
+Apply now
+&lt;a href="https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=cc_amazon"&gt;emiratesislamic.ae/en/person…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -5699,32 +5661,36 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 11:00 AM UTC</t>
+          <t>May 8, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-05-07T11:00:00Z</t>
+          <t>2026-05-08T11:00:00Z</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/personal-banking/cards/credit-cards/amazon-redirection?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=cc_amazon']</t>
+        </is>
+      </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>211</v>
+        <v>61</v>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -5733,20 +5699,28 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.
+Apply now
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني</t>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp; lifestyle benefits
+And much more.
+Terms &amp; conditions apply.
+Apply now
+emiratesislamic.ae/en/person…</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5730,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2052341746671948212</t>
+          <t>2052705068227432806</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052341746671948212</t>
+          <t>https://x.com/emiratesislamic/status/2052705068227432806</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5787,42 +5761,46 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية</t>
         </is>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>['Neli_Brown_']</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 10:56 AM UTC</t>
+          <t>May 8, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-05-07T10:56:00Z</t>
+          <t>2026-05-08T11:00:00Z</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
         <v>0</v>
@@ -5831,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -5840,14 +5818,22 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5843,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2052313830538059926</t>
+          <t>2052659770260111552</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052313830538059926</t>
+          <t>https://x.com/emiratesislamic/status/2052659770260111552</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5888,25 +5874,27 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>القاعدة الذهبية للأمان الرقمي:
+⏸️ توقّف.
+🔍 تحقّق.
+✅ تأكّد.
+لن تطلب منك شركات الطيران أو أي جهة رسمية إجراء عملية دفع عبر رابط عشوائي. احرص على استخدام التطبيقات الرسمية دائماً، وتحكم بشكلٍ كامل في بياناتك.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>القاعدة الذهبية للأمان الرقمي:
+⏸️ توقّف.
+🔍 تحقّق.
+✅ تأكّد.
+لن تطلب منك شركات الطيران أو أي جهة رسمية إجراء عملية دفع عبر رابط عشوائي. احرص على استخدام التطبيقات الرسمية دائماً، وتحكم بشكلٍ كامل في بياناتك.</t>
         </is>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>['6trr_']</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>18h</t>
@@ -5914,12 +5902,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 9:05 AM UTC</t>
+          <t>May 8, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-05-07T09:05:00Z</t>
+          <t>2026-05-08T08:00:00Z</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
@@ -5931,10 +5919,10 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>11</v>
+        <v>200</v>
       </c>
       <c r="W50" t="inlineStr">
         <is>
@@ -5943,16 +5931,22 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>القاعدة الذهبية للأمان الرقمي:
+⏸️ توقّف.
+🔍 تحقّق.
+✅ تأكّد.
+لن تطلب منك شركات الطيران أو أي جهة رسمية إجراء عملية دفع عبر رابط عشوائي. احرص على استخدام التطبيقات الرسمية دائماً، وتحكم بشكلٍ كامل في بياناتك.</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>القاعدة الذهبية للأمان الرقمي:
+⏸️ توقّف.
+🔍 تحقّق.
+✅ تأكّد.
+لن تطلب منك شركات الطيران أو أي جهة رسمية إجراء عملية دفع عبر رابط عشوائي. احرص على استخدام التطبيقات الرسمية دائماً، وتحكم بشكلٍ كامل في بياناتك.</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5956,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2052297395296243819</t>
+          <t>2052641342807740881</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297395296243819</t>
+          <t>https://x.com/emiratesislamic/status/2052641342807740881</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5993,29 +5987,23 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>🚗 Complimentary airport transfers, meet &amp; greet services
-⛳ Golf rounds at select premium courses
-🅿️ Valet parking, and much more
-Valid till 31 May 2026
-Terms and conditions apply
-emiratesislamic.ae/en/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
-⛳ Golf rounds at select premium courses
-🅿️ Valet parking, and much more
-Valid till 31 May 2026
-Terms and conditions apply
-&lt;a href="https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>['urdupoetry1111']</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>20h</t>
@@ -6023,20 +6011,16 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:00 AM UTC</t>
+          <t>May 8, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-05-07T08:00:00Z</t>
+          <t>2026-05-08T06:46:00Z</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
         <v>0</v>
       </c>
@@ -6047,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -6056,24 +6040,14 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>🚗 Complimentary airport transfers, meet &amp; greet services
-⛳ Golf rounds at select premium courses
-🅿️ Valet parking, and much more
-Valid till 31 May 2026
-Terms and conditions apply
-emiratesislamic.ae/en/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>🚗 Complimentary airport transfers, meet &amp; greet services
-⛳ Golf rounds at select premium courses
-🅿️ Valet parking, and much more
-Valid till 31 May 2026
-Terms and conditions apply
-emiratesislamic.ae/en/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6057,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2052297388321104214</t>
+          <t>2052635691859796067</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297388321104214</t>
+          <t>https://x.com/emiratesislamic/status/2052635691859796067</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6114,29 +6088,23 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو2026
-تطبق الشروط والأحكام
-emiratesislamic.ae/ar/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو2026
-تطبق الشروط والأحكام
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=etihad"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>['patilabhijeet45']</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>20h</t>
@@ -6144,20 +6112,16 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:00 AM UTC</t>
+          <t>May 8, 2026 · 6:24 AM UTC</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-05-07T08:00:00Z</t>
+          <t>2026-05-08T06:24:00Z</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/bonus-etihad-miles-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=etihad']</t>
-        </is>
-      </c>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
         <v>1</v>
       </c>
@@ -6168,7 +6132,7 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -6177,24 +6141,14 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو2026
-تطبق الشروط والأحكام
-emiratesislamic.ae/ar/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
-⛳جولات الغولف
-🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو2026
-تطبق الشروط والأحكام
-emiratesislamic.ae/ar/offers…</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
     </row>
@@ -6204,12 +6158,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2052297385615708568</t>
+          <t>2052629126318629363</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297385615708568</t>
+          <t>https://x.com/emiratesislamic/status/2052629126318629363</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6235,23 +6189,23 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="K53" t="b">
         <v>0</v>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>['AsadNoman1']</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>20h</t>
@@ -6259,12 +6213,12 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>May 7, 2026 · 8:00 AM UTC</t>
+          <t>May 8, 2026 · 5:58 AM UTC</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-05-07T08:00:00Z</t>
+          <t>2026-05-08T05:58:00Z</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr"/>
@@ -6276,10 +6230,10 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" t="n">
-        <v>143</v>
+        <v>4</v>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -6288,119 +6242,14 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2052252091914035405</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052252091914035405</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
-Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
-Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
-        </is>
-      </c>
-      <c r="K54" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>May 7, 2026 · 5:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>2026-05-07T05:00:00Z</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1</v>
-      </c>
-      <c r="V54" t="n">
-        <v>95</v>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
-Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>شاركونا في اليوم الأخير لزيارة معرض ’اصنع في الإمارات 2026‘. انضموا إلينا وتعرفوا على أحدث الحلول للخدمات المصرفية للأعمال.
-Last day to visit us at ‘Make It In The Emirates 2026’ exhibition! Join us and explore our latest Business Banking solutions</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -1970,16 +1970,8 @@
           <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
           <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
@@ -2415,19 +2407,11 @@
           <t>Still no update...</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
+          <t>Still no update...</t>
         </is>
       </c>
     </row>
@@ -2524,19 +2508,11 @@
           <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
+          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
         </is>
       </c>
     </row>
@@ -2651,19 +2627,17 @@
 BANK: EMIRATES NBD</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
-        </is>
-      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
+          <t>+971 555 906879 
+BENEFICIARY: 
+AKHTAR NAZIR MOTIWALA
+AC NO: 1014895574401
+IBAN: AE37 0260 0010 1489 5574 401
+Swift: EBILAEADXXX
+BANK: EMIRATES NBD</t>
         </is>
       </c>
     </row>
@@ -2865,8 +2839,16 @@
           <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
@@ -2966,11 +2948,19 @@
           <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>@multibank_io @AECoin_UAE Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
+          <t>@multibank_io @AECoin_UAE Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
     </row>
@@ -3067,151 +3057,12 @@
           <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2052680648222032220</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/HadiAlduba89157</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>HadiAlduba89157</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Hadi Aldubaisi</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>May 8, 2026 · 9:22 AM UTC</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2026-05-08T09:22:00Z</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>69</v>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2052680277336703430</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/multibank_io/status/2052680277336703430</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/multibank_io</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>multibank_io</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>mb.io</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2015689534328250368/-RLE2RH__bigger.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
 Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
@@ -3220,6 +3071,173 @@
 Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2052680648222032220</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/HadiAlduba89157</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HadiAlduba89157</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Hadi Aldubaisi</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>May 8, 2026 · 9:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2026-05-08T09:22:00Z</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>69</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/multibank_io</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>multibank_io</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>mb.io</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2015689534328250368/-RLE2RH__bigger.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
@@ -3281,15 +3299,19 @@
 Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>@multibank_io @AECoin_UAE Yes obviously bring it to mb io this is exactly what the region needs right now</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want $AEC and $USDU on ⬡ mb io? 
-Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
+          <t>@multibank_io @AECoin_UAE Yes obviously bring it to mb io this is exactly what the region needs right now</t>
         </is>
       </c>
     </row>
@@ -3934,8 +3956,17 @@
 Please help.</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://x.com/NaveedDumasia/status/2052649301046915394</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Trying to call @EmiratesNBD_AE  customer support but in vain. 
+Please help.</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>Trying to call @EmiratesNBD_AE  customer support but in vain. 
@@ -4032,8 +4063,16 @@
           <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://x.com/EdutainNinja/status/2052635129198112859</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>Watching Emirates NBD grow 6% deposits this quarter from my living room during the all-clears. AED 1.22T stays put. Locals hedge; outsiders panic. My banking app never flinched.</t>
@@ -4133,8 +4172,16 @@
           <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>https://x.com/memd619/status/2052547700638245362</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA الكاش باك صفر عندي ؟! ايش المشكله</t>
@@ -4234,11 +4281,25 @@
           <t>still not fixed its 2nd day now , how to login and payments ?</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>https://x.com/AsadNoman1/status/2052765405383667833</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>still not fixed its 2nd day now , how to login and payments ?</t>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
         </is>
       </c>
     </row>
@@ -4338,12 +4399,21 @@
 #EmiratesIslamic #IslamicBanking #UAEFinance #ShariahCompliant #FinancialInnovation #BankingSector</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>https://x.com/ForumRemittance/status/2052712527633481877</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>IMKAN Properties, a leading global master developer headquartered in Abu Dhabi, has partnered with Zelo, a UAE-based private financing platform and subsidiary of International Holding Company (IHC)
+#IMKAN #Zelo #AbuDhabi #EmbeddedFinance #Fintech #IHC #RealEstateDevelopment https://t.co/Q8uqxnooKt</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Emirates Islamic, a leading Islamic financial institution in the #UAE, has successfully introduced the country’s first Shari’ah-compliant Certificate of Deposit (CD) Programme
-#EmiratesIslamic #IslamicBanking #UAEFinance #ShariahCompliant #FinancialInnovation #BankingSector</t>
+          <t>IMKAN Properties, a leading global master developer headquartered in Abu Dhabi, has partnered with Zelo, a UAE-based private financing platform and subsidiary of International Holding Company (IHC)
+#IMKAN #Zelo #AbuDhabi #EmbeddedFinance #Fintech #IHC #RealEstateDevelopment https://t.co/Q8uqxnooKt</t>
         </is>
       </c>
     </row>
@@ -4446,23 +4516,13 @@
 emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
-اقرأ المزيد:
- https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
-        </is>
-      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
-اقرأ المزيد:
- https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
+ Read the article: 
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
     </row>
@@ -4577,27 +4637,17 @@
 Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
-        </is>
-      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن emiratesislamic.ae/ar/person…
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
     </row>
@@ -4694,19 +4744,11 @@
           <t>A waiting to connect via dm please</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
-        </is>
-      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+          <t>A waiting to connect via dm please</t>
         </is>
       </c>
     </row>
@@ -4809,23 +4851,13 @@
 emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
  Read the article: 
-https://t.co/V0HzCCKh4m</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
- Read the article: 
-https://t.co/V0HzCCKh4m</t>
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
     </row>
@@ -4928,23 +4960,13 @@
 emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052674875190317079</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
  Read the article: 
-https://t.co/V0HzCCKh4m</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
- Read the article: 
-https://t.co/V0HzCCKh4m</t>
+emiratesislamic.ae/en/news-a…</t>
         </is>
       </c>
     </row>
@@ -5041,8 +5063,16 @@
           <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>@emiratesislamic Hello Team need your assistance please dm.</t>
@@ -5149,12 +5179,16 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>@emiratesislamic شوفو الخاص</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>@emiratesislamic شوفو الخاص</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
     </row>
@@ -5478,11 +5512,19 @@
           <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052707828104655235</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>@emiratesislamic A waiting to connect via dm please</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>@emiratesislamic A waiting to connect via dm please</t>
         </is>
       </c>
     </row>

--- a/df_final.xlsx
+++ b/df_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,63 +566,67 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2052925380936491470</t>
+          <t>2053322615134273715</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/jurian777/status/2052925380936491470</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/jurian777</t>
+          <t>https://x.com/WahibaEsri</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>jurian777</t>
+          <t>WahibaEsri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>齋藤純 Jun Saito</t>
+          <t>Wahiba Esri</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2052150684968218625/9AJu83Hb_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028034758962515968/s2weQOER_bigger.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+          <t>Sure will send now. Thank you 😊</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+          <t>Sure will send now. Thank you 😊</t>
         </is>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>7m</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>May 9, 2026 · 1:35 AM UTC</t>
+          <t>May 10, 2026 · 3:53 AM UTC</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-05-09T01:35:00Z</t>
+          <t>2026-05-10T03:53:00Z</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -637,7 +641,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -646,22 +650,22 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+          <t>Sure will send now. Thank you 😊</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://x.com/jurian777/status/2052925380936491470</t>
+          <t>https://x.com/WahibaEsri/status/2053322615134273715</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
     </row>
@@ -671,43 +675,43 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2052836145461887127</t>
+          <t>2053214685823221984</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008</t>
+          <t>https://x.com/hamad5uae</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>alamair2008</t>
+          <t>hamad5uae</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AZIZ ALGHAMDI</t>
+          <t>حمد الصعاق 🇦🇪</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1060909169958641665/n_4aleHZ_bigger.jpg</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+          <t>الفريق رد برد غبي يقول هاذا عند التحقق و هاذا غير صحيح و صدّر تحديث اليوم اعتقدت انه بيحل الاشكال ولاكن التجاهل واضح يا من يّدعي الخصوصية الخصوصية اصبحت كلام يقال عند الحاجة</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+          <t>الفريق رد برد غبي يقول هاذا عند التحقق و هاذا غير صحيح و صدّر تحديث اليوم اعتقدت انه بيحل الاشكال ولاكن التجاهل واضح يا من يّدعي الخصوصية الخصوصية اصبحت كلام يقال عند الحاجة</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -716,7 +720,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -726,12 +730,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 7:40 PM UTC</t>
+          <t>May 9, 2026 · 8:45 PM UTC</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-05-08T19:40:00Z</t>
+          <t>2026-05-09T20:45:00Z</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -746,7 +750,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -755,40 +759,26 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+          <t>الفريق رد برد غبي يقول هاذا عند التحقق و هاذا غير صحيح و صدّر تحديث اليوم اعتقدت انه بيحل الاشكال ولاكن التجاهل واضح يا من يّدعي الخصوصية الخصوصية اصبحت كلام يقال عند الحاجة</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+          <t>https://x.com/hamad5uae/status/2053214685823221984</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
-رغم ان  (تقييمي 751 ممتاز) 
-الأغرب؟ 
-حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
-رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
-هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
-سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
-من يريد أن يكون الشريك الحقيقي؟ 
-@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
+          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
+By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
+#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
-رغم ان  (تقييمي 751 ممتاز) 
-الأغرب؟ 
-حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
-رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
-هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
-سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
-من يريد أن يكون الشريك الحقيقي؟ 
-@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
+          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
+By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
+#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
         </is>
       </c>
     </row>
@@ -798,43 +788,43 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2052796942841795039</t>
+          <t>2053208001905860832</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn</t>
+          <t>https://x.com/khaja_moin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>hadi_msn</t>
+          <t>khaja_moin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hadi</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1295674429180125184/LuNcyvm9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1550614901487443975/DcrDW-Qa_bigger.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
+          <t>نرجو من Emirates NBD التعامل مع شكاوى العملاء بشكل أفضل وحل المشكلة بأسرع وقت.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
+          <t>نرجو من Emirates NBD التعامل مع شكاوى العملاء بشكل أفضل وحل المشكلة بأسرع وقت.</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -843,28 +833,28 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>['faisalalamoudi3', 'EmiratesNBD_KSA']</t>
+          <t>['khaja_moin', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 5:05 PM UTC</t>
+          <t>May 9, 2026 · 8:18 PM UTC</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-05-08T17:05:00Z</t>
+          <t>2026-05-09T20:18:00Z</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -873,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -882,22 +872,24 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
+          <t>نرجو من Emirates NBD التعامل مع شكاوى العملاء بشكل أفضل وحل المشكلة بأسرع وقت.</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+          <t>https://x.com/khaja_moin/status/2053208001905860832</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
     </row>
@@ -907,73 +899,73 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2052794731063566348</t>
+          <t>2053207767746326594</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
+          <t>https://x.com/khaja_moin/status/2053207767746326594</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn</t>
+          <t>https://x.com/khaja_moin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>hadi_msn</t>
+          <t>khaja_moin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hadi</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1295674429180125184/LuNcyvm9_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1550614901487443975/DcrDW-Qa_bigger.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>راح الرايح
-االتطبيق فيه مشكلة .. النقاط صفر</t>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>راح الرايح
-االتطبيق فيه مشكلة .. النقاط صفر</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 4:56 PM UTC</t>
+          <t>May 9, 2026 · 8:17 PM UTC</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-05-08T16:56:00Z</t>
+          <t>2026-05-09T20:17:00Z</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
@@ -984,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -993,27 +985,16 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>راح الرايح
-االتطبيق فيه مشكلة .. النقاط صفر</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>نفحصها ونعتمدها قبل نمولك 🚙
-انطلق بثقة مع تمويل السيارات المستعملة من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/CXCUIwu26x https://t.co/5sMib0U399</t>
-        </is>
-      </c>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>نفحصها ونعتمدها قبل نمولك 🚙
-انطلق بثقة مع تمويل السيارات المستعملة من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/CXCUIwu26x https://t.co/5sMib0U399</t>
+          <t>@EmiratesNBD_KSA تم خصم رسوم دخول صالة المطار من بطاقتي من قبل بنك الإمارات دبي الوطني بشكل خاطئ، وقمت بتقديم شكوى عبر البريد الإلكتروني والاتصال على الرقم المجاني، لكن للأسف لا يوجد أي رد حتى بعد الانتظار لأكثر من 30 دقيقة على الخط!
+نرجو من ENBD التعامل مع شكاوى العملاء بشكل</t>
         </is>
       </c>
     </row>
@@ -1023,69 +1004,73 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2052788485925617818</t>
+          <t>2053137035909648470</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/goacm/status/2052788485925617818</t>
+          <t>https://x.com/Researchpub9/status/2053137035909648470</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/goacm</t>
+          <t>https://x.com/Researchpub9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>goacm</t>
+          <t>Researchpub9</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CMO Goa</t>
+          <t>المنارة | النشر العلمي</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1649293753528745984/_vioJs5y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2024869127861514241/GV2yemvW_bigger.jpg</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
+          <t>برنامج مميز يعزز مهارات القيادة وصناعة القرار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
+          <t>برنامج مميز يعزز مهارات القيادة وصناعة القرار</t>
         </is>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>['thefaksa', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 4:31 PM UTC</t>
+          <t>May 9, 2026 · 3:36 PM UTC</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-05-08T16:31:00Z</t>
+          <t>2026-05-09T15:36:00Z</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1094,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1103,22 +1088,26 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
+          <t>برنامج مميز يعزز مهارات القيادة وصناعة القرار</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://x.com/goacm/status/2052788485925617818</t>
+          <t>https://x.com/Researchpub9/status/2053137035909648470</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Chief Minister @DrPramodPSawant met Shri R. Subramaniakumar, MD &amp;amp; CEO of @rblbank , and held discussions on various aspects relating to the banking sector, economic growth, and the Bank’s contribution towards India’s financial ecosystem. https://t.co/R2xc5qKMAC</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+#معاً_نصنع_الأثر
+#الأكاديمية_المالية https://t.co/4OzuLTEgnR</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Chief Minister @DrPramodPSawant met Shri R. Subramaniakumar, MD &amp;amp; CEO of @rblbank , and held discussions on various aspects relating to the banking sector, economic growth, and the Bank’s contribution towards India’s financial ecosystem. https://t.co/R2xc5qKMAC</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+#معاً_نصنع_الأثر
+#الأكاديمية_المالية https://t.co/4OzuLTEgnR</t>
         </is>
       </c>
     </row>
@@ -1128,43 +1117,51 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2052787631394619720</t>
+          <t>2053135322284982652</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA/status/2052787631394619720</t>
+          <t>https://x.com/centralbankuae/status/2053135322284982652</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/JJPnlXDGrYuyPOA</t>
+          <t>https://x.com/centralbankuae</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JJPnlXDGrYuyPOA</t>
+          <t>centralbankuae</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>سلطان الصاعدي</t>
+          <t>Central Bank of the UAE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1509025183151104007/5ogA9Xuh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1173,28 +1170,32 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['HussainAzh82168', 'EmiratesNBD_AE', 'WioBank']</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 4:28 PM UTC</t>
+          <t>May 9, 2026 · 3:29 PM UTC</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-05-08T16:28:00Z</t>
+          <t>2026-05-09T15:29:00Z</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
+        </is>
+      </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1203,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1212,14 +1213,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>وش فيها مزيد ماوصلت النقاط الى الان وخدمة الدفع متعطلة !!</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
     </row>
@@ -1229,45 +1238,51 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2052783114410144160</t>
+          <t>2053135160309404091</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052783114410144160</t>
+          <t>https://x.com/centralbankuae/status/2053135160309404091</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157</t>
+          <t>https://x.com/centralbankuae</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HadiAlduba89157</t>
+          <t>centralbankuae</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hadi Aldubaisi</t>
+          <t>Central Bank of the UAE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
-شكرا جزيلا على الاستجابه</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
-شكرا جزيلا على الاستجابه</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1276,28 +1291,32 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['AsliAfnas', 'paywithtabby', 'asktabby', 'ENBDdeals', 'EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 4:10 PM UTC</t>
+          <t>May 9, 2026 · 3:29 PM UTC</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-05-08T16:10:00Z</t>
+          <t>2026-05-09T15:29:00Z</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
+        </is>
+      </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1306,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1315,16 +1334,22 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
-شكرا جزيلا على الاستجابه</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>هذا الرد الاحترافي الذي يحتاجه كل عميل
-شكرا جزيلا على الاستجابه</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
     </row>
@@ -1334,43 +1359,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2052782850760421453</t>
+          <t>2053128972691505181</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052782850760421453</t>
+          <t>https://x.com/OsamaBadandy/status/2053128972691505181</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157</t>
+          <t>https://x.com/OsamaBadandy</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HadiAlduba89157</t>
+          <t>OsamaBadandy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hadi Aldubaisi</t>
+          <t>Osama Badandy</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2021870405548494848/YQ7mP-bp_bigger.jpg</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
+          <t>القيادة اليوم تحتاج توازن بين وضوح الرؤية والقدرة على التنفيذ وبرامج بهالنوع تصنع فرق حقيقي في جاهزية القيادات لمتغيرات السوق خطوة موفقة وشراكة ملهمة تستحق التقدير</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
+          <t>القيادة اليوم تحتاج توازن بين وضوح الرؤية والقدرة على التنفيذ وبرامج بهالنوع تصنع فرق حقيقي في جاهزية القيادات لمتغيرات السوق خطوة موفقة وشراكة ملهمة تستحق التقدير</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1379,22 +1404,22 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['thefaksa', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 4:09 PM UTC</t>
+          <t>May 9, 2026 · 3:04 PM UTC</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-05-08T16:09:00Z</t>
+          <t>2026-05-09T15:04:00Z</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1409,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1418,14 +1443,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
+          <t>القيادة اليوم تحتاج توازن بين وضوح الرؤية والقدرة على التنفيذ وبرامج بهالنوع تصنع فرق حقيقي في جاهزية القيادات لمتغيرات السوق خطوة موفقة وشراكة ملهمة تستحق التقدير</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>اتمنى ان الرسائل الخاصه متاحه لكن منصة اكس تتطلب توثيق برسوم حتى يتسنى لنا ارسال رسالة خاصة</t>
+          <t>القيادة اليوم تحتاج توازن بين وضوح الرؤية والقدرة على التنفيذ وبرامج بهالنوع تصنع فرق حقيقي في جاهزية القيادات لمتغيرات السوق خطوة موفقة وشراكة ملهمة تستحق التقدير</t>
         </is>
       </c>
     </row>
@@ -1435,88 +1460,86 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2052778577695773164</t>
+          <t>2053105582903525791</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008/status/2052778577695773164</t>
+          <t>https://x.com/thefaksa/status/2053105582903525791</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008</t>
+          <t>https://x.com/thefaksa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>alamair2008</t>
+          <t>thefaksa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AZIZ ALGHAMDI</t>
+          <t>الأكاديمية المالية</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1896320398397976576/d6YamQ7a_bigger.jpg</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
-وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
-ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
-من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+#معاً_نصنع_الأثر
+#الأكاديمية_المالية</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
-وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
-ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
-من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني &lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+&lt;a href="/search?f=tweets&amp;amp;q=%23معاً_نصنع_الأثر"&gt;#معاً_نصنع_الأثر&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الأكاديمية_المالية"&gt;#الأكاديمية_المالية&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 3:52 PM UTC</t>
+          <t>May 9, 2026 · 1:31 PM UTC</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-05-08T15:52:00Z</t>
+          <t>2026-05-09T13:31:00Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA', 'https://x.com/search?f=tweets&amp;q=%23معاً_نصنع_الأثر', 'https://x.com/search?f=tweets&amp;q=%23الأكاديمية_المالية']</t>
+        </is>
+      </c>
       <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>17</v>
+        <v>1438</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1525,20 +1548,18 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
-وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
-ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
-من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+#معاً_نصنع_الأثر
+#الأكاديمية_المالية</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
-وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
-ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
-من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
+          <t>اختتام برنامج التفكير الاستراتيجي والتنفيذي بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_KSA ، لتعزيز مهارات التفكير الاستراتيجي والقدرات التنفيذية لقيادة الأعمال بكفاءة.
+#معاً_نصنع_الأثر
+#الأكاديمية_المالية</t>
         </is>
       </c>
     </row>
@@ -1548,75 +1569,71 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2052761822374121589</t>
+          <t>2053101582175326235</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052761822374121589</t>
+          <t>https://x.com/WahibaEsri/status/2053101582175326235</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02</t>
+          <t>https://x.com/WahibaEsri</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>samial7arbi02</t>
+          <t>WahibaEsri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>سامي الحربي</t>
+          <t>Wahiba Esri</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1257489089693171713/34cxDVUO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028034758962515968/s2weQOER_bigger.jpg</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
-وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
-لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
-وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
-لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA', 'ENBDdeals']</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 2:45 PM UTC</t>
+          <t>May 9, 2026 · 1:15 PM UTC</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-05-08T14:45:00Z</t>
+          <t>2026-05-09T13:15:00Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S11" t="n">
         <v>2</v>
       </c>
@@ -1627,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>201</v>
+        <v>6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1636,18 +1653,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
-وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
-لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>أشكر تفاعلكم لكن حفاظاً على دقة الوقائع أرجو تزويدي بوقت وتاريخ وأرقام محاولات التواصل التي أشرتم إليها في الرسائل الخاصة حيث لا يوجد لدي أي اتصال فائت من البنك حتى هذه اللحظة.
-وما زلت حتى الآن غير قادر على رفع شكوى داخلية بخصوص الواقعة رغم مرور أكثر من 24 ساعة وهو جوهر الإشكال منذ البداية، إذ إن الموضوع لم يكن مجرد طلب تمويل بل أيضاً رفض فتح حساب جاري استناداً إلى معلومات تم إبلاغي بها شفهياً حول “بلاك ليست” ومنع مصرفي عام، رغم سلامة سجلي الائتماني وعدم وجود أي مانع بحسب إفادة البنك المركزي السعودي.
-لذلك ما زلت أطلب توضيح الأساس النظامي لهذه الإفادة، وتمكيني من استخدام قنوات الشكاوى الرسمية للتحقق منها أو الاعتراض عليها بصورة مهنية وشفافة تحفظ حق العميل وحق البنك في آنٍ واحد</t>
+          <t>@EmiratesNBD_AE very disappointed, I took your skywards credit card with a promise of an upgrade to silver on my Emirates skywards, I’ve followed up with the sales representative several times and still no change.</t>
         </is>
       </c>
     </row>
@@ -1657,45 +1670,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2052756273901576234</t>
+          <t>2053099385509314696</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/ihab/status/2052756273901576234</t>
+          <t>https://x.com/AnAgitator/status/2053099385509314696</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/ihab</t>
+          <t>https://x.com/AnAgitator</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ihab</t>
+          <t>AnAgitator</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ihab</t>
+          <t>Hunain Pirzada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1990048505319350272/P2gVhwvd_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1747440388019822593/wUUvbdzA_bigger.jpg</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp; apps asking me to update my EmiratesID. 
-Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
+          <t>Let’s see the if the case resolves as early as ENBD response on social media time ticks 🕰️ Email sent</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp;amp; apps asking me to update my EmiratesID. 
-Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
+          <t>Let’s see the if the case resolves as early as ENBD response on social media time ticks 🕰️ Email sent</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1704,22 +1715,22 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>['Hayataholica']</t>
+          <t>['ENBDdeals']</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 2:23 PM UTC</t>
+          <t>May 9, 2026 · 1:06 PM UTC</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-05-08T14:23:00Z</t>
+          <t>2026-05-09T13:06:00Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1731,10 +1742,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>469</v>
+        <v>15</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1743,27 +1754,24 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>No no it’s not a scam message. I’ve just been bombarded with platforms &amp; apps asking me to update my EmiratesID. 
-Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
+          <t>Let’s see the if the case resolves as early as ENBD response on social media time ticks 🕰️ Email sent</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://x.com/ihab/status/2052756273901576234</t>
+          <t>https://x.com/AnAgitator/status/2053099385509314696</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>"Your Emirates ID has expired - Please update it now !!!"
-I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
-"!!! !!! !!! !!!" haha</t>
+          <t>Got Etihad Guest Visa Elevate Card from one of ENBD agent upon signing the docs and before opening he told me that 40K limit will be allocated but upon receiving the card 1300 limit is opened. Now as per the agent technical error is being corrected since 10 days 🙄🤦🏻‍♂️
+@ENBDdeals</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>"Your Emirates ID has expired - Please update it now !!!"
-I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
-"!!! !!! !!! !!!" haha</t>
+          <t>Got Etihad Guest Visa Elevate Card from one of ENBD agent upon signing the docs and before opening he told me that 40K limit will be allocated but upon receiving the card 1300 limit is opened. Now as per the agent technical error is being corrected since 10 days 🙄🤦🏻‍♂️
+@ENBDdeals</t>
         </is>
       </c>
     </row>
@@ -1773,45 +1781,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2052747585438495200</t>
+          <t>2053096589762482434</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak/status/2052747585438495200</t>
+          <t>https://x.com/AnAgitator/status/2053096589762482434</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak</t>
+          <t>https://x.com/AnAgitator</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>masdarak</t>
+          <t>AnAgitator</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>المصدر العقاري</t>
+          <t>Hunain Pirzada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1565412876965318657/wRffEOKq_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1747440388019822593/wUUvbdzA_bigger.jpg</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
-masdarak.com/home-finance/%D…</t>
+          <t>Got Etihad Guest Visa Elevate Card from one of ENBD agent upon signing the docs and before opening he told me that 40K limit will be allocated but upon receiving the card 1300 limit is opened. Now as per the agent technical error is being corrected since 10 days 🙄🤦🏻‍♂️
+@ENBDdeals</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية &lt;a href="/emaardubai" title="Emaar Dubai"&gt;@emaardubai&lt;/a&gt;  بالتعاون مع بنك الإمارات دبي الوطني &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  وبنك أبوظبي التجاري  &lt;a href="/OfficialADCB" title="ADCB بنك أبوظبي التجاري"&gt;@OfficialADCB&lt;/a&gt;  بما يشمل غير المقيمين في دولة الإمارات
-&lt;a href="https://www.masdarak.com/home-finance/%D8%A5%D8%B7%D9%84%D8%A7%D9%82-%D8%AD%D9%84%D9%88%D9%84-%D9%84%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D8%B4%D8%B1%D8%A7%D8%A1-%D8%A7%D9%84%D8%B9%D9%82%D8%A7%D8%B1%D8%A7%D8%AA-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AE%D8%B1%D9%8A%D8%B7%D8%A9-%D9%81%D9%8A-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9-%D8%A5%D8%B9%D9%85%D8%A7%D8%B1"&gt;masdarak.com/home-finance/%D…&lt;/a&gt;</t>
+          <t>Got Etihad Guest Visa Elevate Card from one of ENBD agent upon signing the docs and before opening he told me that 40K limit will be allocated but upon receiving the card 1300 limit is opened. Now as per the agent technical error is being corrected since 10 days 🙄🤦🏻‍♂️
+&lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1821,36 +1829,36 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 1:48 PM UTC</t>
+          <t>May 9, 2026 · 12:55 PM UTC</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-05-08T13:48:00Z</t>
+          <t>2026-05-09T12:55:00Z</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['https://x.com/emaardubai', 'https://x.com/EmiratesNBD_AE', 'https://x.com/OfficialADCB', 'https://www.masdarak.com/home-finance/%D8%A5%D8%B7%D9%84%D8%A7%D9%82-%D8%AD%D9%84%D9%88%D9%84-%D9%84%D8%AA%D9%85%D9%88%D9%8A%D9%84-%D8%B4%D8%B1%D8%A7%D8%A1-%D8%A7%D9%84%D8%B9%D9%82%D8%A7%D8%B1%D8%A7%D8%AA-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AE%D8%B1%D9%8A%D8%B7%D8%A9-%D9%81%D9%8A-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9-%D8%A5%D8%B9%D9%85%D8%A7%D8%B1']</t>
+          <t>['https://x.com/ENBDdeals']</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1859,25 +1867,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
-masdarak.com/home-finance/%D…</t>
+          <t>Got Etihad Guest Visa Elevate Card from one of ENBD agent upon signing the docs and before opening he told me that 40K limit will be allocated but upon receiving the card 1300 limit is opened. Now as per the agent technical error is being corrected since 10 days 🙄🤦🏻‍♂️
+@ENBDdeals</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak/status/2052747585438495200</t>
+          <t>https://x.com/AnAgitator/status/2053096589762482434</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
- https://t.co/bq6bpOlUdV</t>
+          <t>@AnAgitator Hi Hunain, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
- https://t.co/bq6bpOlUdV</t>
+          <t>@AnAgitator Hi Hunain, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
     </row>
@@ -1887,43 +1893,69 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2052739053989007588</t>
+          <t>2053074699110789212</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
+          <t>https://x.com/Kashif111144/status/2053074699110789212</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/Farooq_AI</t>
+          <t>https://x.com/Kashif111144</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Farooq_AI</t>
+          <t>Kashif111144</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TT Aspiring</t>
+          <t>Kashif</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1931385156696244224/ITF6uo1x_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035721972361928704/W-51tE0S_bigger.jpg</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
+          <t>UAE controls Pakistan banking bribing leaders for decades. 
+BANKS owned by UAE in PK(not complete list) 
+1. Alfalah 
+2. Dubai Islamic 
+3. Mashreq 
+4. Emirates NBD 
+5. Emirates Global 
+6. FWB 
+7. Al Baraka 
+8. Ubank 
+9. EasyPaisa 
+10. Jazzcash  
+11. BML  
+#Islamabad #Pakistan #UAE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai&amp;#39;s losing innocence, not capital. I&amp;#39;m watching who positions for the recovery.</t>
+          <t>UAE controls Pakistan banking bribing leaders for decades. 
+BANKS owned by UAE in PK(not complete list) 
+1. Alfalah 
+2. Dubai Islamic 
+3. Mashreq 
+4. Emirates NBD 
+5. Emirates Global 
+6. FWB 
+7. Al Baraka 
+8. Ubank 
+9. EasyPaisa 
+10. Jazzcash  
+11. BML  
+&lt;a href="/search?f=tweets&amp;amp;q=%23Islamabad"&gt;#Islamabad&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Pakistan"&gt;#Pakistan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1933,21 +1965,25 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 1:15 PM UTC</t>
+          <t>May 9, 2026 · 11:28 AM UTC</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-05-08T13:15:00Z</t>
+          <t>2026-05-09T11:28:00Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Islamabad', 'https://x.com/search?f=tweets&amp;q=%23Pakistan', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
+        </is>
+      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -1958,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -1967,14 +2003,37 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
+          <t>UAE controls Pakistan banking bribing leaders for decades. 
+BANKS owned by UAE in PK(not complete list) 
+1. Alfalah 
+2. Dubai Islamic 
+3. Mashreq 
+4. Emirates NBD 
+5. Emirates Global 
+6. FWB 
+7. Al Baraka 
+8. Ubank 
+9. EasyPaisa 
+10. Jazzcash  
+11. BML  
+#Islamabad #Pakistan #UAE</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>https://x.com/Kashif111144/status/2053074699110789212</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>UAE benefits from sanctions on Iran . Becoming 2nd largest trading partner of Iran. If sanctions are lifted all trade will go DIRECT to Iran , no longer any need for  UAE ports 
+ #uae #iran</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
+          <t>UAE benefits from sanctions on Iran . Becoming 2nd largest trading partner of Iran. If sanctions are lifted all trade will go DIRECT to Iran , no longer any need for  UAE ports 
+ #uae #iran</t>
         </is>
       </c>
     </row>
@@ -1984,73 +2043,77 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2052730384857600235</t>
+          <t>2053051787704164789</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+          <t>https://x.com/naser8581/status/2053051787704164789</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157</t>
+          <t>https://x.com/naser8581</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HadiAlduba89157</t>
+          <t>naser8581</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hadi Aldubaisi</t>
+          <t>NASSER</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2041409109241810944/qL1Z5oGu_bigger.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>وانا كذلك المشكلة شائعه
-عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
+          <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>وانا كذلك المشكلة شائعه
-عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
+          <t>&lt;a href="/DXBMediaOffice" title="Dubai Media Office"&gt;@DXBMediaOffice&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  &lt;a href="/EmiratesNBD_EGY" title="Emirates NBD"&gt;@EmiratesNBD_EGY&lt;/a&gt; 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA', 'Moh_Dul95']</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 12:40 PM UTC</t>
+          <t>May 9, 2026 · 9:57 AM UTC</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-05-08T12:40:00Z</t>
+          <t>2026-05-09T09:57:00Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['https://x.com/DXBMediaOffice', 'https://x.com/ENBDdeals', 'https://x.com/EmiratesNBD_AE', 'https://x.com/EmiratesNBD_EGY']</t>
+        </is>
+      </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
@@ -2061,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2070,27 +2133,31 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>وانا كذلك المشكلة شائعه
-عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
+          <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+          <t>https://x.com/naser8581/status/2053051787704164789</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
+          <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
+          <t>@DXBMediaOffice @ENBDdeals @EmiratesNBD_AE  @EmiratesNBD_EGY 
+أرفع هذه الشكوى بسبب تعثرها مع خدمة العملاء وعدم وجود حل واضح. طلبي بسيط: 
+رقم إيصال التحويل لسداد المديونية، 
+لكن تم رفع طلب 3 أيام عمل بلا مبرر. لدي مبلغ محجوز بحجة مخالصة، ومع ذلك سيُخصم قسط مايو. وضع غير منطقي !!!!</t>
         </is>
       </c>
     </row>
@@ -2100,43 +2167,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2052727923002761539</t>
+          <t>2053043908301783179</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
+          <t>https://x.com/HussainAzh82168/status/2053043908301783179</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar</t>
+          <t>https://x.com/HussainAzh82168</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MotiwalaAkhtar</t>
+          <t>HussainAzh82168</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Akhtar Motiwala</t>
+          <t>Azher Hussain</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1771472983200034816/FZyCNOjV_bigger.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
+          <t>@centralbankuae @WioBank 
+5 hours wasted yesterday on the Wio issue and then 2 hours today on eNBD.
+This is amateur hour.
+The issues &amp; work arounds  should have been immediately pushed to customers.
+It shows an utter lack of respect for your CUSTOMERS.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
+          <t>&lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; &lt;a href="/WioBank" title="Wio Bank"&gt;@WioBank&lt;/a&gt; 
+5 hours wasted yesterday on the Wio issue and then 2 hours today on eNBD.
+This is amateur hour.
+The issues &amp;amp; work arounds  should have been immediately pushed to customers.
+It shows an utter lack of respect for your CUSTOMERS.</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -2145,28 +2220,32 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>['MotiwalaAkhtar', 'EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 12:30 PM UTC</t>
+          <t>May 9, 2026 · 9:26 AM UTC</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-05-08T12:30:00Z</t>
+          <t>2026-05-09T09:26:00Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['https://x.com/centralbankuae', 'https://x.com/WioBank']</t>
+        </is>
+      </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2175,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2184,24 +2263,34 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
+          <t>@centralbankuae @WioBank 
+5 hours wasted yesterday on the Wio issue and then 2 hours today on eNBD.
+This is amateur hour.
+The issues &amp; work arounds  should have been immediately pushed to customers.
+It shows an utter lack of respect for your CUSTOMERS.</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
+          <t>https://x.com/HussainAzh82168/status/2053043908301783179</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
+          <t>@EmiratesNBD_AE what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn't working for touchID.
+Has the banking sector moved app testing to AI?
+I've seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
+          <t>@EmiratesNBD_AE what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn't working for touchID.
+Has the banking sector moved app testing to AI?
+I've seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
     </row>
@@ -2211,47 +2300,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2052726323349533050</t>
+          <t>2053034278775353687</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/Moh_Dul95/status/2052726323349533050</t>
+          <t>https://x.com/jurian777/status/2053034278775353687</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Moh_Dul95</t>
+          <t>https://x.com/jurian777</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Moh_Dul95</t>
+          <t>jurian777</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>齋藤純 Jun Saito</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1080059021028192256/Cjkq5nkZ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2052150684968218625/9AJu83Hb_bigger.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
+          <t>【企業統治】ENBDやFABが「王族・国家エリート型」、Mashreqbankが「財閥型」とすると、CBDはその中間で、Family型からState-Elite型へ移る銀行として位置づけ。</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="Emirates NBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
+          <t>【企業統治】ENBDやFABが「王族・国家エリート型」、Mashreqbankが「財閥型」とすると、CBDはその中間で、Family型からState-Elite型へ移る銀行として位置づけ。</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -2261,27 +2346,23 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 12:24 PM UTC</t>
+          <t>May 9, 2026 · 8:48 AM UTC</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-08T12:24:00Z</t>
+          <t>2026-05-09T08:48:00Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -2290,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2299,18 +2380,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>【企業統治】ENBDやFABが「王族・国家エリート型」、Mashreqbankが「財閥型」とすると、CBDはその中間で、Family型からState-Elite型へ移る銀行として位置づけ。</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://x.com/jurian777/status/2053034278775353687</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA السلام عليكم. 
-لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
-ارجوا الدعم….</t>
+          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
         </is>
       </c>
     </row>
@@ -2320,82 +2405,90 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2053020473697673405</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2053020473697673405</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ChoteyMamu</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SHA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1702021256537571328/jh5zD-f-_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2042294543308242946/ScvMjarh_bigger.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Still no update...</t>
+          <t>At Make it in the Emirates 2026, we were inspired by the ambition, innovation and entrepreneurial spirit shaping the UAE's future.
+Emirates NBD was proud to engage with the businesses and visionaries driving the nation forward, reaffirming our commitment to empowering growth, enabling progress and supporting those building a formidable future for this great nation.
+#MIITE2026 #MakeltInTheEmirates
+#EmiratesNBD #StrategicPartnership
+#EmpoweringIndustryGrowth #DrivingEconomicimpact</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Still no update...</t>
+          <t>At Make it in the Emirates 2026, we were inspired by the ambition, innovation and entrepreneurial spirit shaping the UAE&amp;#39;s future.
+Emirates NBD was proud to engage with the businesses and visionaries driving the nation forward, reaffirming our commitment to empowering growth, enabling progress and supporting those building a formidable future for this great nation.
+&lt;a href="/search?f=tweets&amp;amp;q=%23MIITE2026"&gt;#MIITE2026&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23MakeltInTheEmirates"&gt;#MakeltInTheEmirates&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StrategicPartnership"&gt;#StrategicPartnership&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmpoweringIndustryGrowth"&gt;#EmpoweringIndustryGrowth&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DrivingEconomicimpact"&gt;#DrivingEconomicimpact&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K18" t="b">
         <v>0</v>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 10:51 AM UTC</t>
+          <t>May 9, 2026 · 7:53 AM UTC</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-08T10:51:00Z</t>
+          <t>2026-05-09T07:53:00Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23MIITE2026', 'https://x.com/search?f=tweets&amp;q=%23MakeltInTheEmirates', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23StrategicPartnership', 'https://x.com/search?f=tweets&amp;q=%23EmpoweringIndustryGrowth', 'https://x.com/search?f=tweets&amp;q=%23DrivingEconomicimpact']</t>
+        </is>
+      </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2404,14 +2497,34 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Still no update...</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
+          <t>At Make it in the Emirates 2026, we were inspired by the ambition, innovation and entrepreneurial spirit shaping the UAE's future.
+Emirates NBD was proud to engage with the businesses and visionaries driving the nation forward, reaffirming our commitment to empowering growth, enabling progress and supporting those building a formidable future for this great nation.
+#MIITE2026 #MakeltInTheEmirates
+#EmiratesNBD #StrategicPartnership
+#EmpoweringIndustryGrowth #DrivingEconomicimpact</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2053020473697673405</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>At Make it in the Emirates 2026, we were inspired by the ambition, innovation and entrepreneurial spirit shaping the UAE's future.
+Emirates NBD was proud to engage with the businesses and visionaries driving the nation forward, reaffirming our commitment to empowering growth, enabling progress and supporting those building a formidable future for this great nation.
+#MIITE2026 #MakeltInTheEmirates
+#EmiratesNBD #StrategicPartnership
+#EmpoweringIndustryGrowth #DrivingEconomicimpact</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Still no update...</t>
+          <t>At Make it in the Emirates 2026, we were inspired by the ambition, innovation and entrepreneurial spirit shaping the UAE's future.
+Emirates NBD was proud to engage with the businesses and visionaries driving the nation forward, reaffirming our commitment to empowering growth, enabling progress and supporting those building a formidable future for this great nation.
+#MIITE2026 #MakeltInTheEmirates
+#EmiratesNBD #StrategicPartnership
+#EmpoweringIndustryGrowth #DrivingEconomicimpact</t>
         </is>
       </c>
     </row>
@@ -2421,73 +2534,75 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2052701014034108672</t>
+          <t>2053012069453267277</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
+          <t>https://x.com/PBNBHARAT/status/2053012069453267277</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/foode212</t>
+          <t>https://x.com/PBNBHARAT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>foode212</t>
+          <t>PBNBHARAT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fahad 212</t>
+          <t>PBN BHARAT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2027889531282751488/XVlkeZ8o_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1649703414899568640/0TUDRP8k_bigger.jpg</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
+          <t>CM Dr. Pramod Sawant Meets R. Subramaniakumar, Discusses Banking Growth &amp; Investment
+@DrPramodPSawant @rblbank #EmiratesNBD #FDI #BankingSector #EconomicGrowth #CSR #UMEED #EducationSupport #ViksitBharat #GoaNews #IndiaGrowth</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
+          <t>CM Dr. Pramod Sawant Meets R. Subramaniakumar, Discusses Banking Growth &amp;amp; Investment
+&lt;a href="/DrPramodPSawant" title="Dr. Pramod Sawant"&gt;@DrPramodPSawant&lt;/a&gt; &lt;a href="/rblbank" title="RBL Bank"&gt;@rblbank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FDI"&gt;#FDI&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BankingSector"&gt;#BankingSector&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EconomicGrowth"&gt;#EconomicGrowth&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CSR"&gt;#CSR&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UMEED"&gt;#UMEED&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EducationSupport"&gt;#EducationSupport&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ViksitBharat"&gt;#ViksitBharat&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23GoaNews"&gt;#GoaNews&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23IndiaGrowth"&gt;#IndiaGrowth&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 10:43 AM UTC</t>
+          <t>May 9, 2026 · 7:19 AM UTC</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-08T10:43:00Z</t>
+          <t>2026-05-09T07:19:00Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['https://x.com/DrPramodPSawant', 'https://x.com/rblbank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23FDI', 'https://x.com/search?f=tweets&amp;q=%23BankingSector', 'https://x.com/search?f=tweets&amp;q=%23EconomicGrowth', 'https://x.com/search?f=tweets&amp;q=%23CSR', 'https://x.com/search?f=tweets&amp;q=%23UMEED', 'https://x.com/search?f=tweets&amp;q=%23EducationSupport', 'https://x.com/search?f=tweets&amp;q=%23ViksitBharat', 'https://x.com/search?f=tweets&amp;q=%23GoaNews', 'https://x.com/search?f=tweets&amp;q=%23IndiaGrowth']</t>
+        </is>
+      </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2496,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2505,14 +2620,25 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
+          <t>CM Dr. Pramod Sawant Meets R. Subramaniakumar, Discusses Banking Growth &amp; Investment
+@DrPramodPSawant @rblbank #EmiratesNBD #FDI #BankingSector #EconomicGrowth #CSR #UMEED #EducationSupport #ViksitBharat #GoaNews #IndiaGrowth</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://x.com/PBNBHARAT/status/2053012069453267277</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>The price of GOLD in Goa today
+#GoldPrice #GoldPriceGoa #GoldRates #GoldUpdate #TodayGoldPrice #GoldMarket #GoldRatesGoa #PreciousMetals #JewelleryMarket #goldnews https://t.co/HGzdfjtN51</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي</t>
+          <t>The price of GOLD in Goa today
+#GoldPrice #GoldPriceGoa #GoldRates #GoldUpdate #TodayGoldPrice #GoldMarket #GoldRatesGoa #PreciousMetals #JewelleryMarket #goldnews https://t.co/HGzdfjtN51</t>
         </is>
       </c>
     </row>
@@ -2522,83 +2648,79 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2053010609298665966</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
+          <t>https://x.com/HussainAzh82168/status/2053010609298665966</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar</t>
+          <t>https://x.com/HussainAzh82168</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MotiwalaAkhtar</t>
+          <t>HussainAzh82168</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Akhtar Motiwala</t>
+          <t>Azher Hussain</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1771472983200034816/FZyCNOjV_bigger.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>+971 555 906879 
-BENEFICIARY: 
-AKHTAR NAZIR MOTIWALA
-AC NO: 1014895574401
-IBAN: AE37 0260 0010 1489 5574 401
-Swift: EBILAEADXXX
-BANK: EMIRATES NBD</t>
+          <t>@EmiratesNBD_AE what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn't working for touchID.
+Has the banking sector moved app testing to AI?
+I've seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+971 555 906879 
-BENEFICIARY: 
-AKHTAR NAZIR MOTIWALA
-AC NO: 1014895574401
-IBAN: AE37 0260 0010 1489 5574 401
-Swift: EBILAEADXXX
-BANK: EMIRATES NBD</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn&amp;#39;t working for touchID.
+Has the banking sector moved app testing to AI?
+I&amp;#39;ve seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 10:19 AM UTC</t>
+          <t>May 9, 2026 · 7:14 AM UTC</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-08T10:19:00Z</t>
+          <t>2026-05-09T07:14:00Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
@@ -2609,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2618,26 +2740,22 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>+971 555 906879 
-BENEFICIARY: 
-AKHTAR NAZIR MOTIWALA
-AC NO: 1014895574401
-IBAN: AE37 0260 0010 1489 5574 401
-Swift: EBILAEADXXX
-BANK: EMIRATES NBD</t>
+          <t>@EmiratesNBD_AE what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn't working for touchID.
+Has the banking sector moved app testing to AI?
+I've seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>+971 555 906879 
-BENEFICIARY: 
-AKHTAR NAZIR MOTIWALA
-AC NO: 1014895574401
-IBAN: AE37 0260 0010 1489 5574 401
-Swift: EBILAEADXXX
-BANK: EMIRATES NBD</t>
+          <t>@EmiratesNBD_AE what on earth is going on with UAE Banking?
+Yesterday Wio was not working for video verification.
+Today eNBD isn't working for touchID.
+Has the banking sector moved app testing to AI?
+I've seen a lot of incompetence especially at eNBD but not sector wide like this</t>
         </is>
       </c>
     </row>
@@ -2647,45 +2765,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2052691349342941582</t>
+          <t>2052995547032859114</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052691349342941582</t>
+          <t>https://x.com/AsliAfnas/status/2052995547032859114</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar</t>
+          <t>https://x.com/AsliAfnas</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MotiwalaAkhtar</t>
+          <t>AsliAfnas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Akhtar Motiwala</t>
+          <t>Afnas Mohammed</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/579769261016551424/YlkMvNjO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/798233988024274944/Cwty_Xp__bigger.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
+          <t>I request @centralbankuae and @sanadakuae to investigate, without my consent limit of my tabby card was raised and tabby card cancellation request is still pending after 12 days. @paywithtabby @asktabby @ENBDdeals @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I am trying to login my enbd online banking but it&amp;#39;s taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
+          <t>I request &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; and &lt;a href="/SanadakUAE" title="Sanadak"&gt;@sanadakuae&lt;/a&gt; to investigate, without my consent limit of my tabby card was raised and tabby card cancellation request is still pending after 12 days. &lt;a href="/paywithtabby" title="Tabby | تابي"&gt;@paywithtabby&lt;/a&gt; &lt;a href="/asktabby" title="asktabby"&gt;@asktabby&lt;/a&gt; &lt;a href="/ENBDdeals" title="Emirates NBD Deals"&gt;@ENBDdeals&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2695,27 +2811,27 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 10:05 AM UTC</t>
+          <t>May 9, 2026 · 6:14 AM UTC</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-05-08T10:05:00Z</t>
+          <t>2026-05-09T06:14:00Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/centralbankuae', 'https://x.com/SanadakUAE', 'https://x.com/paywithtabby', 'https://x.com/asktabby', 'https://x.com/ENBDdeals', 'https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -2724,7 +2840,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2733,16 +2849,22 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr"/>
+          <t>I request @centralbankuae and @sanadakuae to investigate, without my consent limit of my tabby card was raised and tabby card cancellation request is still pending after 12 days. @paywithtabby @asktabby @ENBDdeals @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://x.com/AsliAfnas/status/2052995547032859114</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>I did a biggest mistake of my life applying a card through @paywithtabby , which was issued within minutes, now when i asked for cancellation it has been 11 days and they are still waiting to cancel, with just a generic update “We are working on it” for 11 days!</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
+          <t>I did a biggest mistake of my life applying a card through @paywithtabby , which was issued within minutes, now when i asked for cancellation it has been 11 days and they are still waiting to cancel, with just a generic update “We are working on it” for 11 days!</t>
         </is>
       </c>
     </row>
@@ -2752,43 +2874,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2052687458446578021</t>
+          <t>2052995160561144095</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
+          <t>https://x.com/financebufffh/status/2052995160561144095</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/IrfanAmeable</t>
+          <t>https://x.com/financebufffh</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IrfanAmeable</t>
+          <t>financebufffh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>mohammed irfan</t>
+          <t>Sal Faisal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1865036200186171392/c0999EJk_bigger.jpg</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
+          <t>Emirates NBD remains at the forefront of digital banking innovation in MENA. This Eid teaser suggests another sophisticated blend of cultural tradition and financial technology advancement.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
+          <t>Emirates NBD remains at the forefront of digital banking innovation in MENA. This Eid teaser suggests another sophisticated blend of cultural tradition and financial technology advancement.</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2798,27 +2920,23 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:50 AM UTC</t>
+          <t>May 9, 2026 · 6:12 AM UTC</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-05-08T09:50:00Z</t>
+          <t>2026-05-09T06:12:00Z</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2827,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2836,22 +2954,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
-        </is>
-      </c>
+          <t>Emirates NBD remains at the forefront of digital banking innovation in MENA. This Eid teaser suggests another sophisticated blend of cultural tradition and financial technology advancement.</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
+          <t>Emirates NBD remains at the forefront of digital banking innovation in MENA. This Eid teaser suggests another sophisticated blend of cultural tradition and financial technology advancement.</t>
         </is>
       </c>
     </row>
@@ -2861,43 +2971,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2052683161734148463</t>
+          <t>2052992363598164059</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
+          <t>https://x.com/AsliAfnas/status/2052992363598164059</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/RohitSa70875783</t>
+          <t>https://x.com/AsliAfnas</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RohitSa70875783</t>
+          <t>AsliAfnas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luna Web3</t>
+          <t>Afnas Mohammed</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2048077886406656000/YiwGVivE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/798233988024274944/Cwty_Xp__bigger.jpg</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
+          <t>@paywithtabby @EmiratesNBD_AE - i don’t want to freeze my tabby card, i want to cancel my card, it’s been 12 days since my request.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
+          <t>&lt;a href="/paywithtabby" title="Tabby | تابي"&gt;@paywithtabby&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; - i don’t want to freeze my tabby card, i want to cancel my card, it’s been 12 days since my request.</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2906,26 +3016,30 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>['multibank_io', 'AECoin_UAE']</t>
+          <t>['asktabby']</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:32 AM UTC</t>
+          <t>May 9, 2026 · 6:01 AM UTC</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-05-08T09:32:00Z</t>
+          <t>2026-05-09T06:01:00Z</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['https://x.com/paywithtabby', 'https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
@@ -2936,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -2945,22 +3059,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>@multibank_io @AECoin_UAE Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
-        </is>
-      </c>
+          <t>@paywithtabby @EmiratesNBD_AE - i don’t want to freeze my tabby card, i want to cancel my card, it’s been 12 days since my request.</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>@multibank_io @AECoin_UAE Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
+          <t>@paywithtabby @EmiratesNBD_AE - i don’t want to freeze my tabby card, i want to cancel my card, it’s been 12 days since my request.</t>
         </is>
       </c>
     </row>
@@ -2970,71 +3076,75 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2052681405897880031</t>
+          <t>2052965788030779743</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
+          <t>https://x.com/Rashtra_TV/status/2052965788030779743</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/Suhrob64184475</t>
+          <t>https://x.com/Rashtra_TV</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Suhrob64184475</t>
+          <t>Rashtra_TV</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Rashtra TV</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2048359076401463296/zyTuEjur_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1933842156307042307/j8vlsSSv_bigger.png</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
+          <t>Goa : CM Dr. Pramod Sawant met R. Subramaniakumar, MD &amp; CEO of RBL Bank, and discussed banking, economic growth, and the Bank’s role in strengthening India’s financial ecosystem.
+The meeting also highlighted the landmark ₹26,850 crore FDI investment from Emirates NBD into RBL Bank, along with CSR initiatives like the ‘UMEED’ cycle distribution programme supporting students across states. Best wishes conveyed for their continued contribution towards a #ViksitBharat.
+#Goa #RBLBank #ViksitBharat #EconomicGrowth #CSR</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Emirates NBD and Mashreq both holding reserves that&amp;#39;s actually solid backing ngl</t>
+          <t>Goa : CM Dr. Pramod Sawant met R. Subramaniakumar, MD &amp;amp; CEO of RBL Bank, and discussed banking, economic growth, and the Bank’s role in strengthening India’s financial ecosystem.
+The meeting also highlighted the landmark ₹26,850 crore FDI investment from Emirates NBD into RBL Bank, along with CSR initiatives like the ‘UMEED’ cycle distribution programme supporting students across states. Best wishes conveyed for their continued contribution towards a &lt;a href="/search?f=tweets&amp;amp;q=%23ViksitBharat"&gt;#ViksitBharat&lt;/a&gt;.
+&lt;a href="/search?f=tweets&amp;amp;q=%23Goa"&gt;#Goa&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23ViksitBharat"&gt;#ViksitBharat&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EconomicGrowth"&gt;#EconomicGrowth&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CSR"&gt;#CSR&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>['multibank_io', 'AECoin_UAE']</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:25 AM UTC</t>
+          <t>May 9, 2026 · 4:16 AM UTC</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-05-08T09:25:00Z</t>
+          <t>2026-05-09T04:16:00Z</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ViksitBharat', 'https://x.com/search?f=tweets&amp;q=%23Goa', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23ViksitBharat', 'https://x.com/search?f=tweets&amp;q=%23EconomicGrowth', 'https://x.com/search?f=tweets&amp;q=%23CSR']</t>
+        </is>
+      </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
@@ -3045,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -3054,30 +3164,18 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want $AEC and $USDU on ⬡ mb io? 
-Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
-        </is>
-      </c>
+          <t>Goa : CM Dr. Pramod Sawant met R. Subramaniakumar, MD &amp; CEO of RBL Bank, and discussed banking, economic growth, and the Bank’s role in strengthening India’s financial ecosystem.
+The meeting also highlighted the landmark ₹26,850 crore FDI investment from Emirates NBD into RBL Bank, along with CSR initiatives like the ‘UMEED’ cycle distribution programme supporting students across states. Best wishes conveyed for their continued contribution towards a #ViksitBharat.
+#Goa #RBLBank #ViksitBharat #EconomicGrowth #CSR</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want $AEC and $USDU on ⬡ mb io? 
-Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
+          <t>Goa : CM Dr. Pramod Sawant met R. Subramaniakumar, MD &amp; CEO of RBL Bank, and discussed banking, economic growth, and the Bank’s role in strengthening India’s financial ecosystem.
+The meeting also highlighted the landmark ₹26,850 crore FDI investment from Emirates NBD into RBL Bank, along with CSR initiatives like the ‘UMEED’ cycle distribution programme supporting students across states. Best wishes conveyed for their continued contribution towards a #ViksitBharat.
+#Goa #RBLBank #ViksitBharat #EconomicGrowth #CSR</t>
         </is>
       </c>
     </row>
@@ -3087,73 +3185,69 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2052680648222032220</t>
+          <t>2052925380936491470</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157</t>
+          <t>https://x.com/jurian777</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HadiAlduba89157</t>
+          <t>jurian777</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hadi Aldubaisi</t>
+          <t>齋藤純 Jun Saito</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1754901286586138625/EFX2BexR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2052150684968218625/9AJu83Hb_bigger.jpg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
         </is>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>May 9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:22 AM UTC</t>
+          <t>May 9, 2026 · 1:35 AM UTC</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-05-08T09:22:00Z</t>
+          <t>2026-05-09T01:35:00Z</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -3162,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -3171,26 +3265,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>لا تشيل هم الفاتورة 🤩
-مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
-للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
-        </is>
-      </c>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>لا تشيل هم الفاتورة 🤩
-مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
-للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
         </is>
       </c>
     </row>
@@ -3200,51 +3282,45 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2052680277336703430</t>
+          <t>2053262874999415084</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/multibank_io/status/2052680277336703430</t>
+          <t>https://x.com/W42RW/status/2053262874999415084</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/multibank_io</t>
+          <t>https://x.com/W42RW</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>multibank_io</t>
+          <t>W42RW</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>mb.io</t>
+          <t>Saud Alanazi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2015689534328250368/-RLE2RH__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899657357107326976/82dbkH1B_bigger.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want $AEC and $USDU on ⬡ mb io? 
-Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
+          <t>@emiratesislamic 
+السلام عليكم ممكن تردون خاص</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want &lt;a href="/search?f=tweets&amp;amp;q=%23AEC"&gt;$AEC&lt;/a&gt; and &lt;a href="/search?f=tweets&amp;amp;q=%23USDU"&gt;$USDU&lt;/a&gt; on ⬡ mb io? 
-Let us know! cc &lt;a href="/AECoin_UAE" title="AE Coin"&gt;@AECoin_UAE&lt;/a&gt;  and &lt;a href="/Universal_USDU" title="USDU / Universal"&gt;@Universal_USDU&lt;/a&gt;</t>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; 
+السلام عليكم ممكن تردون خاص</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -3254,64 +3330,54 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:21 AM UTC</t>
+          <t>May 9, 2026 · 11:56 PM UTC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-05-08T09:21:00Z</t>
+          <t>2026-05-09T23:56:00Z</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23AEC', 'https://x.com/search?f=tweets&amp;q=%23USDU', 'https://x.com/AECoin_UAE', 'https://x.com/Universal_USDU']</t>
+          <t>['https://x.com/emiratesislamic']</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>14051</v>
+        <v>1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
-Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
-The region is building the future! 🔑  
-Would you want $AEC and $USDU on ⬡ mb io? 
-Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://x.com/multibank_io/status/2052680277336703430</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>@multibank_io @AECoin_UAE Yes obviously bring it to mb io this is exactly what the region needs right now</t>
-        </is>
-      </c>
+          <t>@emiratesislamic 
+السلام عليكم ممكن تردون خاص</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>@multibank_io @AECoin_UAE Yes obviously bring it to mb io this is exactly what the region needs right now</t>
+          <t>@emiratesislamic 
+السلام عليكم ممكن تردون خاص</t>
         </is>
       </c>
     </row>
@@ -3321,65 +3387,67 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2052674872631763288</t>
+          <t>2053194406094946347</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2052674872631763288</t>
+          <t>https://x.com/aashiash/status/2053194406094946347</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/aashiash</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>aashiash</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Aashi Ash</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1653174950793035777/wO4_OnRb_bigger.jpg</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
-Tax registration number: 204-897-319</t>
+          <t>I am unable to login into my EI app. The app demands biometric signin when its not been setup.. and I cant set it up because i CANT login!!!</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
-Tax registration number: 204-897-319</t>
+          <t>I am unable to login into my EI app. The app demands biometric signin when its not been setup.. and I cant set it up because i CANT login!!!</t>
         </is>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 9:00 AM UTC</t>
+          <t>May 9, 2026 · 7:24 PM UTC</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-05-08T09:00:00Z</t>
+          <t>2026-05-09T19:24:00Z</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -3394,25 +3462,23 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
-Tax registration number: 204-897-319</t>
+          <t>I am unable to login into my EI app. The app demands biometric signin when its not been setup.. and I cant set it up because i CANT login!!!</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt has signed a strategic partnership with “Sehetna Foundation” to equip a fully integrated ICU at Assiut University Hospital, a key medical hub serving more than seven governorates in Upper Egypt. The initiative aims to support critical cases and enhance the quality of healthcare services through upgraded medical infrastructure.
-Tax registration number: 204-897-319</t>
+          <t>I am unable to login into my EI app. The app demands biometric signin when its not been setup.. and I cant set it up because i CANT login!!!</t>
         </is>
       </c>
     </row>
@@ -3422,51 +3488,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2052663047903473895</t>
+          <t>2053052362344808541</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/Imamx20/status/2052663047903473895</t>
+          <t>https://x.com/emiratesislamic/status/2053052362344808541</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/Imamx20</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Imamx20</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Imam</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2040371356467159040/UjJi1ZiW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.
-#EmiratesNBD</t>
+          <t>Take your business further with tailored banking. Emirates Islamic Business Premium package offers bundled transactional benefits, competitive profit rates on financing, and convenient digital channels.
+emiratesislamic.ae/en/busine…</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp;amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;</t>
+          <t>Take your business further with tailored banking. Emirates Islamic Business Premium package offers bundled transactional benefits, competitive profit rates on financing, and convenient digital channels.
+&lt;a href="https://www.emiratesislamic.ae/en/business-banking/banking-packages/business-premium"&gt;emiratesislamic.ae/en/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -3481,18 +3541,18 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 8:13 AM UTC</t>
+          <t>May 9, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-05-08T08:13:00Z</t>
+          <t>2026-05-09T10:00:00Z</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD']</t>
+          <t>['https://www.emiratesislamic.ae/en/business-banking/banking-packages/business-premium']</t>
         </is>
       </c>
       <c r="S28" t="n">
@@ -3502,34 +3562,28 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.
-#EmiratesNBD</t>
+          <t>Take your business further with tailored banking. Emirates Islamic Business Premium package offers bundled transactional benefits, competitive profit rates on financing, and convenient digital channels.
+emiratesislamic.ae/en/busine…</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.
-#EmiratesNBD</t>
+          <t>Take your business further with tailored banking. Emirates Islamic Business Premium package offers bundled transactional benefits, competitive profit rates on financing, and convenient digital channels.
+emiratesislamic.ae/en/busine…</t>
         </is>
       </c>
     </row>
@@ -3539,77 +3593,71 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2052662496658673916</t>
+          <t>2053029141390258649</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/Imamx20/status/2052662496658673916</t>
+          <t>https://x.com/abbarsy/status/2053029141390258649</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/Imamx20</t>
+          <t>https://x.com/abbarsy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Imamx20</t>
+          <t>abbarsy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Imam</t>
+          <t>Ɓingel 🇳🇬 𞤀𞤦𞥆𞤢𞥄𞤧</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2040371356467159040/UjJi1ZiW_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1482834059621552136/QBo9aH1G_bigger.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.</t>
+          <t>But dat analogy doesnt really fit wat happened in hausaland. d Sokkoto Caliphate dint simply ‘replace the manager’ while leaving everything untouched. d ruling structure changed from largely independent hausa kingdoms in2 a caliphal system tied 2gada through emirates, Islamic</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp;amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.</t>
+          <t>But dat analogy doesnt really fit wat happened in hausaland. d Sokkoto Caliphate dint simply ‘replace the manager’ while leaving everything untouched. d ruling structure changed from largely independent hausa kingdoms in2 a caliphal system tied 2gada through emirates, Islamic</t>
         </is>
       </c>
       <c r="K29" t="b">
         <v>0</v>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>['Jajjage', 'abbarsy']</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>May 8, 2026 · 8:10 AM UTC</t>
+          <t>May 9, 2026 · 8:27 AM UTC</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-05-08T08:10:00Z</t>
+          <t>2026-05-09T08:27:00Z</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="n">
         <v>1</v>
       </c>
@@ -3620,29 +3668,23 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.</t>
+          <t>But dat analogy doesnt really fit wat happened in hausaland. d Sokkoto Caliphate dint simply ‘replace the manager’ while leaving everything untouched. d ruling structure changed from largely independent hausa kingdoms in2 a caliphal system tied 2gada through emirates, Islamic</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Unauthorized transaction from my Emirates NBD account on 4th May at 4:22 AM. Money was transferred to an e&amp; money wallet without my permission.
-Dispute raised: SR No. 235754008145
-Police case also filed.
-Still waiting for action and refund from Emirates NBD.</t>
+          <t>But dat analogy doesnt really fit wat happened in hausaland. d Sokkoto Caliphate dint simply ‘replace the manager’ while leaving everything untouched. d ruling structure changed from largely independent hausa kingdoms in2 a caliphal system tied 2gada through emirates, Islamic</t>
         </is>
       </c>
     </row>
@@ -3652,106 +3694,102 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2052661557209768191</t>
+          <t>2053022168665993266</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008/status/2052661557209768191</t>
+          <t>https://x.com/emiratesislamic/status/2053022168665993266</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/alamair2008</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>alamair2008</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZIZ ALGHAMDI</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1533332501040664576/qTQ5EoD5_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
-أنا المتضرر</t>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
+💳 0% Easy P